--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -264,7 +264,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -353,12 +353,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1710,7 +1704,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="365">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2935,9 +2929,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -2959,14 +2950,6 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
@@ -5381,26 +5364,21 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
+      <c r="E9" s="183" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I9" s="183" t="inlineStr">
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="inlineStr">
         <is>
           <t>Hist - Wag
-1º e 2º tempos</t>
-        </is>
-      </c>
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="H9" s="183" t="n"/>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -5478,13 +5456,13 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+10º ao 12º tempos</t>
+        </is>
+      </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="inlineStr">
         <is>
@@ -5492,12 +5470,7 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -5556,17 +5529,22 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
+          <t>Ing - Isb
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -5628,18 +5606,23 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Geo - Mar
 2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -5707,12 +5690,7 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="inlineStr">
         <is>
@@ -5792,8 +5770,8 @@
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="inlineStr">
         <is>
-          <t>Hist - Wag
-11º e 12º tempos</t>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G24" s="79" t="n"/>
@@ -5817,13 +5795,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -5836,13 +5814,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -5869,17 +5847,22 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
+      <c r="E27" s="78" t="inlineStr">
+        <is>
+          <t>Ing - Isb
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F27" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-10º ao 12º tempos</t>
+          <t>Hist - Wag
+11º e 12º tempos</t>
         </is>
       </c>
       <c r="G27" s="283" t="inlineStr">
         <is>
           <t>Fil - LAn
-4º tempo</t>
+10º tempo</t>
         </is>
       </c>
       <c r="H27" s="283" t="n"/>
@@ -5897,13 +5880,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -5916,13 +5899,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -5950,17 +5933,17 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G30" s="283" t="n"/>
+      <c r="F30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+11º e 12º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="283" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
-6º e 7º tempos</t>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
         </is>
       </c>
       <c r="I30" s="283" t="n"/>
@@ -5981,7 +5964,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -6000,7 +5983,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -6070,7 +6053,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -6092,7 +6075,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -6132,11 +6115,16 @@
       <c r="E36" s="283" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
-2º e 3º tempos</t>
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -6155,13 +6143,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -6177,13 +6165,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -6205,39 +6193,39 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -6260,7 +6248,7 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Fis - Cadu
+          <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
@@ -6279,26 +6267,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6319,21 +6307,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F45" s="283" t="n"/>
+      <c r="E45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="358" t="inlineStr">
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="357" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -6346,26 +6329,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -6387,7 +6370,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="inlineStr">
+      <c r="F48" s="360" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -6406,25 +6389,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -6448,32 +6431,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="n"/>
+      <c r="I51" s="357" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -6504,25 +6487,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -6543,7 +6526,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="n"/>
+      <c r="F57" s="360" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -6553,25 +6536,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -6603,24 +6586,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -8603,12 +8586,7 @@
       </c>
       <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="inlineStr">
         <is>
@@ -8695,19 +8673,19 @@
       </c>
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -8768,17 +8746,17 @@
       <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Hist - JuLa
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -8838,7 +8816,12 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Geo - Mar
@@ -8847,8 +8830,8 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
+          <t>Redação - Raf
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="n"/>
@@ -8919,13 +8902,13 @@
       </c>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -8989,14 +8972,19 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="n"/>
-      <c r="G24" s="353" t="inlineStr">
-        <is>
-          <t>Port - Jana
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -9012,13 +9000,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -9031,13 +9019,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -9065,12 +9053,7 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="inlineStr">
@@ -9092,13 +9075,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -9111,13 +9094,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -9144,16 +9127,16 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -9171,7 +9154,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -9190,7 +9173,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -9260,7 +9243,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -9282,7 +9265,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -9321,13 +9304,13 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+2º tempo</t>
+        </is>
+      </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
@@ -9350,13 +9333,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -9372,13 +9355,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -9402,8 +9385,8 @@
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
-          <t>Qui - Fab
-2º tempo</t>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
@@ -9414,25 +9397,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -9453,14 +9436,14 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="n"/>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -9474,26 +9457,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9521,14 +9504,14 @@
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="358" t="n"/>
+      <c r="I45" s="357" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -9536,26 +9519,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -9577,11 +9560,11 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="n"/>
+      <c r="F48" s="360" t="n"/>
       <c r="G48" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-3º tempo</t>
+          <t>Port - Jana
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H48" s="283" t="n"/>
@@ -9596,25 +9579,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -9638,7 +9621,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="inlineStr">
+      <c r="I51" s="357" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -9650,25 +9633,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -9699,25 +9682,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -9738,7 +9721,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="inlineStr">
+      <c r="F57" s="360" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -9753,25 +9736,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -9803,24 +9786,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -10269,12 +10252,7 @@
       </c>
       <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="inlineStr">
         <is>
@@ -10361,19 +10339,19 @@
       </c>
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -10434,17 +10412,17 @@
       <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Hist - JuLa
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -10504,7 +10482,12 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Geo - Mar
@@ -10513,8 +10496,8 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
+          <t>Redação - Raf
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="n"/>
@@ -10585,13 +10568,13 @@
       </c>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -10655,14 +10638,19 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="n"/>
-      <c r="G24" s="353" t="inlineStr">
-        <is>
-          <t>Port - Jana
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -10678,13 +10666,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -10697,13 +10685,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -10731,12 +10719,7 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="inlineStr">
@@ -10758,13 +10741,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -10777,13 +10760,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -10810,16 +10793,16 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -10837,7 +10820,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -10856,7 +10839,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -10926,7 +10909,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -10948,7 +10931,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -10987,13 +10970,13 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+2º tempo</t>
+        </is>
+      </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
@@ -11016,13 +10999,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -11038,13 +11021,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -11068,8 +11051,8 @@
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
-          <t>Qui - Fab
-2º tempo</t>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
@@ -11080,25 +11063,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -11119,14 +11102,14 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="n"/>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -11140,26 +11123,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11187,14 +11170,14 @@
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="358" t="n"/>
+      <c r="I45" s="357" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -11202,26 +11185,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -11243,11 +11226,11 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="n"/>
+      <c r="F48" s="360" t="n"/>
       <c r="G48" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-3º tempo</t>
+          <t>Port - Jana
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H48" s="283" t="n"/>
@@ -11262,25 +11245,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -11304,7 +11287,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="inlineStr">
+      <c r="I51" s="357" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -11316,25 +11299,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -11365,25 +11348,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -11404,7 +11387,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="inlineStr">
+      <c r="F57" s="360" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -11419,25 +11402,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -11469,24 +11452,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -11933,24 +11916,24 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="inlineStr">
         <is>
           <t>Bio - Lza
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G9" s="183" t="n"/>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
+          <t>Geo - Mlo
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J9" s="183" t="n"/>
@@ -12032,21 +12015,21 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Fis - VSi
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Ing - APa
 2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -12106,23 +12089,18 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="363" t="inlineStr">
-        <is>
-          <t>Ing - APa
-3º e 4º tempos</t>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+          <t>Fis - VSi
+9º e 10º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -12185,12 +12163,17 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-1º e 2º tempos</t>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="inlineStr">
@@ -12264,21 +12247,16 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F21" s="62" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -12341,16 +12319,16 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -12364,13 +12342,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -12383,13 +12361,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -12417,20 +12395,15 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="n"/>
+      <c r="F27" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I27" s="364" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="H27" s="283" t="n"/>
+      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -12444,13 +12417,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -12463,13 +12436,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -12498,7 +12471,12 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="283" t="inlineStr">
         <is>
           <t>Fis - VSi
@@ -12523,7 +12501,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -12542,7 +12520,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -12612,7 +12590,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -12634,7 +12612,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -12675,12 +12653,17 @@
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
+          <t>Fil - LAn
+1º tempo</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -12697,13 +12680,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -12719,13 +12702,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -12746,14 +12729,19 @@
         <v/>
       </c>
       <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="n"/>
+      <c r="F39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -12761,25 +12749,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -12801,16 +12789,11 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="inlineStr">
         <is>
-          <t>Ing - APa
-2º e 3º tempos</t>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I42" s="283" t="n"/>
@@ -12826,26 +12809,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -12866,21 +12849,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-9º ao 11º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="358" t="inlineStr">
+          <t>Ing - APa
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I45" s="357" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -12893,26 +12876,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -12934,7 +12917,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="inlineStr">
+      <c r="F48" s="360" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -12953,25 +12936,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -12995,32 +12978,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="n"/>
+      <c r="I51" s="357" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -13051,25 +13034,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -13090,7 +13073,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="n"/>
+      <c r="F57" s="360" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -13100,25 +13083,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -13150,24 +13133,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -13614,24 +13597,24 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="inlineStr">
         <is>
           <t>Bio - Lza
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G9" s="183" t="n"/>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
+          <t>Geo - Mlo
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J9" s="183" t="n"/>
@@ -13713,23 +13696,18 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Fis - VSi
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -13787,23 +13765,23 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+          <t>Fis - VSi
+9º e 10º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -13866,12 +13844,17 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-1º e 2º tempos</t>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="inlineStr">
@@ -13945,21 +13928,16 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F21" s="62" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -14022,21 +14000,16 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="353" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -14050,13 +14023,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -14069,13 +14042,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -14103,20 +14076,15 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="n"/>
+      <c r="F27" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I27" s="364" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="H27" s="283" t="n"/>
+      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -14130,13 +14098,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -14149,13 +14117,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -14184,7 +14152,12 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="283" t="inlineStr">
         <is>
           <t>Fis - VSi
@@ -14209,7 +14182,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -14228,7 +14201,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -14298,7 +14271,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -14320,7 +14293,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -14361,12 +14334,17 @@
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
+          <t>Fil - LAn
+1º tempo</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -14383,13 +14361,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -14405,13 +14383,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -14432,14 +14410,19 @@
         <v/>
       </c>
       <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="n"/>
+      <c r="F39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -14447,25 +14430,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -14487,13 +14470,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
-      <c r="H42" s="283" t="n"/>
+      <c r="G42" s="283" t="n"/>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -14507,26 +14490,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -14547,21 +14530,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-9º ao 11º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="358" t="inlineStr">
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="357" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -14574,26 +14557,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -14615,7 +14598,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="inlineStr">
+      <c r="F48" s="360" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -14634,25 +14617,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -14676,7 +14659,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="inlineStr">
+      <c r="I51" s="357" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -14688,25 +14671,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -14737,25 +14720,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -14776,7 +14759,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="inlineStr">
+      <c r="F57" s="360" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -14791,25 +14774,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -14841,24 +14824,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -15315,21 +15298,21 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
           <t>Qui - CAl
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H9" s="183" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>Fis - Cadu
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I9" s="183" t="n"/>
@@ -15412,8 +15395,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-1º ao 3º tempos</t>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -15488,8 +15471,8 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
+          <t>Ing - Bea
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -15501,8 +15484,8 @@
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Ing - Bea
-6º e 7º tempos</t>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+9º ao 11º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -15573,14 +15556,14 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-4º e 5º tempos</t>
+          <t>Bio - Ale
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="n"/>
@@ -15650,15 +15633,20 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-9º tempo</t>
-        </is>
-      </c>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+8º ao 10º tempos</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -15744,13 +15732,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -15763,13 +15751,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -15796,14 +15784,14 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
+      <c r="E27" s="78" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="inlineStr">
         <is>
           <t>Fis - Cadu
@@ -15824,13 +15812,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -15843,13 +15831,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -15879,18 +15867,18 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
+          <t>Hist - Ver
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -15908,7 +15896,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -15927,7 +15915,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -15997,7 +15985,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -16019,7 +16007,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -16056,20 +16044,15 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -16087,13 +16070,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -16109,13 +16092,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -16156,25 +16139,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -16197,16 +16180,11 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Hist - Ver
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Qui - CAl
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
@@ -16221,26 +16199,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -16262,15 +16240,20 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-9º ao 11º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="358" t="n"/>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I45" s="357" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -16278,26 +16261,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -16319,13 +16302,13 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-8º e 9º tempos</t>
-        </is>
-      </c>
-      <c r="G48" s="283" t="n"/>
+      <c r="F48" s="360" t="n"/>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
@@ -16338,25 +16321,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -16380,7 +16363,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="inlineStr">
+      <c r="I51" s="357" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -16392,25 +16375,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -16441,25 +16424,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -16480,7 +16463,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="inlineStr">
+      <c r="F57" s="360" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -16495,25 +16478,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -16545,24 +16528,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -17011,21 +16994,21 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
           <t>Qui - CAl
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H9" s="183" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>Fis - Cadu
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I9" s="183" t="n"/>
@@ -17108,8 +17091,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-1º ao 3º tempos</t>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -17182,12 +17165,7 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Hist - Ver
@@ -17195,7 +17173,12 @@
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+9º ao 11º tempos</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
           <t>Ing - PaH
@@ -17269,14 +17252,14 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-4º e 5º tempos</t>
+          <t>Bio - Ale
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="n"/>
@@ -17346,15 +17329,20 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-9º tempo</t>
-        </is>
-      </c>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+8º ao 10º tempos</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -17440,13 +17428,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -17459,13 +17447,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -17494,12 +17482,7 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="inlineStr">
         <is>
           <t>Fis - Cadu
@@ -17520,13 +17503,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -17539,13 +17522,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -17575,18 +17558,18 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
+          <t>Hist - Ver
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -17604,7 +17587,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -17623,7 +17606,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -17693,7 +17676,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -17715,7 +17698,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -17759,13 +17742,13 @@
         </is>
       </c>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -17783,13 +17766,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -17805,13 +17788,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -17852,25 +17835,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -17893,16 +17876,11 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Hist - Ver
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Qui - CAl
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
@@ -17917,26 +17895,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -17958,15 +17936,20 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-9º ao 11º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="358" t="n"/>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I45" s="357" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -17974,26 +17957,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -18015,13 +17998,13 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-8º e 9º tempos</t>
-        </is>
-      </c>
-      <c r="G48" s="283" t="n"/>
+      <c r="F48" s="360" t="n"/>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
@@ -18034,25 +18017,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -18076,7 +18059,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="inlineStr">
+      <c r="I51" s="357" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -18088,25 +18071,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -18137,25 +18120,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -18176,7 +18159,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="inlineStr">
+      <c r="F57" s="360" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -18191,25 +18174,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -18241,24 +18224,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -18705,26 +18688,21 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
+      <c r="E9" s="183" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I9" s="183" t="inlineStr">
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="inlineStr">
         <is>
           <t>Hist - Wag
-1º e 2º tempos</t>
-        </is>
-      </c>
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="H9" s="183" t="n"/>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -18802,13 +18780,13 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+10º ao 12º tempos</t>
+        </is>
+      </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="inlineStr">
         <is>
@@ -18816,12 +18794,7 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -18880,17 +18853,22 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
-4º e 5º tempos</t>
+          <t>Ing - PaH
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -18952,18 +18930,23 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Geo - Mar
 2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -19111,8 +19094,8 @@
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="inlineStr">
         <is>
-          <t>Hist - Wag
-11º e 12º tempos</t>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G24" s="79" t="n"/>
@@ -19136,13 +19119,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -19155,13 +19138,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -19191,14 +19174,14 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-10º ao 12º tempos</t>
+          <t>Hist - Wag
+11º e 12º tempos</t>
         </is>
       </c>
       <c r="G27" s="283" t="inlineStr">
         <is>
           <t>Fil - LAn
-4º tempo</t>
+10º tempo</t>
         </is>
       </c>
       <c r="H27" s="283" t="n"/>
@@ -19216,13 +19199,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -19235,13 +19218,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -19269,17 +19252,17 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G30" s="283" t="n"/>
+      <c r="F30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+11º e 12º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="283" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
-6º e 7º tempos</t>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
         </is>
       </c>
       <c r="I30" s="283" t="n"/>
@@ -19300,7 +19283,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -19319,7 +19302,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -19389,7 +19372,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -19411,7 +19394,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -19451,11 +19434,16 @@
       <c r="E36" s="283" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
-2º e 3º tempos</t>
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -19474,13 +19462,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -19496,13 +19484,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -19522,46 +19510,41 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -19584,12 +19567,17 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Fis - Cadu
+          <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="n"/>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -19603,26 +19591,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -19643,21 +19631,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F45" s="283" t="n"/>
+      <c r="E45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="358" t="inlineStr">
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="357" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -19670,26 +19653,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -19711,7 +19694,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="inlineStr">
+      <c r="F48" s="360" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -19730,25 +19713,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -19772,32 +19755,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="n"/>
+      <c r="I51" s="357" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -19828,25 +19811,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -19867,7 +19850,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="n"/>
+      <c r="F57" s="360" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -19877,25 +19860,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -19927,24 +19910,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -264,7 +264,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -353,6 +353,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1704,7 +1710,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="362">
+  <cellXfs count="364">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2929,6 +2935,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -2950,6 +2959,10 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
@@ -5364,20 +5377,20 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="n"/>
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -5456,21 +5469,26 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Ing - Isb
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-10º ao 12º tempos</t>
+          <t>Hist - Wag
+10º e 11º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -5529,7 +5547,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Ing - Isb
+          <t>DaF - CBu-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
@@ -5541,12 +5559,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -5621,7 +5634,7 @@
       </c>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>Geo - Mar
+          <t>Qui - CAl/Fab
 2º e 3º tempos</t>
         </is>
       </c>
@@ -5768,18 +5781,18 @@
         <v/>
       </c>
       <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="inlineStr">
+      <c r="F24" s="283" t="n"/>
+      <c r="G24" s="79" t="n"/>
+      <c r="H24" s="283" t="inlineStr">
         <is>
           <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="78" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
-6º e 7º tempos</t>
+          <t>Qui - CAl/Fab
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J24" s="265" t="n"/>
@@ -5795,13 +5808,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -5814,13 +5827,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -5855,16 +5868,11 @@
       </c>
       <c r="F27" s="283" t="inlineStr">
         <is>
-          <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="G27" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-10º tempo</t>
-        </is>
-      </c>
+          <t>Bio - Ale
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
@@ -5880,13 +5888,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -5899,13 +5907,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -5932,14 +5940,14 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-11º e 12º tempos</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
@@ -5964,7 +5972,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -5983,7 +5991,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -6053,7 +6061,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -6075,7 +6083,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -6112,19 +6120,14 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+11º ao 13º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -6143,13 +6146,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -6165,13 +6168,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -6193,39 +6196,39 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+10º tempo</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -6248,12 +6251,17 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>Hist - Wag
+10º e 11º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="n"/>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -6267,26 +6275,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6308,15 +6316,20 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+6º tempo</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -6329,26 +6342,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -6370,7 +6383,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="361" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -6389,25 +6402,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -6431,32 +6444,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="n"/>
+      <c r="I51" s="358" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -6487,25 +6500,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -6526,7 +6539,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="n"/>
+      <c r="F57" s="361" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -6536,25 +6549,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -6586,24 +6599,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -8585,15 +8598,20 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="n"/>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -8672,20 +8690,20 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -8743,12 +8761,7 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -8756,7 +8769,12 @@
         </is>
       </c>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -8818,23 +8836,18 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>DaF - Caro-SGa-EFr
+          <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -8902,13 +8915,13 @@
       </c>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -8972,21 +8985,21 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
+      <c r="E24" s="283" t="n"/>
+      <c r="F24" s="283" t="n"/>
+      <c r="G24" s="353" t="inlineStr">
         <is>
           <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+3º tempo</t>
+        </is>
+      </c>
+      <c r="H24" s="283" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -9000,13 +9013,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -9019,13 +9032,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -9075,13 +9088,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -9094,13 +9107,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -9129,12 +9142,17 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Redação - Raf
-6º e 7º tempos</t>
+          <t>Fis - VSi
+2º tempo</t>
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>Port - Jana
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -9154,7 +9172,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -9173,7 +9191,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -9243,7 +9261,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -9265,7 +9283,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -9303,18 +9321,18 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-2º tempo</t>
-        </is>
-      </c>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J36" s="265" t="n"/>
@@ -9333,13 +9351,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -9355,13 +9373,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -9385,8 +9403,8 @@
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
+          <t>Qui - Fab
+2º tempo</t>
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
@@ -9397,25 +9415,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -9437,13 +9455,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -9457,26 +9475,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9497,21 +9515,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -9519,26 +9532,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -9560,14 +9573,14 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="n"/>
-      <c r="G48" s="283" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H48" s="283" t="n"/>
+      <c r="F48" s="361" t="n"/>
+      <c r="G48" s="283" t="n"/>
+      <c r="H48" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -9579,25 +9592,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -9621,7 +9634,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="358" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -9633,25 +9646,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -9682,25 +9695,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -9721,7 +9734,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="361" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -9736,25 +9749,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -9786,24 +9799,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -10251,15 +10264,20 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="n"/>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -10338,20 +10356,20 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -10409,12 +10427,7 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -10422,7 +10435,12 @@
         </is>
       </c>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -10484,23 +10502,18 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>DaF - Caro-SGa-EFr
+          <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -10568,13 +10581,13 @@
       </c>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -10638,21 +10651,21 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
+      <c r="E24" s="283" t="n"/>
+      <c r="F24" s="283" t="n"/>
+      <c r="G24" s="353" t="inlineStr">
         <is>
           <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+3º tempo</t>
+        </is>
+      </c>
+      <c r="H24" s="283" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -10666,13 +10679,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -10685,13 +10698,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -10741,13 +10754,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -10760,13 +10773,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -10795,12 +10808,17 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Redação - Raf
-6º e 7º tempos</t>
+          <t>Fis - VSi
+2º tempo</t>
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>Port - Jana
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -10820,7 +10838,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -10839,7 +10857,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -10909,7 +10927,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -10931,7 +10949,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -10969,18 +10987,18 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-2º tempo</t>
-        </is>
-      </c>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J36" s="265" t="n"/>
@@ -10999,13 +11017,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -11021,13 +11039,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -11051,8 +11069,8 @@
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
+          <t>Qui - Fab
+2º tempo</t>
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
@@ -11063,25 +11081,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -11103,13 +11121,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -11123,26 +11141,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11163,21 +11181,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -11185,26 +11198,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -11226,14 +11239,14 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="n"/>
-      <c r="G48" s="283" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H48" s="283" t="n"/>
+      <c r="F48" s="361" t="n"/>
+      <c r="G48" s="283" t="n"/>
+      <c r="H48" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -11245,25 +11258,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -11287,7 +11300,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="358" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -11299,25 +11312,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -11348,25 +11361,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -11387,7 +11400,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="361" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -11402,25 +11415,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -11452,24 +11465,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -12249,14 +12262,14 @@
       </c>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="n"/>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -12319,16 +12332,21 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="n"/>
+      <c r="E24" s="283" t="n"/>
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -12342,13 +12360,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -12361,13 +12379,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -12395,14 +12413,14 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -12417,13 +12435,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -12436,13 +12454,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -12471,16 +12489,11 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
+      <c r="G30" s="283" t="n"/>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
 2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H30" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
         </is>
       </c>
       <c r="I30" s="283" t="n"/>
@@ -12501,7 +12514,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -12520,7 +12533,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -12590,7 +12603,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -12612,7 +12625,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -12649,21 +12662,21 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-1º tempo</t>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -12680,13 +12693,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -12702,13 +12715,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -12730,44 +12743,39 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+      <c r="G39" s="283" t="n"/>
+      <c r="H39" s="283" t="n"/>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H39" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -12789,7 +12797,12 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H42" s="283" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
@@ -12809,26 +12822,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -12863,7 +12876,7 @@
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -12876,26 +12889,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -12917,7 +12930,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="361" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -12936,25 +12949,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -12978,32 +12991,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="n"/>
+      <c r="I51" s="358" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -13034,25 +13047,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -13073,7 +13086,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="n"/>
+      <c r="F57" s="361" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -13083,25 +13096,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -13133,24 +13146,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -13930,14 +13943,14 @@
       </c>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="n"/>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -14000,16 +14013,21 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="n"/>
+      <c r="E24" s="283" t="n"/>
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -14023,13 +14041,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -14042,13 +14060,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -14076,14 +14094,19 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="F27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -14098,13 +14121,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -14117,13 +14140,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -14152,16 +14175,11 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
+      <c r="G30" s="283" t="n"/>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
 2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H30" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
         </is>
       </c>
       <c r="I30" s="283" t="n"/>
@@ -14182,7 +14200,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -14201,7 +14219,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -14271,7 +14289,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -14293,7 +14311,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -14330,21 +14348,21 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-1º tempo</t>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -14361,13 +14379,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -14383,13 +14401,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -14411,44 +14429,39 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+      <c r="G39" s="283" t="n"/>
+      <c r="H39" s="283" t="n"/>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H39" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -14470,7 +14483,12 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H42" s="283" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
@@ -14490,26 +14508,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -14537,14 +14555,9 @@
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -14557,26 +14570,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -14598,7 +14611,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="361" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -14617,25 +14630,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -14659,7 +14672,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="358" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -14671,25 +14684,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -14720,25 +14733,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -14759,7 +14772,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="361" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -14774,25 +14787,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -14824,24 +14837,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -15296,22 +15309,22 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="inlineStr">
         <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H9" s="183" t="inlineStr">
         <is>
-          <t>Fis - Cadu
+          <t>Ing - Bea
 4º e 5º tempos</t>
         </is>
       </c>
@@ -15395,8 +15408,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
+          <t>Bio - Ale
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -15411,7 +15424,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -15471,23 +15489,23 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Ing - Bea
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-9º ao 11º tempos</t>
-        </is>
-      </c>
+      <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -15550,20 +15568,15 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+9º ao 11º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="n"/>
@@ -15635,18 +15648,18 @@
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-8º ao 10º tempos</t>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -15709,15 +15722,15 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -15732,13 +15745,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -15751,13 +15764,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -15790,14 +15803,14 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="F27" s="283" t="n"/>
+      <c r="F27" s="363" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -15812,13 +15825,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -15831,13 +15844,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -15864,17 +15877,17 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="363" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+3º ao 5º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
+          <t>Fil - LAn
+9º tempo</t>
         </is>
       </c>
       <c r="H30" s="283" t="n"/>
@@ -15896,7 +15909,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -15915,7 +15928,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -15985,7 +15998,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -16007,7 +16020,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -16044,12 +16057,17 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-9º tempo</t>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
@@ -16070,13 +16088,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -16092,13 +16110,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -16139,25 +16157,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -16178,15 +16196,15 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -16199,26 +16217,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -16242,18 +16260,13 @@
       <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
+          <t>Qui - CAl
+8º e 9º tempos</t>
         </is>
       </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="357" t="n"/>
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -16261,26 +16274,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -16301,14 +16314,14 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="n"/>
-      <c r="G48" s="283" t="inlineStr">
+      <c r="E48" s="283" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
         </is>
       </c>
+      <c r="F48" s="361" t="n"/>
+      <c r="G48" s="283" t="n"/>
       <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
@@ -16321,25 +16334,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -16363,7 +16376,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="358" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -16375,25 +16388,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -16424,25 +16437,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -16463,7 +16476,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="361" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -16478,25 +16491,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -16528,24 +16541,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -16992,25 +17005,20 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="inlineStr">
         <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
+          <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -17091,8 +17099,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
+          <t>Bio - Ale
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -17107,7 +17115,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -17165,26 +17178,26 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-9º ao 11º tempos</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Ing - PaH
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
 6º e 7º tempos</t>
         </is>
       </c>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -17246,23 +17259,23 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="n"/>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+9º ao 11º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -17331,18 +17344,18 @@
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="62" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-8º ao 10º tempos</t>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -17405,15 +17418,15 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -17428,13 +17441,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -17447,13 +17460,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -17481,14 +17494,14 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="n"/>
+      <c r="F27" s="363" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -17503,13 +17516,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -17522,13 +17535,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -17555,17 +17568,17 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="363" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+3º ao 5º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
+          <t>Fil - LAn
+9º tempo</t>
         </is>
       </c>
       <c r="H30" s="283" t="n"/>
@@ -17587,7 +17600,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -17606,7 +17619,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -17676,7 +17689,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -17698,7 +17711,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -17737,15 +17750,15 @@
       </c>
       <c r="E36" s="283" t="inlineStr">
         <is>
-          <t>Ing - PaH
-4º e 5º tempos</t>
+          <t>Geo - Mar
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-9º tempo</t>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
@@ -17766,13 +17779,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -17788,13 +17801,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -17835,25 +17848,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -17874,15 +17887,15 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -17895,26 +17908,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -17935,21 +17948,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
+          <t>Qui - CAl
+8º e 9º tempos</t>
         </is>
       </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="357" t="n"/>
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -17957,26 +17970,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -17997,14 +18010,14 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="n"/>
-      <c r="G48" s="283" t="inlineStr">
+      <c r="E48" s="283" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
         </is>
       </c>
+      <c r="F48" s="361" t="n"/>
+      <c r="G48" s="283" t="n"/>
       <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
@@ -18017,25 +18030,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -18059,7 +18072,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="358" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -18071,25 +18084,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -18120,25 +18133,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -18159,7 +18172,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="361" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -18174,25 +18187,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -18224,24 +18237,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -18688,20 +18701,20 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="n"/>
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -18780,21 +18793,26 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-10º ao 12º tempos</t>
+          <t>Hist - Wag
+10º e 11º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -18853,8 +18871,8 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="n"/>
@@ -18865,12 +18883,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -18945,7 +18958,7 @@
       </c>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>Geo - Mar
+          <t>Qui - CAl/Fab
 2º e 3º tempos</t>
         </is>
       </c>
@@ -19092,18 +19105,18 @@
         <v/>
       </c>
       <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="inlineStr">
+      <c r="F24" s="283" t="n"/>
+      <c r="G24" s="79" t="n"/>
+      <c r="H24" s="283" t="inlineStr">
         <is>
           <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="78" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
-6º e 7º tempos</t>
+          <t>Qui - CAl/Fab
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J24" s="265" t="n"/>
@@ -19119,13 +19132,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="354" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="355" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -19138,13 +19151,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="354" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="355" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -19174,16 +19187,11 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="inlineStr">
         <is>
-          <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="G27" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-10º tempo</t>
-        </is>
-      </c>
+          <t>Bio - Ale
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
@@ -19199,13 +19207,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="354" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="355" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -19218,13 +19226,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="354" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="355" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -19251,14 +19259,14 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-11º e 12º tempos</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
@@ -19283,7 +19291,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="354" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -19302,7 +19310,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="354" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -19372,7 +19380,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="356" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -19394,7 +19402,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="357" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -19431,19 +19439,14 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+11º ao 13º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -19462,13 +19465,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="354" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="355" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -19484,13 +19487,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="354" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="355" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -19510,41 +19513,46 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+10º tempo</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="354" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="355" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="354" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="355" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -19567,14 +19575,14 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>Hist - Wag
+10º e 11º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="inlineStr">
         <is>
-          <t>Ing - PaH
+          <t>Mat - Bre/JJ
 4º e 5º tempos</t>
         </is>
       </c>
@@ -19591,26 +19599,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="354" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="355" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="354" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="355" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -19632,15 +19640,20 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+6º tempo</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -19653,26 +19666,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="354" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="359" t="n"/>
+      <c r="J46" s="355" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="354" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="360" t="n"/>
+      <c r="J47" s="355" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -19694,7 +19707,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="361" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -19713,25 +19726,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="354" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="359" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="355" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="354" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="360" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="355" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -19755,32 +19768,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="n"/>
+      <c r="I51" s="358" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="354" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="359" t="n"/>
+      <c r="J52" s="355" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="354" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="360" t="n"/>
+      <c r="J53" s="355" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -19811,25 +19824,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="354" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="355" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="354" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="355" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -19850,7 +19863,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="n"/>
+      <c r="F57" s="361" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -19860,25 +19873,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="354" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="359" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="355" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="354" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="360" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="355" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -19910,24 +19923,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="359" t="n"/>
+      <c r="F61" s="359" t="n"/>
+      <c r="G61" s="359" t="n"/>
+      <c r="H61" s="359" t="n"/>
+      <c r="I61" s="359" t="n"/>
+      <c r="J61" s="359" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="362" t="n"/>
+      <c r="F62" s="362" t="n"/>
+      <c r="G62" s="362" t="n"/>
+      <c r="H62" s="362" t="n"/>
+      <c r="I62" s="362" t="n"/>
+      <c r="J62" s="362" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -2935,9 +2935,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -2964,6 +2961,9 @@
     <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5378,19 +5378,9 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -5477,18 +5467,13 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Hist - Wag
-10º e 11º tempos</t>
+          <t>LP/LIT/RED - AMu/Deb
+10º ao 12º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -5559,7 +5544,12 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="n"/>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -5628,14 +5618,14 @@
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Hist - Wag
 4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-2º e 3º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -5704,7 +5694,12 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
           <t>S4-12
@@ -5717,7 +5712,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -5782,17 +5782,17 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G24" s="363" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-2º e 3º tempos</t>
+          <t>DaF - CBu-EFr-Eth
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="J24" s="265" t="n"/>
@@ -5808,13 +5808,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -5827,13 +5827,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -5860,15 +5860,10 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
+          <t>Fis - Cadu
 1º e 2º tempos</t>
         </is>
       </c>
@@ -5888,13 +5883,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -5907,13 +5902,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -5942,7 +5937,7 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mar
+          <t>Ing - Isb
 4º e 5º tempos</t>
         </is>
       </c>
@@ -5972,7 +5967,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -5991,7 +5986,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -6061,7 +6056,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -6083,7 +6078,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -6124,7 +6119,7 @@
       <c r="F36" s="283" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
-11º ao 13º tempos</t>
+10º ao 12º tempos</t>
         </is>
       </c>
       <c r="G36" s="283" t="n"/>
@@ -6146,13 +6141,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -6168,13 +6163,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -6198,11 +6193,16 @@
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-10º tempo</t>
-        </is>
-      </c>
-      <c r="H39" s="283" t="n"/>
+          <t>Soc - Kle
+6º tempo</t>
+        </is>
+      </c>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -6210,25 +6210,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -6251,17 +6251,17 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Hist - Wag
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Bio - Ale
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -6275,26 +6275,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6315,21 +6315,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="inlineStr">
         <is>
-          <t>Soc - Kle
-6º tempo</t>
-        </is>
-      </c>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="358" t="inlineStr">
+          <t>Hist - Wag
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="357" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -6342,26 +6342,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -6383,7 +6383,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="inlineStr">
+      <c r="F48" s="360" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -6402,25 +6402,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -6444,32 +6444,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="n"/>
+      <c r="I51" s="357" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -6500,25 +6500,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -6539,7 +6539,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="n"/>
+      <c r="F57" s="360" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -6549,25 +6549,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -6599,24 +6599,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -8598,18 +8598,8 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
@@ -8692,17 +8682,17 @@
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>DaF - Caro-SGa-EFr
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Mat - BrSa
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -8761,20 +8751,20 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Port - Jana
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -8834,18 +8824,18 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -8914,15 +8904,20 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -8985,21 +8980,16 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="353" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-3º tempo</t>
-        </is>
-      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -9013,13 +9003,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -9032,13 +9022,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -9068,7 +9058,12 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="inlineStr">
         <is>
           <t>AG9
@@ -9088,13 +9083,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -9107,13 +9102,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -9140,21 +9135,16 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="283" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -9172,7 +9162,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -9191,7 +9181,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -9261,7 +9251,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -9283,7 +9273,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -9321,18 +9311,13 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J36" s="265" t="n"/>
@@ -9351,13 +9336,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -9373,13 +9358,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -9399,15 +9384,20 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-2º tempo</t>
-        </is>
-      </c>
-      <c r="H39" s="283" t="n"/>
+      <c r="G39" s="283" t="n"/>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -9415,25 +9405,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -9454,10 +9444,15 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G42" s="283" t="inlineStr">
         <is>
-          <t>Mat - BrSa
+          <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
@@ -9475,26 +9470,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9524,7 +9519,7 @@
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="358" t="n"/>
+      <c r="I45" s="357" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -9532,26 +9527,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -9572,15 +9567,20 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="n"/>
-      <c r="G48" s="283" t="n"/>
-      <c r="H48" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E48" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
+      <c r="F48" s="360" t="n"/>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+2º tempo</t>
+        </is>
+      </c>
+      <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -9592,25 +9592,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -9634,7 +9634,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="inlineStr">
+      <c r="I51" s="357" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -9646,25 +9646,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -9695,25 +9695,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -9734,7 +9734,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="inlineStr">
+      <c r="F57" s="360" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -9749,25 +9749,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -9799,24 +9799,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -10264,18 +10264,8 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
@@ -10358,17 +10348,17 @@
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>DaF - Caro-SGa-EFr
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Mat - BrSa
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -10427,20 +10417,20 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Port - Jana
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -10500,18 +10490,18 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -10580,15 +10570,20 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -10651,21 +10646,16 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="353" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-3º tempo</t>
-        </is>
-      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -10679,13 +10669,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -10698,13 +10688,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -10734,7 +10724,12 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="inlineStr">
         <is>
           <t>AG9
@@ -10754,13 +10749,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -10773,13 +10768,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -10806,21 +10801,16 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="283" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -10838,7 +10828,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -10857,7 +10847,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -10927,7 +10917,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -10949,7 +10939,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -10987,18 +10977,13 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="inlineStr">
         <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J36" s="265" t="n"/>
@@ -11017,13 +11002,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -11039,13 +11024,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -11065,15 +11050,20 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-2º tempo</t>
-        </is>
-      </c>
-      <c r="H39" s="283" t="n"/>
+      <c r="G39" s="283" t="n"/>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -11081,25 +11071,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -11120,10 +11110,15 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G42" s="283" t="inlineStr">
         <is>
-          <t>Mat - BrSa
+          <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
@@ -11141,26 +11136,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11190,7 +11185,7 @@
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="358" t="n"/>
+      <c r="I45" s="357" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -11198,26 +11193,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -11238,15 +11233,20 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="n"/>
-      <c r="G48" s="283" t="n"/>
-      <c r="H48" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E48" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
+      <c r="F48" s="360" t="n"/>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+2º tempo</t>
+        </is>
+      </c>
+      <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -11258,25 +11258,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -11300,7 +11300,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="inlineStr">
+      <c r="I51" s="357" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -11312,25 +11312,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -11361,25 +11361,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -11400,7 +11400,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="inlineStr">
+      <c r="F57" s="360" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -11415,25 +11415,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -11465,24 +11465,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -11930,25 +11930,10 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -12028,21 +12013,21 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
+          <t>Mat - BrSa/FBri
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Ing - APa
-2º e 3º tempos</t>
+          <t>Fis - VSi
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -12102,18 +12087,18 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Hist - ALu
 2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -12178,21 +12163,21 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
+          <t>Bio - Lza
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Hist - ALu
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
+      <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>AG10
-2º ao 7º tempos</t>
+          <t>Geo - Mlo
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -12260,16 +12245,26 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Ing - APa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>AG10
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -12333,18 +12328,18 @@
         <v/>
       </c>
       <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="78" t="inlineStr">
         <is>
-          <t>Soc - Kle
-5º tempo</t>
+          <t>Geo - Mlo
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J24" s="265" t="n"/>
@@ -12360,13 +12355,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -12379,13 +12374,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -12414,11 +12409,16 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H27" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I27" s="283" t="n"/>
@@ -12435,13 +12435,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -12454,13 +12454,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -12488,15 +12488,20 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="n"/>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I30" s="283" t="n"/>
+      <c r="H30" s="283" t="n"/>
+      <c r="I30" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -12514,7 +12519,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -12533,7 +12538,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -12603,7 +12608,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -12625,7 +12630,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -12662,17 +12667,17 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F36" s="283" t="n"/>
+      <c r="E36" s="283" t="n"/>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
+          <t>Fil - LAn
+1º tempo</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
@@ -12693,13 +12698,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -12715,13 +12720,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -12741,41 +12746,41 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -12799,16 +12804,11 @@
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
+          <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -12822,26 +12822,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -12873,10 +12873,10 @@
       <c r="H45" s="283" t="inlineStr">
         <is>
           <t>Ing - APa
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="358" t="inlineStr">
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I45" s="357" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -12889,26 +12889,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -12930,7 +12930,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="inlineStr">
+      <c r="F48" s="360" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -12949,25 +12949,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -12991,32 +12991,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="n"/>
+      <c r="I51" s="357" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -13047,25 +13047,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -13086,7 +13086,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="n"/>
+      <c r="F57" s="360" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -13096,25 +13096,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -13146,24 +13146,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -13611,25 +13611,10 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -13709,18 +13694,23 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+          <t>Mat - BrSa/FBri
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -13778,23 +13768,23 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Hist - ALu
 2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -13859,21 +13849,21 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
+          <t>Bio - Lza
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Hist - ALu
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
+      <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>AG10
-2º ao 7º tempos</t>
+          <t>Geo - Mlo
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -13941,16 +13931,21 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
+      <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>AG10
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -14014,18 +14009,18 @@
         <v/>
       </c>
       <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="78" t="inlineStr">
         <is>
-          <t>Soc - Kle
-5º tempo</t>
+          <t>Geo - Mlo
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J24" s="265" t="n"/>
@@ -14041,13 +14036,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -14060,13 +14055,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -14097,14 +14092,14 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="inlineStr">
         <is>
-          <t>Ing - Vir
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H27" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
         </is>
       </c>
       <c r="I27" s="283" t="n"/>
@@ -14121,13 +14116,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -14140,13 +14135,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -14174,15 +14169,20 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="n"/>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I30" s="283" t="n"/>
+      <c r="H30" s="283" t="n"/>
+      <c r="I30" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -14200,7 +14200,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -14219,7 +14219,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -14289,7 +14289,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -14311,7 +14311,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -14348,17 +14348,17 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F36" s="283" t="n"/>
+      <c r="E36" s="283" t="n"/>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
+          <t>Fil - LAn
+1º tempo</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
@@ -14379,13 +14379,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -14401,13 +14401,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -14427,41 +14427,41 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -14485,16 +14485,11 @@
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
+          <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -14508,26 +14503,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -14555,9 +14550,14 @@
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="358" t="inlineStr">
+      <c r="I45" s="357" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -14570,26 +14570,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -14611,7 +14611,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="inlineStr">
+      <c r="F48" s="360" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -14630,25 +14630,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -14672,7 +14672,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="inlineStr">
+      <c r="I51" s="357" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -14684,25 +14684,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -14733,25 +14733,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -14772,7 +14772,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="inlineStr">
+      <c r="F57" s="360" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -14787,25 +14787,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -14837,24 +14837,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -15310,24 +15310,9 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -15408,8 +15393,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -15426,8 +15411,8 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
+          <t>Ing - Bea
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -15487,25 +15472,25 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mar
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Hist - Ver
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-11º e 12º tempos</t>
-        </is>
-      </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="n"/>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -15568,17 +15553,17 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-9º ao 11º tempos</t>
-        </is>
-      </c>
+      <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
@@ -15645,18 +15630,23 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
+          <t>Qui - CAl
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-4º e 5º tempos</t>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+9º ao 11º tempos</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -15722,16 +15712,21 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="362" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+4º ao 6º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I24" s="78" t="n"/>
+      <c r="H24" s="283" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -15745,13 +15740,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -15764,13 +15759,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -15797,20 +15792,15 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F27" s="363" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="78" t="n"/>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -15825,13 +15815,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -15844,13 +15834,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -15877,19 +15867,14 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="363" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-3º ao 5º tempos</t>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-9º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -15909,7 +15894,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -15928,7 +15913,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -15998,7 +15983,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -16020,7 +16005,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -16057,17 +16042,12 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
@@ -16088,13 +16068,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -16110,13 +16090,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -16148,7 +16128,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -16157,25 +16142,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -16196,15 +16181,20 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -16217,26 +16207,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -16260,13 +16250,18 @@
       <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="inlineStr">
         <is>
-          <t>Qui - CAl
-8º e 9º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
+          <t>Hist - Ver
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="358" t="n"/>
+      <c r="I45" s="357" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -16274,26 +16269,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -16316,11 +16311,16 @@
       </c>
       <c r="E48" s="283" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F48" s="361" t="n"/>
+          <t>Ing - Bea
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="F48" s="360" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+8º e 9º tempos</t>
+        </is>
+      </c>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
@@ -16334,25 +16334,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -16376,7 +16376,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="inlineStr">
+      <c r="I51" s="357" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -16388,25 +16388,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -16437,25 +16437,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -16476,7 +16476,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="inlineStr">
+      <c r="F57" s="360" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -16491,25 +16491,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -16541,24 +16541,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -17006,18 +17006,8 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
@@ -17099,8 +17089,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -17115,13 +17105,13 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -17178,25 +17168,25 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mar
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Hist - Ver
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-11º e 12º tempos</t>
-        </is>
-      </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="n"/>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -17259,23 +17249,18 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-9º ao 11º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -17341,18 +17326,23 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
+          <t>Qui - CAl
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-4º e 5º tempos</t>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+9º ao 11º tempos</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -17418,16 +17408,21 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="362" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+4º ao 6º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I24" s="78" t="n"/>
+      <c r="H24" s="283" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -17441,13 +17436,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -17460,13 +17455,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -17494,14 +17489,14 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="363" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -17516,13 +17511,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -17535,13 +17530,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -17568,19 +17563,14 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="363" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-3º ao 5º tempos</t>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-9º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -17600,7 +17590,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -17619,7 +17609,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -17689,7 +17679,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -17711,7 +17701,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -17748,17 +17738,12 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
@@ -17779,13 +17764,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -17801,13 +17786,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -17839,7 +17824,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -17848,25 +17838,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -17887,15 +17877,20 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -17908,26 +17903,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -17948,21 +17943,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="inlineStr">
         <is>
-          <t>Qui - CAl
-8º e 9º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
+          <t>Hist - Ver
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="358" t="n"/>
+      <c r="I45" s="357" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -17970,26 +17965,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -18012,11 +18007,16 @@
       </c>
       <c r="E48" s="283" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F48" s="361" t="n"/>
+          <t>Ing - PaH
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F48" s="360" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+8º e 9º tempos</t>
+        </is>
+      </c>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
@@ -18030,25 +18030,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -18072,7 +18072,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="inlineStr">
+      <c r="I51" s="357" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -18084,25 +18084,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -18133,25 +18133,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -18172,7 +18172,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="inlineStr">
+      <c r="F57" s="360" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -18187,25 +18187,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -18237,24 +18237,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">
@@ -18702,19 +18702,9 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -18801,18 +18791,13 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Hist - Wag
-10º e 11º tempos</t>
+          <t>LP/LIT/RED - AMu/Deb
+10º ao 12º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -18883,7 +18868,12 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="n"/>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -18952,14 +18942,14 @@
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Hist - Wag
 4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-2º e 3º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -19028,7 +19018,12 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
           <t>S4-12
@@ -19041,7 +19036,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -19106,17 +19106,17 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G24" s="363" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-2º e 3º tempos</t>
+          <t>DaF - CBu-EFr-Eth
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="J24" s="265" t="n"/>
@@ -19132,13 +19132,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="354" t="n"/>
+      <c r="D25" s="353" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="355" t="n"/>
+      <c r="J25" s="354" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -19151,13 +19151,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="354" t="n"/>
+      <c r="D26" s="353" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="355" t="n"/>
+      <c r="J26" s="354" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -19184,10 +19184,15 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
+      <c r="E27" s="78" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F27" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
+          <t>Fis - Cadu
 1º e 2º tempos</t>
         </is>
       </c>
@@ -19207,13 +19212,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="354" t="n"/>
+      <c r="D28" s="353" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="355" t="n"/>
+      <c r="J28" s="354" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -19226,13 +19231,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="354" t="n"/>
+      <c r="D29" s="353" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="355" t="n"/>
+      <c r="J29" s="354" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -19259,12 +19264,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="inlineStr">
@@ -19291,7 +19291,7 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="354" t="n"/>
+      <c r="D31" s="353" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
@@ -19310,7 +19310,7 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="354" t="n"/>
+      <c r="D32" s="353" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
@@ -19380,7 +19380,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="356" t="n"/>
+      <c r="D34" s="355" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -19402,7 +19402,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="357" t="n"/>
+      <c r="D35" s="356" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -19443,7 +19443,7 @@
       <c r="F36" s="283" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
-11º ao 13º tempos</t>
+10º ao 12º tempos</t>
         </is>
       </c>
       <c r="G36" s="283" t="n"/>
@@ -19465,13 +19465,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="354" t="n"/>
+      <c r="D37" s="353" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="355" t="n"/>
+      <c r="J37" s="354" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -19487,13 +19487,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="354" t="n"/>
+      <c r="D38" s="353" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="355" t="n"/>
+      <c r="J38" s="354" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -19513,20 +19513,20 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-10º tempo</t>
-        </is>
-      </c>
-      <c r="H39" s="283" t="n"/>
+          <t>Soc - Kle
+6º tempo</t>
+        </is>
+      </c>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -19534,25 +19534,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="354" t="n"/>
+      <c r="D40" s="353" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="355" t="n"/>
+      <c r="J40" s="354" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="354" t="n"/>
+      <c r="D41" s="353" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="355" t="n"/>
+      <c r="J41" s="354" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -19575,17 +19575,17 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Hist - Wag
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Bio - Ale
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -19599,26 +19599,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="354" t="n"/>
+      <c r="D43" s="353" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="355" t="n"/>
+      <c r="J43" s="354" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="354" t="n"/>
+      <c r="D44" s="353" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="355" t="n"/>
+      <c r="J44" s="354" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -19639,21 +19639,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="inlineStr">
         <is>
-          <t>Soc - Kle
-6º tempo</t>
-        </is>
-      </c>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="358" t="inlineStr">
+          <t>Hist - Wag
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="357" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -19666,26 +19666,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="354" t="n"/>
+      <c r="D46" s="353" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="359" t="n"/>
-      <c r="J46" s="355" t="n"/>
+      <c r="I46" s="358" t="n"/>
+      <c r="J46" s="354" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="354" t="n"/>
+      <c r="D47" s="353" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="360" t="n"/>
-      <c r="J47" s="355" t="n"/>
+      <c r="I47" s="359" t="n"/>
+      <c r="J47" s="354" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -19707,7 +19707,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="361" t="inlineStr">
+      <c r="F48" s="360" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -19726,25 +19726,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="354" t="n"/>
+      <c r="D49" s="353" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="359" t="n"/>
+      <c r="F49" s="358" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="355" t="n"/>
+      <c r="J49" s="354" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="354" t="n"/>
+      <c r="D50" s="353" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="360" t="n"/>
+      <c r="F50" s="359" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="355" t="n"/>
+      <c r="J50" s="354" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -19768,32 +19768,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="358" t="n"/>
+      <c r="I51" s="357" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="354" t="n"/>
+      <c r="D52" s="353" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="359" t="n"/>
-      <c r="J52" s="355" t="n"/>
+      <c r="I52" s="358" t="n"/>
+      <c r="J52" s="354" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="354" t="n"/>
+      <c r="D53" s="353" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="360" t="n"/>
-      <c r="J53" s="355" t="n"/>
+      <c r="I53" s="359" t="n"/>
+      <c r="J53" s="354" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -19824,25 +19824,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="354" t="n"/>
+      <c r="D55" s="353" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="355" t="n"/>
+      <c r="J55" s="354" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="354" t="n"/>
+      <c r="D56" s="353" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="355" t="n"/>
+      <c r="J56" s="354" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -19863,7 +19863,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="361" t="n"/>
+      <c r="F57" s="360" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -19873,25 +19873,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="354" t="n"/>
+      <c r="D58" s="353" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="359" t="n"/>
+      <c r="F58" s="358" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="355" t="n"/>
+      <c r="J58" s="354" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="354" t="n"/>
+      <c r="D59" s="353" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="360" t="n"/>
+      <c r="F59" s="359" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="355" t="n"/>
+      <c r="J59" s="354" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -19923,24 +19923,24 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="359" t="n"/>
-      <c r="F61" s="359" t="n"/>
-      <c r="G61" s="359" t="n"/>
-      <c r="H61" s="359" t="n"/>
-      <c r="I61" s="359" t="n"/>
-      <c r="J61" s="359" t="n"/>
+      <c r="E61" s="358" t="n"/>
+      <c r="F61" s="358" t="n"/>
+      <c r="G61" s="358" t="n"/>
+      <c r="H61" s="358" t="n"/>
+      <c r="I61" s="358" t="n"/>
+      <c r="J61" s="358" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="362" t="n"/>
-      <c r="F62" s="362" t="n"/>
-      <c r="G62" s="362" t="n"/>
-      <c r="H62" s="362" t="n"/>
-      <c r="I62" s="362" t="n"/>
-      <c r="J62" s="362" t="n"/>
+      <c r="E62" s="361" t="n"/>
+      <c r="F62" s="361" t="n"/>
+      <c r="G62" s="361" t="n"/>
+      <c r="H62" s="361" t="n"/>
+      <c r="I62" s="361" t="n"/>
+      <c r="J62" s="361" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="146">

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -12161,12 +12161,7 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
@@ -12251,7 +12246,12 @@
 1º ao 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="inlineStr">
         <is>
@@ -12259,12 +12259,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>AG10
-2º ao 7º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -12327,19 +12322,19 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
+          <t>AG10
+2º ao 7º tempos</t>
         </is>
       </c>
       <c r="J24" s="265" t="n"/>
@@ -12408,20 +12403,20 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+      <c r="F27" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G27" s="283" t="n"/>
+      <c r="H27" s="283" t="n"/>
+      <c r="I27" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H27" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -12488,20 +12483,15 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -12668,19 +12658,19 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
-      <c r="H36" s="283" t="n"/>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H36" s="283" t="inlineStr">
+        <is>
+          <t>Ing - APa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -12746,16 +12736,21 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -12801,10 +12796,15 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G42" s="283" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
+          <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
@@ -12864,18 +12864,18 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+          <t>Qui - CAl
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Ing - APa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="n"/>
       <c r="I45" s="357" t="inlineStr">
         <is>
           <t>2CH
@@ -13847,12 +13847,7 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
@@ -13937,15 +13932,15 @@
 1º ao 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>AG10
-2º ao 7º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -14008,19 +14003,19 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
+          <t>AG10
+2º ao 7º tempos</t>
         </is>
       </c>
       <c r="J24" s="265" t="n"/>
@@ -14089,20 +14084,20 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+      <c r="F27" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G27" s="283" t="n"/>
+      <c r="H27" s="283" t="n"/>
+      <c r="I27" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H27" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -14169,20 +14164,15 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -14351,14 +14341,14 @@
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="inlineStr">
         <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
+          <t>Ing - Vir
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-1º tempo</t>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
@@ -14427,16 +14417,21 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -14482,10 +14477,15 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G42" s="283" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
+          <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
@@ -14545,15 +14545,15 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+          <t>Qui - CAl
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="inlineStr">
         <is>
-          <t>Ing - Vir
-4º e 5º tempos</t>
+          <t>Fil - LAn
+1º tempo</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -264,7 +264,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="32">
     <fill>
       <patternFill/>
     </fill>
@@ -357,12 +357,102 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6E7CF"/>
+        <bgColor rgb="00C6E7CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E7E4"/>
+        <bgColor rgb="00C6E7E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7C6E1"/>
+        <bgColor rgb="00E7C6E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E7C6"/>
+        <bgColor rgb="00C8E7C6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7C6D6"/>
+        <bgColor rgb="00E7C6D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDE7C6"/>
+        <bgColor rgb="00DDE7C6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D2E7C6"/>
+        <bgColor rgb="00D2E7C6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E7D9"/>
+        <bgColor rgb="00C6E7D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6CAE7"/>
+        <bgColor rgb="00C6CAE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6DFE7"/>
+        <bgColor rgb="00C6DFE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6D4E7"/>
+        <bgColor rgb="00C6D4E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2C6E7"/>
+        <bgColor rgb="00E2C6E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CDC6E7"/>
+        <bgColor rgb="00CDC6E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D7C6E7"/>
+        <bgColor rgb="00D7C6E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="108">
+  <borders count="111">
     <border>
       <left/>
       <right/>
@@ -1703,6 +1793,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1710,7 +1814,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="364">
+  <cellXfs count="431">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2925,6 +3029,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="96" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="105" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="105" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
@@ -2935,19 +3119,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -2955,15 +3131,153 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="105" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="82" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="82" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="82" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="107" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="105" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="105" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="105" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5459,13 +5773,13 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="411" t="inlineStr">
         <is>
           <t>Ing - Isb
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="418" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 10º ao 12º tempos</t>
@@ -5485,8 +5799,8 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="222" t="n"/>
-      <c r="F13" s="222" t="n"/>
+      <c r="E13" s="404" t="n"/>
+      <c r="F13" s="404" t="n"/>
       <c r="G13" s="222" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
@@ -5501,8 +5815,8 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="222" t="n"/>
-      <c r="F14" s="222" t="n"/>
+      <c r="E14" s="405" t="n"/>
+      <c r="F14" s="405" t="n"/>
       <c r="G14" s="222" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
@@ -5530,7 +5844,7 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="406" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 4º e 5º tempos</t>
@@ -5538,13 +5852,13 @@
       </c>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="415" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="416" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 2º e 3º tempos</t>
@@ -5560,11 +5874,11 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="222" t="n"/>
+      <c r="E16" s="404" t="n"/>
       <c r="F16" s="222" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="222" t="n"/>
-      <c r="I16" s="222" t="n"/>
+      <c r="H16" s="404" t="n"/>
+      <c r="I16" s="404" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -5576,11 +5890,11 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="222" t="n"/>
+      <c r="E17" s="405" t="n"/>
       <c r="F17" s="222" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="222" t="n"/>
-      <c r="I17" s="222" t="n"/>
+      <c r="H17" s="405" t="n"/>
+      <c r="I17" s="405" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -5609,30 +5923,26 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="414" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="413" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I18" s="350" t="inlineStr">
+      <c r="I18" s="425" t="inlineStr">
         <is>
           <t>Hist - Wag
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="J18" s="262" t="inlineStr">
-        <is>
-          <t>2CH 9,10,11,12</t>
-        </is>
-      </c>
+      <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -5643,10 +5953,10 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="222" t="n"/>
+      <c r="F19" s="404" t="n"/>
       <c r="G19" s="222" t="n"/>
-      <c r="H19" s="222" t="n"/>
-      <c r="I19" s="351" t="n"/>
+      <c r="H19" s="404" t="n"/>
+      <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
         <is>
@@ -5666,10 +5976,10 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="222" t="n"/>
+      <c r="F20" s="405" t="n"/>
       <c r="G20" s="222" t="n"/>
-      <c r="H20" s="222" t="n"/>
-      <c r="I20" s="352" t="n"/>
+      <c r="H20" s="405" t="n"/>
+      <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
@@ -5694,31 +6004,35 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="inlineStr">
+      <c r="F21" s="402" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="412" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="412" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="403" t="inlineStr">
         <is>
           <t>Geo - Mar
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="J21" s="183" t="n"/>
+      <c r="J21" s="262" t="inlineStr">
+        <is>
+          <t>2CH 9,10,11,12</t>
+        </is>
+      </c>
       <c r="L21" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">15.09 </t>
@@ -5737,10 +6051,10 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="63" t="n"/>
-      <c r="G22" s="222" t="n"/>
-      <c r="H22" s="222" t="n"/>
-      <c r="I22" s="222" t="n"/>
+      <c r="F22" s="404" t="n"/>
+      <c r="G22" s="404" t="n"/>
+      <c r="H22" s="404" t="n"/>
+      <c r="I22" s="404" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -5752,10 +6066,10 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="63" t="n"/>
-      <c r="G23" s="222" t="n"/>
-      <c r="H23" s="222" t="n"/>
-      <c r="I23" s="222" t="n"/>
+      <c r="F23" s="405" t="n"/>
+      <c r="G23" s="405" t="n"/>
+      <c r="H23" s="405" t="n"/>
+      <c r="I23" s="405" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -5782,14 +6096,14 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="363" t="inlineStr">
+      <c r="G24" s="426" t="inlineStr">
         <is>
           <t>Geo - Mar
 11º e 12º tempos</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
+      <c r="I24" s="427" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 6º e 7º tempos</t>
@@ -5808,13 +6122,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="79" t="n"/>
+      <c r="G25" s="428" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="I25" s="404" t="n"/>
+      <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -5827,13 +6141,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="79" t="n"/>
+      <c r="G26" s="429" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="I26" s="405" t="n"/>
+      <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -5861,7 +6175,7 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="inlineStr">
+      <c r="F27" s="415" t="inlineStr">
         <is>
           <t>Fis - Cadu
 1º e 2º tempos</t>
@@ -5883,13 +6197,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
-      <c r="F28" s="283" t="n"/>
+      <c r="F28" s="404" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -5902,13 +6216,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
-      <c r="F29" s="283" t="n"/>
+      <c r="F29" s="405" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -5935,7 +6249,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
+      <c r="E30" s="411" t="inlineStr">
         <is>
           <t>Ing - Isb
 4º e 5º tempos</t>
@@ -5943,7 +6257,7 @@
       </c>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="inlineStr">
+      <c r="H30" s="413" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
@@ -5967,11 +6281,11 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
-      <c r="E31" s="283" t="n"/>
+      <c r="D31" s="350" t="n"/>
+      <c r="E31" s="404" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="283" t="n"/>
+      <c r="H31" s="404" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -5986,11 +6300,11 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
-      <c r="E32" s="283" t="n"/>
+      <c r="D32" s="350" t="n"/>
+      <c r="E32" s="405" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="283" t="n"/>
+      <c r="H32" s="405" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -6056,7 +6370,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="366" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -6078,7 +6392,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="385" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -6116,7 +6430,7 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
+      <c r="F36" s="418" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 10º ao 12º tempos</t>
@@ -6141,13 +6455,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="283" t="n"/>
+      <c r="F37" s="404" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -6163,13 +6477,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="283" t="n"/>
+      <c r="F38" s="405" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -6191,13 +6505,13 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
+      <c r="G39" s="420" t="inlineStr">
         <is>
           <t>Soc - Kle
 6º tempo</t>
         </is>
       </c>
-      <c r="H39" s="283" t="inlineStr">
+      <c r="H39" s="402" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 4º e 5º tempos</t>
@@ -6210,25 +6524,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="283" t="n"/>
-      <c r="H40" s="283" t="n"/>
+      <c r="G40" s="404" t="n"/>
+      <c r="H40" s="404" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="283" t="n"/>
-      <c r="H41" s="283" t="n"/>
+      <c r="G41" s="405" t="n"/>
+      <c r="H41" s="405" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -6249,13 +6563,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
+      <c r="F42" s="414" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G42" s="283" t="inlineStr">
+      <c r="G42" s="421" t="inlineStr">
         <is>
           <t>Fil - LAn
 4º tempo</t>
@@ -6275,26 +6589,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
-      <c r="G43" s="283" t="n"/>
+      <c r="F43" s="404" t="n"/>
+      <c r="G43" s="404" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
-      <c r="G44" s="283" t="n"/>
+      <c r="F44" s="405" t="n"/>
+      <c r="G44" s="405" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6315,21 +6629,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
+      <c r="E45" s="416" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 6º e 7º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
+      <c r="G45" s="410" t="inlineStr">
         <is>
           <t>Hist - Wag
 11º e 12º tempos</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -6342,26 +6656,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
-      <c r="E46" s="283" t="n"/>
+      <c r="D46" s="350" t="n"/>
+      <c r="E46" s="404" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="283" t="n"/>
+      <c r="G46" s="404" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="351" t="n"/>
+      <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
-      <c r="E47" s="283" t="n"/>
+      <c r="D47" s="350" t="n"/>
+      <c r="E47" s="405" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="283" t="n"/>
+      <c r="G47" s="405" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="387" t="n"/>
+      <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -6383,7 +6697,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="388" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -6402,25 +6716,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="350" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="352" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="350" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="352" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -6444,32 +6758,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="n"/>
+      <c r="I51" s="386" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="350" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="351" t="n"/>
+      <c r="J52" s="352" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="350" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="387" t="n"/>
+      <c r="J53" s="352" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -6500,25 +6814,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="350" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="352" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="350" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="352" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -6539,7 +6853,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="n"/>
+      <c r="F57" s="388" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -6549,25 +6863,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="350" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="351" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="352" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="350" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="387" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="352" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -6599,27 +6913,27 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="351" t="n"/>
+      <c r="F61" s="351" t="n"/>
+      <c r="G61" s="351" t="n"/>
+      <c r="H61" s="351" t="n"/>
+      <c r="I61" s="351" t="n"/>
+      <c r="J61" s="351" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="353" t="n"/>
+      <c r="F62" s="353" t="n"/>
+      <c r="G62" s="353" t="n"/>
+      <c r="H62" s="353" t="n"/>
+      <c r="I62" s="353" t="n"/>
+      <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="146">
+  <mergeCells count="169">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -6646,9 +6960,13 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
+    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -6658,18 +6976,25 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E30:E32"/>
     <mergeCell ref="A12:A14"/>
+    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
+    <mergeCell ref="F27:F29"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="I15:I17"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
@@ -6706,6 +7031,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -6715,19 +7041,28 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
+    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
+    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="I24:I26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -6745,6 +7080,7 @@
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
+    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -6762,6 +7098,7 @@
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
+    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>
@@ -8680,13 +9017,13 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="402" t="inlineStr">
         <is>
           <t>Mat - BrSa
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="403" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -8706,8 +9043,8 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="222" t="n"/>
-      <c r="F13" s="222" t="n"/>
-      <c r="G13" s="222" t="n"/>
+      <c r="F13" s="404" t="n"/>
+      <c r="G13" s="404" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
@@ -8722,8 +9059,8 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="222" t="n"/>
-      <c r="F14" s="222" t="n"/>
-      <c r="G14" s="222" t="n"/>
+      <c r="F14" s="405" t="n"/>
+      <c r="G14" s="405" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
@@ -8751,14 +9088,14 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="406" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="407" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
@@ -8776,9 +9113,9 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
-      <c r="F16" s="222" t="n"/>
+      <c r="F16" s="404" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="222" t="n"/>
+      <c r="H16" s="404" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -8792,9 +9129,9 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
-      <c r="F17" s="222" t="n"/>
+      <c r="F17" s="405" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="222" t="n"/>
+      <c r="H17" s="405" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -8825,24 +9162,20 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="408" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="350" t="inlineStr">
+      <c r="I18" s="409" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="J18" s="262" t="inlineStr">
-        <is>
-          <t>2CH 9,10,11,12</t>
-        </is>
-      </c>
+      <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -8854,9 +9187,9 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="222" t="n"/>
+      <c r="G19" s="404" t="n"/>
       <c r="H19" s="222" t="n"/>
-      <c r="I19" s="351" t="n"/>
+      <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
         <is>
@@ -8877,9 +9210,9 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="222" t="n"/>
+      <c r="G20" s="405" t="n"/>
       <c r="H20" s="222" t="n"/>
-      <c r="I20" s="352" t="n"/>
+      <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
@@ -8904,7 +9237,7 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="inlineStr">
+      <c r="F21" s="410" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
@@ -8912,13 +9245,17 @@
       </c>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="411" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="J21" s="183" t="n"/>
+      <c r="J21" s="262" t="inlineStr">
+        <is>
+          <t>2CH 9,10,11,12</t>
+        </is>
+      </c>
       <c r="L21" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">15.09 </t>
@@ -8937,10 +9274,10 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="63" t="n"/>
+      <c r="F22" s="404" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="222" t="n"/>
-      <c r="I22" s="222" t="n"/>
+      <c r="I22" s="404" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -8952,10 +9289,10 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="63" t="n"/>
+      <c r="F23" s="405" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="222" t="n"/>
-      <c r="I23" s="222" t="n"/>
+      <c r="I23" s="405" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -8980,7 +9317,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
+      <c r="E24" s="407" t="inlineStr">
         <is>
           <t>Redação - Raf
 6º e 7º tempos</t>
@@ -9003,13 +9340,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
-      <c r="E25" s="283" t="n"/>
+      <c r="D25" s="350" t="n"/>
+      <c r="E25" s="404" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -9022,13 +9359,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
-      <c r="E26" s="283" t="n"/>
+      <c r="D26" s="350" t="n"/>
+      <c r="E26" s="405" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -9058,13 +9395,13 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="inlineStr">
+      <c r="H27" s="406" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I27" s="283" t="inlineStr">
+      <c r="I27" s="412" t="inlineStr">
         <is>
           <t>AG9
 2º ao 7º tempos</t>
@@ -9083,13 +9420,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
-      <c r="H28" s="283" t="n"/>
-      <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="H28" s="404" t="n"/>
+      <c r="I28" s="404" t="n"/>
+      <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -9102,13 +9439,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
-      <c r="H29" s="283" t="n"/>
-      <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="H29" s="405" t="n"/>
+      <c r="I29" s="405" t="n"/>
+      <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -9139,7 +9476,7 @@
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="inlineStr">
+      <c r="I30" s="411" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -9162,12 +9499,12 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="283" t="n"/>
-      <c r="I31" s="283" t="n"/>
+      <c r="I31" s="404" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -9181,12 +9518,12 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="283" t="n"/>
-      <c r="I32" s="283" t="n"/>
+      <c r="I32" s="405" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -9251,7 +9588,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="366" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -9273,7 +9610,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="385" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -9314,7 +9651,7 @@
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
+      <c r="I36" s="413" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
@@ -9336,13 +9673,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="I37" s="404" t="n"/>
+      <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -9358,13 +9695,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="I38" s="405" t="n"/>
+      <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -9384,7 +9721,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
+      <c r="E39" s="414" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º tempo</t>
@@ -9392,7 +9729,7 @@
       </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="inlineStr">
+      <c r="H39" s="402" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
@@ -9405,25 +9742,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
-      <c r="E40" s="283" t="n"/>
+      <c r="D40" s="350" t="n"/>
+      <c r="E40" s="404" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="283" t="n"/>
+      <c r="H40" s="404" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
-      <c r="E41" s="283" t="n"/>
+      <c r="D41" s="350" t="n"/>
+      <c r="E41" s="405" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="283" t="n"/>
+      <c r="H41" s="405" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -9444,13 +9781,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
+      <c r="F42" s="410" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G42" s="283" t="inlineStr">
+      <c r="G42" s="408" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
@@ -9470,26 +9807,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
-      <c r="G43" s="283" t="n"/>
+      <c r="F43" s="404" t="n"/>
+      <c r="G43" s="404" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
-      <c r="G44" s="283" t="n"/>
+      <c r="F44" s="405" t="n"/>
+      <c r="G44" s="405" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9512,14 +9849,14 @@
       </c>
       <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
+      <c r="G45" s="403" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="n"/>
+      <c r="I45" s="386" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -9527,26 +9864,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="283" t="n"/>
+      <c r="G46" s="404" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="351" t="n"/>
+      <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="283" t="n"/>
+      <c r="G47" s="405" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="387" t="n"/>
+      <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -9567,14 +9904,14 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
+      <c r="E48" s="415" t="inlineStr">
         <is>
           <t>Fis - VSi
 2º tempo</t>
         </is>
       </c>
-      <c r="F48" s="360" t="n"/>
-      <c r="G48" s="283" t="inlineStr">
+      <c r="F48" s="388" t="n"/>
+      <c r="G48" s="416" t="inlineStr">
         <is>
           <t>Qui - Fab
 2º tempo</t>
@@ -9592,25 +9929,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
-      <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
-      <c r="G49" s="283" t="n"/>
+      <c r="D49" s="350" t="n"/>
+      <c r="E49" s="404" t="n"/>
+      <c r="F49" s="351" t="n"/>
+      <c r="G49" s="404" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="352" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
-      <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
-      <c r="G50" s="283" t="n"/>
+      <c r="D50" s="350" t="n"/>
+      <c r="E50" s="405" t="n"/>
+      <c r="F50" s="387" t="n"/>
+      <c r="G50" s="405" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="352" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -9634,7 +9971,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="386" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -9646,25 +9983,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="350" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="351" t="n"/>
+      <c r="J52" s="352" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="350" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="387" t="n"/>
+      <c r="J53" s="352" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -9695,25 +10032,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="350" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="352" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="350" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="352" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -9734,7 +10071,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="388" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -9749,25 +10086,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="350" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="351" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="352" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="350" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="387" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="352" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -9799,27 +10136,27 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="351" t="n"/>
+      <c r="F61" s="351" t="n"/>
+      <c r="G61" s="351" t="n"/>
+      <c r="H61" s="351" t="n"/>
+      <c r="I61" s="351" t="n"/>
+      <c r="J61" s="351" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="353" t="n"/>
+      <c r="F62" s="353" t="n"/>
+      <c r="G62" s="353" t="n"/>
+      <c r="H62" s="353" t="n"/>
+      <c r="I62" s="353" t="n"/>
+      <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="146">
+  <mergeCells count="165">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -9846,8 +10183,12 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
@@ -9861,10 +10202,12 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H27:H29"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
@@ -9874,11 +10217,14 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -9906,6 +10252,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -9915,6 +10262,8 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="E39:E41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
@@ -9922,12 +10271,15 @@
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G18:G20"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -9953,7 +10305,10 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="I27:I29"/>
     <mergeCell ref="A39:A41"/>
+    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -9962,6 +10317,7 @@
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
+    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>
@@ -10346,13 +10702,13 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="402" t="inlineStr">
         <is>
           <t>Mat - BrSa
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="403" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -10372,8 +10728,8 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="222" t="n"/>
-      <c r="F13" s="222" t="n"/>
-      <c r="G13" s="222" t="n"/>
+      <c r="F13" s="404" t="n"/>
+      <c r="G13" s="404" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
@@ -10388,8 +10744,8 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="222" t="n"/>
-      <c r="F14" s="222" t="n"/>
-      <c r="G14" s="222" t="n"/>
+      <c r="F14" s="405" t="n"/>
+      <c r="G14" s="405" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
@@ -10417,14 +10773,14 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="406" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="407" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
@@ -10442,9 +10798,9 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
-      <c r="F16" s="222" t="n"/>
+      <c r="F16" s="404" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="222" t="n"/>
+      <c r="H16" s="404" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -10458,9 +10814,9 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
-      <c r="F17" s="222" t="n"/>
+      <c r="F17" s="405" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="222" t="n"/>
+      <c r="H17" s="405" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -10491,24 +10847,20 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="408" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="350" t="inlineStr">
+      <c r="I18" s="409" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="J18" s="262" t="inlineStr">
-        <is>
-          <t>2CH 9,10,11,12</t>
-        </is>
-      </c>
+      <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -10520,9 +10872,9 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="222" t="n"/>
+      <c r="G19" s="404" t="n"/>
       <c r="H19" s="222" t="n"/>
-      <c r="I19" s="351" t="n"/>
+      <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
         <is>
@@ -10543,9 +10895,9 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="222" t="n"/>
+      <c r="G20" s="405" t="n"/>
       <c r="H20" s="222" t="n"/>
-      <c r="I20" s="352" t="n"/>
+      <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
@@ -10570,7 +10922,7 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="inlineStr">
+      <c r="F21" s="410" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
@@ -10578,13 +10930,17 @@
       </c>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="411" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="J21" s="183" t="n"/>
+      <c r="J21" s="262" t="inlineStr">
+        <is>
+          <t>2CH 9,10,11,12</t>
+        </is>
+      </c>
       <c r="L21" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">15.09 </t>
@@ -10603,10 +10959,10 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="63" t="n"/>
+      <c r="F22" s="404" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="222" t="n"/>
-      <c r="I22" s="222" t="n"/>
+      <c r="I22" s="404" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -10618,10 +10974,10 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="63" t="n"/>
+      <c r="F23" s="405" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="222" t="n"/>
-      <c r="I23" s="222" t="n"/>
+      <c r="I23" s="405" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -10646,7 +11002,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
+      <c r="E24" s="407" t="inlineStr">
         <is>
           <t>Redação - Raf
 6º e 7º tempos</t>
@@ -10669,13 +11025,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
-      <c r="E25" s="283" t="n"/>
+      <c r="D25" s="350" t="n"/>
+      <c r="E25" s="404" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -10688,13 +11044,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
-      <c r="E26" s="283" t="n"/>
+      <c r="D26" s="350" t="n"/>
+      <c r="E26" s="405" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -10724,13 +11080,13 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="inlineStr">
+      <c r="H27" s="406" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I27" s="283" t="inlineStr">
+      <c r="I27" s="412" t="inlineStr">
         <is>
           <t>AG9
 2º ao 7º tempos</t>
@@ -10749,13 +11105,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
-      <c r="H28" s="283" t="n"/>
-      <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="H28" s="404" t="n"/>
+      <c r="I28" s="404" t="n"/>
+      <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -10768,13 +11124,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
-      <c r="H29" s="283" t="n"/>
-      <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="H29" s="405" t="n"/>
+      <c r="I29" s="405" t="n"/>
+      <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -10805,7 +11161,7 @@
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="inlineStr">
+      <c r="I30" s="411" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -10828,12 +11184,12 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="283" t="n"/>
-      <c r="I31" s="283" t="n"/>
+      <c r="I31" s="404" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -10847,12 +11203,12 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="283" t="n"/>
-      <c r="I32" s="283" t="n"/>
+      <c r="I32" s="405" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -10917,7 +11273,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="366" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -10939,7 +11295,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="385" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -10980,7 +11336,7 @@
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
+      <c r="I36" s="413" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
@@ -11002,13 +11358,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="I37" s="404" t="n"/>
+      <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -11024,13 +11380,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="I38" s="405" t="n"/>
+      <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -11050,7 +11406,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
+      <c r="E39" s="414" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º tempo</t>
@@ -11058,7 +11414,7 @@
       </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="inlineStr">
+      <c r="H39" s="402" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
@@ -11071,25 +11427,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
-      <c r="E40" s="283" t="n"/>
+      <c r="D40" s="350" t="n"/>
+      <c r="E40" s="404" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="283" t="n"/>
+      <c r="H40" s="404" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
-      <c r="E41" s="283" t="n"/>
+      <c r="D41" s="350" t="n"/>
+      <c r="E41" s="405" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="283" t="n"/>
+      <c r="H41" s="405" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -11110,13 +11466,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
+      <c r="F42" s="410" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G42" s="283" t="inlineStr">
+      <c r="G42" s="408" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
@@ -11136,26 +11492,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
-      <c r="G43" s="283" t="n"/>
+      <c r="F43" s="404" t="n"/>
+      <c r="G43" s="404" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
-      <c r="G44" s="283" t="n"/>
+      <c r="F44" s="405" t="n"/>
+      <c r="G44" s="405" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11178,14 +11534,14 @@
       </c>
       <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
+      <c r="G45" s="403" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="n"/>
+      <c r="I45" s="386" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -11193,26 +11549,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="283" t="n"/>
+      <c r="G46" s="404" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="351" t="n"/>
+      <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="283" t="n"/>
+      <c r="G47" s="405" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="387" t="n"/>
+      <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -11233,14 +11589,14 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
+      <c r="E48" s="415" t="inlineStr">
         <is>
           <t>Fis - VSi
 2º tempo</t>
         </is>
       </c>
-      <c r="F48" s="360" t="n"/>
-      <c r="G48" s="283" t="inlineStr">
+      <c r="F48" s="388" t="n"/>
+      <c r="G48" s="416" t="inlineStr">
         <is>
           <t>Qui - Fab
 2º tempo</t>
@@ -11258,25 +11614,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
-      <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
-      <c r="G49" s="283" t="n"/>
+      <c r="D49" s="350" t="n"/>
+      <c r="E49" s="404" t="n"/>
+      <c r="F49" s="351" t="n"/>
+      <c r="G49" s="404" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="352" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
-      <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
-      <c r="G50" s="283" t="n"/>
+      <c r="D50" s="350" t="n"/>
+      <c r="E50" s="405" t="n"/>
+      <c r="F50" s="387" t="n"/>
+      <c r="G50" s="405" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="352" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -11300,7 +11656,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="386" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -11312,25 +11668,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="350" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="351" t="n"/>
+      <c r="J52" s="352" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="350" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="387" t="n"/>
+      <c r="J53" s="352" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -11361,25 +11717,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="350" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="352" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="350" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="352" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -11400,7 +11756,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="388" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -11415,25 +11771,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="350" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="351" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="352" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="350" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="387" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="352" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -11465,27 +11821,27 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="351" t="n"/>
+      <c r="F61" s="351" t="n"/>
+      <c r="G61" s="351" t="n"/>
+      <c r="H61" s="351" t="n"/>
+      <c r="I61" s="351" t="n"/>
+      <c r="J61" s="351" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="353" t="n"/>
+      <c r="F62" s="353" t="n"/>
+      <c r="G62" s="353" t="n"/>
+      <c r="H62" s="353" t="n"/>
+      <c r="I62" s="353" t="n"/>
+      <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="146">
+  <mergeCells count="165">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -11512,8 +11868,12 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
@@ -11527,10 +11887,12 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H27:H29"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
@@ -11540,11 +11902,14 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -11572,6 +11937,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -11581,6 +11947,8 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="E39:E41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
@@ -11588,12 +11956,15 @@
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G18:G20"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -11619,7 +11990,10 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="I27:I29"/>
     <mergeCell ref="A39:A41"/>
+    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -11628,6 +12002,7 @@
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
+    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>
@@ -12011,20 +12386,20 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="402" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="413" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="415" t="inlineStr">
         <is>
           <t>Fis - VSi
 1º e 2º tempos</t>
@@ -12042,10 +12417,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="222" t="n"/>
+      <c r="E13" s="404" t="n"/>
       <c r="F13" s="222" t="n"/>
-      <c r="G13" s="222" t="n"/>
-      <c r="H13" s="222" t="n"/>
+      <c r="G13" s="404" t="n"/>
+      <c r="H13" s="404" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -12058,10 +12433,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="222" t="n"/>
+      <c r="E14" s="405" t="n"/>
       <c r="F14" s="222" t="n"/>
-      <c r="G14" s="222" t="n"/>
-      <c r="H14" s="222" t="n"/>
+      <c r="G14" s="405" t="n"/>
+      <c r="H14" s="405" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -12087,7 +12462,7 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="416" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
@@ -12095,7 +12470,7 @@
       </c>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="410" t="inlineStr">
         <is>
           <t>Hist - ALu
 2º e 3º tempos</t>
@@ -12112,10 +12487,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="222" t="n"/>
+      <c r="E16" s="404" t="n"/>
       <c r="F16" s="222" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="222" t="n"/>
+      <c r="H16" s="404" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -12128,10 +12503,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="222" t="n"/>
+      <c r="E17" s="405" t="n"/>
       <c r="F17" s="222" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="222" t="n"/>
+      <c r="H17" s="405" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -12162,24 +12537,20 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="406" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="350" t="inlineStr">
+      <c r="I18" s="417" t="inlineStr">
         <is>
           <t>Geo - Mlo
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="J18" s="262" t="inlineStr">
-        <is>
-          <t>2CH 9,10,11,12</t>
-        </is>
-      </c>
+      <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -12191,9 +12562,9 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="222" t="n"/>
+      <c r="G19" s="404" t="n"/>
       <c r="H19" s="222" t="n"/>
-      <c r="I19" s="351" t="n"/>
+      <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
         <is>
@@ -12214,9 +12585,9 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="222" t="n"/>
+      <c r="G20" s="405" t="n"/>
       <c r="H20" s="222" t="n"/>
-      <c r="I20" s="352" t="n"/>
+      <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
@@ -12240,27 +12611,31 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="418" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="inlineStr">
+      <c r="F21" s="414" t="inlineStr">
         <is>
           <t>Bio - Lza
 6º e 7º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="411" t="inlineStr">
         <is>
           <t>Ing - APa
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
-      <c r="J21" s="183" t="n"/>
+      <c r="J21" s="262" t="inlineStr">
+        <is>
+          <t>2CH 9,10,11,12</t>
+        </is>
+      </c>
       <c r="L21" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">15.09 </t>
@@ -12278,10 +12653,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="222" t="n"/>
-      <c r="F22" s="63" t="n"/>
+      <c r="E22" s="404" t="n"/>
+      <c r="F22" s="404" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="222" t="n"/>
+      <c r="H22" s="404" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -12293,10 +12668,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="222" t="n"/>
-      <c r="F23" s="63" t="n"/>
+      <c r="E23" s="405" t="n"/>
+      <c r="F23" s="405" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="222" t="n"/>
+      <c r="H23" s="405" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -12322,7 +12697,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
+      <c r="E24" s="418" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
@@ -12331,7 +12706,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
+      <c r="I24" s="419" t="inlineStr">
         <is>
           <t>AG10
 2º ao 7º tempos</t>
@@ -12350,13 +12725,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
-      <c r="E25" s="283" t="n"/>
+      <c r="D25" s="350" t="n"/>
+      <c r="E25" s="404" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="I25" s="404" t="n"/>
+      <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -12369,13 +12744,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
-      <c r="E26" s="283" t="n"/>
+      <c r="D26" s="350" t="n"/>
+      <c r="E26" s="405" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="I26" s="405" t="n"/>
+      <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -12403,7 +12778,7 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="inlineStr">
+      <c r="F27" s="414" t="inlineStr">
         <is>
           <t>Bio - Lza
 10º e 11º tempos</t>
@@ -12411,7 +12786,7 @@
       </c>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="inlineStr">
+      <c r="I27" s="403" t="inlineStr">
         <is>
           <t>Geo - Mlo
 2º e 3º tempos</t>
@@ -12430,13 +12805,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
-      <c r="F28" s="283" t="n"/>
+      <c r="F28" s="404" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="I28" s="404" t="n"/>
+      <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -12449,13 +12824,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
-      <c r="F29" s="283" t="n"/>
+      <c r="F29" s="405" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="I29" s="405" t="n"/>
+      <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -12485,7 +12860,7 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="inlineStr">
+      <c r="H30" s="415" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
@@ -12509,11 +12884,11 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="283" t="n"/>
+      <c r="H31" s="404" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -12528,11 +12903,11 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="283" t="n"/>
+      <c r="H32" s="405" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -12598,7 +12973,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="366" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -12620,7 +12995,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="385" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -12659,13 +13034,13 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
+      <c r="G36" s="406" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H36" s="283" t="inlineStr">
+      <c r="H36" s="411" t="inlineStr">
         <is>
           <t>Ing - APa
 2º e 3º tempos</t>
@@ -12688,13 +13063,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
-      <c r="G37" s="283" t="n"/>
-      <c r="H37" s="283" t="n"/>
+      <c r="G37" s="404" t="n"/>
+      <c r="H37" s="404" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -12710,13 +13085,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
-      <c r="G38" s="283" t="n"/>
-      <c r="H38" s="283" t="n"/>
+      <c r="G38" s="405" t="n"/>
+      <c r="H38" s="405" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -12739,13 +13114,13 @@
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="inlineStr">
+      <c r="H39" s="402" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I39" s="283" t="inlineStr">
+      <c r="I39" s="420" t="inlineStr">
         <is>
           <t>Soc - Kle
 5º tempo</t>
@@ -12757,25 +13132,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="283" t="n"/>
-      <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="H40" s="404" t="n"/>
+      <c r="I40" s="404" t="n"/>
+      <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="283" t="n"/>
-      <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="H41" s="405" t="n"/>
+      <c r="I41" s="405" t="n"/>
+      <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -12796,13 +13171,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
+      <c r="F42" s="410" t="inlineStr">
         <is>
           <t>Hist - ALu
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G42" s="283" t="inlineStr">
+      <c r="G42" s="413" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
@@ -12822,26 +13197,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
-      <c r="G43" s="283" t="n"/>
+      <c r="F43" s="404" t="n"/>
+      <c r="G43" s="404" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
-      <c r="G44" s="283" t="n"/>
+      <c r="F44" s="405" t="n"/>
+      <c r="G44" s="405" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -12862,21 +13237,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
+      <c r="E45" s="416" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
+      <c r="G45" s="421" t="inlineStr">
         <is>
           <t>Fil - LAn
 1º tempo</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -12889,26 +13264,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
-      <c r="E46" s="283" t="n"/>
+      <c r="D46" s="350" t="n"/>
+      <c r="E46" s="404" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="283" t="n"/>
+      <c r="G46" s="404" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="351" t="n"/>
+      <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
-      <c r="E47" s="283" t="n"/>
+      <c r="D47" s="350" t="n"/>
+      <c r="E47" s="405" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="283" t="n"/>
+      <c r="G47" s="405" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="387" t="n"/>
+      <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -12930,7 +13305,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="388" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -12949,25 +13324,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="350" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="352" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="350" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="352" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -12991,32 +13366,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="n"/>
+      <c r="I51" s="386" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="350" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="351" t="n"/>
+      <c r="J52" s="352" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="350" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="387" t="n"/>
+      <c r="J53" s="352" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -13047,25 +13422,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="350" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="352" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="350" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="352" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -13086,7 +13461,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="n"/>
+      <c r="F57" s="388" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -13096,25 +13471,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="350" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="351" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="352" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="350" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="387" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="352" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -13146,27 +13521,27 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="351" t="n"/>
+      <c r="F61" s="351" t="n"/>
+      <c r="G61" s="351" t="n"/>
+      <c r="H61" s="351" t="n"/>
+      <c r="I61" s="351" t="n"/>
+      <c r="J61" s="351" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="353" t="n"/>
+      <c r="F62" s="353" t="n"/>
+      <c r="G62" s="353" t="n"/>
+      <c r="H62" s="353" t="n"/>
+      <c r="I62" s="353" t="n"/>
+      <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="146">
+  <mergeCells count="168">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -13193,9 +13568,12 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
+    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -13206,15 +13584,21 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="A12:A14"/>
+    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
+    <mergeCell ref="F27:F29"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
+    <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -13226,6 +13610,7 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -13253,6 +13638,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -13262,6 +13648,7 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G12:G14"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
@@ -13269,12 +13656,18 @@
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="H36:H38"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="I24:I26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -13287,11 +13680,13 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
+    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -13300,6 +13695,8 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="I27:I29"/>
+    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
@@ -13692,20 +14089,20 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="402" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="413" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="415" t="inlineStr">
         <is>
           <t>Fis - VSi
 1º e 2º tempos</t>
@@ -13723,10 +14120,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="222" t="n"/>
+      <c r="E13" s="404" t="n"/>
       <c r="F13" s="222" t="n"/>
-      <c r="G13" s="222" t="n"/>
-      <c r="H13" s="222" t="n"/>
+      <c r="G13" s="404" t="n"/>
+      <c r="H13" s="404" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -13739,10 +14136,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="222" t="n"/>
+      <c r="E14" s="405" t="n"/>
       <c r="F14" s="222" t="n"/>
-      <c r="G14" s="222" t="n"/>
-      <c r="H14" s="222" t="n"/>
+      <c r="G14" s="405" t="n"/>
+      <c r="H14" s="405" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -13768,20 +14165,20 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="416" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="411" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="410" t="inlineStr">
         <is>
           <t>Hist - ALu
 2º e 3º tempos</t>
@@ -13798,10 +14195,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="222" t="n"/>
-      <c r="F16" s="222" t="n"/>
+      <c r="E16" s="404" t="n"/>
+      <c r="F16" s="404" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="222" t="n"/>
+      <c r="H16" s="404" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -13814,10 +14211,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="222" t="n"/>
-      <c r="F17" s="222" t="n"/>
+      <c r="E17" s="405" t="n"/>
+      <c r="F17" s="405" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="222" t="n"/>
+      <c r="H17" s="405" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -13848,24 +14245,20 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="406" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="350" t="inlineStr">
+      <c r="I18" s="417" t="inlineStr">
         <is>
           <t>Geo - Mlo
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="J18" s="262" t="inlineStr">
-        <is>
-          <t>2CH 9,10,11,12</t>
-        </is>
-      </c>
+      <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -13877,9 +14270,9 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="222" t="n"/>
+      <c r="G19" s="404" t="n"/>
       <c r="H19" s="222" t="n"/>
-      <c r="I19" s="351" t="n"/>
+      <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
         <is>
@@ -13900,9 +14293,9 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="222" t="n"/>
+      <c r="G20" s="405" t="n"/>
       <c r="H20" s="222" t="n"/>
-      <c r="I20" s="352" t="n"/>
+      <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
@@ -13926,13 +14319,13 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="418" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="inlineStr">
+      <c r="F21" s="414" t="inlineStr">
         <is>
           <t>Bio - Lza
 6º e 7º tempos</t>
@@ -13941,7 +14334,11 @@
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
-      <c r="J21" s="183" t="n"/>
+      <c r="J21" s="262" t="inlineStr">
+        <is>
+          <t>2CH 9,10,11,12</t>
+        </is>
+      </c>
       <c r="L21" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">15.09 </t>
@@ -13959,8 +14356,8 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="222" t="n"/>
-      <c r="F22" s="63" t="n"/>
+      <c r="E22" s="404" t="n"/>
+      <c r="F22" s="404" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="222" t="n"/>
       <c r="I22" s="222" t="n"/>
@@ -13974,8 +14371,8 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="222" t="n"/>
-      <c r="F23" s="63" t="n"/>
+      <c r="E23" s="405" t="n"/>
+      <c r="F23" s="405" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="222" t="n"/>
       <c r="I23" s="222" t="n"/>
@@ -14003,7 +14400,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
+      <c r="E24" s="418" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
@@ -14012,7 +14409,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
+      <c r="I24" s="419" t="inlineStr">
         <is>
           <t>AG10
 2º ao 7º tempos</t>
@@ -14031,13 +14428,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
-      <c r="E25" s="283" t="n"/>
+      <c r="D25" s="350" t="n"/>
+      <c r="E25" s="404" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="I25" s="404" t="n"/>
+      <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -14050,13 +14447,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
-      <c r="E26" s="283" t="n"/>
+      <c r="D26" s="350" t="n"/>
+      <c r="E26" s="405" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="I26" s="405" t="n"/>
+      <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -14084,7 +14481,7 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="inlineStr">
+      <c r="F27" s="414" t="inlineStr">
         <is>
           <t>Bio - Lza
 10º e 11º tempos</t>
@@ -14092,7 +14489,7 @@
       </c>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="inlineStr">
+      <c r="I27" s="403" t="inlineStr">
         <is>
           <t>Geo - Mlo
 2º e 3º tempos</t>
@@ -14111,13 +14508,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
-      <c r="F28" s="283" t="n"/>
+      <c r="F28" s="404" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="I28" s="404" t="n"/>
+      <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -14130,13 +14527,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
-      <c r="F29" s="283" t="n"/>
+      <c r="F29" s="405" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="I29" s="405" t="n"/>
+      <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -14166,7 +14563,7 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="inlineStr">
+      <c r="H30" s="415" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
@@ -14190,11 +14587,11 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="283" t="n"/>
+      <c r="H31" s="404" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -14209,11 +14606,11 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="283" t="n"/>
+      <c r="H32" s="405" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -14279,7 +14676,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="366" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -14301,7 +14698,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="385" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -14339,13 +14736,13 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
+      <c r="F36" s="411" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G36" s="283" t="inlineStr">
+      <c r="G36" s="406" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
@@ -14369,13 +14766,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="283" t="n"/>
-      <c r="G37" s="283" t="n"/>
+      <c r="F37" s="404" t="n"/>
+      <c r="G37" s="404" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -14391,13 +14788,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="283" t="n"/>
-      <c r="G38" s="283" t="n"/>
+      <c r="F38" s="405" t="n"/>
+      <c r="G38" s="405" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -14420,13 +14817,13 @@
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="inlineStr">
+      <c r="H39" s="402" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I39" s="283" t="inlineStr">
+      <c r="I39" s="420" t="inlineStr">
         <is>
           <t>Soc - Kle
 5º tempo</t>
@@ -14438,25 +14835,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="283" t="n"/>
-      <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="H40" s="404" t="n"/>
+      <c r="I40" s="404" t="n"/>
+      <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="283" t="n"/>
-      <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="H41" s="405" t="n"/>
+      <c r="I41" s="405" t="n"/>
+      <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -14477,13 +14874,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
+      <c r="F42" s="410" t="inlineStr">
         <is>
           <t>Hist - ALu
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G42" s="283" t="inlineStr">
+      <c r="G42" s="413" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
@@ -14503,26 +14900,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
-      <c r="G43" s="283" t="n"/>
+      <c r="F43" s="404" t="n"/>
+      <c r="G43" s="404" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
-      <c r="G44" s="283" t="n"/>
+      <c r="F44" s="405" t="n"/>
+      <c r="G44" s="405" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -14543,21 +14940,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
+      <c r="E45" s="416" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
+      <c r="G45" s="421" t="inlineStr">
         <is>
           <t>Fil - LAn
 1º tempo</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -14570,26 +14967,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
-      <c r="E46" s="283" t="n"/>
+      <c r="D46" s="350" t="n"/>
+      <c r="E46" s="404" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="283" t="n"/>
+      <c r="G46" s="404" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="351" t="n"/>
+      <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
-      <c r="E47" s="283" t="n"/>
+      <c r="D47" s="350" t="n"/>
+      <c r="E47" s="405" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="283" t="n"/>
+      <c r="G47" s="405" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="387" t="n"/>
+      <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -14611,7 +15008,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="388" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -14630,25 +15027,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="350" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="352" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="350" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="352" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -14672,7 +15069,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="386" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -14684,25 +15081,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="350" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="351" t="n"/>
+      <c r="J52" s="352" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="350" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="387" t="n"/>
+      <c r="J53" s="352" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -14733,25 +15130,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="350" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="352" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="350" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="352" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -14772,7 +15169,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="388" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -14787,25 +15184,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="350" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="351" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="352" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="350" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="387" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="352" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -14837,27 +15234,27 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="351" t="n"/>
+      <c r="F61" s="351" t="n"/>
+      <c r="G61" s="351" t="n"/>
+      <c r="H61" s="351" t="n"/>
+      <c r="I61" s="351" t="n"/>
+      <c r="J61" s="351" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="353" t="n"/>
+      <c r="F62" s="353" t="n"/>
+      <c r="G62" s="353" t="n"/>
+      <c r="H62" s="353" t="n"/>
+      <c r="I62" s="353" t="n"/>
+      <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="146">
+  <mergeCells count="168">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -14884,8 +15281,11 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
@@ -14897,15 +15297,21 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="A12:A14"/>
+    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
+    <mergeCell ref="F27:F29"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
+    <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -14917,6 +15323,7 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -14944,6 +15351,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -14953,19 +15361,26 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G12:G14"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
+    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="I24:I26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -14978,11 +15393,13 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
+    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -14991,6 +15408,8 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="I27:I29"/>
+    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
@@ -15391,25 +15810,25 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="402" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="412" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="412" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="411" t="inlineStr">
         <is>
           <t>Ing - Bea
 4º e 5º tempos</t>
@@ -15427,10 +15846,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="222" t="n"/>
-      <c r="F13" s="222" t="n"/>
-      <c r="G13" s="222" t="n"/>
-      <c r="H13" s="222" t="n"/>
+      <c r="E13" s="404" t="n"/>
+      <c r="F13" s="404" t="n"/>
+      <c r="G13" s="404" t="n"/>
+      <c r="H13" s="404" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -15443,10 +15862,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="222" t="n"/>
-      <c r="F14" s="222" t="n"/>
-      <c r="G14" s="222" t="n"/>
-      <c r="H14" s="222" t="n"/>
+      <c r="E14" s="405" t="n"/>
+      <c r="F14" s="405" t="n"/>
+      <c r="G14" s="405" t="n"/>
+      <c r="H14" s="405" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -15473,19 +15892,19 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="410" t="inlineStr">
         <is>
           <t>Hist - Ver
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="413" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="415" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
@@ -15503,9 +15922,9 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
-      <c r="F16" s="222" t="n"/>
-      <c r="G16" s="222" t="n"/>
-      <c r="H16" s="222" t="n"/>
+      <c r="F16" s="404" t="n"/>
+      <c r="G16" s="404" t="n"/>
+      <c r="H16" s="404" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -15519,9 +15938,9 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
-      <c r="F17" s="222" t="n"/>
-      <c r="G17" s="222" t="n"/>
-      <c r="H17" s="222" t="n"/>
+      <c r="F17" s="405" t="n"/>
+      <c r="G17" s="405" t="n"/>
+      <c r="H17" s="405" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -15551,25 +15970,21 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="406" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="403" t="inlineStr">
         <is>
           <t>Geo - Mar
 1º e 2º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="350" t="n"/>
-      <c r="J18" s="262" t="inlineStr">
-        <is>
-          <t>2CH 9,10,11,12</t>
-        </is>
-      </c>
+      <c r="I18" s="382" t="n"/>
+      <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -15580,10 +15995,10 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="222" t="n"/>
-      <c r="G19" s="222" t="n"/>
+      <c r="F19" s="404" t="n"/>
+      <c r="G19" s="404" t="n"/>
       <c r="H19" s="222" t="n"/>
-      <c r="I19" s="351" t="n"/>
+      <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
         <is>
@@ -15603,10 +16018,10 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="222" t="n"/>
-      <c r="G20" s="222" t="n"/>
+      <c r="F20" s="405" t="n"/>
+      <c r="G20" s="405" t="n"/>
       <c r="H20" s="222" t="n"/>
-      <c r="I20" s="352" t="n"/>
+      <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
@@ -15630,27 +16045,31 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="414" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="inlineStr">
+      <c r="F21" s="416" t="inlineStr">
         <is>
           <t>Qui - CAl
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="418" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
-      <c r="J21" s="183" t="n"/>
+      <c r="J21" s="262" t="inlineStr">
+        <is>
+          <t>2CH 9,10,11,12</t>
+        </is>
+      </c>
       <c r="L21" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">15.09 </t>
@@ -15668,10 +16087,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="222" t="n"/>
-      <c r="F22" s="63" t="n"/>
+      <c r="E22" s="404" t="n"/>
+      <c r="F22" s="404" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="222" t="n"/>
+      <c r="H22" s="404" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -15683,10 +16102,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="222" t="n"/>
-      <c r="F23" s="63" t="n"/>
+      <c r="E23" s="405" t="n"/>
+      <c r="F23" s="405" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="222" t="n"/>
+      <c r="H23" s="405" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -15712,7 +16131,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="362" t="inlineStr">
+      <c r="E24" s="422" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 4º ao 6º tempos</t>
@@ -15721,7 +16140,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
+      <c r="I24" s="423" t="inlineStr">
         <is>
           <t>Soc - Kle
 4º tempo</t>
@@ -15740,13 +16159,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
-      <c r="E25" s="283" t="n"/>
+      <c r="D25" s="350" t="n"/>
+      <c r="E25" s="404" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="I25" s="404" t="n"/>
+      <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -15759,13 +16178,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
-      <c r="E26" s="283" t="n"/>
+      <c r="D26" s="350" t="n"/>
+      <c r="E26" s="405" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="I26" s="405" t="n"/>
+      <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -15795,7 +16214,7 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="inlineStr">
+      <c r="H27" s="415" t="inlineStr">
         <is>
           <t>Fis - Cadu
 4º e 5º tempos</t>
@@ -15815,13 +16234,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
-      <c r="H28" s="283" t="n"/>
+      <c r="H28" s="404" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -15834,13 +16253,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
-      <c r="H29" s="283" t="n"/>
+      <c r="H29" s="405" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -15867,7 +16286,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
+      <c r="E30" s="403" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -15894,8 +16313,8 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
-      <c r="E31" s="283" t="n"/>
+      <c r="D31" s="350" t="n"/>
+      <c r="E31" s="404" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="283" t="n"/>
@@ -15913,8 +16332,8 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
-      <c r="E32" s="283" t="n"/>
+      <c r="D32" s="350" t="n"/>
+      <c r="E32" s="405" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="283" t="n"/>
@@ -15983,7 +16402,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="366" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -16005,7 +16424,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="385" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -16044,7 +16463,7 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
+      <c r="G36" s="402" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
@@ -16068,13 +16487,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
-      <c r="G37" s="283" t="n"/>
+      <c r="G37" s="404" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -16090,13 +16509,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
-      <c r="G38" s="283" t="n"/>
+      <c r="G38" s="405" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -16116,19 +16535,19 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
+      <c r="E39" s="412" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="F39" s="283" t="inlineStr">
+      <c r="F39" s="412" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G39" s="283" t="inlineStr">
+      <c r="G39" s="413" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
@@ -16142,25 +16561,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
-      <c r="E40" s="283" t="n"/>
-      <c r="F40" s="283" t="n"/>
-      <c r="G40" s="283" t="n"/>
+      <c r="D40" s="350" t="n"/>
+      <c r="E40" s="404" t="n"/>
+      <c r="F40" s="404" t="n"/>
+      <c r="G40" s="404" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
-      <c r="E41" s="283" t="n"/>
-      <c r="F41" s="283" t="n"/>
-      <c r="G41" s="283" t="n"/>
+      <c r="D41" s="350" t="n"/>
+      <c r="E41" s="405" t="n"/>
+      <c r="F41" s="405" t="n"/>
+      <c r="G41" s="405" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -16181,14 +16600,14 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
+      <c r="F42" s="406" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
+      <c r="H42" s="414" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
@@ -16207,26 +16626,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
+      <c r="F43" s="404" t="n"/>
       <c r="G43" s="283" t="n"/>
-      <c r="H43" s="283" t="n"/>
+      <c r="H43" s="404" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
+      <c r="F44" s="405" t="n"/>
       <c r="G44" s="283" t="n"/>
-      <c r="H44" s="283" t="n"/>
+      <c r="H44" s="405" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -16248,20 +16667,20 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="inlineStr">
+      <c r="F45" s="410" t="inlineStr">
         <is>
           <t>Hist - Ver
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G45" s="283" t="inlineStr">
+      <c r="G45" s="421" t="inlineStr">
         <is>
           <t>Fil - LAn
 9º tempo</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="n"/>
+      <c r="I45" s="386" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -16269,26 +16688,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="283" t="n"/>
-      <c r="G46" s="283" t="n"/>
+      <c r="F46" s="404" t="n"/>
+      <c r="G46" s="404" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="351" t="n"/>
+      <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="283" t="n"/>
-      <c r="G47" s="283" t="n"/>
+      <c r="F47" s="405" t="n"/>
+      <c r="G47" s="405" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="387" t="n"/>
+      <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -16309,13 +16728,13 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
+      <c r="E48" s="411" t="inlineStr">
         <is>
           <t>Ing - Bea
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="424" t="inlineStr">
         <is>
           <t>Qui - CAl
 8º e 9º tempos</t>
@@ -16334,25 +16753,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
-      <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="D49" s="350" t="n"/>
+      <c r="E49" s="404" t="n"/>
+      <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="352" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
-      <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="D50" s="350" t="n"/>
+      <c r="E50" s="405" t="n"/>
+      <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="352" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -16376,7 +16795,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="386" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -16388,25 +16807,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="350" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="351" t="n"/>
+      <c r="J52" s="352" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="350" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="387" t="n"/>
+      <c r="J53" s="352" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -16437,25 +16856,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="350" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="352" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="350" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="352" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -16476,7 +16895,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="388" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -16491,25 +16910,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="350" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="351" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="352" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="350" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="387" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="352" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -16541,27 +16960,27 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="351" t="n"/>
+      <c r="F61" s="351" t="n"/>
+      <c r="G61" s="351" t="n"/>
+      <c r="H61" s="351" t="n"/>
+      <c r="I61" s="351" t="n"/>
+      <c r="J61" s="351" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="353" t="n"/>
+      <c r="F62" s="353" t="n"/>
+      <c r="G62" s="353" t="n"/>
+      <c r="H62" s="353" t="n"/>
+      <c r="I62" s="353" t="n"/>
+      <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="146">
+  <mergeCells count="171">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -16576,6 +16995,7 @@
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D30:D32"/>
+    <mergeCell ref="F39:F41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="C24:C26"/>
@@ -16588,9 +17008,13 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
+    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
+    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -16600,27 +17024,35 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E30:E32"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H27:H29"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -16648,6 +17080,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -16657,19 +17090,28 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
+    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="J36:J38"/>
+    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="I24:I26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -16682,6 +17124,7 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
@@ -16695,6 +17138,7 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
@@ -17087,26 +17531,26 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="402" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="412" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="412" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="411" t="inlineStr">
         <is>
           <t>Ing - PaH
 6º e 7º tempos</t>
@@ -17123,11 +17567,11 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="222" t="n"/>
-      <c r="F13" s="222" t="n"/>
-      <c r="G13" s="222" t="n"/>
+      <c r="E13" s="404" t="n"/>
+      <c r="F13" s="404" t="n"/>
+      <c r="G13" s="404" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="222" t="n"/>
+      <c r="I13" s="404" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -17139,11 +17583,11 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="222" t="n"/>
-      <c r="F14" s="222" t="n"/>
-      <c r="G14" s="222" t="n"/>
+      <c r="E14" s="405" t="n"/>
+      <c r="F14" s="405" t="n"/>
+      <c r="G14" s="405" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="222" t="n"/>
+      <c r="I14" s="405" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -17169,19 +17613,19 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="410" t="inlineStr">
         <is>
           <t>Hist - Ver
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="413" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="415" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
@@ -17199,9 +17643,9 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
-      <c r="F16" s="222" t="n"/>
-      <c r="G16" s="222" t="n"/>
-      <c r="H16" s="222" t="n"/>
+      <c r="F16" s="404" t="n"/>
+      <c r="G16" s="404" t="n"/>
+      <c r="H16" s="404" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -17215,9 +17659,9 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
-      <c r="F17" s="222" t="n"/>
-      <c r="G17" s="222" t="n"/>
-      <c r="H17" s="222" t="n"/>
+      <c r="F17" s="405" t="n"/>
+      <c r="G17" s="405" t="n"/>
+      <c r="H17" s="405" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -17247,25 +17691,21 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="406" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="403" t="inlineStr">
         <is>
           <t>Geo - Mar
 1º e 2º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="350" t="n"/>
-      <c r="J18" s="262" t="inlineStr">
-        <is>
-          <t>2CH 9,10,11,12</t>
-        </is>
-      </c>
+      <c r="I18" s="382" t="n"/>
+      <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -17276,10 +17716,10 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="222" t="n"/>
-      <c r="G19" s="222" t="n"/>
+      <c r="F19" s="404" t="n"/>
+      <c r="G19" s="404" t="n"/>
       <c r="H19" s="222" t="n"/>
-      <c r="I19" s="351" t="n"/>
+      <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
         <is>
@@ -17299,10 +17739,10 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="222" t="n"/>
-      <c r="G20" s="222" t="n"/>
+      <c r="F20" s="405" t="n"/>
+      <c r="G20" s="405" t="n"/>
       <c r="H20" s="222" t="n"/>
-      <c r="I20" s="352" t="n"/>
+      <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
@@ -17326,27 +17766,31 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="414" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="inlineStr">
+      <c r="F21" s="416" t="inlineStr">
         <is>
           <t>Qui - CAl
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="418" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 9º ao 11º tempos</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
-      <c r="J21" s="183" t="n"/>
+      <c r="J21" s="262" t="inlineStr">
+        <is>
+          <t>2CH 9,10,11,12</t>
+        </is>
+      </c>
       <c r="L21" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">15.09 </t>
@@ -17364,10 +17808,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="222" t="n"/>
-      <c r="F22" s="63" t="n"/>
+      <c r="E22" s="404" t="n"/>
+      <c r="F22" s="404" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="222" t="n"/>
+      <c r="H22" s="404" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -17379,10 +17823,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="222" t="n"/>
-      <c r="F23" s="63" t="n"/>
+      <c r="E23" s="405" t="n"/>
+      <c r="F23" s="405" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="222" t="n"/>
+      <c r="H23" s="405" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -17408,7 +17852,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="362" t="inlineStr">
+      <c r="E24" s="422" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 4º ao 6º tempos</t>
@@ -17417,7 +17861,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
+      <c r="I24" s="423" t="inlineStr">
         <is>
           <t>Soc - Kle
 4º tempo</t>
@@ -17436,13 +17880,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
-      <c r="E25" s="283" t="n"/>
+      <c r="D25" s="350" t="n"/>
+      <c r="E25" s="404" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="I25" s="404" t="n"/>
+      <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -17455,13 +17899,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
-      <c r="E26" s="283" t="n"/>
+      <c r="D26" s="350" t="n"/>
+      <c r="E26" s="405" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="I26" s="405" t="n"/>
+      <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -17491,7 +17935,7 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="inlineStr">
+      <c r="H27" s="415" t="inlineStr">
         <is>
           <t>Fis - Cadu
 4º e 5º tempos</t>
@@ -17511,13 +17955,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
+      <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
-      <c r="H28" s="283" t="n"/>
+      <c r="H28" s="404" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -17530,13 +17974,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
+      <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
-      <c r="H29" s="283" t="n"/>
+      <c r="H29" s="405" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -17563,7 +18007,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
+      <c r="E30" s="403" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -17590,8 +18034,8 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
-      <c r="E31" s="283" t="n"/>
+      <c r="D31" s="350" t="n"/>
+      <c r="E31" s="404" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="283" t="n"/>
@@ -17609,8 +18053,8 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
-      <c r="E32" s="283" t="n"/>
+      <c r="D32" s="350" t="n"/>
+      <c r="E32" s="405" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="283" t="n"/>
@@ -17679,7 +18123,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="366" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -17701,7 +18145,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="385" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -17740,7 +18184,7 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
+      <c r="G36" s="402" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
@@ -17764,13 +18208,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
-      <c r="G37" s="283" t="n"/>
+      <c r="G37" s="404" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -17786,13 +18230,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
-      <c r="G38" s="283" t="n"/>
+      <c r="G38" s="405" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -17812,19 +18256,19 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
+      <c r="E39" s="412" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="F39" s="283" t="inlineStr">
+      <c r="F39" s="412" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G39" s="283" t="inlineStr">
+      <c r="G39" s="413" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
@@ -17838,25 +18282,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
-      <c r="E40" s="283" t="n"/>
-      <c r="F40" s="283" t="n"/>
-      <c r="G40" s="283" t="n"/>
+      <c r="D40" s="350" t="n"/>
+      <c r="E40" s="404" t="n"/>
+      <c r="F40" s="404" t="n"/>
+      <c r="G40" s="404" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
-      <c r="E41" s="283" t="n"/>
-      <c r="F41" s="283" t="n"/>
-      <c r="G41" s="283" t="n"/>
+      <c r="D41" s="350" t="n"/>
+      <c r="E41" s="405" t="n"/>
+      <c r="F41" s="405" t="n"/>
+      <c r="G41" s="405" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -17877,14 +18321,14 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
+      <c r="F42" s="406" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
+      <c r="H42" s="414" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
@@ -17903,26 +18347,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
+      <c r="F43" s="404" t="n"/>
       <c r="G43" s="283" t="n"/>
-      <c r="H43" s="283" t="n"/>
+      <c r="H43" s="404" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
+      <c r="F44" s="405" t="n"/>
       <c r="G44" s="283" t="n"/>
-      <c r="H44" s="283" t="n"/>
+      <c r="H44" s="405" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -17944,20 +18388,20 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="inlineStr">
+      <c r="F45" s="410" t="inlineStr">
         <is>
           <t>Hist - Ver
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G45" s="283" t="inlineStr">
+      <c r="G45" s="421" t="inlineStr">
         <is>
           <t>Fil - LAn
 9º tempo</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="n"/>
+      <c r="I45" s="386" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -17965,26 +18409,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
+      <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="283" t="n"/>
-      <c r="G46" s="283" t="n"/>
+      <c r="F46" s="404" t="n"/>
+      <c r="G46" s="404" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="351" t="n"/>
+      <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
+      <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="283" t="n"/>
-      <c r="G47" s="283" t="n"/>
+      <c r="F47" s="405" t="n"/>
+      <c r="G47" s="405" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="387" t="n"/>
+      <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -18005,13 +18449,13 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
+      <c r="E48" s="411" t="inlineStr">
         <is>
           <t>Ing - PaH
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="424" t="inlineStr">
         <is>
           <t>Qui - CAl
 8º e 9º tempos</t>
@@ -18030,25 +18474,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
-      <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="D49" s="350" t="n"/>
+      <c r="E49" s="404" t="n"/>
+      <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="352" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
-      <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="D50" s="350" t="n"/>
+      <c r="E50" s="405" t="n"/>
+      <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="352" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -18072,7 +18516,7 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="inlineStr">
+      <c r="I51" s="386" t="inlineStr">
         <is>
           <t>2CH
 9,11</t>
@@ -18084,25 +18528,25 @@
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="350" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="351" t="n"/>
+      <c r="J52" s="352" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="350" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="387" t="n"/>
+      <c r="J53" s="352" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -18133,25 +18577,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="350" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="352" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="350" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="352" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -18172,7 +18616,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="inlineStr">
+      <c r="F57" s="388" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -18187,25 +18631,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="350" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="351" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="352" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="350" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="387" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="352" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -18237,27 +18681,27 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="351" t="n"/>
+      <c r="F61" s="351" t="n"/>
+      <c r="G61" s="351" t="n"/>
+      <c r="H61" s="351" t="n"/>
+      <c r="I61" s="351" t="n"/>
+      <c r="J61" s="351" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="353" t="n"/>
+      <c r="F62" s="353" t="n"/>
+      <c r="G62" s="353" t="n"/>
+      <c r="H62" s="353" t="n"/>
+      <c r="I62" s="353" t="n"/>
+      <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="146">
+  <mergeCells count="171">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -18272,6 +18716,7 @@
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D30:D32"/>
+    <mergeCell ref="F39:F41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="C24:C26"/>
@@ -18284,9 +18729,13 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
+    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
+    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -18296,27 +18745,35 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E30:E32"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H27:H29"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -18344,6 +18801,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -18353,19 +18811,28 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
+    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="J36:J38"/>
+    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="I24:I26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -18391,6 +18858,7 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
@@ -18398,6 +18866,7 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
+    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>
@@ -18783,13 +19252,13 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="411" t="inlineStr">
         <is>
           <t>Ing - PaH
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="418" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 10º ao 12º tempos</t>
@@ -18809,8 +19278,8 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="222" t="n"/>
-      <c r="F13" s="222" t="n"/>
+      <c r="E13" s="404" t="n"/>
+      <c r="F13" s="404" t="n"/>
       <c r="G13" s="222" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
@@ -18825,8 +19294,8 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="222" t="n"/>
-      <c r="F14" s="222" t="n"/>
+      <c r="E14" s="405" t="n"/>
+      <c r="F14" s="405" t="n"/>
       <c r="G14" s="222" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
@@ -18854,7 +19323,7 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="406" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 4º e 5º tempos</t>
@@ -18862,13 +19331,13 @@
       </c>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="415" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="416" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 2º e 3º tempos</t>
@@ -18884,11 +19353,11 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="222" t="n"/>
+      <c r="E16" s="404" t="n"/>
       <c r="F16" s="222" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="222" t="n"/>
-      <c r="I16" s="222" t="n"/>
+      <c r="H16" s="404" t="n"/>
+      <c r="I16" s="404" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -18900,11 +19369,11 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="222" t="n"/>
+      <c r="E17" s="405" t="n"/>
       <c r="F17" s="222" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="222" t="n"/>
-      <c r="I17" s="222" t="n"/>
+      <c r="H17" s="405" t="n"/>
+      <c r="I17" s="405" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -18933,30 +19402,26 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="414" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="413" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I18" s="350" t="inlineStr">
+      <c r="I18" s="425" t="inlineStr">
         <is>
           <t>Hist - Wag
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="J18" s="262" t="inlineStr">
-        <is>
-          <t>2CH 9,10,11,12</t>
-        </is>
-      </c>
+      <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -18967,10 +19432,10 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="222" t="n"/>
+      <c r="F19" s="404" t="n"/>
       <c r="G19" s="222" t="n"/>
-      <c r="H19" s="222" t="n"/>
-      <c r="I19" s="351" t="n"/>
+      <c r="H19" s="404" t="n"/>
+      <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
         <is>
@@ -18990,10 +19455,10 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="222" t="n"/>
+      <c r="F20" s="405" t="n"/>
       <c r="G20" s="222" t="n"/>
-      <c r="H20" s="222" t="n"/>
-      <c r="I20" s="352" t="n"/>
+      <c r="H20" s="405" t="n"/>
+      <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
@@ -19018,31 +19483,35 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="inlineStr">
+      <c r="F21" s="402" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="412" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="412" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="403" t="inlineStr">
         <is>
           <t>Geo - Mar
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="J21" s="183" t="n"/>
+      <c r="J21" s="262" t="inlineStr">
+        <is>
+          <t>2CH 9,10,11,12</t>
+        </is>
+      </c>
       <c r="L21" s="80" t="inlineStr">
         <is>
           <t xml:space="preserve">15.09 </t>
@@ -19061,10 +19530,10 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="63" t="n"/>
-      <c r="G22" s="222" t="n"/>
-      <c r="H22" s="222" t="n"/>
-      <c r="I22" s="222" t="n"/>
+      <c r="F22" s="404" t="n"/>
+      <c r="G22" s="404" t="n"/>
+      <c r="H22" s="404" t="n"/>
+      <c r="I22" s="404" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -19076,10 +19545,10 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="63" t="n"/>
-      <c r="G23" s="222" t="n"/>
-      <c r="H23" s="222" t="n"/>
-      <c r="I23" s="222" t="n"/>
+      <c r="F23" s="405" t="n"/>
+      <c r="G23" s="405" t="n"/>
+      <c r="H23" s="405" t="n"/>
+      <c r="I23" s="405" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -19106,14 +19575,14 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="363" t="inlineStr">
+      <c r="G24" s="426" t="inlineStr">
         <is>
           <t>Geo - Mar
 11º e 12º tempos</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
+      <c r="I24" s="427" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 6º e 7º tempos</t>
@@ -19132,13 +19601,13 @@
       <c r="A25" s="316" t="n"/>
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
-      <c r="D25" s="353" t="n"/>
+      <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="79" t="n"/>
+      <c r="G25" s="428" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="78" t="n"/>
-      <c r="J25" s="354" t="n"/>
+      <c r="I25" s="404" t="n"/>
+      <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
         <is>
@@ -19151,13 +19620,13 @@
       <c r="A26" s="316" t="n"/>
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
-      <c r="D26" s="353" t="n"/>
+      <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="79" t="n"/>
+      <c r="G26" s="429" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="78" t="n"/>
-      <c r="J26" s="354" t="n"/>
+      <c r="I26" s="405" t="n"/>
+      <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
         <is>
@@ -19184,13 +19653,13 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
+      <c r="E27" s="430" t="inlineStr">
         <is>
           <t>Ing - PaH
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F27" s="283" t="inlineStr">
+      <c r="F27" s="415" t="inlineStr">
         <is>
           <t>Fis - Cadu
 1º e 2º tempos</t>
@@ -19212,13 +19681,13 @@
       <c r="A28" s="316" t="n"/>
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
-      <c r="D28" s="353" t="n"/>
-      <c r="E28" s="78" t="n"/>
-      <c r="F28" s="283" t="n"/>
+      <c r="D28" s="350" t="n"/>
+      <c r="E28" s="404" t="n"/>
+      <c r="F28" s="404" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
-      <c r="J28" s="354" t="n"/>
+      <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
         <is>
@@ -19231,13 +19700,13 @@
       <c r="A29" s="316" t="n"/>
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
-      <c r="D29" s="353" t="n"/>
-      <c r="E29" s="78" t="n"/>
-      <c r="F29" s="283" t="n"/>
+      <c r="D29" s="350" t="n"/>
+      <c r="E29" s="405" t="n"/>
+      <c r="F29" s="405" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
-      <c r="J29" s="354" t="n"/>
+      <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
         <is>
@@ -19267,7 +19736,7 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="inlineStr">
+      <c r="H30" s="413" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
@@ -19291,11 +19760,11 @@
       <c r="A31" s="316" t="n"/>
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
-      <c r="D31" s="353" t="n"/>
+      <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="283" t="n"/>
+      <c r="H31" s="404" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -19310,11 +19779,11 @@
       <c r="A32" s="316" t="n"/>
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
-      <c r="D32" s="353" t="n"/>
+      <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="283" t="n"/>
+      <c r="H32" s="405" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -19380,7 +19849,7 @@
     <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
       <c r="A34" s="330" t="n"/>
       <c r="B34" s="331" t="n"/>
-      <c r="D34" s="355" t="n"/>
+      <c r="D34" s="366" t="n"/>
       <c r="E34" s="315" t="n"/>
       <c r="F34" s="315" t="n"/>
       <c r="G34" s="315" t="n"/>
@@ -19402,7 +19871,7 @@
     <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A35" s="330" t="n"/>
       <c r="B35" s="332" t="n"/>
-      <c r="D35" s="356" t="n"/>
+      <c r="D35" s="385" t="n"/>
       <c r="E35" s="315" t="n"/>
       <c r="F35" s="315" t="n"/>
       <c r="G35" s="315" t="n"/>
@@ -19440,7 +19909,7 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
+      <c r="F36" s="418" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 10º ao 12º tempos</t>
@@ -19465,13 +19934,13 @@
       <c r="A37" s="316" t="n"/>
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
-      <c r="D37" s="353" t="n"/>
+      <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="283" t="n"/>
+      <c r="F37" s="404" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
-      <c r="J37" s="354" t="n"/>
+      <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
           <t>18.08,19.08</t>
@@ -19487,13 +19956,13 @@
       <c r="A38" s="316" t="n"/>
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
-      <c r="D38" s="353" t="n"/>
+      <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="283" t="n"/>
+      <c r="F38" s="405" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
-      <c r="J38" s="354" t="n"/>
+      <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A39" s="119">
@@ -19515,13 +19984,13 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
+      <c r="G39" s="420" t="inlineStr">
         <is>
           <t>Soc - Kle
 6º tempo</t>
         </is>
       </c>
-      <c r="H39" s="283" t="inlineStr">
+      <c r="H39" s="402" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 4º e 5º tempos</t>
@@ -19534,25 +20003,25 @@
       <c r="A40" s="316" t="n"/>
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
-      <c r="D40" s="353" t="n"/>
+      <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="283" t="n"/>
-      <c r="H40" s="283" t="n"/>
+      <c r="G40" s="404" t="n"/>
+      <c r="H40" s="404" t="n"/>
       <c r="I40" s="283" t="n"/>
-      <c r="J40" s="354" t="n"/>
+      <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A41" s="316" t="n"/>
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
-      <c r="D41" s="353" t="n"/>
+      <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="283" t="n"/>
-      <c r="H41" s="283" t="n"/>
+      <c r="G41" s="405" t="n"/>
+      <c r="H41" s="405" t="n"/>
       <c r="I41" s="283" t="n"/>
-      <c r="J41" s="354" t="n"/>
+      <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A42" s="119">
@@ -19573,13 +20042,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
+      <c r="F42" s="414" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G42" s="283" t="inlineStr">
+      <c r="G42" s="421" t="inlineStr">
         <is>
           <t>Fil - LAn
 4º tempo</t>
@@ -19599,26 +20068,26 @@
       <c r="A43" s="316" t="n"/>
       <c r="B43" s="313" t="n"/>
       <c r="C43" s="313" t="n"/>
-      <c r="D43" s="353" t="n"/>
+      <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
-      <c r="G43" s="283" t="n"/>
+      <c r="F43" s="404" t="n"/>
+      <c r="G43" s="404" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
-      <c r="J43" s="354" t="n"/>
+      <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
     <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A44" s="316" t="n"/>
       <c r="B44" s="313" t="n"/>
       <c r="C44" s="313" t="n"/>
-      <c r="D44" s="353" t="n"/>
+      <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
-      <c r="G44" s="283" t="n"/>
+      <c r="F44" s="405" t="n"/>
+      <c r="G44" s="405" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
-      <c r="J44" s="354" t="n"/>
+      <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
     <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
@@ -19639,21 +20108,21 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
+      <c r="E45" s="416" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 6º e 7º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
+      <c r="G45" s="410" t="inlineStr">
         <is>
           <t>Hist - Wag
 11º e 12º tempos</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="inlineStr">
+      <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
 10,12</t>
@@ -19666,26 +20135,26 @@
       <c r="A46" s="316" t="n"/>
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
-      <c r="D46" s="353" t="n"/>
-      <c r="E46" s="283" t="n"/>
+      <c r="D46" s="350" t="n"/>
+      <c r="E46" s="404" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="283" t="n"/>
+      <c r="G46" s="404" t="n"/>
       <c r="H46" s="283" t="n"/>
-      <c r="I46" s="358" t="n"/>
-      <c r="J46" s="354" t="n"/>
+      <c r="I46" s="351" t="n"/>
+      <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
     <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A47" s="316" t="n"/>
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
-      <c r="D47" s="353" t="n"/>
-      <c r="E47" s="283" t="n"/>
+      <c r="D47" s="350" t="n"/>
+      <c r="E47" s="405" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="283" t="n"/>
+      <c r="G47" s="405" t="n"/>
       <c r="H47" s="283" t="n"/>
-      <c r="I47" s="359" t="n"/>
-      <c r="J47" s="354" t="n"/>
+      <c r="I47" s="387" t="n"/>
+      <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
     <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
@@ -19707,7 +20176,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="360" t="inlineStr">
+      <c r="F48" s="388" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -19726,25 +20195,25 @@
       <c r="A49" s="316" t="n"/>
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
-      <c r="D49" s="353" t="n"/>
+      <c r="D49" s="350" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="358" t="n"/>
+      <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
-      <c r="J49" s="354" t="n"/>
+      <c r="J49" s="352" t="n"/>
     </row>
     <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A50" s="316" t="n"/>
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
-      <c r="D50" s="353" t="n"/>
+      <c r="D50" s="350" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="359" t="n"/>
+      <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
-      <c r="J50" s="354" t="n"/>
+      <c r="J50" s="352" t="n"/>
     </row>
     <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A51" s="119">
@@ -19768,32 +20237,32 @@
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
-      <c r="I51" s="357" t="n"/>
+      <c r="I51" s="386" t="n"/>
       <c r="J51" s="274" t="n"/>
     </row>
     <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A52" s="316" t="n"/>
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
-      <c r="D52" s="353" t="n"/>
+      <c r="D52" s="350" t="n"/>
       <c r="E52" s="283" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
-      <c r="I52" s="358" t="n"/>
-      <c r="J52" s="354" t="n"/>
+      <c r="I52" s="351" t="n"/>
+      <c r="J52" s="352" t="n"/>
     </row>
     <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A53" s="316" t="n"/>
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
-      <c r="D53" s="353" t="n"/>
+      <c r="D53" s="350" t="n"/>
       <c r="E53" s="283" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
-      <c r="I53" s="359" t="n"/>
-      <c r="J53" s="354" t="n"/>
+      <c r="I53" s="387" t="n"/>
+      <c r="J53" s="352" t="n"/>
     </row>
     <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A54" s="119">
@@ -19824,25 +20293,25 @@
       <c r="A55" s="316" t="n"/>
       <c r="B55" s="313" t="n"/>
       <c r="C55" s="313" t="n"/>
-      <c r="D55" s="353" t="n"/>
+      <c r="D55" s="350" t="n"/>
       <c r="E55" s="315" t="n"/>
       <c r="F55" s="315" t="n"/>
       <c r="G55" s="315" t="n"/>
       <c r="H55" s="315" t="n"/>
       <c r="I55" s="315" t="n"/>
-      <c r="J55" s="354" t="n"/>
+      <c r="J55" s="352" t="n"/>
     </row>
     <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A56" s="316" t="n"/>
       <c r="B56" s="313" t="n"/>
       <c r="C56" s="313" t="n"/>
-      <c r="D56" s="353" t="n"/>
+      <c r="D56" s="350" t="n"/>
       <c r="E56" s="315" t="n"/>
       <c r="F56" s="315" t="n"/>
       <c r="G56" s="315" t="n"/>
       <c r="H56" s="315" t="n"/>
       <c r="I56" s="315" t="n"/>
-      <c r="J56" s="354" t="n"/>
+      <c r="J56" s="352" t="n"/>
     </row>
     <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
       <c r="A57" s="119">
@@ -19863,7 +20332,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="360" t="n"/>
+      <c r="F57" s="388" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -19873,25 +20342,25 @@
       <c r="A58" s="316" t="n"/>
       <c r="B58" s="313" t="n"/>
       <c r="C58" s="313" t="n"/>
-      <c r="D58" s="353" t="n"/>
+      <c r="D58" s="350" t="n"/>
       <c r="E58" s="315" t="n"/>
-      <c r="F58" s="358" t="n"/>
+      <c r="F58" s="351" t="n"/>
       <c r="G58" s="315" t="n"/>
       <c r="H58" s="315" t="n"/>
       <c r="I58" s="315" t="n"/>
-      <c r="J58" s="354" t="n"/>
+      <c r="J58" s="352" t="n"/>
     </row>
     <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
       <c r="A59" s="316" t="n"/>
       <c r="B59" s="313" t="n"/>
       <c r="C59" s="313" t="n"/>
-      <c r="D59" s="353" t="n"/>
+      <c r="D59" s="350" t="n"/>
       <c r="E59" s="315" t="n"/>
-      <c r="F59" s="359" t="n"/>
+      <c r="F59" s="387" t="n"/>
       <c r="G59" s="315" t="n"/>
       <c r="H59" s="315" t="n"/>
       <c r="I59" s="315" t="n"/>
-      <c r="J59" s="354" t="n"/>
+      <c r="J59" s="352" t="n"/>
     </row>
     <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A60" s="281">
@@ -19923,27 +20392,27 @@
       <c r="B61" s="331" t="n"/>
       <c r="C61" s="331" t="n"/>
       <c r="D61" s="331" t="n"/>
-      <c r="E61" s="358" t="n"/>
-      <c r="F61" s="358" t="n"/>
-      <c r="G61" s="358" t="n"/>
-      <c r="H61" s="358" t="n"/>
-      <c r="I61" s="358" t="n"/>
-      <c r="J61" s="358" t="n"/>
+      <c r="E61" s="351" t="n"/>
+      <c r="F61" s="351" t="n"/>
+      <c r="G61" s="351" t="n"/>
+      <c r="H61" s="351" t="n"/>
+      <c r="I61" s="351" t="n"/>
+      <c r="J61" s="351" t="n"/>
     </row>
     <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
       <c r="A62" s="332" t="n"/>
       <c r="B62" s="332" t="n"/>
       <c r="C62" s="332" t="n"/>
       <c r="D62" s="332" t="n"/>
-      <c r="E62" s="361" t="n"/>
-      <c r="F62" s="361" t="n"/>
-      <c r="G62" s="361" t="n"/>
-      <c r="H62" s="361" t="n"/>
-      <c r="I62" s="361" t="n"/>
-      <c r="J62" s="361" t="n"/>
+      <c r="E62" s="353" t="n"/>
+      <c r="F62" s="353" t="n"/>
+      <c r="G62" s="353" t="n"/>
+      <c r="H62" s="353" t="n"/>
+      <c r="I62" s="353" t="n"/>
+      <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="146">
+  <mergeCells count="169">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -19970,9 +20439,13 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
+    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -19983,17 +20456,23 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="A12:A14"/>
+    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
+    <mergeCell ref="F27:F29"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="I15:I17"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
@@ -20019,6 +20498,7 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
+    <mergeCell ref="E27:E29"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -20030,6 +20510,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -20039,19 +20520,28 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
+    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
+    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="I24:I26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -20069,6 +20559,7 @@
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
+    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -20086,6 +20577,7 @@
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
+    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -357,98 +357,98 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E7CF"/>
-        <bgColor rgb="00C6E7CF"/>
+        <fgColor rgb="FFC6E7CF"/>
+        <bgColor rgb="FFC6E7CF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E7E4"/>
-        <bgColor rgb="00C6E7E4"/>
+        <fgColor rgb="FFC6E7E4"/>
+        <bgColor rgb="FFC6E7E4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7C6E1"/>
-        <bgColor rgb="00E7C6E1"/>
+        <fgColor rgb="FFE7C6E1"/>
+        <bgColor rgb="FFE7C6E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E7C6"/>
-        <bgColor rgb="00C8E7C6"/>
+        <fgColor rgb="FFC8E7C6"/>
+        <bgColor rgb="FFC8E7C6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7C6D6"/>
-        <bgColor rgb="00E7C6D6"/>
+        <fgColor rgb="FFE7C6D6"/>
+        <bgColor rgb="FFE7C6D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDE7C6"/>
-        <bgColor rgb="00DDE7C6"/>
+        <fgColor rgb="FFDDE7C6"/>
+        <bgColor rgb="FFDDE7C6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D2E7C6"/>
-        <bgColor rgb="00D2E7C6"/>
+        <fgColor rgb="FFD2E7C6"/>
+        <bgColor rgb="FFD2E7C6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E7D9"/>
-        <bgColor rgb="00C6E7D9"/>
+        <fgColor rgb="FFC6E7D9"/>
+        <bgColor rgb="FFC6E7D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6CAE7"/>
-        <bgColor rgb="00C6CAE7"/>
+        <fgColor rgb="FFC6CAE7"/>
+        <bgColor rgb="FFC6CAE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6DFE7"/>
-        <bgColor rgb="00C6DFE7"/>
+        <fgColor rgb="FFC6DFE7"/>
+        <bgColor rgb="FFC6DFE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6D4E7"/>
-        <bgColor rgb="00C6D4E7"/>
+        <fgColor rgb="FFC6D4E7"/>
+        <bgColor rgb="FFC6D4E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2C6E7"/>
-        <bgColor rgb="00E2C6E7"/>
+        <fgColor rgb="FFE2C6E7"/>
+        <bgColor rgb="FFE2C6E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CDC6E7"/>
-        <bgColor rgb="00CDC6E7"/>
+        <fgColor rgb="FFCDC6E7"/>
+        <bgColor rgb="FFCDC6E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D7C6E7"/>
-        <bgColor rgb="00D7C6E7"/>
+        <fgColor rgb="FFD7C6E7"/>
+        <bgColor rgb="FFD7C6E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1814,7 +1814,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="431">
+  <cellXfs count="432">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3171,6 +3171,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5773,13 +5777,13 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="411" t="inlineStr">
+      <c r="E12" s="412" t="inlineStr">
         <is>
           <t>Ing - Isb
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="F12" s="418" t="inlineStr">
+      <c r="F12" s="419" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 10º ao 12º tempos</t>
@@ -5799,8 +5803,8 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="404" t="n"/>
-      <c r="F13" s="404" t="n"/>
+      <c r="E13" s="405" t="n"/>
+      <c r="F13" s="405" t="n"/>
       <c r="G13" s="222" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
@@ -5815,8 +5819,8 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="405" t="n"/>
-      <c r="F14" s="405" t="n"/>
+      <c r="E14" s="406" t="n"/>
+      <c r="F14" s="406" t="n"/>
       <c r="G14" s="222" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
@@ -5844,7 +5848,7 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="406" t="inlineStr">
+      <c r="E15" s="407" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 4º e 5º tempos</t>
@@ -5852,13 +5856,13 @@
       </c>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="415" t="inlineStr">
+      <c r="H15" s="416" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="416" t="inlineStr">
+      <c r="I15" s="417" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 2º e 3º tempos</t>
@@ -5874,11 +5878,11 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="404" t="n"/>
+      <c r="E16" s="405" t="n"/>
       <c r="F16" s="222" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="404" t="n"/>
-      <c r="I16" s="404" t="n"/>
+      <c r="H16" s="405" t="n"/>
+      <c r="I16" s="405" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -5890,11 +5894,11 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="405" t="n"/>
+      <c r="E17" s="406" t="n"/>
       <c r="F17" s="222" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="405" t="n"/>
-      <c r="I17" s="405" t="n"/>
+      <c r="H17" s="406" t="n"/>
+      <c r="I17" s="406" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -5923,20 +5927,20 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="414" t="inlineStr">
+      <c r="F18" s="415" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="413" t="inlineStr">
+      <c r="H18" s="414" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I18" s="425" t="inlineStr">
+      <c r="I18" s="426" t="inlineStr">
         <is>
           <t>Hist - Wag
 4º e 5º tempos</t>
@@ -5953,9 +5957,9 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="404" t="n"/>
+      <c r="F19" s="405" t="n"/>
       <c r="G19" s="222" t="n"/>
-      <c r="H19" s="404" t="n"/>
+      <c r="H19" s="405" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -5976,9 +5980,9 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="405" t="n"/>
+      <c r="F20" s="406" t="n"/>
       <c r="G20" s="222" t="n"/>
-      <c r="H20" s="405" t="n"/>
+      <c r="H20" s="406" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -6004,25 +6008,25 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="402" t="inlineStr">
+      <c r="F21" s="403" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G21" s="412" t="inlineStr">
+      <c r="G21" s="413" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H21" s="412" t="inlineStr">
+      <c r="H21" s="413" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="403" t="inlineStr">
+      <c r="I21" s="404" t="inlineStr">
         <is>
           <t>Geo - Mar
 2º e 3º tempos</t>
@@ -6051,10 +6055,10 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="404" t="n"/>
-      <c r="G22" s="404" t="n"/>
-      <c r="H22" s="404" t="n"/>
-      <c r="I22" s="404" t="n"/>
+      <c r="F22" s="405" t="n"/>
+      <c r="G22" s="405" t="n"/>
+      <c r="H22" s="405" t="n"/>
+      <c r="I22" s="405" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -6066,10 +6070,10 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="405" t="n"/>
-      <c r="G23" s="405" t="n"/>
-      <c r="H23" s="405" t="n"/>
-      <c r="I23" s="405" t="n"/>
+      <c r="F23" s="406" t="n"/>
+      <c r="G23" s="406" t="n"/>
+      <c r="H23" s="406" t="n"/>
+      <c r="I23" s="406" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -6096,14 +6100,14 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="426" t="inlineStr">
+      <c r="G24" s="427" t="inlineStr">
         <is>
           <t>Geo - Mar
 11º e 12º tempos</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="427" t="inlineStr">
+      <c r="I24" s="428" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 6º e 7º tempos</t>
@@ -6125,9 +6129,9 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="428" t="n"/>
+      <c r="G25" s="429" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="404" t="n"/>
+      <c r="I25" s="405" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -6144,9 +6148,9 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="429" t="n"/>
+      <c r="G26" s="430" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="405" t="n"/>
+      <c r="I26" s="406" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -6175,7 +6179,7 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="415" t="inlineStr">
+      <c r="F27" s="416" t="inlineStr">
         <is>
           <t>Fis - Cadu
 1º e 2º tempos</t>
@@ -6199,7 +6203,7 @@
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
-      <c r="F28" s="404" t="n"/>
+      <c r="F28" s="405" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
@@ -6218,7 +6222,7 @@
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
-      <c r="F29" s="405" t="n"/>
+      <c r="F29" s="406" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
@@ -6249,7 +6253,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="411" t="inlineStr">
+      <c r="E30" s="412" t="inlineStr">
         <is>
           <t>Ing - Isb
 4º e 5º tempos</t>
@@ -6257,7 +6261,7 @@
       </c>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="413" t="inlineStr">
+      <c r="H30" s="414" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
@@ -6282,10 +6286,10 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="404" t="n"/>
+      <c r="E31" s="405" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="404" t="n"/>
+      <c r="H31" s="405" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -6301,10 +6305,10 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="405" t="n"/>
+      <c r="E32" s="406" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="405" t="n"/>
+      <c r="H32" s="406" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -6430,7 +6434,7 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="418" t="inlineStr">
+      <c r="F36" s="419" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 10º ao 12º tempos</t>
@@ -6457,7 +6461,7 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="404" t="n"/>
+      <c r="F37" s="405" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
@@ -6479,7 +6483,7 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="405" t="n"/>
+      <c r="F38" s="406" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
@@ -6505,13 +6509,13 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="420" t="inlineStr">
+      <c r="G39" s="421" t="inlineStr">
         <is>
           <t>Soc - Kle
 6º tempo</t>
         </is>
       </c>
-      <c r="H39" s="402" t="inlineStr">
+      <c r="H39" s="403" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 4º e 5º tempos</t>
@@ -6527,8 +6531,8 @@
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="404" t="n"/>
-      <c r="H40" s="404" t="n"/>
+      <c r="G40" s="405" t="n"/>
+      <c r="H40" s="405" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
@@ -6539,8 +6543,8 @@
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="405" t="n"/>
-      <c r="H41" s="405" t="n"/>
+      <c r="G41" s="406" t="n"/>
+      <c r="H41" s="406" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
@@ -6563,13 +6567,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="414" t="inlineStr">
+      <c r="F42" s="415" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G42" s="421" t="inlineStr">
+      <c r="G42" s="422" t="inlineStr">
         <is>
           <t>Fil - LAn
 4º tempo</t>
@@ -6591,8 +6595,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="404" t="n"/>
-      <c r="G43" s="404" t="n"/>
+      <c r="F43" s="405" t="n"/>
+      <c r="G43" s="405" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -6604,8 +6608,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="405" t="n"/>
-      <c r="G44" s="405" t="n"/>
+      <c r="F44" s="406" t="n"/>
+      <c r="G44" s="406" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -6629,14 +6633,14 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="416" t="inlineStr">
+      <c r="E45" s="417" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 6º e 7º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="410" t="inlineStr">
+      <c r="G45" s="411" t="inlineStr">
         <is>
           <t>Hist - Wag
 11º e 12º tempos</t>
@@ -6657,9 +6661,9 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="404" t="n"/>
+      <c r="E46" s="405" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="404" t="n"/>
+      <c r="G46" s="405" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -6670,9 +6674,9 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="405" t="n"/>
+      <c r="E47" s="406" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="405" t="n"/>
+      <c r="G47" s="406" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -6697,7 +6701,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="388" t="inlineStr">
+      <c r="F48" s="402" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -6853,7 +6857,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="388" t="n"/>
+      <c r="F57" s="402" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -9017,13 +9021,13 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="402" t="inlineStr">
+      <c r="F12" s="403" t="inlineStr">
         <is>
           <t>Mat - BrSa
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="G12" s="403" t="inlineStr">
+      <c r="G12" s="404" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -9043,8 +9047,8 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="222" t="n"/>
-      <c r="F13" s="404" t="n"/>
-      <c r="G13" s="404" t="n"/>
+      <c r="F13" s="405" t="n"/>
+      <c r="G13" s="405" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
@@ -9059,8 +9063,8 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="222" t="n"/>
-      <c r="F14" s="405" t="n"/>
-      <c r="G14" s="405" t="n"/>
+      <c r="F14" s="406" t="n"/>
+      <c r="G14" s="406" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
@@ -9088,14 +9092,14 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="406" t="inlineStr">
+      <c r="F15" s="407" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="407" t="inlineStr">
+      <c r="H15" s="408" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
@@ -9113,9 +9117,9 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
-      <c r="F16" s="404" t="n"/>
+      <c r="F16" s="405" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="404" t="n"/>
+      <c r="H16" s="405" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -9129,9 +9133,9 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
-      <c r="F17" s="405" t="n"/>
+      <c r="F17" s="406" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="405" t="n"/>
+      <c r="H17" s="406" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -9162,14 +9166,14 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="408" t="inlineStr">
+      <c r="G18" s="409" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="409" t="inlineStr">
+      <c r="I18" s="410" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
@@ -9187,7 +9191,7 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="404" t="n"/>
+      <c r="G19" s="405" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -9210,7 +9214,7 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="405" t="n"/>
+      <c r="G20" s="406" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -9237,7 +9241,7 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="410" t="inlineStr">
+      <c r="F21" s="411" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
@@ -9245,7 +9249,7 @@
       </c>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="411" t="inlineStr">
+      <c r="I21" s="412" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -9274,10 +9278,10 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="404" t="n"/>
+      <c r="F22" s="405" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="222" t="n"/>
-      <c r="I22" s="404" t="n"/>
+      <c r="I22" s="405" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -9289,10 +9293,10 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="405" t="n"/>
+      <c r="F23" s="406" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="222" t="n"/>
-      <c r="I23" s="405" t="n"/>
+      <c r="I23" s="406" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -9317,7 +9321,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="407" t="inlineStr">
+      <c r="E24" s="408" t="inlineStr">
         <is>
           <t>Redação - Raf
 6º e 7º tempos</t>
@@ -9341,7 +9345,7 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="404" t="n"/>
+      <c r="E25" s="405" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -9360,7 +9364,7 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="405" t="n"/>
+      <c r="E26" s="406" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -9395,13 +9399,13 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="406" t="inlineStr">
+      <c r="H27" s="407" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I27" s="412" t="inlineStr">
+      <c r="I27" s="413" t="inlineStr">
         <is>
           <t>AG9
 2º ao 7º tempos</t>
@@ -9424,8 +9428,8 @@
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
-      <c r="H28" s="404" t="n"/>
-      <c r="I28" s="404" t="n"/>
+      <c r="H28" s="405" t="n"/>
+      <c r="I28" s="405" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -9443,8 +9447,8 @@
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
-      <c r="H29" s="405" t="n"/>
-      <c r="I29" s="405" t="n"/>
+      <c r="H29" s="406" t="n"/>
+      <c r="I29" s="406" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -9476,7 +9480,7 @@
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="411" t="inlineStr">
+      <c r="I30" s="412" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -9504,7 +9508,7 @@
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="283" t="n"/>
-      <c r="I31" s="404" t="n"/>
+      <c r="I31" s="405" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -9523,7 +9527,7 @@
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="283" t="n"/>
-      <c r="I32" s="405" t="n"/>
+      <c r="I32" s="406" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -9651,7 +9655,7 @@
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="413" t="inlineStr">
+      <c r="I36" s="414" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
@@ -9678,7 +9682,7 @@
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="404" t="n"/>
+      <c r="I37" s="405" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -9700,7 +9704,7 @@
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="405" t="n"/>
+      <c r="I38" s="406" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9721,7 +9725,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="414" t="inlineStr">
+      <c r="E39" s="415" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º tempo</t>
@@ -9729,7 +9733,7 @@
       </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="402" t="inlineStr">
+      <c r="H39" s="403" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
@@ -9743,10 +9747,10 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="404" t="n"/>
+      <c r="E40" s="405" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="404" t="n"/>
+      <c r="H40" s="405" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
@@ -9755,10 +9759,10 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="405" t="n"/>
+      <c r="E41" s="406" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="405" t="n"/>
+      <c r="H41" s="406" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
@@ -9781,13 +9785,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="410" t="inlineStr">
+      <c r="F42" s="411" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G42" s="408" t="inlineStr">
+      <c r="G42" s="409" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
@@ -9809,8 +9813,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="404" t="n"/>
-      <c r="G43" s="404" t="n"/>
+      <c r="F43" s="405" t="n"/>
+      <c r="G43" s="405" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -9822,8 +9826,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="405" t="n"/>
-      <c r="G44" s="405" t="n"/>
+      <c r="F44" s="406" t="n"/>
+      <c r="G44" s="406" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -9849,7 +9853,7 @@
       </c>
       <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="403" t="inlineStr">
+      <c r="G45" s="404" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -9867,7 +9871,7 @@
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="404" t="n"/>
+      <c r="G46" s="405" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -9880,7 +9884,7 @@
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="405" t="n"/>
+      <c r="G47" s="406" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -9904,14 +9908,14 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="415" t="inlineStr">
+      <c r="E48" s="416" t="inlineStr">
         <is>
           <t>Fis - VSi
 2º tempo</t>
         </is>
       </c>
-      <c r="F48" s="388" t="n"/>
-      <c r="G48" s="416" t="inlineStr">
+      <c r="F48" s="402" t="n"/>
+      <c r="G48" s="417" t="inlineStr">
         <is>
           <t>Qui - Fab
 2º tempo</t>
@@ -9930,9 +9934,9 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="404" t="n"/>
+      <c r="E49" s="405" t="n"/>
       <c r="F49" s="351" t="n"/>
-      <c r="G49" s="404" t="n"/>
+      <c r="G49" s="405" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
@@ -9942,9 +9946,9 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="405" t="n"/>
+      <c r="E50" s="406" t="n"/>
       <c r="F50" s="387" t="n"/>
-      <c r="G50" s="405" t="n"/>
+      <c r="G50" s="406" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
@@ -10071,7 +10075,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="388" t="inlineStr">
+      <c r="F57" s="402" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -10702,13 +10706,13 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="402" t="inlineStr">
+      <c r="F12" s="403" t="inlineStr">
         <is>
           <t>Mat - BrSa
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="G12" s="403" t="inlineStr">
+      <c r="G12" s="404" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -10728,8 +10732,8 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="222" t="n"/>
-      <c r="F13" s="404" t="n"/>
-      <c r="G13" s="404" t="n"/>
+      <c r="F13" s="405" t="n"/>
+      <c r="G13" s="405" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
@@ -10744,8 +10748,8 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="222" t="n"/>
-      <c r="F14" s="405" t="n"/>
-      <c r="G14" s="405" t="n"/>
+      <c r="F14" s="406" t="n"/>
+      <c r="G14" s="406" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
@@ -10773,14 +10777,14 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="406" t="inlineStr">
+      <c r="F15" s="407" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="407" t="inlineStr">
+      <c r="H15" s="408" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
@@ -10798,9 +10802,9 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
-      <c r="F16" s="404" t="n"/>
+      <c r="F16" s="405" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="404" t="n"/>
+      <c r="H16" s="405" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -10814,9 +10818,9 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
-      <c r="F17" s="405" t="n"/>
+      <c r="F17" s="406" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="405" t="n"/>
+      <c r="H17" s="406" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -10847,14 +10851,14 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="408" t="inlineStr">
+      <c r="G18" s="409" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="409" t="inlineStr">
+      <c r="I18" s="410" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
@@ -10872,7 +10876,7 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="404" t="n"/>
+      <c r="G19" s="405" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -10895,7 +10899,7 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="405" t="n"/>
+      <c r="G20" s="406" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -10922,7 +10926,7 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="410" t="inlineStr">
+      <c r="F21" s="411" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
@@ -10930,7 +10934,7 @@
       </c>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="411" t="inlineStr">
+      <c r="I21" s="412" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -10959,10 +10963,10 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="404" t="n"/>
+      <c r="F22" s="405" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="222" t="n"/>
-      <c r="I22" s="404" t="n"/>
+      <c r="I22" s="405" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -10974,10 +10978,10 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="405" t="n"/>
+      <c r="F23" s="406" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="222" t="n"/>
-      <c r="I23" s="405" t="n"/>
+      <c r="I23" s="406" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -11002,7 +11006,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="407" t="inlineStr">
+      <c r="E24" s="408" t="inlineStr">
         <is>
           <t>Redação - Raf
 6º e 7º tempos</t>
@@ -11026,7 +11030,7 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="404" t="n"/>
+      <c r="E25" s="405" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -11045,7 +11049,7 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="405" t="n"/>
+      <c r="E26" s="406" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -11080,13 +11084,13 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="406" t="inlineStr">
+      <c r="H27" s="407" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I27" s="412" t="inlineStr">
+      <c r="I27" s="413" t="inlineStr">
         <is>
           <t>AG9
 2º ao 7º tempos</t>
@@ -11109,8 +11113,8 @@
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
-      <c r="H28" s="404" t="n"/>
-      <c r="I28" s="404" t="n"/>
+      <c r="H28" s="405" t="n"/>
+      <c r="I28" s="405" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -11128,8 +11132,8 @@
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
-      <c r="H29" s="405" t="n"/>
-      <c r="I29" s="405" t="n"/>
+      <c r="H29" s="406" t="n"/>
+      <c r="I29" s="406" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -11161,7 +11165,7 @@
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="411" t="inlineStr">
+      <c r="I30" s="412" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -11189,7 +11193,7 @@
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="283" t="n"/>
-      <c r="I31" s="404" t="n"/>
+      <c r="I31" s="405" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -11208,7 +11212,7 @@
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="283" t="n"/>
-      <c r="I32" s="405" t="n"/>
+      <c r="I32" s="406" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -11336,7 +11340,7 @@
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="413" t="inlineStr">
+      <c r="I36" s="414" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
@@ -11363,7 +11367,7 @@
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="404" t="n"/>
+      <c r="I37" s="405" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -11385,7 +11389,7 @@
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="405" t="n"/>
+      <c r="I38" s="406" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11406,7 +11410,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="414" t="inlineStr">
+      <c r="E39" s="415" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º tempo</t>
@@ -11414,7 +11418,7 @@
       </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="402" t="inlineStr">
+      <c r="H39" s="403" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
@@ -11428,10 +11432,10 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="404" t="n"/>
+      <c r="E40" s="405" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="404" t="n"/>
+      <c r="H40" s="405" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
@@ -11440,10 +11444,10 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="405" t="n"/>
+      <c r="E41" s="406" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="405" t="n"/>
+      <c r="H41" s="406" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
@@ -11466,13 +11470,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="410" t="inlineStr">
+      <c r="F42" s="411" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G42" s="408" t="inlineStr">
+      <c r="G42" s="409" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
@@ -11494,8 +11498,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="404" t="n"/>
-      <c r="G43" s="404" t="n"/>
+      <c r="F43" s="405" t="n"/>
+      <c r="G43" s="405" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -11507,8 +11511,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="405" t="n"/>
-      <c r="G44" s="405" t="n"/>
+      <c r="F44" s="406" t="n"/>
+      <c r="G44" s="406" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -11534,7 +11538,7 @@
       </c>
       <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="403" t="inlineStr">
+      <c r="G45" s="404" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -11552,7 +11556,7 @@
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="404" t="n"/>
+      <c r="G46" s="405" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -11565,7 +11569,7 @@
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="405" t="n"/>
+      <c r="G47" s="406" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -11589,14 +11593,14 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="415" t="inlineStr">
+      <c r="E48" s="416" t="inlineStr">
         <is>
           <t>Fis - VSi
 2º tempo</t>
         </is>
       </c>
-      <c r="F48" s="388" t="n"/>
-      <c r="G48" s="416" t="inlineStr">
+      <c r="F48" s="402" t="n"/>
+      <c r="G48" s="417" t="inlineStr">
         <is>
           <t>Qui - Fab
 2º tempo</t>
@@ -11615,9 +11619,9 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="404" t="n"/>
+      <c r="E49" s="405" t="n"/>
       <c r="F49" s="351" t="n"/>
-      <c r="G49" s="404" t="n"/>
+      <c r="G49" s="405" t="n"/>
       <c r="H49" s="283" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
@@ -11627,9 +11631,9 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="405" t="n"/>
+      <c r="E50" s="406" t="n"/>
       <c r="F50" s="387" t="n"/>
-      <c r="G50" s="405" t="n"/>
+      <c r="G50" s="406" t="n"/>
       <c r="H50" s="283" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
@@ -11756,7 +11760,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="388" t="inlineStr">
+      <c r="F57" s="402" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -12386,20 +12390,20 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="402" t="inlineStr">
+      <c r="E12" s="403" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="413" t="inlineStr">
+      <c r="G12" s="414" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H12" s="415" t="inlineStr">
+      <c r="H12" s="416" t="inlineStr">
         <is>
           <t>Fis - VSi
 1º e 2º tempos</t>
@@ -12417,10 +12421,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="404" t="n"/>
+      <c r="E13" s="405" t="n"/>
       <c r="F13" s="222" t="n"/>
-      <c r="G13" s="404" t="n"/>
-      <c r="H13" s="404" t="n"/>
+      <c r="G13" s="405" t="n"/>
+      <c r="H13" s="405" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -12433,10 +12437,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="405" t="n"/>
+      <c r="E14" s="406" t="n"/>
       <c r="F14" s="222" t="n"/>
-      <c r="G14" s="405" t="n"/>
-      <c r="H14" s="405" t="n"/>
+      <c r="G14" s="406" t="n"/>
+      <c r="H14" s="406" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -12462,7 +12466,7 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="416" t="inlineStr">
+      <c r="E15" s="417" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
@@ -12470,7 +12474,7 @@
       </c>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="410" t="inlineStr">
+      <c r="H15" s="411" t="inlineStr">
         <is>
           <t>Hist - ALu
 2º e 3º tempos</t>
@@ -12487,10 +12491,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="404" t="n"/>
+      <c r="E16" s="405" t="n"/>
       <c r="F16" s="222" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="404" t="n"/>
+      <c r="H16" s="405" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -12503,10 +12507,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="405" t="n"/>
+      <c r="E17" s="406" t="n"/>
       <c r="F17" s="222" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="405" t="n"/>
+      <c r="H17" s="406" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -12537,14 +12541,14 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="406" t="inlineStr">
+      <c r="G18" s="407" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="417" t="inlineStr">
+      <c r="I18" s="418" t="inlineStr">
         <is>
           <t>Geo - Mlo
 1º e 2º tempos</t>
@@ -12562,7 +12566,7 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="404" t="n"/>
+      <c r="G19" s="405" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -12585,7 +12589,7 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="405" t="n"/>
+      <c r="G20" s="406" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -12611,20 +12615,20 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="418" t="inlineStr">
+      <c r="E21" s="419" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="414" t="inlineStr">
+      <c r="F21" s="415" t="inlineStr">
         <is>
           <t>Bio - Lza
 6º e 7º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="411" t="inlineStr">
+      <c r="H21" s="412" t="inlineStr">
         <is>
           <t>Ing - APa
 2º e 3º tempos</t>
@@ -12653,10 +12657,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="404" t="n"/>
-      <c r="F22" s="404" t="n"/>
+      <c r="E22" s="405" t="n"/>
+      <c r="F22" s="405" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="404" t="n"/>
+      <c r="H22" s="405" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -12668,10 +12672,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="405" t="n"/>
-      <c r="F23" s="405" t="n"/>
+      <c r="E23" s="406" t="n"/>
+      <c r="F23" s="406" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="405" t="n"/>
+      <c r="H23" s="406" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -12697,7 +12701,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="418" t="inlineStr">
+      <c r="E24" s="419" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
@@ -12706,7 +12710,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="419" t="inlineStr">
+      <c r="I24" s="420" t="inlineStr">
         <is>
           <t>AG10
 2º ao 7º tempos</t>
@@ -12726,11 +12730,11 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="404" t="n"/>
+      <c r="E25" s="405" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="404" t="n"/>
+      <c r="I25" s="405" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -12745,11 +12749,11 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="405" t="n"/>
+      <c r="E26" s="406" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="405" t="n"/>
+      <c r="I26" s="406" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -12778,7 +12782,7 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="414" t="inlineStr">
+      <c r="F27" s="415" t="inlineStr">
         <is>
           <t>Bio - Lza
 10º e 11º tempos</t>
@@ -12786,7 +12790,7 @@
       </c>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="403" t="inlineStr">
+      <c r="I27" s="404" t="inlineStr">
         <is>
           <t>Geo - Mlo
 2º e 3º tempos</t>
@@ -12807,10 +12811,10 @@
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
-      <c r="F28" s="404" t="n"/>
+      <c r="F28" s="405" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="404" t="n"/>
+      <c r="I28" s="405" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -12826,10 +12830,10 @@
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
-      <c r="F29" s="405" t="n"/>
+      <c r="F29" s="406" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="405" t="n"/>
+      <c r="I29" s="406" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -12860,7 +12864,7 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="415" t="inlineStr">
+      <c r="H30" s="416" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
@@ -12888,7 +12892,7 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="404" t="n"/>
+      <c r="H31" s="405" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -12907,7 +12911,7 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="405" t="n"/>
+      <c r="H32" s="406" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -13034,13 +13038,13 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="406" t="inlineStr">
+      <c r="G36" s="407" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H36" s="411" t="inlineStr">
+      <c r="H36" s="412" t="inlineStr">
         <is>
           <t>Ing - APa
 2º e 3º tempos</t>
@@ -13066,8 +13070,8 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
-      <c r="G37" s="404" t="n"/>
-      <c r="H37" s="404" t="n"/>
+      <c r="G37" s="405" t="n"/>
+      <c r="H37" s="405" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -13088,8 +13092,8 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
-      <c r="G38" s="405" t="n"/>
-      <c r="H38" s="405" t="n"/>
+      <c r="G38" s="406" t="n"/>
+      <c r="H38" s="406" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -13114,13 +13118,13 @@
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="402" t="inlineStr">
+      <c r="H39" s="403" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I39" s="420" t="inlineStr">
+      <c r="I39" s="421" t="inlineStr">
         <is>
           <t>Soc - Kle
 5º tempo</t>
@@ -13136,8 +13140,8 @@
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="404" t="n"/>
-      <c r="I40" s="404" t="n"/>
+      <c r="H40" s="405" t="n"/>
+      <c r="I40" s="405" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -13148,8 +13152,8 @@
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="405" t="n"/>
-      <c r="I41" s="405" t="n"/>
+      <c r="H41" s="406" t="n"/>
+      <c r="I41" s="406" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -13171,13 +13175,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="410" t="inlineStr">
+      <c r="F42" s="411" t="inlineStr">
         <is>
           <t>Hist - ALu
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G42" s="413" t="inlineStr">
+      <c r="G42" s="414" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
@@ -13199,8 +13203,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="404" t="n"/>
-      <c r="G43" s="404" t="n"/>
+      <c r="F43" s="405" t="n"/>
+      <c r="G43" s="405" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -13212,8 +13216,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="405" t="n"/>
-      <c r="G44" s="405" t="n"/>
+      <c r="F44" s="406" t="n"/>
+      <c r="G44" s="406" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -13237,14 +13241,14 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="416" t="inlineStr">
+      <c r="E45" s="417" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="421" t="inlineStr">
+      <c r="G45" s="422" t="inlineStr">
         <is>
           <t>Fil - LAn
 1º tempo</t>
@@ -13265,9 +13269,9 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="404" t="n"/>
+      <c r="E46" s="405" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="404" t="n"/>
+      <c r="G46" s="405" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -13278,9 +13282,9 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="405" t="n"/>
+      <c r="E47" s="406" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="405" t="n"/>
+      <c r="G47" s="406" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -13305,7 +13309,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="388" t="inlineStr">
+      <c r="F48" s="402" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -13461,7 +13465,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="388" t="n"/>
+      <c r="F57" s="402" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>
@@ -14089,20 +14093,20 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="402" t="inlineStr">
+      <c r="E12" s="403" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="413" t="inlineStr">
+      <c r="G12" s="414" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H12" s="415" t="inlineStr">
+      <c r="H12" s="416" t="inlineStr">
         <is>
           <t>Fis - VSi
 1º e 2º tempos</t>
@@ -14120,10 +14124,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="404" t="n"/>
+      <c r="E13" s="405" t="n"/>
       <c r="F13" s="222" t="n"/>
-      <c r="G13" s="404" t="n"/>
-      <c r="H13" s="404" t="n"/>
+      <c r="G13" s="405" t="n"/>
+      <c r="H13" s="405" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -14136,10 +14140,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="405" t="n"/>
+      <c r="E14" s="406" t="n"/>
       <c r="F14" s="222" t="n"/>
-      <c r="G14" s="405" t="n"/>
-      <c r="H14" s="405" t="n"/>
+      <c r="G14" s="406" t="n"/>
+      <c r="H14" s="406" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -14165,20 +14169,20 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="416" t="inlineStr">
+      <c r="E15" s="417" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="411" t="inlineStr">
+      <c r="F15" s="412" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="410" t="inlineStr">
+      <c r="H15" s="411" t="inlineStr">
         <is>
           <t>Hist - ALu
 2º e 3º tempos</t>
@@ -14195,10 +14199,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="404" t="n"/>
-      <c r="F16" s="404" t="n"/>
+      <c r="E16" s="405" t="n"/>
+      <c r="F16" s="405" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="404" t="n"/>
+      <c r="H16" s="405" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -14211,10 +14215,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="405" t="n"/>
-      <c r="F17" s="405" t="n"/>
+      <c r="E17" s="406" t="n"/>
+      <c r="F17" s="406" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="405" t="n"/>
+      <c r="H17" s="406" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -14245,14 +14249,14 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="406" t="inlineStr">
+      <c r="G18" s="407" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="417" t="inlineStr">
+      <c r="I18" s="418" t="inlineStr">
         <is>
           <t>Geo - Mlo
 1º e 2º tempos</t>
@@ -14270,7 +14274,7 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="404" t="n"/>
+      <c r="G19" s="405" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -14293,7 +14297,7 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="405" t="n"/>
+      <c r="G20" s="406" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -14319,13 +14323,13 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="418" t="inlineStr">
+      <c r="E21" s="419" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="414" t="inlineStr">
+      <c r="F21" s="415" t="inlineStr">
         <is>
           <t>Bio - Lza
 6º e 7º tempos</t>
@@ -14356,8 +14360,8 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="404" t="n"/>
-      <c r="F22" s="404" t="n"/>
+      <c r="E22" s="405" t="n"/>
+      <c r="F22" s="405" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="222" t="n"/>
       <c r="I22" s="222" t="n"/>
@@ -14371,8 +14375,8 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="405" t="n"/>
-      <c r="F23" s="405" t="n"/>
+      <c r="E23" s="406" t="n"/>
+      <c r="F23" s="406" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="222" t="n"/>
       <c r="I23" s="222" t="n"/>
@@ -14400,7 +14404,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="418" t="inlineStr">
+      <c r="E24" s="419" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
@@ -14409,7 +14413,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="419" t="inlineStr">
+      <c r="I24" s="420" t="inlineStr">
         <is>
           <t>AG10
 2º ao 7º tempos</t>
@@ -14429,11 +14433,11 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="404" t="n"/>
+      <c r="E25" s="405" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="404" t="n"/>
+      <c r="I25" s="405" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -14448,11 +14452,11 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="405" t="n"/>
+      <c r="E26" s="406" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="405" t="n"/>
+      <c r="I26" s="406" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -14481,7 +14485,7 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="414" t="inlineStr">
+      <c r="F27" s="415" t="inlineStr">
         <is>
           <t>Bio - Lza
 10º e 11º tempos</t>
@@ -14489,7 +14493,7 @@
       </c>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="403" t="inlineStr">
+      <c r="I27" s="404" t="inlineStr">
         <is>
           <t>Geo - Mlo
 2º e 3º tempos</t>
@@ -14510,10 +14514,10 @@
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
-      <c r="F28" s="404" t="n"/>
+      <c r="F28" s="405" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="404" t="n"/>
+      <c r="I28" s="405" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -14529,10 +14533,10 @@
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
-      <c r="F29" s="405" t="n"/>
+      <c r="F29" s="406" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="405" t="n"/>
+      <c r="I29" s="406" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -14563,7 +14567,7 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="415" t="inlineStr">
+      <c r="H30" s="416" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
@@ -14591,7 +14595,7 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="404" t="n"/>
+      <c r="H31" s="405" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -14610,7 +14614,7 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="405" t="n"/>
+      <c r="H32" s="406" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -14736,13 +14740,13 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="411" t="inlineStr">
+      <c r="F36" s="412" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G36" s="406" t="inlineStr">
+      <c r="G36" s="407" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
@@ -14768,8 +14772,8 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="404" t="n"/>
-      <c r="G37" s="404" t="n"/>
+      <c r="F37" s="405" t="n"/>
+      <c r="G37" s="405" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -14790,8 +14794,8 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="405" t="n"/>
-      <c r="G38" s="405" t="n"/>
+      <c r="F38" s="406" t="n"/>
+      <c r="G38" s="406" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -14817,13 +14821,13 @@
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="402" t="inlineStr">
+      <c r="H39" s="403" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I39" s="420" t="inlineStr">
+      <c r="I39" s="421" t="inlineStr">
         <is>
           <t>Soc - Kle
 5º tempo</t>
@@ -14839,8 +14843,8 @@
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="404" t="n"/>
-      <c r="I40" s="404" t="n"/>
+      <c r="H40" s="405" t="n"/>
+      <c r="I40" s="405" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -14851,8 +14855,8 @@
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="405" t="n"/>
-      <c r="I41" s="405" t="n"/>
+      <c r="H41" s="406" t="n"/>
+      <c r="I41" s="406" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -14874,13 +14878,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="410" t="inlineStr">
+      <c r="F42" s="411" t="inlineStr">
         <is>
           <t>Hist - ALu
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G42" s="413" t="inlineStr">
+      <c r="G42" s="414" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
@@ -14902,8 +14906,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="404" t="n"/>
-      <c r="G43" s="404" t="n"/>
+      <c r="F43" s="405" t="n"/>
+      <c r="G43" s="405" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -14915,8 +14919,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="405" t="n"/>
-      <c r="G44" s="405" t="n"/>
+      <c r="F44" s="406" t="n"/>
+      <c r="G44" s="406" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -14940,14 +14944,14 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="416" t="inlineStr">
+      <c r="E45" s="417" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="421" t="inlineStr">
+      <c r="G45" s="422" t="inlineStr">
         <is>
           <t>Fil - LAn
 1º tempo</t>
@@ -14968,9 +14972,9 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="404" t="n"/>
+      <c r="E46" s="405" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="404" t="n"/>
+      <c r="G46" s="405" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -14981,9 +14985,9 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="405" t="n"/>
+      <c r="E47" s="406" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="405" t="n"/>
+      <c r="G47" s="406" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -15008,7 +15012,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="388" t="inlineStr">
+      <c r="F48" s="402" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -15169,7 +15173,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="388" t="inlineStr">
+      <c r="F57" s="402" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -15810,25 +15814,25 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="402" t="inlineStr">
+      <c r="E12" s="403" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F12" s="412" t="inlineStr">
+      <c r="F12" s="413" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G12" s="412" t="inlineStr">
+      <c r="G12" s="413" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="411" t="inlineStr">
+      <c r="H12" s="412" t="inlineStr">
         <is>
           <t>Ing - Bea
 4º e 5º tempos</t>
@@ -15846,10 +15850,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="404" t="n"/>
-      <c r="F13" s="404" t="n"/>
-      <c r="G13" s="404" t="n"/>
-      <c r="H13" s="404" t="n"/>
+      <c r="E13" s="405" t="n"/>
+      <c r="F13" s="405" t="n"/>
+      <c r="G13" s="405" t="n"/>
+      <c r="H13" s="405" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -15862,10 +15866,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="405" t="n"/>
-      <c r="F14" s="405" t="n"/>
-      <c r="G14" s="405" t="n"/>
-      <c r="H14" s="405" t="n"/>
+      <c r="E14" s="406" t="n"/>
+      <c r="F14" s="406" t="n"/>
+      <c r="G14" s="406" t="n"/>
+      <c r="H14" s="406" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -15892,19 +15896,19 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="410" t="inlineStr">
+      <c r="F15" s="411" t="inlineStr">
         <is>
           <t>Hist - Ver
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="G15" s="413" t="inlineStr">
+      <c r="G15" s="414" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H15" s="415" t="inlineStr">
+      <c r="H15" s="416" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
@@ -15922,9 +15926,9 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
-      <c r="F16" s="404" t="n"/>
-      <c r="G16" s="404" t="n"/>
-      <c r="H16" s="404" t="n"/>
+      <c r="F16" s="405" t="n"/>
+      <c r="G16" s="405" t="n"/>
+      <c r="H16" s="405" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -15938,9 +15942,9 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
-      <c r="F17" s="405" t="n"/>
-      <c r="G17" s="405" t="n"/>
-      <c r="H17" s="405" t="n"/>
+      <c r="F17" s="406" t="n"/>
+      <c r="G17" s="406" t="n"/>
+      <c r="H17" s="406" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -15970,13 +15974,13 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="406" t="inlineStr">
+      <c r="F18" s="407" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G18" s="403" t="inlineStr">
+      <c r="G18" s="404" t="inlineStr">
         <is>
           <t>Geo - Mar
 1º e 2º tempos</t>
@@ -15995,8 +15999,8 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="404" t="n"/>
-      <c r="G19" s="404" t="n"/>
+      <c r="F19" s="405" t="n"/>
+      <c r="G19" s="405" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -16018,8 +16022,8 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="405" t="n"/>
-      <c r="G20" s="405" t="n"/>
+      <c r="F20" s="406" t="n"/>
+      <c r="G20" s="406" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -16045,20 +16049,20 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="414" t="inlineStr">
+      <c r="E21" s="415" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="416" t="inlineStr">
+      <c r="F21" s="417" t="inlineStr">
         <is>
           <t>Qui - CAl
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="418" t="inlineStr">
+      <c r="H21" s="419" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 9º ao 11º tempos</t>
@@ -16087,10 +16091,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="404" t="n"/>
-      <c r="F22" s="404" t="n"/>
+      <c r="E22" s="405" t="n"/>
+      <c r="F22" s="405" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="404" t="n"/>
+      <c r="H22" s="405" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -16102,10 +16106,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="405" t="n"/>
-      <c r="F23" s="405" t="n"/>
+      <c r="E23" s="406" t="n"/>
+      <c r="F23" s="406" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="405" t="n"/>
+      <c r="H23" s="406" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -16131,7 +16135,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="422" t="inlineStr">
+      <c r="E24" s="423" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 4º ao 6º tempos</t>
@@ -16140,7 +16144,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="423" t="inlineStr">
+      <c r="I24" s="424" t="inlineStr">
         <is>
           <t>Soc - Kle
 4º tempo</t>
@@ -16160,11 +16164,11 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="404" t="n"/>
+      <c r="E25" s="405" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="404" t="n"/>
+      <c r="I25" s="405" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -16179,11 +16183,11 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="405" t="n"/>
+      <c r="E26" s="406" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="405" t="n"/>
+      <c r="I26" s="406" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -16214,7 +16218,7 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="415" t="inlineStr">
+      <c r="H27" s="416" t="inlineStr">
         <is>
           <t>Fis - Cadu
 4º e 5º tempos</t>
@@ -16238,7 +16242,7 @@
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
-      <c r="H28" s="404" t="n"/>
+      <c r="H28" s="405" t="n"/>
       <c r="I28" s="283" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
@@ -16257,7 +16261,7 @@
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
-      <c r="H29" s="405" t="n"/>
+      <c r="H29" s="406" t="n"/>
       <c r="I29" s="283" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
@@ -16286,7 +16290,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="403" t="inlineStr">
+      <c r="E30" s="404" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -16314,7 +16318,7 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="404" t="n"/>
+      <c r="E31" s="405" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="283" t="n"/>
@@ -16333,7 +16337,7 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="405" t="n"/>
+      <c r="E32" s="406" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="283" t="n"/>
@@ -16463,7 +16467,7 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="402" t="inlineStr">
+      <c r="G36" s="403" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
@@ -16490,7 +16494,7 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
-      <c r="G37" s="404" t="n"/>
+      <c r="G37" s="405" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -16512,7 +16516,7 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
-      <c r="G38" s="405" t="n"/>
+      <c r="G38" s="406" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -16535,19 +16539,19 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="412" t="inlineStr">
+      <c r="E39" s="413" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="F39" s="412" t="inlineStr">
+      <c r="F39" s="413" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G39" s="413" t="inlineStr">
+      <c r="G39" s="414" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
@@ -16562,9 +16566,9 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="404" t="n"/>
-      <c r="F40" s="404" t="n"/>
-      <c r="G40" s="404" t="n"/>
+      <c r="E40" s="405" t="n"/>
+      <c r="F40" s="405" t="n"/>
+      <c r="G40" s="405" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
@@ -16574,9 +16578,9 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="405" t="n"/>
-      <c r="F41" s="405" t="n"/>
-      <c r="G41" s="405" t="n"/>
+      <c r="E41" s="406" t="n"/>
+      <c r="F41" s="406" t="n"/>
+      <c r="G41" s="406" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
@@ -16600,14 +16604,14 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="406" t="inlineStr">
+      <c r="F42" s="407" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="414" t="inlineStr">
+      <c r="H42" s="415" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
@@ -16628,9 +16632,9 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="404" t="n"/>
+      <c r="F43" s="405" t="n"/>
       <c r="G43" s="283" t="n"/>
-      <c r="H43" s="404" t="n"/>
+      <c r="H43" s="405" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -16641,9 +16645,9 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="405" t="n"/>
+      <c r="F44" s="406" t="n"/>
       <c r="G44" s="283" t="n"/>
-      <c r="H44" s="405" t="n"/>
+      <c r="H44" s="406" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -16667,13 +16671,13 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="410" t="inlineStr">
+      <c r="F45" s="411" t="inlineStr">
         <is>
           <t>Hist - Ver
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G45" s="421" t="inlineStr">
+      <c r="G45" s="422" t="inlineStr">
         <is>
           <t>Fil - LAn
 9º tempo</t>
@@ -16690,8 +16694,8 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="404" t="n"/>
-      <c r="G46" s="404" t="n"/>
+      <c r="F46" s="405" t="n"/>
+      <c r="G46" s="405" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -16703,8 +16707,8 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="405" t="n"/>
-      <c r="G47" s="405" t="n"/>
+      <c r="F47" s="406" t="n"/>
+      <c r="G47" s="406" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -16728,13 +16732,13 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="411" t="inlineStr">
+      <c r="E48" s="412" t="inlineStr">
         <is>
           <t>Ing - Bea
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="F48" s="424" t="inlineStr">
+      <c r="F48" s="425" t="inlineStr">
         <is>
           <t>Qui - CAl
 8º e 9º tempos</t>
@@ -16754,7 +16758,7 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="404" t="n"/>
+      <c r="E49" s="405" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
@@ -16766,7 +16770,7 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="405" t="n"/>
+      <c r="E50" s="406" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
@@ -16895,7 +16899,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="388" t="inlineStr">
+      <c r="F57" s="402" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -17531,26 +17535,26 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="402" t="inlineStr">
+      <c r="E12" s="403" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F12" s="412" t="inlineStr">
+      <c r="F12" s="413" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G12" s="412" t="inlineStr">
+      <c r="G12" s="413" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="411" t="inlineStr">
+      <c r="I12" s="412" t="inlineStr">
         <is>
           <t>Ing - PaH
 6º e 7º tempos</t>
@@ -17567,11 +17571,11 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="404" t="n"/>
-      <c r="F13" s="404" t="n"/>
-      <c r="G13" s="404" t="n"/>
+      <c r="E13" s="405" t="n"/>
+      <c r="F13" s="405" t="n"/>
+      <c r="G13" s="405" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="404" t="n"/>
+      <c r="I13" s="405" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -17583,11 +17587,11 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="405" t="n"/>
-      <c r="F14" s="405" t="n"/>
-      <c r="G14" s="405" t="n"/>
+      <c r="E14" s="406" t="n"/>
+      <c r="F14" s="406" t="n"/>
+      <c r="G14" s="406" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="405" t="n"/>
+      <c r="I14" s="406" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -17613,19 +17617,19 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="410" t="inlineStr">
+      <c r="F15" s="411" t="inlineStr">
         <is>
           <t>Hist - Ver
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="G15" s="413" t="inlineStr">
+      <c r="G15" s="414" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H15" s="415" t="inlineStr">
+      <c r="H15" s="416" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
@@ -17643,9 +17647,9 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
-      <c r="F16" s="404" t="n"/>
-      <c r="G16" s="404" t="n"/>
-      <c r="H16" s="404" t="n"/>
+      <c r="F16" s="405" t="n"/>
+      <c r="G16" s="405" t="n"/>
+      <c r="H16" s="405" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -17659,9 +17663,9 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
-      <c r="F17" s="405" t="n"/>
-      <c r="G17" s="405" t="n"/>
-      <c r="H17" s="405" t="n"/>
+      <c r="F17" s="406" t="n"/>
+      <c r="G17" s="406" t="n"/>
+      <c r="H17" s="406" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -17691,13 +17695,13 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="406" t="inlineStr">
+      <c r="F18" s="407" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G18" s="403" t="inlineStr">
+      <c r="G18" s="404" t="inlineStr">
         <is>
           <t>Geo - Mar
 1º e 2º tempos</t>
@@ -17716,8 +17720,8 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="404" t="n"/>
-      <c r="G19" s="404" t="n"/>
+      <c r="F19" s="405" t="n"/>
+      <c r="G19" s="405" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -17739,8 +17743,8 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="405" t="n"/>
-      <c r="G20" s="405" t="n"/>
+      <c r="F20" s="406" t="n"/>
+      <c r="G20" s="406" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -17766,20 +17770,20 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="414" t="inlineStr">
+      <c r="E21" s="415" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="416" t="inlineStr">
+      <c r="F21" s="417" t="inlineStr">
         <is>
           <t>Qui - CAl
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="418" t="inlineStr">
+      <c r="H21" s="419" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 9º ao 11º tempos</t>
@@ -17808,10 +17812,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="404" t="n"/>
-      <c r="F22" s="404" t="n"/>
+      <c r="E22" s="405" t="n"/>
+      <c r="F22" s="405" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="404" t="n"/>
+      <c r="H22" s="405" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -17823,10 +17827,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="405" t="n"/>
-      <c r="F23" s="405" t="n"/>
+      <c r="E23" s="406" t="n"/>
+      <c r="F23" s="406" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="405" t="n"/>
+      <c r="H23" s="406" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -17852,7 +17856,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="422" t="inlineStr">
+      <c r="E24" s="423" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 4º ao 6º tempos</t>
@@ -17861,7 +17865,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="423" t="inlineStr">
+      <c r="I24" s="424" t="inlineStr">
         <is>
           <t>Soc - Kle
 4º tempo</t>
@@ -17881,11 +17885,11 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="404" t="n"/>
+      <c r="E25" s="405" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="404" t="n"/>
+      <c r="I25" s="405" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -17900,11 +17904,11 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="405" t="n"/>
+      <c r="E26" s="406" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="405" t="n"/>
+      <c r="I26" s="406" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -17935,7 +17939,7 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="415" t="inlineStr">
+      <c r="H27" s="416" t="inlineStr">
         <is>
           <t>Fis - Cadu
 4º e 5º tempos</t>
@@ -17959,7 +17963,7 @@
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
-      <c r="H28" s="404" t="n"/>
+      <c r="H28" s="405" t="n"/>
       <c r="I28" s="283" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
@@ -17978,7 +17982,7 @@
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
-      <c r="H29" s="405" t="n"/>
+      <c r="H29" s="406" t="n"/>
       <c r="I29" s="283" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
@@ -18007,7 +18011,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="403" t="inlineStr">
+      <c r="E30" s="404" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -18035,7 +18039,7 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="404" t="n"/>
+      <c r="E31" s="405" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="283" t="n"/>
@@ -18054,7 +18058,7 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="405" t="n"/>
+      <c r="E32" s="406" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="283" t="n"/>
@@ -18184,7 +18188,7 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="402" t="inlineStr">
+      <c r="G36" s="403" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
@@ -18211,7 +18215,7 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
-      <c r="G37" s="404" t="n"/>
+      <c r="G37" s="405" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -18233,7 +18237,7 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
-      <c r="G38" s="405" t="n"/>
+      <c r="G38" s="406" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -18256,19 +18260,19 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="412" t="inlineStr">
+      <c r="E39" s="413" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="F39" s="412" t="inlineStr">
+      <c r="F39" s="413" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G39" s="413" t="inlineStr">
+      <c r="G39" s="414" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
@@ -18283,9 +18287,9 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="404" t="n"/>
-      <c r="F40" s="404" t="n"/>
-      <c r="G40" s="404" t="n"/>
+      <c r="E40" s="405" t="n"/>
+      <c r="F40" s="405" t="n"/>
+      <c r="G40" s="405" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
@@ -18295,9 +18299,9 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="405" t="n"/>
-      <c r="F41" s="405" t="n"/>
-      <c r="G41" s="405" t="n"/>
+      <c r="E41" s="406" t="n"/>
+      <c r="F41" s="406" t="n"/>
+      <c r="G41" s="406" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
@@ -18321,14 +18325,14 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="406" t="inlineStr">
+      <c r="F42" s="407" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="414" t="inlineStr">
+      <c r="H42" s="415" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
@@ -18349,9 +18353,9 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="404" t="n"/>
+      <c r="F43" s="405" t="n"/>
       <c r="G43" s="283" t="n"/>
-      <c r="H43" s="404" t="n"/>
+      <c r="H43" s="405" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -18362,9 +18366,9 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="405" t="n"/>
+      <c r="F44" s="406" t="n"/>
       <c r="G44" s="283" t="n"/>
-      <c r="H44" s="405" t="n"/>
+      <c r="H44" s="406" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -18388,13 +18392,13 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="410" t="inlineStr">
+      <c r="F45" s="411" t="inlineStr">
         <is>
           <t>Hist - Ver
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G45" s="421" t="inlineStr">
+      <c r="G45" s="422" t="inlineStr">
         <is>
           <t>Fil - LAn
 9º tempo</t>
@@ -18411,8 +18415,8 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="404" t="n"/>
-      <c r="G46" s="404" t="n"/>
+      <c r="F46" s="405" t="n"/>
+      <c r="G46" s="405" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -18424,8 +18428,8 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="405" t="n"/>
-      <c r="G47" s="405" t="n"/>
+      <c r="F47" s="406" t="n"/>
+      <c r="G47" s="406" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -18449,13 +18453,13 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="411" t="inlineStr">
+      <c r="E48" s="412" t="inlineStr">
         <is>
           <t>Ing - PaH
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F48" s="424" t="inlineStr">
+      <c r="F48" s="425" t="inlineStr">
         <is>
           <t>Qui - CAl
 8º e 9º tempos</t>
@@ -18475,7 +18479,7 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="404" t="n"/>
+      <c r="E49" s="405" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="283" t="n"/>
@@ -18487,7 +18491,7 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="405" t="n"/>
+      <c r="E50" s="406" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="283" t="n"/>
@@ -18616,7 +18620,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="388" t="inlineStr">
+      <c r="F57" s="402" t="inlineStr">
         <is>
           <t>CC
 9,11</t>
@@ -19252,13 +19256,13 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="411" t="inlineStr">
+      <c r="E12" s="412" t="inlineStr">
         <is>
           <t>Ing - PaH
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F12" s="418" t="inlineStr">
+      <c r="F12" s="419" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 10º ao 12º tempos</t>
@@ -19278,8 +19282,8 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="404" t="n"/>
-      <c r="F13" s="404" t="n"/>
+      <c r="E13" s="405" t="n"/>
+      <c r="F13" s="405" t="n"/>
       <c r="G13" s="222" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
@@ -19294,8 +19298,8 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="405" t="n"/>
-      <c r="F14" s="405" t="n"/>
+      <c r="E14" s="406" t="n"/>
+      <c r="F14" s="406" t="n"/>
       <c r="G14" s="222" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
@@ -19323,7 +19327,7 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="406" t="inlineStr">
+      <c r="E15" s="407" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 4º e 5º tempos</t>
@@ -19331,13 +19335,13 @@
       </c>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="415" t="inlineStr">
+      <c r="H15" s="416" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="416" t="inlineStr">
+      <c r="I15" s="417" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 2º e 3º tempos</t>
@@ -19353,11 +19357,11 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="404" t="n"/>
+      <c r="E16" s="405" t="n"/>
       <c r="F16" s="222" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="404" t="n"/>
-      <c r="I16" s="404" t="n"/>
+      <c r="H16" s="405" t="n"/>
+      <c r="I16" s="405" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -19369,11 +19373,11 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="405" t="n"/>
+      <c r="E17" s="406" t="n"/>
       <c r="F17" s="222" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="405" t="n"/>
-      <c r="I17" s="405" t="n"/>
+      <c r="H17" s="406" t="n"/>
+      <c r="I17" s="406" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -19402,20 +19406,20 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="414" t="inlineStr">
+      <c r="F18" s="415" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="413" t="inlineStr">
+      <c r="H18" s="414" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I18" s="425" t="inlineStr">
+      <c r="I18" s="426" t="inlineStr">
         <is>
           <t>Hist - Wag
 4º e 5º tempos</t>
@@ -19432,9 +19436,9 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="404" t="n"/>
+      <c r="F19" s="405" t="n"/>
       <c r="G19" s="222" t="n"/>
-      <c r="H19" s="404" t="n"/>
+      <c r="H19" s="405" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -19455,9 +19459,9 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="405" t="n"/>
+      <c r="F20" s="406" t="n"/>
       <c r="G20" s="222" t="n"/>
-      <c r="H20" s="405" t="n"/>
+      <c r="H20" s="406" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -19483,25 +19487,25 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="402" t="inlineStr">
+      <c r="F21" s="403" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G21" s="412" t="inlineStr">
+      <c r="G21" s="413" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H21" s="412" t="inlineStr">
+      <c r="H21" s="413" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="403" t="inlineStr">
+      <c r="I21" s="404" t="inlineStr">
         <is>
           <t>Geo - Mar
 2º e 3º tempos</t>
@@ -19530,10 +19534,10 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="404" t="n"/>
-      <c r="G22" s="404" t="n"/>
-      <c r="H22" s="404" t="n"/>
-      <c r="I22" s="404" t="n"/>
+      <c r="F22" s="405" t="n"/>
+      <c r="G22" s="405" t="n"/>
+      <c r="H22" s="405" t="n"/>
+      <c r="I22" s="405" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -19545,10 +19549,10 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="405" t="n"/>
-      <c r="G23" s="405" t="n"/>
-      <c r="H23" s="405" t="n"/>
-      <c r="I23" s="405" t="n"/>
+      <c r="F23" s="406" t="n"/>
+      <c r="G23" s="406" t="n"/>
+      <c r="H23" s="406" t="n"/>
+      <c r="I23" s="406" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -19575,14 +19579,14 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="426" t="inlineStr">
+      <c r="G24" s="427" t="inlineStr">
         <is>
           <t>Geo - Mar
 11º e 12º tempos</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="427" t="inlineStr">
+      <c r="I24" s="428" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 6º e 7º tempos</t>
@@ -19604,9 +19608,9 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="428" t="n"/>
+      <c r="G25" s="429" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="404" t="n"/>
+      <c r="I25" s="405" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -19623,9 +19627,9 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="429" t="n"/>
+      <c r="G26" s="430" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="405" t="n"/>
+      <c r="I26" s="406" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -19653,13 +19657,13 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="430" t="inlineStr">
+      <c r="E27" s="431" t="inlineStr">
         <is>
           <t>Ing - PaH
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F27" s="415" t="inlineStr">
+      <c r="F27" s="416" t="inlineStr">
         <is>
           <t>Fis - Cadu
 1º e 2º tempos</t>
@@ -19682,8 +19686,8 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="404" t="n"/>
-      <c r="F28" s="404" t="n"/>
+      <c r="E28" s="405" t="n"/>
+      <c r="F28" s="405" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
@@ -19701,8 +19705,8 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="405" t="n"/>
-      <c r="F29" s="405" t="n"/>
+      <c r="E29" s="406" t="n"/>
+      <c r="F29" s="406" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
@@ -19736,7 +19740,7 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="413" t="inlineStr">
+      <c r="H30" s="414" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
@@ -19764,7 +19768,7 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="404" t="n"/>
+      <c r="H31" s="405" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -19783,7 +19787,7 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="405" t="n"/>
+      <c r="H32" s="406" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -19909,7 +19913,7 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="418" t="inlineStr">
+      <c r="F36" s="419" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 10º ao 12º tempos</t>
@@ -19936,7 +19940,7 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="404" t="n"/>
+      <c r="F37" s="405" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="283" t="n"/>
@@ -19958,7 +19962,7 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="405" t="n"/>
+      <c r="F38" s="406" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="283" t="n"/>
@@ -19984,13 +19988,13 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="420" t="inlineStr">
+      <c r="G39" s="421" t="inlineStr">
         <is>
           <t>Soc - Kle
 6º tempo</t>
         </is>
       </c>
-      <c r="H39" s="402" t="inlineStr">
+      <c r="H39" s="403" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 4º e 5º tempos</t>
@@ -20006,8 +20010,8 @@
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="404" t="n"/>
-      <c r="H40" s="404" t="n"/>
+      <c r="G40" s="405" t="n"/>
+      <c r="H40" s="405" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
@@ -20018,8 +20022,8 @@
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="405" t="n"/>
-      <c r="H41" s="405" t="n"/>
+      <c r="G41" s="406" t="n"/>
+      <c r="H41" s="406" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
@@ -20042,13 +20046,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="414" t="inlineStr">
+      <c r="F42" s="415" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G42" s="421" t="inlineStr">
+      <c r="G42" s="422" t="inlineStr">
         <is>
           <t>Fil - LAn
 4º tempo</t>
@@ -20070,8 +20074,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="404" t="n"/>
-      <c r="G43" s="404" t="n"/>
+      <c r="F43" s="405" t="n"/>
+      <c r="G43" s="405" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -20083,8 +20087,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="405" t="n"/>
-      <c r="G44" s="405" t="n"/>
+      <c r="F44" s="406" t="n"/>
+      <c r="G44" s="406" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -20108,14 +20112,14 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="416" t="inlineStr">
+      <c r="E45" s="417" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 6º e 7º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="410" t="inlineStr">
+      <c r="G45" s="411" t="inlineStr">
         <is>
           <t>Hist - Wag
 11º e 12º tempos</t>
@@ -20136,9 +20140,9 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="404" t="n"/>
+      <c r="E46" s="405" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="404" t="n"/>
+      <c r="G46" s="405" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -20149,9 +20153,9 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="405" t="n"/>
+      <c r="E47" s="406" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="405" t="n"/>
+      <c r="G47" s="406" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -20176,7 +20180,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="388" t="inlineStr">
+      <c r="F48" s="402" t="inlineStr">
         <is>
           <t>CC
 10,12</t>
@@ -20332,7 +20336,7 @@
         <v/>
       </c>
       <c r="E57" s="183" t="n"/>
-      <c r="F57" s="388" t="n"/>
+      <c r="F57" s="402" t="n"/>
       <c r="G57" s="183" t="n"/>
       <c r="H57" s="183" t="n"/>
       <c r="I57" s="183" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -357,14 +357,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CF"/>
-        <bgColor rgb="FFC6E7CF"/>
+        <fgColor rgb="FFC6E7E4"/>
+        <bgColor rgb="FFC6E7E4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7E4"/>
-        <bgColor rgb="FFC6E7E4"/>
+        <fgColor rgb="FFC6E7CF"/>
+        <bgColor rgb="FFC6E7CF"/>
       </patternFill>
     </fill>
     <fill>
@@ -411,14 +411,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6DFE7"/>
-        <bgColor rgb="FFC6DFE7"/>
+        <fgColor rgb="FFC6D4E7"/>
+        <bgColor rgb="FFC6D4E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6D4E7"/>
-        <bgColor rgb="FFC6D4E7"/>
+        <fgColor rgb="FFC6DFE7"/>
+        <bgColor rgb="FFC6DFE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1814,7 +1814,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="432">
+  <cellXfs count="434">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3176,14 +3176,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="109" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -3194,52 +3198,83 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="105" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -3247,39 +3282,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="105" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="105" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5776,18 +5783,23 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="423" t="inlineStr">
+      <c r="E12" s="408" t="inlineStr">
+        <is>
+          <t>Ing - Isb
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="421" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
-10º ao 12º tempos</t>
+9º ao 11º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="412" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-11º e 12º tempos</t>
+      <c r="H12" s="405" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -5802,10 +5814,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="222" t="n"/>
-      <c r="F13" s="405" t="n"/>
+      <c r="E13" s="406" t="n"/>
+      <c r="F13" s="406" t="n"/>
       <c r="G13" s="222" t="n"/>
-      <c r="H13" s="405" t="n"/>
+      <c r="H13" s="406" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -5818,10 +5830,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="222" t="n"/>
-      <c r="F14" s="406" t="n"/>
+      <c r="E14" s="407" t="n"/>
+      <c r="F14" s="407" t="n"/>
       <c r="G14" s="222" t="n"/>
-      <c r="H14" s="406" t="n"/>
+      <c r="H14" s="407" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -5847,26 +5859,21 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="408" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
+      <c r="E15" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n"/>
+      <c r="F15" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="418" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I15" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -5877,11 +5884,11 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="405" t="n"/>
-      <c r="F16" s="222" t="n"/>
+      <c r="E16" s="406" t="n"/>
+      <c r="F16" s="406" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="405" t="n"/>
-      <c r="I16" s="405" t="n"/>
+      <c r="H16" s="222" t="n"/>
+      <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -5893,11 +5900,11 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="406" t="n"/>
-      <c r="F17" s="222" t="n"/>
+      <c r="E17" s="407" t="n"/>
+      <c r="F17" s="407" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="406" t="n"/>
-      <c r="I17" s="406" t="n"/>
+      <c r="H17" s="222" t="n"/>
+      <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -5926,23 +5933,23 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Ale
+      <c r="F18" s="403" t="inlineStr">
+        <is>
+          <t>Hist - Wag
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="409" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="432" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
 2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="403" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="430" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-4º e 5º tempos</t>
         </is>
       </c>
       <c r="J18" s="183" t="n"/>
@@ -5956,9 +5963,9 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="405" t="n"/>
+      <c r="F19" s="406" t="n"/>
       <c r="G19" s="222" t="n"/>
-      <c r="H19" s="405" t="n"/>
+      <c r="H19" s="406" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -5979,9 +5986,9 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="406" t="n"/>
+      <c r="F20" s="407" t="n"/>
       <c r="G20" s="222" t="n"/>
-      <c r="H20" s="406" t="n"/>
+      <c r="H20" s="407" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -6006,31 +6013,31 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="409" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
+      <c r="E21" s="411" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="420" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G21" s="416" t="inlineStr">
+      <c r="G21" s="418" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H21" s="416" t="inlineStr">
+      <c r="H21" s="418" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="407" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -6053,11 +6060,11 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="222" t="n"/>
-      <c r="F22" s="405" t="n"/>
-      <c r="G22" s="405" t="n"/>
-      <c r="H22" s="405" t="n"/>
-      <c r="I22" s="405" t="n"/>
+      <c r="E22" s="406" t="n"/>
+      <c r="F22" s="406" t="n"/>
+      <c r="G22" s="406" t="n"/>
+      <c r="H22" s="406" t="n"/>
+      <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -6068,11 +6075,11 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="222" t="n"/>
-      <c r="F23" s="406" t="n"/>
-      <c r="G23" s="406" t="n"/>
-      <c r="H23" s="406" t="n"/>
-      <c r="I23" s="406" t="n"/>
+      <c r="E23" s="407" t="n"/>
+      <c r="F23" s="407" t="n"/>
+      <c r="G23" s="407" t="n"/>
+      <c r="H23" s="407" t="n"/>
+      <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -6099,10 +6106,10 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="431" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
+      <c r="G24" s="433" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
@@ -6123,7 +6130,7 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="414" t="n"/>
+      <c r="G25" s="415" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
@@ -6142,7 +6149,7 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="415" t="n"/>
+      <c r="G26" s="416" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
@@ -6172,14 +6179,19 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
+      <c r="E27" s="429" t="inlineStr">
+        <is>
+          <t>Ing - Isb
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="408" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
-6º e 7º tempos</t>
+      <c r="I27" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="J27" s="265" t="n"/>
@@ -6196,11 +6208,11 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="78" t="n"/>
+      <c r="E28" s="406" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="405" t="n"/>
+      <c r="I28" s="406" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -6215,11 +6227,11 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="78" t="n"/>
+      <c r="E29" s="407" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="406" t="n"/>
+      <c r="I29" s="407" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -6247,20 +6259,20 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="423" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-11º ao 13º tempos</t>
+      <c r="E30" s="283" t="n"/>
+      <c r="F30" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
+      <c r="H30" s="405" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
@@ -6280,10 +6292,10 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="405" t="n"/>
-      <c r="F31" s="405" t="n"/>
+      <c r="E31" s="283" t="n"/>
+      <c r="F31" s="406" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="283" t="n"/>
+      <c r="H31" s="406" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -6299,10 +6311,10 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="406" t="n"/>
-      <c r="F32" s="406" t="n"/>
+      <c r="E32" s="283" t="n"/>
+      <c r="F32" s="407" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="283" t="n"/>
+      <c r="H32" s="407" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -6428,20 +6440,20 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G36" s="410" t="inlineStr">
+      <c r="F36" s="403" t="inlineStr">
         <is>
           <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -6460,10 +6472,10 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="405" t="n"/>
-      <c r="G37" s="405" t="n"/>
+      <c r="F37" s="406" t="n"/>
+      <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="283" t="n"/>
+      <c r="I37" s="406" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -6482,10 +6494,10 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="406" t="n"/>
-      <c r="G38" s="406" t="n"/>
+      <c r="F38" s="407" t="n"/>
+      <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="283" t="n"/>
+      <c r="I38" s="407" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6506,21 +6518,21 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="412" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="403" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I39" s="283" t="n"/>
+      <c r="H39" s="420" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I39" s="411" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6528,11 +6540,11 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="405" t="n"/>
+      <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="405" t="n"/>
-      <c r="I40" s="283" t="n"/>
+      <c r="H40" s="406" t="n"/>
+      <c r="I40" s="406" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -6540,11 +6552,11 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="406" t="n"/>
+      <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="406" t="n"/>
-      <c r="I41" s="283" t="n"/>
+      <c r="H41" s="407" t="n"/>
+      <c r="I41" s="407" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6566,20 +6578,15 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="418" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="425" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="n"/>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -6594,10 +6601,10 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="405" t="n"/>
-      <c r="G43" s="405" t="n"/>
+      <c r="F43" s="283" t="n"/>
+      <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
-      <c r="I43" s="283" t="n"/>
+      <c r="I43" s="406" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -6607,10 +6614,10 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="406" t="n"/>
-      <c r="G44" s="406" t="n"/>
+      <c r="F44" s="283" t="n"/>
+      <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
-      <c r="I44" s="283" t="n"/>
+      <c r="I44" s="407" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -6633,19 +6640,19 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="407" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="H45" s="409" t="inlineStr">
+      <c r="F45" s="409" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G45" s="427" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
@@ -6661,9 +6668,9 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="283" t="n"/>
-      <c r="G46" s="405" t="n"/>
-      <c r="H46" s="405" t="n"/>
+      <c r="F46" s="406" t="n"/>
+      <c r="G46" s="406" t="n"/>
+      <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -6674,9 +6681,9 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="283" t="n"/>
-      <c r="G47" s="406" t="n"/>
-      <c r="H47" s="406" t="n"/>
+      <c r="F47" s="407" t="n"/>
+      <c r="G47" s="407" t="n"/>
+      <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -6963,7 +6970,7 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
-    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -6979,11 +6986,11 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
-    <mergeCell ref="E30:E32"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="G45:G47"/>
+    <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -6991,10 +6998,11 @@
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
+    <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="I15:I17"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
@@ -7009,7 +7017,6 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -7022,6 +7029,8 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
+    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="E27:E29"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -7033,7 +7042,6 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
-    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -7044,7 +7052,6 @@
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
     <mergeCell ref="G21:G23"/>
-    <mergeCell ref="E39:E41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
@@ -7054,9 +7061,9 @@
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F45:F47"/>
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="F42:F44"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
@@ -7082,6 +7089,7 @@
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
+    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -7091,8 +7099,8 @@
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="I27:I29"/>
-    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
+    <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -7101,7 +7109,6 @@
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>
@@ -9019,13 +9026,13 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="403" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="403" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G12" s="404" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -9033,7 +9040,12 @@
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
+      <c r="I12" s="405" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -9045,11 +9057,11 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="405" t="n"/>
-      <c r="F13" s="222" t="n"/>
-      <c r="G13" s="405" t="n"/>
+      <c r="E13" s="222" t="n"/>
+      <c r="F13" s="406" t="n"/>
+      <c r="G13" s="406" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="222" t="n"/>
+      <c r="I13" s="406" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -9061,11 +9073,11 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="406" t="n"/>
-      <c r="F14" s="222" t="n"/>
-      <c r="G14" s="406" t="n"/>
+      <c r="E14" s="222" t="n"/>
+      <c r="F14" s="407" t="n"/>
+      <c r="G14" s="407" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="222" t="n"/>
+      <c r="I14" s="407" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -9092,19 +9104,14 @@
       </c>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="407" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="408" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="408" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -9117,9 +9124,9 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
       <c r="F16" s="222" t="n"/>
-      <c r="G16" s="405" t="n"/>
-      <c r="H16" s="405" t="n"/>
-      <c r="I16" s="222" t="n"/>
+      <c r="G16" s="222" t="n"/>
+      <c r="H16" s="222" t="n"/>
+      <c r="I16" s="406" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -9133,9 +9140,9 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
       <c r="F17" s="222" t="n"/>
-      <c r="G17" s="406" t="n"/>
-      <c r="H17" s="406" t="n"/>
-      <c r="I17" s="222" t="n"/>
+      <c r="G17" s="222" t="n"/>
+      <c r="H17" s="222" t="n"/>
+      <c r="I17" s="407" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -9164,11 +9171,16 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="409" t="inlineStr">
+      <c r="F18" s="409" t="inlineStr">
         <is>
           <t>Mat - BrSa
-4º e 5º tempos</t>
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
@@ -9184,8 +9196,8 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="222" t="n"/>
-      <c r="G19" s="405" t="n"/>
+      <c r="F19" s="406" t="n"/>
+      <c r="G19" s="406" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -9207,8 +9219,8 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="222" t="n"/>
-      <c r="G20" s="406" t="n"/>
+      <c r="F20" s="407" t="n"/>
+      <c r="G20" s="407" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -9235,25 +9247,20 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="410" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+      <c r="F21" s="411" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="411" t="inlineStr">
+      <c r="H21" s="412" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I21" s="412" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -9277,10 +9284,10 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="405" t="n"/>
+      <c r="F22" s="406" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="405" t="n"/>
-      <c r="I22" s="405" t="n"/>
+      <c r="H22" s="406" t="n"/>
+      <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -9292,10 +9299,10 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="406" t="n"/>
+      <c r="F23" s="407" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="406" t="n"/>
-      <c r="I23" s="406" t="n"/>
+      <c r="H23" s="407" t="n"/>
+      <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -9329,7 +9336,12 @@
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="414" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -9346,9 +9358,9 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="414" t="n"/>
+      <c r="G25" s="415" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="78" t="n"/>
+      <c r="I25" s="406" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -9365,9 +9377,9 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="415" t="n"/>
+      <c r="G26" s="416" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="78" t="n"/>
+      <c r="I26" s="407" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -9397,14 +9409,14 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
-      <c r="H27" s="408" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I27" s="416" t="inlineStr">
+      <c r="G27" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+3º tempo</t>
+        </is>
+      </c>
+      <c r="H27" s="283" t="n"/>
+      <c r="I27" s="418" t="inlineStr">
         <is>
           <t>AG9
 2º ao 7º tempos</t>
@@ -9426,9 +9438,9 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="283" t="n"/>
-      <c r="H28" s="405" t="n"/>
-      <c r="I28" s="405" t="n"/>
+      <c r="G28" s="406" t="n"/>
+      <c r="H28" s="283" t="n"/>
+      <c r="I28" s="406" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -9445,9 +9457,9 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="283" t="n"/>
-      <c r="H29" s="406" t="n"/>
-      <c r="I29" s="406" t="n"/>
+      <c r="G29" s="407" t="n"/>
+      <c r="H29" s="283" t="n"/>
+      <c r="I29" s="407" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -9477,10 +9489,10 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="407" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
+      <c r="G30" s="419" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+2º tempo</t>
         </is>
       </c>
       <c r="H30" s="283" t="n"/>
@@ -9505,7 +9517,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="405" t="n"/>
+      <c r="G31" s="406" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -9524,7 +9536,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="406" t="n"/>
+      <c r="G32" s="407" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -9651,10 +9663,15 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
+      <c r="F36" s="403" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="412" t="inlineStr">
+      <c r="I36" s="408" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -9678,10 +9695,10 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="283" t="n"/>
+      <c r="F37" s="406" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="405" t="n"/>
+      <c r="I37" s="406" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -9700,10 +9717,10 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="283" t="n"/>
+      <c r="F38" s="407" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="406" t="n"/>
+      <c r="I38" s="407" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9726,13 +9743,13 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
-      <c r="H39" s="411" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G39" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -9743,8 +9760,8 @@
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="283" t="n"/>
-      <c r="H40" s="405" t="n"/>
+      <c r="G40" s="406" t="n"/>
+      <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
@@ -9755,8 +9772,8 @@
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="283" t="n"/>
-      <c r="H41" s="406" t="n"/>
+      <c r="G41" s="407" t="n"/>
+      <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
@@ -9779,16 +9796,11 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="410" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+      <c r="F42" s="283" t="n"/>
+      <c r="G42" s="409" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
 4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-3º tempo</t>
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
@@ -9807,8 +9819,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="405" t="n"/>
-      <c r="G43" s="405" t="n"/>
+      <c r="F43" s="283" t="n"/>
+      <c r="G43" s="406" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -9820,8 +9832,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="406" t="n"/>
-      <c r="G44" s="406" t="n"/>
+      <c r="F44" s="283" t="n"/>
+      <c r="G44" s="407" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -9845,21 +9857,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="418" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
-      <c r="I45" s="419" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="411" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I45" s="386" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -9868,10 +9875,10 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="405" t="n"/>
+      <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
-      <c r="H46" s="283" t="n"/>
+      <c r="H46" s="406" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -9881,10 +9888,10 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="406" t="n"/>
+      <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
-      <c r="H47" s="283" t="n"/>
+      <c r="H47" s="407" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -9907,20 +9914,20 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="n"/>
-      <c r="F48" s="420" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
+      <c r="E48" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
+      <c r="F48" s="402" t="n"/>
+      <c r="G48" s="283" t="n"/>
+      <c r="H48" s="412" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G48" s="421" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-2º tempo</t>
-        </is>
-      </c>
-      <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -9933,10 +9940,10 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="283" t="n"/>
+      <c r="E49" s="406" t="n"/>
       <c r="F49" s="351" t="n"/>
-      <c r="G49" s="405" t="n"/>
-      <c r="H49" s="283" t="n"/>
+      <c r="G49" s="283" t="n"/>
+      <c r="H49" s="406" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -9945,10 +9952,10 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="78" t="n"/>
+      <c r="E50" s="407" t="n"/>
       <c r="F50" s="387" t="n"/>
-      <c r="G50" s="406" t="n"/>
-      <c r="H50" s="283" t="n"/>
+      <c r="G50" s="283" t="n"/>
+      <c r="H50" s="407" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -10159,7 +10166,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="166">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -10188,6 +10195,7 @@
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
@@ -10202,7 +10210,6 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="A12:A14"/>
-    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="G30:G32"/>
@@ -10210,19 +10217,18 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
-    <mergeCell ref="H27:H29"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
-    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="I15:I17"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
@@ -10231,6 +10237,7 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
+    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -10254,7 +10261,6 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
-    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -10265,25 +10271,26 @@
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
     <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
+    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
+    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
-    <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="F42:F44"/>
     <mergeCell ref="J36:J38"/>
-    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="G18:G20"/>
+    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="I18:I20"/>
     <mergeCell ref="G24:G26"/>
-    <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
     <mergeCell ref="D12:D14"/>
@@ -10298,6 +10305,7 @@
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
+    <mergeCell ref="H48:H50"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
     <mergeCell ref="J39:J41"/>
@@ -10308,6 +10316,7 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G27:G29"/>
     <mergeCell ref="I27:I29"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
@@ -10317,9 +10326,9 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
+    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>
@@ -10703,13 +10712,13 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="403" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="403" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G12" s="404" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -10717,7 +10726,12 @@
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
+      <c r="I12" s="405" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -10729,11 +10743,11 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="405" t="n"/>
-      <c r="F13" s="222" t="n"/>
-      <c r="G13" s="405" t="n"/>
+      <c r="E13" s="222" t="n"/>
+      <c r="F13" s="406" t="n"/>
+      <c r="G13" s="406" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="222" t="n"/>
+      <c r="I13" s="406" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -10745,11 +10759,11 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="406" t="n"/>
-      <c r="F14" s="222" t="n"/>
-      <c r="G14" s="406" t="n"/>
+      <c r="E14" s="222" t="n"/>
+      <c r="F14" s="407" t="n"/>
+      <c r="G14" s="407" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="222" t="n"/>
+      <c r="I14" s="407" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -10776,19 +10790,14 @@
       </c>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="407" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="408" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="408" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -10801,9 +10810,9 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
       <c r="F16" s="222" t="n"/>
-      <c r="G16" s="405" t="n"/>
-      <c r="H16" s="405" t="n"/>
-      <c r="I16" s="222" t="n"/>
+      <c r="G16" s="222" t="n"/>
+      <c r="H16" s="222" t="n"/>
+      <c r="I16" s="406" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -10817,9 +10826,9 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
       <c r="F17" s="222" t="n"/>
-      <c r="G17" s="406" t="n"/>
-      <c r="H17" s="406" t="n"/>
-      <c r="I17" s="222" t="n"/>
+      <c r="G17" s="222" t="n"/>
+      <c r="H17" s="222" t="n"/>
+      <c r="I17" s="407" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -10848,11 +10857,16 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="409" t="inlineStr">
+      <c r="F18" s="409" t="inlineStr">
         <is>
           <t>Mat - BrSa
-4º e 5º tempos</t>
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
@@ -10868,8 +10882,8 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="222" t="n"/>
-      <c r="G19" s="405" t="n"/>
+      <c r="F19" s="406" t="n"/>
+      <c r="G19" s="406" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -10891,8 +10905,8 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="222" t="n"/>
-      <c r="G20" s="406" t="n"/>
+      <c r="F20" s="407" t="n"/>
+      <c r="G20" s="407" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -10919,25 +10933,20 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="410" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+      <c r="F21" s="411" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="411" t="inlineStr">
+      <c r="H21" s="412" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I21" s="412" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -10961,10 +10970,10 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="405" t="n"/>
+      <c r="F22" s="406" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="405" t="n"/>
-      <c r="I22" s="405" t="n"/>
+      <c r="H22" s="406" t="n"/>
+      <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -10976,10 +10985,10 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="406" t="n"/>
+      <c r="F23" s="407" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="406" t="n"/>
-      <c r="I23" s="406" t="n"/>
+      <c r="H23" s="407" t="n"/>
+      <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -11013,7 +11022,12 @@
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="414" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -11030,9 +11044,9 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="414" t="n"/>
+      <c r="G25" s="415" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="78" t="n"/>
+      <c r="I25" s="406" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -11049,9 +11063,9 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="415" t="n"/>
+      <c r="G26" s="416" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="78" t="n"/>
+      <c r="I26" s="407" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -11081,14 +11095,14 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
-      <c r="H27" s="408" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I27" s="416" t="inlineStr">
+      <c r="G27" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+3º tempo</t>
+        </is>
+      </c>
+      <c r="H27" s="283" t="n"/>
+      <c r="I27" s="418" t="inlineStr">
         <is>
           <t>AG9
 2º ao 7º tempos</t>
@@ -11110,9 +11124,9 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="283" t="n"/>
-      <c r="H28" s="405" t="n"/>
-      <c r="I28" s="405" t="n"/>
+      <c r="G28" s="406" t="n"/>
+      <c r="H28" s="283" t="n"/>
+      <c r="I28" s="406" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -11129,9 +11143,9 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="283" t="n"/>
-      <c r="H29" s="406" t="n"/>
-      <c r="I29" s="406" t="n"/>
+      <c r="G29" s="407" t="n"/>
+      <c r="H29" s="283" t="n"/>
+      <c r="I29" s="407" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -11161,10 +11175,10 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="407" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
+      <c r="G30" s="419" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+2º tempo</t>
         </is>
       </c>
       <c r="H30" s="283" t="n"/>
@@ -11189,7 +11203,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="405" t="n"/>
+      <c r="G31" s="406" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -11208,7 +11222,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="406" t="n"/>
+      <c r="G32" s="407" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -11335,10 +11349,15 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
+      <c r="F36" s="403" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="412" t="inlineStr">
+      <c r="I36" s="408" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -11362,10 +11381,10 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="283" t="n"/>
+      <c r="F37" s="406" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="405" t="n"/>
+      <c r="I37" s="406" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -11384,10 +11403,10 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="283" t="n"/>
+      <c r="F38" s="407" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="406" t="n"/>
+      <c r="I38" s="407" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11410,13 +11429,13 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
-      <c r="H39" s="411" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G39" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -11427,8 +11446,8 @@
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="283" t="n"/>
-      <c r="H40" s="405" t="n"/>
+      <c r="G40" s="406" t="n"/>
+      <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
@@ -11439,8 +11458,8 @@
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="283" t="n"/>
-      <c r="H41" s="406" t="n"/>
+      <c r="G41" s="407" t="n"/>
+      <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
@@ -11463,16 +11482,11 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="410" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+      <c r="F42" s="283" t="n"/>
+      <c r="G42" s="409" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
 4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-3º tempo</t>
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
@@ -11491,8 +11505,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="405" t="n"/>
-      <c r="G43" s="405" t="n"/>
+      <c r="F43" s="283" t="n"/>
+      <c r="G43" s="406" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -11504,8 +11518,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="406" t="n"/>
-      <c r="G44" s="406" t="n"/>
+      <c r="F44" s="283" t="n"/>
+      <c r="G44" s="407" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -11529,21 +11543,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="418" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
-      <c r="I45" s="419" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="411" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I45" s="386" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -11552,10 +11561,10 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="405" t="n"/>
+      <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
-      <c r="H46" s="283" t="n"/>
+      <c r="H46" s="406" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -11565,10 +11574,10 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="406" t="n"/>
+      <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
-      <c r="H47" s="283" t="n"/>
+      <c r="H47" s="407" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -11591,20 +11600,20 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="n"/>
-      <c r="F48" s="420" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
+      <c r="E48" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
+      <c r="F48" s="402" t="n"/>
+      <c r="G48" s="283" t="n"/>
+      <c r="H48" s="412" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G48" s="421" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-2º tempo</t>
-        </is>
-      </c>
-      <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -11617,10 +11626,10 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="283" t="n"/>
+      <c r="E49" s="406" t="n"/>
       <c r="F49" s="351" t="n"/>
-      <c r="G49" s="405" t="n"/>
-      <c r="H49" s="283" t="n"/>
+      <c r="G49" s="283" t="n"/>
+      <c r="H49" s="406" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -11629,10 +11638,10 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="78" t="n"/>
+      <c r="E50" s="407" t="n"/>
       <c r="F50" s="387" t="n"/>
-      <c r="G50" s="406" t="n"/>
-      <c r="H50" s="283" t="n"/>
+      <c r="G50" s="283" t="n"/>
+      <c r="H50" s="407" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -11843,7 +11852,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="166">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -11872,6 +11881,7 @@
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
@@ -11886,7 +11896,6 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="A12:A14"/>
-    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="G30:G32"/>
@@ -11894,19 +11903,18 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
-    <mergeCell ref="H27:H29"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
-    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="I15:I17"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
@@ -11915,6 +11923,7 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
+    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -11938,7 +11947,6 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
-    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -11949,25 +11957,26 @@
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
     <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
+    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
+    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
-    <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="F42:F44"/>
     <mergeCell ref="J36:J38"/>
-    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="G18:G20"/>
+    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="I18:I20"/>
     <mergeCell ref="G24:G26"/>
-    <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
     <mergeCell ref="D12:D14"/>
@@ -11982,6 +11991,7 @@
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
+    <mergeCell ref="H48:H50"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
     <mergeCell ref="J39:J41"/>
@@ -11992,6 +12002,7 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G27:G29"/>
     <mergeCell ref="I27:I29"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
@@ -12001,9 +12012,9 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
+    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>
@@ -12387,25 +12398,25 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="409" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="403" t="inlineStr">
+      <c r="E12" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="405" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H12" s="418" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -12418,10 +12429,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="405" t="n"/>
-      <c r="F13" s="222" t="n"/>
-      <c r="G13" s="405" t="n"/>
-      <c r="H13" s="405" t="n"/>
+      <c r="E13" s="406" t="n"/>
+      <c r="F13" s="406" t="n"/>
+      <c r="G13" s="406" t="n"/>
+      <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -12434,10 +12445,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="406" t="n"/>
-      <c r="F14" s="222" t="n"/>
-      <c r="G14" s="406" t="n"/>
-      <c r="H14" s="406" t="n"/>
+      <c r="E14" s="407" t="n"/>
+      <c r="F14" s="407" t="n"/>
+      <c r="G14" s="407" t="n"/>
+      <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -12463,18 +12474,18 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="410" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+      <c r="G15" s="422" t="inlineStr">
+        <is>
+          <t>Ing - APa
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="H15" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -12488,10 +12499,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="405" t="n"/>
+      <c r="E16" s="222" t="n"/>
       <c r="F16" s="222" t="n"/>
-      <c r="G16" s="222" t="n"/>
-      <c r="H16" s="405" t="n"/>
+      <c r="G16" s="406" t="n"/>
+      <c r="H16" s="406" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -12504,10 +12515,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="406" t="n"/>
+      <c r="E17" s="222" t="n"/>
       <c r="F17" s="222" t="n"/>
-      <c r="G17" s="222" t="n"/>
-      <c r="H17" s="406" t="n"/>
+      <c r="G17" s="407" t="n"/>
+      <c r="H17" s="407" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -12538,14 +12549,19 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="408" t="inlineStr">
+      <c r="G18" s="411" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="422" t="inlineStr">
+      <c r="H18" s="403" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="423" t="inlineStr">
         <is>
           <t>Geo - Mlo
 1º e 2º tempos</t>
@@ -12563,8 +12579,8 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="405" t="n"/>
-      <c r="H19" s="222" t="n"/>
+      <c r="G19" s="406" t="n"/>
+      <c r="H19" s="406" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -12586,8 +12602,8 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="406" t="n"/>
-      <c r="H20" s="222" t="n"/>
+      <c r="G20" s="407" t="n"/>
+      <c r="H20" s="407" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -12612,23 +12628,18 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="423" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F21" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="412" t="inlineStr">
-        <is>
-          <t>Ing - APa
-2º e 3º tempos</t>
+      <c r="H21" s="409" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -12654,10 +12665,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="405" t="n"/>
-      <c r="F22" s="405" t="n"/>
+      <c r="E22" s="406" t="n"/>
+      <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="405" t="n"/>
+      <c r="H22" s="406" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -12669,10 +12680,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="406" t="n"/>
-      <c r="F23" s="406" t="n"/>
+      <c r="E23" s="407" t="n"/>
+      <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="406" t="n"/>
+      <c r="H23" s="407" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -12726,7 +12737,7 @@
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="405" t="n"/>
+      <c r="I25" s="406" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -12745,7 +12756,7 @@
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="406" t="n"/>
+      <c r="I26" s="407" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -12773,16 +12784,21 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
-      <c r="F27" s="410" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="425" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="n"/>
+      <c r="I27" s="426" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -12797,11 +12813,11 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="78" t="n"/>
-      <c r="F28" s="405" t="n"/>
+      <c r="E28" s="406" t="n"/>
+      <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="283" t="n"/>
+      <c r="I28" s="406" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -12816,11 +12832,11 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="78" t="n"/>
-      <c r="F29" s="406" t="n"/>
+      <c r="E29" s="407" t="n"/>
+      <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="283" t="n"/>
+      <c r="I29" s="407" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -12848,16 +12864,16 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
-      <c r="I30" s="407" t="inlineStr">
+      <c r="H30" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="I30" s="410" t="inlineStr">
         <is>
           <t>Geo - Mlo
 2º e 3º tempos</t>
@@ -12881,11 +12897,11 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="405" t="n"/>
+      <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="283" t="n"/>
-      <c r="I31" s="405" t="n"/>
+      <c r="H31" s="406" t="n"/>
+      <c r="I31" s="406" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -12900,11 +12916,11 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="406" t="n"/>
+      <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="283" t="n"/>
-      <c r="I32" s="406" t="n"/>
+      <c r="H32" s="407" t="n"/>
+      <c r="I32" s="407" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -13028,9 +13044,14 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
+      <c r="E36" s="408" t="inlineStr">
+        <is>
+          <t>Ing - APa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="403" t="inlineStr">
+      <c r="G36" s="405" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
@@ -13060,10 +13081,10 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="283" t="n"/>
+      <c r="E37" s="406" t="n"/>
       <c r="F37" s="283" t="n"/>
-      <c r="G37" s="405" t="n"/>
-      <c r="H37" s="405" t="n"/>
+      <c r="G37" s="406" t="n"/>
+      <c r="H37" s="406" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -13082,10 +13103,10 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="283" t="n"/>
+      <c r="E38" s="407" t="n"/>
       <c r="F38" s="283" t="n"/>
-      <c r="G38" s="406" t="n"/>
-      <c r="H38" s="406" t="n"/>
+      <c r="G38" s="407" t="n"/>
+      <c r="H38" s="407" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -13108,17 +13129,17 @@
         <v/>
       </c>
       <c r="E39" s="283" t="n"/>
-      <c r="F39" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G39" s="283" t="n"/>
-      <c r="H39" s="418" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
+      <c r="F39" s="283" t="n"/>
+      <c r="G39" s="427" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
+      <c r="H39" s="403" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I39" s="283" t="n"/>
@@ -13130,9 +13151,9 @@
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
-      <c r="F40" s="405" t="n"/>
-      <c r="G40" s="283" t="n"/>
-      <c r="H40" s="405" t="n"/>
+      <c r="F40" s="283" t="n"/>
+      <c r="G40" s="406" t="n"/>
+      <c r="H40" s="406" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
@@ -13142,9 +13163,9 @@
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
-      <c r="F41" s="406" t="n"/>
-      <c r="G41" s="283" t="n"/>
-      <c r="H41" s="406" t="n"/>
+      <c r="F41" s="283" t="n"/>
+      <c r="G41" s="407" t="n"/>
+      <c r="H41" s="407" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
@@ -13167,25 +13188,20 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
-      <c r="G42" s="408" t="inlineStr">
+      <c r="F42" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G42" s="411" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H42" s="412" t="inlineStr">
-        <is>
-          <t>Ing - APa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I42" s="425" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H42" s="283" t="n"/>
+      <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -13200,10 +13216,10 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
-      <c r="G43" s="405" t="n"/>
-      <c r="H43" s="405" t="n"/>
-      <c r="I43" s="405" t="n"/>
+      <c r="F43" s="406" t="n"/>
+      <c r="G43" s="406" t="n"/>
+      <c r="H43" s="283" t="n"/>
+      <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -13213,10 +13229,10 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
-      <c r="G44" s="406" t="n"/>
-      <c r="H44" s="406" t="n"/>
-      <c r="I44" s="406" t="n"/>
+      <c r="F44" s="407" t="n"/>
+      <c r="G44" s="407" t="n"/>
+      <c r="H44" s="283" t="n"/>
+      <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -13238,19 +13254,14 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="423" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+      <c r="E45" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="426" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
@@ -13266,9 +13277,9 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="405" t="n"/>
+      <c r="E46" s="406" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="405" t="n"/>
+      <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -13279,9 +13290,9 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="406" t="n"/>
+      <c r="E47" s="407" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="406" t="n"/>
+      <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -13557,7 +13568,6 @@
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D30:D32"/>
-    <mergeCell ref="F39:F41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="C24:C26"/>
@@ -13572,8 +13582,8 @@
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
-    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
@@ -13585,23 +13595,21 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
-    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="G45:G47"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
-    <mergeCell ref="F27:F29"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="E21:E23"/>
-    <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -13629,7 +13637,7 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
-    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="E27:E29"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -13652,6 +13660,7 @@
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
     <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
@@ -13661,9 +13670,10 @@
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="H36:H38"/>
     <mergeCell ref="J36:J38"/>
+    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
@@ -13682,12 +13692,12 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
+    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -13696,6 +13706,7 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I30:I32"/>
@@ -14090,25 +14101,25 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="409" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="403" t="inlineStr">
+      <c r="E12" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="405" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H12" s="418" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -14121,10 +14132,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="405" t="n"/>
-      <c r="F13" s="222" t="n"/>
-      <c r="G13" s="405" t="n"/>
-      <c r="H13" s="405" t="n"/>
+      <c r="E13" s="406" t="n"/>
+      <c r="F13" s="406" t="n"/>
+      <c r="G13" s="406" t="n"/>
+      <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -14137,10 +14148,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="406" t="n"/>
-      <c r="F14" s="222" t="n"/>
-      <c r="G14" s="406" t="n"/>
-      <c r="H14" s="406" t="n"/>
+      <c r="E14" s="407" t="n"/>
+      <c r="F14" s="407" t="n"/>
+      <c r="G14" s="407" t="n"/>
+      <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -14166,23 +14177,18 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="412" t="inlineStr">
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="408" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="410" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+      <c r="H15" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -14196,10 +14202,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="405" t="n"/>
-      <c r="F16" s="405" t="n"/>
+      <c r="E16" s="222" t="n"/>
+      <c r="F16" s="406" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="405" t="n"/>
+      <c r="H16" s="406" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -14212,10 +14218,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="406" t="n"/>
-      <c r="F17" s="406" t="n"/>
+      <c r="E17" s="222" t="n"/>
+      <c r="F17" s="407" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="406" t="n"/>
+      <c r="H17" s="407" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -14246,14 +14252,19 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="408" t="inlineStr">
+      <c r="G18" s="411" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="422" t="inlineStr">
+      <c r="H18" s="403" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="423" t="inlineStr">
         <is>
           <t>Geo - Mlo
 1º e 2º tempos</t>
@@ -14271,8 +14282,8 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="405" t="n"/>
-      <c r="H19" s="222" t="n"/>
+      <c r="G19" s="406" t="n"/>
+      <c r="H19" s="406" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -14294,8 +14305,8 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="406" t="n"/>
-      <c r="H20" s="222" t="n"/>
+      <c r="G20" s="407" t="n"/>
+      <c r="H20" s="407" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -14320,20 +14331,20 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="423" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F21" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
+      <c r="H21" s="409" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
@@ -14357,10 +14368,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="405" t="n"/>
-      <c r="F22" s="405" t="n"/>
+      <c r="E22" s="406" t="n"/>
+      <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="222" t="n"/>
+      <c r="H22" s="406" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -14372,10 +14383,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="406" t="n"/>
-      <c r="F23" s="406" t="n"/>
+      <c r="E23" s="407" t="n"/>
+      <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="222" t="n"/>
+      <c r="H23" s="407" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -14429,7 +14440,7 @@
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="405" t="n"/>
+      <c r="I25" s="406" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -14448,7 +14459,7 @@
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="406" t="n"/>
+      <c r="I26" s="407" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -14476,21 +14487,21 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
-      <c r="F27" s="410" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G27" s="412" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="425" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="283" t="n"/>
+      <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="n"/>
+      <c r="I27" s="426" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -14505,11 +14516,11 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="78" t="n"/>
-      <c r="F28" s="405" t="n"/>
-      <c r="G28" s="405" t="n"/>
+      <c r="E28" s="406" t="n"/>
+      <c r="F28" s="283" t="n"/>
+      <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="283" t="n"/>
+      <c r="I28" s="406" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -14524,11 +14535,11 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="78" t="n"/>
-      <c r="F29" s="406" t="n"/>
-      <c r="G29" s="406" t="n"/>
+      <c r="E29" s="407" t="n"/>
+      <c r="F29" s="283" t="n"/>
+      <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="283" t="n"/>
+      <c r="I29" s="407" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -14556,16 +14567,16 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
-      <c r="I30" s="407" t="inlineStr">
+      <c r="H30" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="I30" s="410" t="inlineStr">
         <is>
           <t>Geo - Mlo
 2º e 3º tempos</t>
@@ -14589,11 +14600,11 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="405" t="n"/>
+      <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="283" t="n"/>
-      <c r="I31" s="405" t="n"/>
+      <c r="H31" s="406" t="n"/>
+      <c r="I31" s="406" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -14608,11 +14619,11 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="406" t="n"/>
+      <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="283" t="n"/>
-      <c r="I32" s="406" t="n"/>
+      <c r="H32" s="407" t="n"/>
+      <c r="I32" s="407" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -14738,7 +14749,7 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="403" t="inlineStr">
+      <c r="G36" s="405" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
@@ -14770,8 +14781,8 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
-      <c r="G37" s="405" t="n"/>
-      <c r="H37" s="405" t="n"/>
+      <c r="G37" s="406" t="n"/>
+      <c r="H37" s="406" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -14792,8 +14803,8 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
-      <c r="G38" s="406" t="n"/>
-      <c r="H38" s="406" t="n"/>
+      <c r="G38" s="407" t="n"/>
+      <c r="H38" s="407" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -14816,17 +14827,17 @@
         <v/>
       </c>
       <c r="E39" s="283" t="n"/>
-      <c r="F39" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G39" s="283" t="n"/>
-      <c r="H39" s="418" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
+      <c r="F39" s="283" t="n"/>
+      <c r="G39" s="427" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
+      <c r="H39" s="403" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I39" s="283" t="n"/>
@@ -14838,9 +14849,9 @@
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
-      <c r="F40" s="405" t="n"/>
-      <c r="G40" s="283" t="n"/>
-      <c r="H40" s="405" t="n"/>
+      <c r="F40" s="283" t="n"/>
+      <c r="G40" s="406" t="n"/>
+      <c r="H40" s="406" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
@@ -14850,9 +14861,9 @@
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
-      <c r="F41" s="406" t="n"/>
-      <c r="G41" s="283" t="n"/>
-      <c r="H41" s="406" t="n"/>
+      <c r="F41" s="283" t="n"/>
+      <c r="G41" s="407" t="n"/>
+      <c r="H41" s="407" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
@@ -14875,20 +14886,20 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
-      <c r="G42" s="408" t="inlineStr">
+      <c r="F42" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G42" s="411" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="425" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -14903,10 +14914,10 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
-      <c r="G43" s="405" t="n"/>
+      <c r="F43" s="406" t="n"/>
+      <c r="G43" s="406" t="n"/>
       <c r="H43" s="283" t="n"/>
-      <c r="I43" s="405" t="n"/>
+      <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -14916,10 +14927,10 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
-      <c r="G44" s="406" t="n"/>
+      <c r="F44" s="407" t="n"/>
+      <c r="G44" s="407" t="n"/>
       <c r="H44" s="283" t="n"/>
-      <c r="I44" s="406" t="n"/>
+      <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -14941,17 +14952,17 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="423" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+      <c r="E45" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="426" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
+      <c r="G45" s="408" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
@@ -14969,9 +14980,9 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="405" t="n"/>
+      <c r="E46" s="406" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="405" t="n"/>
+      <c r="G46" s="406" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -14982,9 +14993,9 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="406" t="n"/>
+      <c r="E47" s="407" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="406" t="n"/>
+      <c r="G47" s="407" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -15270,7 +15281,6 @@
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D30:D32"/>
-    <mergeCell ref="F39:F41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="C24:C26"/>
@@ -15286,9 +15296,10 @@
     <mergeCell ref="G42:G44"/>
     <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
-    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
+    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -15298,7 +15309,6 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
-    <mergeCell ref="E30:E32"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
@@ -15307,8 +15317,8 @@
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
-    <mergeCell ref="F27:F29"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="E12:E14"/>
@@ -15341,7 +15351,7 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
-    <mergeCell ref="I42:I44"/>
+    <mergeCell ref="E27:E29"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -15364,6 +15374,7 @@
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
     <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
@@ -15373,7 +15384,7 @@
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="H36:H38"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
@@ -15394,12 +15405,12 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
+    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -15408,7 +15419,7 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I30:I32"/>
@@ -15811,28 +15822,28 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="409" t="inlineStr">
+      <c r="E12" s="408" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="418" t="inlineStr">
+        <is>
+          <t>S3-11
+2º ao 7º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="418" t="inlineStr">
+        <is>
+          <t>S3-11
+2º ao 7º tempos</t>
+        </is>
+      </c>
+      <c r="H12" s="409" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="416" t="inlineStr">
-        <is>
-          <t>S3-11
-2º ao 7º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="416" t="inlineStr">
-        <is>
-          <t>S3-11
-2º ao 7º tempos</t>
-        </is>
-      </c>
-      <c r="H12" s="412" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-4º e 5º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -15847,10 +15858,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="405" t="n"/>
-      <c r="F13" s="405" t="n"/>
-      <c r="G13" s="405" t="n"/>
-      <c r="H13" s="405" t="n"/>
+      <c r="E13" s="406" t="n"/>
+      <c r="F13" s="406" t="n"/>
+      <c r="G13" s="406" t="n"/>
+      <c r="H13" s="406" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -15863,10 +15874,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="406" t="n"/>
-      <c r="F14" s="406" t="n"/>
-      <c r="G14" s="406" t="n"/>
-      <c r="H14" s="406" t="n"/>
+      <c r="E14" s="407" t="n"/>
+      <c r="F14" s="407" t="n"/>
+      <c r="G14" s="407" t="n"/>
+      <c r="H14" s="407" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -15892,23 +15903,23 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="410" t="inlineStr">
+      <c r="E15" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="403" t="inlineStr">
         <is>
           <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="403" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="418" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+9º ao 11º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -15922,10 +15933,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="222" t="n"/>
-      <c r="F16" s="405" t="n"/>
-      <c r="G16" s="405" t="n"/>
-      <c r="H16" s="405" t="n"/>
+      <c r="E16" s="406" t="n"/>
+      <c r="F16" s="406" t="n"/>
+      <c r="G16" s="222" t="n"/>
+      <c r="H16" s="406" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -15938,10 +15949,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="222" t="n"/>
-      <c r="F17" s="406" t="n"/>
-      <c r="G17" s="406" t="n"/>
-      <c r="H17" s="406" t="n"/>
+      <c r="E17" s="407" t="n"/>
+      <c r="F17" s="407" t="n"/>
+      <c r="G17" s="222" t="n"/>
+      <c r="H17" s="407" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -15971,16 +15982,16 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="408" t="inlineStr">
+      <c r="F18" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="411" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="407" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="H18" s="11" t="n"/>
@@ -15996,8 +16007,8 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="405" t="n"/>
-      <c r="G19" s="405" t="n"/>
+      <c r="F19" s="406" t="n"/>
+      <c r="G19" s="406" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -16019,8 +16030,8 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="406" t="n"/>
-      <c r="G20" s="406" t="n"/>
+      <c r="F20" s="407" t="n"/>
+      <c r="G20" s="407" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -16052,17 +16063,17 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="423" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-9º ao 11º tempos</t>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="405" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H21" s="420" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -16088,10 +16099,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="405" t="n"/>
-      <c r="F22" s="405" t="n"/>
-      <c r="G22" s="222" t="n"/>
-      <c r="H22" s="405" t="n"/>
+      <c r="E22" s="406" t="n"/>
+      <c r="F22" s="63" t="n"/>
+      <c r="G22" s="406" t="n"/>
+      <c r="H22" s="406" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -16103,10 +16114,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="406" t="n"/>
-      <c r="F23" s="406" t="n"/>
-      <c r="G23" s="222" t="n"/>
-      <c r="H23" s="406" t="n"/>
+      <c r="E23" s="407" t="n"/>
+      <c r="F23" s="63" t="n"/>
+      <c r="G23" s="407" t="n"/>
+      <c r="H23" s="407" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -16134,14 +16145,14 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
+      <c r="G24" s="428" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="427" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -16158,9 +16169,9 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="79" t="n"/>
+      <c r="G25" s="415" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="405" t="n"/>
+      <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -16177,9 +16188,9 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="79" t="n"/>
+      <c r="G26" s="416" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="406" t="n"/>
+      <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -16207,19 +16218,19 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="n"/>
-      <c r="F27" s="410" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G27" s="426" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-9º tempo</t>
-        </is>
-      </c>
+      <c r="E27" s="429" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+8º ao 10º tempos</t>
+        </is>
+      </c>
+      <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
@@ -16236,9 +16247,9 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="78" t="n"/>
-      <c r="F28" s="405" t="n"/>
-      <c r="G28" s="405" t="n"/>
+      <c r="E28" s="406" t="n"/>
+      <c r="F28" s="406" t="n"/>
+      <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
       <c r="J28" s="352" t="n"/>
@@ -16255,9 +16266,9 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="78" t="n"/>
-      <c r="F29" s="406" t="n"/>
-      <c r="G29" s="406" t="n"/>
+      <c r="E29" s="407" t="n"/>
+      <c r="F29" s="407" t="n"/>
+      <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
       <c r="J29" s="352" t="n"/>
@@ -16287,7 +16298,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="407" t="inlineStr">
+      <c r="E30" s="410" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -16315,7 +16326,7 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="405" t="n"/>
+      <c r="E31" s="406" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="283" t="n"/>
@@ -16334,7 +16345,7 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="406" t="n"/>
+      <c r="E32" s="407" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="283" t="n"/>
@@ -16462,21 +16473,21 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="428" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-4º ao 6º tempos</t>
-        </is>
-      </c>
-      <c r="F36" s="283" t="n"/>
+      <c r="E36" s="283" t="n"/>
+      <c r="F36" s="403" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I36" s="283" t="n"/>
+      <c r="H36" s="283" t="n"/>
+      <c r="I36" s="426" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -16494,11 +16505,11 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="405" t="n"/>
-      <c r="F37" s="283" t="n"/>
+      <c r="E37" s="283" t="n"/>
+      <c r="F37" s="406" t="n"/>
       <c r="G37" s="283" t="n"/>
-      <c r="H37" s="405" t="n"/>
-      <c r="I37" s="283" t="n"/>
+      <c r="H37" s="283" t="n"/>
+      <c r="I37" s="406" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -16516,11 +16527,11 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="406" t="n"/>
-      <c r="F38" s="283" t="n"/>
+      <c r="E38" s="283" t="n"/>
+      <c r="F38" s="407" t="n"/>
       <c r="G38" s="283" t="n"/>
-      <c r="H38" s="406" t="n"/>
-      <c r="I38" s="283" t="n"/>
+      <c r="H38" s="283" t="n"/>
+      <c r="I38" s="407" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -16541,25 +16552,25 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="416" t="inlineStr">
+      <c r="E39" s="418" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="F39" s="416" t="inlineStr">
+      <c r="F39" s="418" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G39" s="283" t="n"/>
-      <c r="H39" s="412" t="inlineStr">
-        <is>
-          <t>Ing - Bea
+      <c r="G39" s="411" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
 6º e 7º tempos</t>
         </is>
       </c>
+      <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -16568,10 +16579,10 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="405" t="n"/>
-      <c r="F40" s="405" t="n"/>
-      <c r="G40" s="283" t="n"/>
-      <c r="H40" s="405" t="n"/>
+      <c r="E40" s="406" t="n"/>
+      <c r="F40" s="406" t="n"/>
+      <c r="G40" s="406" t="n"/>
+      <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
@@ -16580,10 +16591,10 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="406" t="n"/>
-      <c r="F41" s="406" t="n"/>
-      <c r="G41" s="283" t="n"/>
-      <c r="H41" s="406" t="n"/>
+      <c r="E41" s="407" t="n"/>
+      <c r="F41" s="407" t="n"/>
+      <c r="G41" s="407" t="n"/>
+      <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
@@ -16606,16 +16617,11 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-8º e 9º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="403" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
+      <c r="F42" s="283" t="n"/>
+      <c r="G42" s="409" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
@@ -16634,8 +16640,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="405" t="n"/>
-      <c r="G43" s="405" t="n"/>
+      <c r="F43" s="283" t="n"/>
+      <c r="G43" s="406" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -16647,8 +16653,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="406" t="n"/>
-      <c r="G44" s="406" t="n"/>
+      <c r="F44" s="283" t="n"/>
+      <c r="G44" s="407" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -16673,11 +16679,16 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="409" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
+      <c r="F45" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G45" s="405" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
@@ -16691,8 +16702,8 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="283" t="n"/>
-      <c r="G46" s="405" t="n"/>
+      <c r="F46" s="406" t="n"/>
+      <c r="G46" s="406" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -16704,8 +16715,8 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="283" t="n"/>
-      <c r="G47" s="406" t="n"/>
+      <c r="F47" s="407" t="n"/>
+      <c r="G47" s="407" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -16730,14 +16741,14 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="429" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
+      <c r="F48" s="430" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G48" s="283" t="n"/>
-      <c r="H48" s="418" t="inlineStr">
+      <c r="H48" s="420" t="inlineStr">
         <is>
           <t>Fis - Cadu
 4º e 5º tempos</t>
@@ -16758,7 +16769,7 @@
       <c r="E49" s="283" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
-      <c r="H49" s="405" t="n"/>
+      <c r="H49" s="406" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -16770,7 +16781,7 @@
       <c r="E50" s="78" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
-      <c r="H50" s="406" t="n"/>
+      <c r="H50" s="407" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -17014,7 +17025,1727 @@
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
-    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="H51:H53"/>
+    <mergeCell ref="J24:J26"/>
+    <mergeCell ref="H60:H62"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="F27:F29"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="J18:J20"/>
+    <mergeCell ref="H33:H35"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="J33:J35"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="J42:J44"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="J60:J62"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="J57:J59"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="I57:I59"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="J30:J32"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="G33:G35"/>
+    <mergeCell ref="J54:J56"/>
+    <mergeCell ref="I33:I35"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="G60:G62"/>
+    <mergeCell ref="G9:G11"/>
+    <mergeCell ref="L16:N17"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="J48:J50"/>
+    <mergeCell ref="D51:D53"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="D60:D62"/>
+    <mergeCell ref="F60:F62"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="I54:I56"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="H9:H11"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F45:F47"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="J36:J38"/>
+    <mergeCell ref="J45:J47"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E57:E59"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="I51:I53"/>
+    <mergeCell ref="E54:E56"/>
+    <mergeCell ref="I60:I62"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="D54:D56"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="H48:H50"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="J39:J41"/>
+    <mergeCell ref="J51:J53"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="E33:E35"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="I9:I11"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="I45:I47"/>
+    <mergeCell ref="F54:F56"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="J27:J29"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.4705555555555556" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="64"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P62"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="0.44140625" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="4" customWidth="1" style="2" min="1" max="1"/>
+    <col width="11.5546875" customWidth="1" min="2" max="2"/>
+    <col width="2.88671875" customWidth="1" min="3" max="3"/>
+    <col width="11.33203125" customWidth="1" min="4" max="4"/>
+    <col width="12.109375" customWidth="1" style="3" min="5" max="9"/>
+    <col width="16.5546875" customWidth="1" style="3" min="10" max="10"/>
+    <col width="4.33203125" customWidth="1" min="11" max="11"/>
+    <col width="12.33203125" customWidth="1" min="12" max="12"/>
+    <col width="12.5546875" customWidth="1" min="13" max="13"/>
+    <col width="27.6640625" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="21.33203125" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35.1" customHeight="1">
+      <c r="A1" s="173" t="inlineStr">
+        <is>
+          <t>Prüfungsplan Klasse 11C2 | Plano das Provas Turma 11C2</t>
+        </is>
+      </c>
+      <c r="B1" s="307" t="n"/>
+      <c r="C1" s="307" t="n"/>
+      <c r="D1" s="307" t="n"/>
+      <c r="E1" s="307" t="n"/>
+      <c r="F1" s="307" t="n"/>
+      <c r="G1" s="307" t="n"/>
+      <c r="H1" s="307" t="n"/>
+      <c r="I1" s="307" t="n"/>
+      <c r="J1" s="67" t="inlineStr">
+        <is>
+          <t>Anzahl SuS |
+Número alunos:19</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="n"/>
+      <c r="O1" s="5" t="n"/>
+      <c r="P1" s="5" t="n"/>
+    </row>
+    <row r="2" ht="31.5" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="B2" s="308" t="inlineStr">
+        <is>
+          <t>Datum von bis</t>
+        </is>
+      </c>
+      <c r="C2" s="309" t="n"/>
+      <c r="D2" s="310" t="n"/>
+      <c r="E2" s="35" t="inlineStr">
+        <is>
+          <t>Montag
+Segunda</t>
+        </is>
+      </c>
+      <c r="F2" s="35" t="inlineStr">
+        <is>
+          <t>Dienstag
+Terça</t>
+        </is>
+      </c>
+      <c r="G2" s="35" t="inlineStr">
+        <is>
+          <t>Mittwoch
+Quarta</t>
+        </is>
+      </c>
+      <c r="H2" s="35" t="inlineStr">
+        <is>
+          <t>Donnerstag
+Quinta</t>
+        </is>
+      </c>
+      <c r="I2" s="35" t="inlineStr">
+        <is>
+          <t>Freitag
+Sexta</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>Samstag
+Sábado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customFormat="1" customHeight="1" s="4">
+      <c r="A3" s="137" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="139" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C3" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="125">
+        <f>B3+4</f>
+        <v/>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Fach | Lehrkraft</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Matéria | Prof.</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="62" t="n"/>
+      <c r="J3" s="183" t="n"/>
+      <c r="K3" s="9" t="n"/>
+      <c r="L3" s="222" t="inlineStr">
+        <is>
+          <t>Fach | Lehrkraft</t>
+        </is>
+      </c>
+      <c r="M3" s="222" t="inlineStr">
+        <is>
+          <t>Matéria | Prof.</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="n"/>
+    </row>
+    <row r="4" ht="14.25" customFormat="1" customHeight="1" s="4">
+      <c r="A4" s="311" t="n"/>
+      <c r="B4" s="312" t="n"/>
+      <c r="C4" s="313" t="n"/>
+      <c r="D4" s="314" t="n"/>
+      <c r="E4" s="222" t="inlineStr">
+        <is>
+          <t>Raumwunsch</t>
+        </is>
+      </c>
+      <c r="F4" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Solicitação Sala</t>
+        </is>
+      </c>
+      <c r="G4" s="222" t="n"/>
+      <c r="H4" s="222" t="n"/>
+      <c r="I4" s="63" t="n"/>
+      <c r="J4" s="315" t="n"/>
+      <c r="K4" s="9" t="n"/>
+      <c r="L4" s="222" t="inlineStr">
+        <is>
+          <t>Raumwunsch</t>
+        </is>
+      </c>
+      <c r="M4" s="222" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Solicitação Sala</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="n"/>
+    </row>
+    <row r="5" customFormat="1" s="4">
+      <c r="A5" s="311" t="n"/>
+      <c r="B5" s="312" t="n"/>
+      <c r="C5" s="313" t="n"/>
+      <c r="D5" s="314" t="n"/>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>U-Stunden</t>
+        </is>
+      </c>
+      <c r="F5" s="222" t="inlineStr">
+        <is>
+          <t>Horário</t>
+        </is>
+      </c>
+      <c r="G5" s="222" t="n"/>
+      <c r="H5" s="222" t="n"/>
+      <c r="I5" s="63" t="n"/>
+      <c r="J5" s="315" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="222" t="inlineStr">
+        <is>
+          <t>U-Stunden</t>
+        </is>
+      </c>
+      <c r="M5" s="222" t="inlineStr">
+        <is>
+          <t>Horário</t>
+        </is>
+      </c>
+      <c r="N5" s="15" t="n"/>
+    </row>
+    <row r="6" customFormat="1" s="4">
+      <c r="A6" s="119">
+        <f>A3+1</f>
+        <v/>
+      </c>
+      <c r="B6" s="121">
+        <f>D3+3</f>
+        <v/>
+      </c>
+      <c r="C6" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="125">
+        <f>B6+4</f>
+        <v/>
+      </c>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="183" t="n"/>
+      <c r="K6" s="1" t="n"/>
+      <c r="L6" s="15" t="n"/>
+      <c r="M6" s="15" t="n"/>
+      <c r="N6" s="15" t="n"/>
+    </row>
+    <row r="7" ht="14.25" customFormat="1" customHeight="1" s="4">
+      <c r="A7" s="316" t="n"/>
+      <c r="B7" s="313" t="n"/>
+      <c r="C7" s="313" t="n"/>
+      <c r="D7" s="314" t="n"/>
+      <c r="E7" s="222" t="n"/>
+      <c r="F7" s="222" t="n"/>
+      <c r="G7" s="222" t="n"/>
+      <c r="H7" s="222" t="n"/>
+      <c r="I7" s="222" t="n"/>
+      <c r="J7" s="315" t="n"/>
+      <c r="K7" s="1" t="n"/>
+      <c r="L7" s="15" t="n"/>
+      <c r="M7" s="15" t="n"/>
+      <c r="N7" s="15" t="n"/>
+    </row>
+    <row r="8" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A8" s="316" t="n"/>
+      <c r="B8" s="313" t="n"/>
+      <c r="C8" s="313" t="n"/>
+      <c r="D8" s="314" t="n"/>
+      <c r="E8" s="222" t="n"/>
+      <c r="F8" s="222" t="n"/>
+      <c r="G8" s="222" t="n"/>
+      <c r="H8" s="222" t="n"/>
+      <c r="I8" s="222" t="n"/>
+      <c r="J8" s="315" t="n"/>
+      <c r="K8" s="1" t="n"/>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>Beispiel:</t>
+        </is>
+      </c>
+      <c r="M8" s="33" t="inlineStr">
+        <is>
+          <t>Exemplo:</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="n"/>
+    </row>
+    <row r="9" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A9" s="119">
+        <f>A6+1</f>
+        <v/>
+      </c>
+      <c r="B9" s="121">
+        <f>D6+3</f>
+        <v/>
+      </c>
+      <c r="C9" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="125">
+        <f>B9+4</f>
+        <v/>
+      </c>
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="n"/>
+      <c r="I9" s="183" t="n"/>
+      <c r="J9" s="183" t="n"/>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>Mat | Sal</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>Pgram | Jana</t>
+        </is>
+      </c>
+      <c r="N9" s="15" t="n"/>
+    </row>
+    <row r="10" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A10" s="316" t="n"/>
+      <c r="B10" s="313" t="n"/>
+      <c r="C10" s="313" t="n"/>
+      <c r="D10" s="314" t="n"/>
+      <c r="E10" s="315" t="n"/>
+      <c r="F10" s="315" t="n"/>
+      <c r="G10" s="315" t="n"/>
+      <c r="H10" s="315" t="n"/>
+      <c r="I10" s="315" t="n"/>
+      <c r="J10" s="315" t="n"/>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>Prüfungsraum</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>Sala de Provas</t>
+        </is>
+      </c>
+      <c r="N10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A11" s="316" t="n"/>
+      <c r="B11" s="313" t="n"/>
+      <c r="C11" s="313" t="n"/>
+      <c r="D11" s="314" t="n"/>
+      <c r="E11" s="315" t="n"/>
+      <c r="F11" s="315" t="n"/>
+      <c r="G11" s="315" t="n"/>
+      <c r="H11" s="315" t="n"/>
+      <c r="I11" s="315" t="n"/>
+      <c r="J11" s="315" t="n"/>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>2.-3. Std.</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>2a e 3a aula</t>
+        </is>
+      </c>
+      <c r="N11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A12" s="119">
+        <f>A9+1</f>
+        <v/>
+      </c>
+      <c r="B12" s="121">
+        <f>D9+3</f>
+        <v/>
+      </c>
+      <c r="C12" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="125">
+        <f>B12+4</f>
+        <v/>
+      </c>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="418" t="inlineStr">
+        <is>
+          <t>S3-11
+2º ao 7º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="418" t="inlineStr">
+        <is>
+          <t>S3-11
+2º ao 7º tempos</t>
+        </is>
+      </c>
+      <c r="H12" s="409" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="183" t="n"/>
+      <c r="L12" s="15" t="n"/>
+      <c r="M12" s="15" t="n"/>
+      <c r="N12" s="15" t="n"/>
+      <c r="O12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A13" s="316" t="n"/>
+      <c r="B13" s="313" t="n"/>
+      <c r="C13" s="313" t="n"/>
+      <c r="D13" s="314" t="n"/>
+      <c r="E13" s="222" t="n"/>
+      <c r="F13" s="406" t="n"/>
+      <c r="G13" s="406" t="n"/>
+      <c r="H13" s="406" t="n"/>
+      <c r="I13" s="222" t="n"/>
+      <c r="J13" s="315" t="n"/>
+      <c r="L13" s="15" t="n"/>
+      <c r="M13" s="15" t="n"/>
+      <c r="N13" s="15" t="n"/>
+      <c r="O13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A14" s="316" t="n"/>
+      <c r="B14" s="313" t="n"/>
+      <c r="C14" s="313" t="n"/>
+      <c r="D14" s="314" t="n"/>
+      <c r="E14" s="222" t="n"/>
+      <c r="F14" s="407" t="n"/>
+      <c r="G14" s="407" t="n"/>
+      <c r="H14" s="407" t="n"/>
+      <c r="I14" s="222" t="n"/>
+      <c r="J14" s="315" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="n"/>
+      <c r="N14" s="15" t="n"/>
+      <c r="O14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A15" s="119">
+        <f>A12+1</f>
+        <v/>
+      </c>
+      <c r="B15" s="121">
+        <f>D12+3</f>
+        <v/>
+      </c>
+      <c r="C15" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="125">
+        <f>B15+4</f>
+        <v/>
+      </c>
+      <c r="E15" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="403" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+9º ao 11º tempos</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="183" t="n"/>
+      <c r="L15" s="17" t="n"/>
+      <c r="M15" s="15" t="n"/>
+      <c r="N15" s="15" t="n"/>
+    </row>
+    <row r="16" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A16" s="316" t="n"/>
+      <c r="B16" s="313" t="n"/>
+      <c r="C16" s="313" t="n"/>
+      <c r="D16" s="314" t="n"/>
+      <c r="E16" s="406" t="n"/>
+      <c r="F16" s="406" t="n"/>
+      <c r="G16" s="222" t="n"/>
+      <c r="H16" s="406" t="n"/>
+      <c r="I16" s="222" t="n"/>
+      <c r="J16" s="315" t="n"/>
+      <c r="L16" s="141" t="n"/>
+      <c r="M16" s="317" t="n"/>
+      <c r="N16" s="317" t="n"/>
+      <c r="P16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A17" s="316" t="n"/>
+      <c r="B17" s="313" t="n"/>
+      <c r="C17" s="313" t="n"/>
+      <c r="D17" s="314" t="n"/>
+      <c r="E17" s="407" t="n"/>
+      <c r="F17" s="407" t="n"/>
+      <c r="G17" s="222" t="n"/>
+      <c r="H17" s="407" t="n"/>
+      <c r="I17" s="222" t="n"/>
+      <c r="J17" s="315" t="n"/>
+      <c r="L17" s="317" t="n"/>
+      <c r="M17" s="317" t="n"/>
+      <c r="N17" s="317" t="n"/>
+    </row>
+    <row r="18" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A18" s="119">
+        <f>A15+1</f>
+        <v/>
+      </c>
+      <c r="B18" s="121">
+        <f>D15+3</f>
+        <v/>
+      </c>
+      <c r="C18" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="125">
+        <f>B18+4</f>
+        <v/>
+      </c>
+      <c r="E18" s="183" t="inlineStr">
+        <is>
+          <t>unterrichtsfrei sem aula</t>
+        </is>
+      </c>
+      <c r="F18" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="411" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="431" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="J18" s="183" t="n"/>
+      <c r="L18" s="17" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A19" s="316" t="n"/>
+      <c r="B19" s="313" t="n"/>
+      <c r="C19" s="313" t="n"/>
+      <c r="D19" s="314" t="n"/>
+      <c r="E19" s="315" t="n"/>
+      <c r="F19" s="406" t="n"/>
+      <c r="G19" s="406" t="n"/>
+      <c r="H19" s="222" t="n"/>
+      <c r="I19" s="383" t="n"/>
+      <c r="J19" s="315" t="n"/>
+      <c r="L19" s="29" t="inlineStr">
+        <is>
+          <t>07.08</t>
+        </is>
+      </c>
+      <c r="M19" s="264" t="inlineStr">
+        <is>
+          <t>2,3 TLS turmas 10 palestra sobre ADOLESENCIA E COMPORTAMENTOS DE RISCO</t>
+        </is>
+      </c>
+      <c r="N19" s="317" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A20" s="316" t="n"/>
+      <c r="B20" s="313" t="n"/>
+      <c r="C20" s="313" t="n"/>
+      <c r="D20" s="314" t="n"/>
+      <c r="E20" s="315" t="n"/>
+      <c r="F20" s="407" t="n"/>
+      <c r="G20" s="407" t="n"/>
+      <c r="H20" s="222" t="n"/>
+      <c r="I20" s="384" t="n"/>
+      <c r="J20" s="315" t="n"/>
+      <c r="L20" s="29" t="n"/>
+      <c r="M20" s="29" t="n"/>
+      <c r="N20" s="29" t="n"/>
+    </row>
+    <row r="21" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A21" s="119">
+        <f>A18+1</f>
+        <v/>
+      </c>
+      <c r="B21" s="121">
+        <f>D18+3</f>
+        <v/>
+      </c>
+      <c r="C21" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="125">
+        <f>B21+4</f>
+        <v/>
+      </c>
+      <c r="E21" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="405" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H21" s="420" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="262" t="inlineStr">
+        <is>
+          <t>2CH 9,10,11,12</t>
+        </is>
+      </c>
+      <c r="L21" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15.09 </t>
+        </is>
+      </c>
+      <c r="M21" s="80" t="inlineStr">
+        <is>
+          <t>Cartas Azuis</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A22" s="316" t="n"/>
+      <c r="B22" s="313" t="n"/>
+      <c r="C22" s="313" t="n"/>
+      <c r="D22" s="314" t="n"/>
+      <c r="E22" s="406" t="n"/>
+      <c r="F22" s="63" t="n"/>
+      <c r="G22" s="406" t="n"/>
+      <c r="H22" s="406" t="n"/>
+      <c r="I22" s="222" t="n"/>
+      <c r="J22" s="315" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="M22" s="18" t="n"/>
+      <c r="N22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A23" s="316" t="n"/>
+      <c r="B23" s="313" t="n"/>
+      <c r="C23" s="313" t="n"/>
+      <c r="D23" s="314" t="n"/>
+      <c r="E23" s="407" t="n"/>
+      <c r="F23" s="63" t="n"/>
+      <c r="G23" s="407" t="n"/>
+      <c r="H23" s="407" t="n"/>
+      <c r="I23" s="222" t="n"/>
+      <c r="J23" s="315" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="15" t="n"/>
+    </row>
+    <row r="24" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A24" s="119">
+        <f>A21+1</f>
+        <v/>
+      </c>
+      <c r="B24" s="121">
+        <f>D21+3</f>
+        <v/>
+      </c>
+      <c r="C24" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="203">
+        <f>B24+4</f>
+        <v/>
+      </c>
+      <c r="E24" s="283" t="n"/>
+      <c r="F24" s="283" t="n"/>
+      <c r="G24" s="428" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
+      <c r="H24" s="283" t="n"/>
+      <c r="I24" s="78" t="n"/>
+      <c r="J24" s="265" t="n"/>
+      <c r="L24" s="318" t="inlineStr">
+        <is>
+          <t>Nur Segmentleitung: Folgende Termine markieren:</t>
+        </is>
+      </c>
+      <c r="M24" s="319" t="n"/>
+      <c r="N24" s="320" t="n"/>
+    </row>
+    <row r="25" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A25" s="316" t="n"/>
+      <c r="B25" s="313" t="n"/>
+      <c r="C25" s="313" t="n"/>
+      <c r="D25" s="350" t="n"/>
+      <c r="E25" s="283" t="n"/>
+      <c r="F25" s="283" t="n"/>
+      <c r="G25" s="415" t="n"/>
+      <c r="H25" s="283" t="n"/>
+      <c r="I25" s="78" t="n"/>
+      <c r="J25" s="352" t="n"/>
+      <c r="L25" s="44" t="n"/>
+      <c r="M25" s="321" t="inlineStr">
+        <is>
+          <t>unterrichtsfrei | sem aula</t>
+        </is>
+      </c>
+      <c r="N25" s="322" t="n"/>
+    </row>
+    <row r="26" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A26" s="316" t="n"/>
+      <c r="B26" s="313" t="n"/>
+      <c r="C26" s="313" t="n"/>
+      <c r="D26" s="350" t="n"/>
+      <c r="E26" s="283" t="n"/>
+      <c r="F26" s="283" t="n"/>
+      <c r="G26" s="416" t="n"/>
+      <c r="H26" s="283" t="n"/>
+      <c r="I26" s="78" t="n"/>
+      <c r="J26" s="352" t="n"/>
+      <c r="L26" s="43" t="n"/>
+      <c r="M26" s="323" t="inlineStr">
+        <is>
+          <t>Nachschreibtermine | Segunda Chamada</t>
+        </is>
+      </c>
+      <c r="N26" s="324" t="n"/>
+    </row>
+    <row r="27" ht="30.75" customFormat="1" customHeight="1" s="4">
+      <c r="A27" s="119">
+        <f>A24+1</f>
+        <v/>
+      </c>
+      <c r="B27" s="121">
+        <f>D24+3</f>
+        <v/>
+      </c>
+      <c r="C27" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="203">
+        <f>B27+4</f>
+        <v/>
+      </c>
+      <c r="E27" s="78" t="n"/>
+      <c r="F27" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+8º ao 10º tempos</t>
+        </is>
+      </c>
+      <c r="G27" s="283" t="n"/>
+      <c r="H27" s="283" t="n"/>
+      <c r="I27" s="283" t="n"/>
+      <c r="J27" s="265" t="n"/>
+      <c r="L27" s="45" t="n"/>
+      <c r="M27" s="323" t="inlineStr">
+        <is>
+          <t>Klassenfahrten | Viagem da Turma</t>
+        </is>
+      </c>
+      <c r="N27" s="324" t="n"/>
+    </row>
+    <row r="28" customFormat="1" s="4">
+      <c r="A28" s="316" t="n"/>
+      <c r="B28" s="313" t="n"/>
+      <c r="C28" s="313" t="n"/>
+      <c r="D28" s="350" t="n"/>
+      <c r="E28" s="78" t="n"/>
+      <c r="F28" s="406" t="n"/>
+      <c r="G28" s="283" t="n"/>
+      <c r="H28" s="283" t="n"/>
+      <c r="I28" s="283" t="n"/>
+      <c r="J28" s="352" t="n"/>
+      <c r="L28" s="23" t="n"/>
+      <c r="M28" s="325" t="inlineStr">
+        <is>
+          <t>Woche der dt. Sprache | Semana da língua alemã</t>
+        </is>
+      </c>
+      <c r="N28" s="326" t="n"/>
+    </row>
+    <row r="29" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A29" s="316" t="n"/>
+      <c r="B29" s="313" t="n"/>
+      <c r="C29" s="313" t="n"/>
+      <c r="D29" s="350" t="n"/>
+      <c r="E29" s="78" t="n"/>
+      <c r="F29" s="407" t="n"/>
+      <c r="G29" s="283" t="n"/>
+      <c r="H29" s="283" t="n"/>
+      <c r="I29" s="283" t="n"/>
+      <c r="J29" s="352" t="n"/>
+      <c r="L29" s="46" t="n"/>
+      <c r="M29" s="157" t="inlineStr">
+        <is>
+          <t>Schulsamstag | Sábado letivo</t>
+        </is>
+      </c>
+      <c r="N29" s="327" t="n"/>
+    </row>
+    <row r="30" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A30" s="119">
+        <f>A27+1</f>
+        <v/>
+      </c>
+      <c r="B30" s="121">
+        <f>D27+3</f>
+        <v/>
+      </c>
+      <c r="C30" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="203">
+        <f>B30+4</f>
+        <v/>
+      </c>
+      <c r="E30" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
+      <c r="G30" s="283" t="n"/>
+      <c r="H30" s="283" t="n"/>
+      <c r="I30" s="283" t="n"/>
+      <c r="J30" s="183" t="inlineStr">
+        <is>
+          <t>unterrichtsfrei sem aula</t>
+        </is>
+      </c>
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="25" t="inlineStr">
+        <is>
+          <t>Schriftliches Abitur | Abitur escrito</t>
+        </is>
+      </c>
+      <c r="N30" s="26" t="n"/>
+    </row>
+    <row r="31" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A31" s="316" t="n"/>
+      <c r="B31" s="313" t="n"/>
+      <c r="C31" s="313" t="n"/>
+      <c r="D31" s="350" t="n"/>
+      <c r="E31" s="406" t="n"/>
+      <c r="F31" s="283" t="n"/>
+      <c r="G31" s="283" t="n"/>
+      <c r="H31" s="283" t="n"/>
+      <c r="I31" s="283" t="n"/>
+      <c r="J31" s="315" t="n"/>
+      <c r="L31" s="27" t="n"/>
+      <c r="M31" s="328" t="inlineStr">
+        <is>
+          <t>Mündliches Abitur |Abitur oral</t>
+        </is>
+      </c>
+      <c r="N31" s="329" t="n"/>
+    </row>
+    <row r="32" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A32" s="316" t="n"/>
+      <c r="B32" s="313" t="n"/>
+      <c r="C32" s="313" t="n"/>
+      <c r="D32" s="350" t="n"/>
+      <c r="E32" s="407" t="n"/>
+      <c r="F32" s="283" t="n"/>
+      <c r="G32" s="283" t="n"/>
+      <c r="H32" s="283" t="n"/>
+      <c r="I32" s="283" t="n"/>
+      <c r="J32" s="315" t="n"/>
+      <c r="L32" s="28" t="n"/>
+      <c r="M32" s="15" t="n"/>
+      <c r="N32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="22.5" customFormat="1" customHeight="1" s="4">
+      <c r="A33" s="127">
+        <f>A30+1</f>
+        <v/>
+      </c>
+      <c r="B33" s="129">
+        <f>D30+3</f>
+        <v/>
+      </c>
+      <c r="C33" s="132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="266">
+        <f>B33+4</f>
+        <v/>
+      </c>
+      <c r="E33" s="183" t="inlineStr">
+        <is>
+          <t>unterrichtsfrei sem aula</t>
+        </is>
+      </c>
+      <c r="F33" s="183" t="inlineStr">
+        <is>
+          <t>unterrichtsfrei sem aula</t>
+        </is>
+      </c>
+      <c r="G33" s="183" t="inlineStr">
+        <is>
+          <t>unterrichtsfrei sem aula</t>
+        </is>
+      </c>
+      <c r="H33" s="183" t="inlineStr">
+        <is>
+          <t>unterrichtsfrei sem aula</t>
+        </is>
+      </c>
+      <c r="I33" s="183" t="inlineStr">
+        <is>
+          <t>unterrichtsfrei sem aula</t>
+        </is>
+      </c>
+      <c r="J33" s="183" t="inlineStr">
+        <is>
+          <t>unterrichtsfrei sem aula</t>
+        </is>
+      </c>
+      <c r="L33" s="15" t="inlineStr">
+        <is>
+          <t>DATAS IMPORTANTES</t>
+        </is>
+      </c>
+      <c r="M33" s="15" t="n"/>
+      <c r="N33" s="29" t="n"/>
+    </row>
+    <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
+      <c r="A34" s="330" t="n"/>
+      <c r="B34" s="331" t="n"/>
+      <c r="D34" s="366" t="n"/>
+      <c r="E34" s="315" t="n"/>
+      <c r="F34" s="315" t="n"/>
+      <c r="G34" s="315" t="n"/>
+      <c r="H34" s="315" t="n"/>
+      <c r="I34" s="315" t="n"/>
+      <c r="J34" s="315" t="n"/>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>13.05</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="N34" s="161" t="n"/>
+    </row>
+    <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A35" s="330" t="n"/>
+      <c r="B35" s="332" t="n"/>
+      <c r="D35" s="385" t="n"/>
+      <c r="E35" s="315" t="n"/>
+      <c r="F35" s="315" t="n"/>
+      <c r="G35" s="315" t="n"/>
+      <c r="H35" s="315" t="n"/>
+      <c r="I35" s="315" t="n"/>
+      <c r="J35" s="315" t="n"/>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>27.04</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>LANÇAMENTO DE NOTAS NO PORTAL</t>
+        </is>
+      </c>
+      <c r="N35" s="15" t="n"/>
+    </row>
+    <row r="36" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A36" s="119">
+        <f>A33+1</f>
+        <v/>
+      </c>
+      <c r="B36" s="121">
+        <f>D33+3</f>
+        <v/>
+      </c>
+      <c r="C36" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="203">
+        <f>B36+4</f>
+        <v/>
+      </c>
+      <c r="E36" s="408" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F36" s="403" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
+      <c r="H36" s="283" t="n"/>
+      <c r="I36" s="426" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
+      <c r="J36" s="265" t="n"/>
+      <c r="L36" s="81" t="inlineStr">
+        <is>
+          <t>11.10 E 15.10</t>
+        </is>
+      </c>
+      <c r="M36" s="81" t="inlineStr">
+        <is>
+          <t>PROVAS DA PUC</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A37" s="316" t="n"/>
+      <c r="B37" s="313" t="n"/>
+      <c r="C37" s="313" t="n"/>
+      <c r="D37" s="350" t="n"/>
+      <c r="E37" s="406" t="n"/>
+      <c r="F37" s="406" t="n"/>
+      <c r="G37" s="283" t="n"/>
+      <c r="H37" s="283" t="n"/>
+      <c r="I37" s="406" t="n"/>
+      <c r="J37" s="352" t="n"/>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>18.08,19.08</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>curso para representantes de turmas 9,10,11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A38" s="316" t="n"/>
+      <c r="B38" s="313" t="n"/>
+      <c r="C38" s="313" t="n"/>
+      <c r="D38" s="350" t="n"/>
+      <c r="E38" s="407" t="n"/>
+      <c r="F38" s="407" t="n"/>
+      <c r="G38" s="283" t="n"/>
+      <c r="H38" s="283" t="n"/>
+      <c r="I38" s="407" t="n"/>
+      <c r="J38" s="352" t="n"/>
+    </row>
+    <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A39" s="119">
+        <f>A36+1</f>
+        <v/>
+      </c>
+      <c r="B39" s="121">
+        <f>D36+3</f>
+        <v/>
+      </c>
+      <c r="C39" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D39" s="203">
+        <f>B39+4</f>
+        <v/>
+      </c>
+      <c r="E39" s="418" t="inlineStr">
+        <is>
+          <t>S4-11
+2º ao 7º tempos</t>
+        </is>
+      </c>
+      <c r="F39" s="418" t="inlineStr">
+        <is>
+          <t>S4-11
+2º ao 7º tempos</t>
+        </is>
+      </c>
+      <c r="G39" s="411" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H39" s="283" t="n"/>
+      <c r="I39" s="283" t="n"/>
+      <c r="J39" s="265" t="n"/>
+    </row>
+    <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A40" s="316" t="n"/>
+      <c r="B40" s="313" t="n"/>
+      <c r="C40" s="313" t="n"/>
+      <c r="D40" s="350" t="n"/>
+      <c r="E40" s="406" t="n"/>
+      <c r="F40" s="406" t="n"/>
+      <c r="G40" s="406" t="n"/>
+      <c r="H40" s="283" t="n"/>
+      <c r="I40" s="283" t="n"/>
+      <c r="J40" s="352" t="n"/>
+    </row>
+    <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A41" s="316" t="n"/>
+      <c r="B41" s="313" t="n"/>
+      <c r="C41" s="313" t="n"/>
+      <c r="D41" s="350" t="n"/>
+      <c r="E41" s="407" t="n"/>
+      <c r="F41" s="407" t="n"/>
+      <c r="G41" s="407" t="n"/>
+      <c r="H41" s="283" t="n"/>
+      <c r="I41" s="283" t="n"/>
+      <c r="J41" s="352" t="n"/>
+    </row>
+    <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A42" s="119">
+        <f>A39+1</f>
+        <v/>
+      </c>
+      <c r="B42" s="121">
+        <f>D39+3</f>
+        <v/>
+      </c>
+      <c r="C42" s="123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D42" s="203">
+        <f>B42+4</f>
+        <v/>
+      </c>
+      <c r="E42" s="283" t="n"/>
+      <c r="F42" s="283" t="n"/>
+      <c r="G42" s="409" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
+      <c r="I42" s="283" t="n"/>
+      <c r="J42" s="265" t="n"/>
+      <c r="L42" s="259" t="inlineStr">
+        <is>
+          <t>ENEM
+08.11,15.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A43" s="316" t="n"/>
+      <c r="B43" s="313" t="n"/>
+      <c r="C43" s="313" t="n"/>
+      <c r="D43" s="350" t="n"/>
+      <c r="E43" s="283" t="n"/>
+      <c r="F43" s="283" t="n"/>
+      <c r="G43" s="406" t="n"/>
+      <c r="H43" s="283" t="n"/>
+      <c r="I43" s="283" t="n"/>
+      <c r="J43" s="352" t="n"/>
+      <c r="L43" s="331" t="n"/>
+    </row>
+    <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A44" s="316" t="n"/>
+      <c r="B44" s="313" t="n"/>
+      <c r="C44" s="313" t="n"/>
+      <c r="D44" s="350" t="n"/>
+      <c r="E44" s="283" t="n"/>
+      <c r="F44" s="283" t="n"/>
+      <c r="G44" s="407" t="n"/>
+      <c r="H44" s="283" t="n"/>
+      <c r="I44" s="283" t="n"/>
+      <c r="J44" s="352" t="n"/>
+      <c r="L44" s="331" t="n"/>
+    </row>
+    <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A45" s="119">
+        <f>A42+1</f>
+        <v/>
+      </c>
+      <c r="B45" s="121">
+        <f>D42+3</f>
+        <v/>
+      </c>
+      <c r="C45" s="162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="203">
+        <f>B45+4</f>
+        <v/>
+      </c>
+      <c r="E45" s="283" t="n"/>
+      <c r="F45" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G45" s="405" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="n"/>
+      <c r="I45" s="386" t="n"/>
+      <c r="J45" s="269" t="n"/>
+      <c r="L45" s="331" t="n"/>
+    </row>
+    <row r="46" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A46" s="316" t="n"/>
+      <c r="B46" s="313" t="n"/>
+      <c r="C46" s="313" t="n"/>
+      <c r="D46" s="350" t="n"/>
+      <c r="E46" s="283" t="n"/>
+      <c r="F46" s="406" t="n"/>
+      <c r="G46" s="406" t="n"/>
+      <c r="H46" s="283" t="n"/>
+      <c r="I46" s="351" t="n"/>
+      <c r="J46" s="352" t="n"/>
+      <c r="L46" s="331" t="n"/>
+    </row>
+    <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A47" s="316" t="n"/>
+      <c r="B47" s="313" t="n"/>
+      <c r="C47" s="313" t="n"/>
+      <c r="D47" s="350" t="n"/>
+      <c r="E47" s="283" t="n"/>
+      <c r="F47" s="407" t="n"/>
+      <c r="G47" s="407" t="n"/>
+      <c r="H47" s="283" t="n"/>
+      <c r="I47" s="387" t="n"/>
+      <c r="J47" s="352" t="n"/>
+      <c r="L47" s="332" t="n"/>
+    </row>
+    <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
+      <c r="A48" s="119">
+        <f>A45+1</f>
+        <v/>
+      </c>
+      <c r="B48" s="121">
+        <f>D45+3</f>
+        <v/>
+      </c>
+      <c r="C48" s="162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="203">
+        <f>B48+4</f>
+        <v/>
+      </c>
+      <c r="E48" s="283" t="n"/>
+      <c r="F48" s="430" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G48" s="283" t="n"/>
+      <c r="H48" s="420" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I48" s="183" t="inlineStr">
+        <is>
+          <t>unterrichtsfrei sem aula</t>
+        </is>
+      </c>
+      <c r="J48" s="276" t="n"/>
+    </row>
+    <row r="49" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A49" s="316" t="n"/>
+      <c r="B49" s="313" t="n"/>
+      <c r="C49" s="313" t="n"/>
+      <c r="D49" s="350" t="n"/>
+      <c r="E49" s="283" t="n"/>
+      <c r="F49" s="351" t="n"/>
+      <c r="G49" s="283" t="n"/>
+      <c r="H49" s="406" t="n"/>
+      <c r="I49" s="315" t="n"/>
+      <c r="J49" s="352" t="n"/>
+    </row>
+    <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A50" s="316" t="n"/>
+      <c r="B50" s="313" t="n"/>
+      <c r="C50" s="313" t="n"/>
+      <c r="D50" s="350" t="n"/>
+      <c r="E50" s="78" t="n"/>
+      <c r="F50" s="387" t="n"/>
+      <c r="G50" s="283" t="n"/>
+      <c r="H50" s="407" t="n"/>
+      <c r="I50" s="315" t="n"/>
+      <c r="J50" s="352" t="n"/>
+    </row>
+    <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A51" s="119">
+        <f>A48+1</f>
+        <v/>
+      </c>
+      <c r="B51" s="121">
+        <f>D48+3</f>
+        <v/>
+      </c>
+      <c r="C51" s="162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="203">
+        <f>B51+4</f>
+        <v/>
+      </c>
+      <c r="E51" s="283" t="n"/>
+      <c r="F51" s="183" t="n"/>
+      <c r="G51" s="183" t="n"/>
+      <c r="H51" s="183" t="n"/>
+      <c r="I51" s="386" t="inlineStr">
+        <is>
+          <t>2CH
+9,11</t>
+        </is>
+      </c>
+      <c r="J51" s="274" t="n"/>
+    </row>
+    <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A52" s="316" t="n"/>
+      <c r="B52" s="313" t="n"/>
+      <c r="C52" s="313" t="n"/>
+      <c r="D52" s="350" t="n"/>
+      <c r="E52" s="283" t="n"/>
+      <c r="F52" s="315" t="n"/>
+      <c r="G52" s="315" t="n"/>
+      <c r="H52" s="315" t="n"/>
+      <c r="I52" s="351" t="n"/>
+      <c r="J52" s="352" t="n"/>
+    </row>
+    <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A53" s="316" t="n"/>
+      <c r="B53" s="313" t="n"/>
+      <c r="C53" s="313" t="n"/>
+      <c r="D53" s="350" t="n"/>
+      <c r="E53" s="283" t="n"/>
+      <c r="F53" s="315" t="n"/>
+      <c r="G53" s="315" t="n"/>
+      <c r="H53" s="315" t="n"/>
+      <c r="I53" s="387" t="n"/>
+      <c r="J53" s="352" t="n"/>
+    </row>
+    <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A54" s="119">
+        <f>A51+1</f>
+        <v/>
+      </c>
+      <c r="B54" s="121">
+        <f>D51+3</f>
+        <v/>
+      </c>
+      <c r="C54" s="162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="203">
+        <f>B54+4</f>
+        <v/>
+      </c>
+      <c r="E54" s="183" t="n"/>
+      <c r="F54" s="183" t="n"/>
+      <c r="G54" s="183" t="n"/>
+      <c r="H54" s="183" t="n"/>
+      <c r="I54" s="183" t="n"/>
+      <c r="J54" s="274" t="n"/>
+    </row>
+    <row r="55" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A55" s="316" t="n"/>
+      <c r="B55" s="313" t="n"/>
+      <c r="C55" s="313" t="n"/>
+      <c r="D55" s="350" t="n"/>
+      <c r="E55" s="315" t="n"/>
+      <c r="F55" s="315" t="n"/>
+      <c r="G55" s="315" t="n"/>
+      <c r="H55" s="315" t="n"/>
+      <c r="I55" s="315" t="n"/>
+      <c r="J55" s="352" t="n"/>
+    </row>
+    <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A56" s="316" t="n"/>
+      <c r="B56" s="313" t="n"/>
+      <c r="C56" s="313" t="n"/>
+      <c r="D56" s="350" t="n"/>
+      <c r="E56" s="315" t="n"/>
+      <c r="F56" s="315" t="n"/>
+      <c r="G56" s="315" t="n"/>
+      <c r="H56" s="315" t="n"/>
+      <c r="I56" s="315" t="n"/>
+      <c r="J56" s="352" t="n"/>
+    </row>
+    <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
+      <c r="A57" s="119">
+        <f>A54+1</f>
+        <v/>
+      </c>
+      <c r="B57" s="121">
+        <f>D54+3</f>
+        <v/>
+      </c>
+      <c r="C57" s="162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="203">
+        <f>B57+4</f>
+        <v/>
+      </c>
+      <c r="E57" s="183" t="n"/>
+      <c r="F57" s="402" t="inlineStr">
+        <is>
+          <t>CC
+9,11</t>
+        </is>
+      </c>
+      <c r="G57" s="183" t="n"/>
+      <c r="H57" s="183" t="n"/>
+      <c r="I57" s="183" t="n"/>
+      <c r="J57" s="265" t="n"/>
+    </row>
+    <row r="58" ht="24" customFormat="1" customHeight="1" s="4">
+      <c r="A58" s="316" t="n"/>
+      <c r="B58" s="313" t="n"/>
+      <c r="C58" s="313" t="n"/>
+      <c r="D58" s="350" t="n"/>
+      <c r="E58" s="315" t="n"/>
+      <c r="F58" s="351" t="n"/>
+      <c r="G58" s="315" t="n"/>
+      <c r="H58" s="315" t="n"/>
+      <c r="I58" s="315" t="n"/>
+      <c r="J58" s="352" t="n"/>
+    </row>
+    <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
+      <c r="A59" s="316" t="n"/>
+      <c r="B59" s="313" t="n"/>
+      <c r="C59" s="313" t="n"/>
+      <c r="D59" s="350" t="n"/>
+      <c r="E59" s="315" t="n"/>
+      <c r="F59" s="387" t="n"/>
+      <c r="G59" s="315" t="n"/>
+      <c r="H59" s="315" t="n"/>
+      <c r="I59" s="315" t="n"/>
+      <c r="J59" s="352" t="n"/>
+    </row>
+    <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A60" s="281">
+        <f>A57+1</f>
+        <v/>
+      </c>
+      <c r="B60" s="131">
+        <f>D57+3</f>
+        <v/>
+      </c>
+      <c r="C60" s="282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="131">
+        <f>B60+4</f>
+        <v/>
+      </c>
+      <c r="E60" s="284" t="n"/>
+      <c r="F60" s="284" t="n"/>
+      <c r="G60" s="284" t="n"/>
+      <c r="H60" s="284" t="n"/>
+      <c r="I60" s="283" t="n"/>
+      <c r="J60" s="283" t="n"/>
+    </row>
+    <row r="61" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A61" s="331" t="n"/>
+      <c r="B61" s="331" t="n"/>
+      <c r="C61" s="331" t="n"/>
+      <c r="D61" s="331" t="n"/>
+      <c r="E61" s="351" t="n"/>
+      <c r="F61" s="351" t="n"/>
+      <c r="G61" s="351" t="n"/>
+      <c r="H61" s="351" t="n"/>
+      <c r="I61" s="351" t="n"/>
+      <c r="J61" s="351" t="n"/>
+    </row>
+    <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
+      <c r="A62" s="332" t="n"/>
+      <c r="B62" s="332" t="n"/>
+      <c r="C62" s="332" t="n"/>
+      <c r="D62" s="332" t="n"/>
+      <c r="E62" s="353" t="n"/>
+      <c r="F62" s="353" t="n"/>
+      <c r="G62" s="353" t="n"/>
+      <c r="H62" s="353" t="n"/>
+      <c r="I62" s="353" t="n"/>
+      <c r="J62" s="353" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="170">
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="I48:I50"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="H54:H56"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="L42:L47"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E60:E62"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="B57:B59"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
@@ -17039,7 +18770,6 @@
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
-    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
@@ -17090,28 +18820,29 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G21:G23"/>
     <mergeCell ref="G12:G14"/>
     <mergeCell ref="E39:E41"/>
+    <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
+    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
-    <mergeCell ref="H39:H41"/>
+    <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="H36:H38"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
-    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="G18:G20"/>
-    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="G24:G26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -17139,1735 +18870,14 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G27:G29"/>
     <mergeCell ref="A39:A41"/>
+    <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="F33:F35"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="J27:J29"/>
-    <mergeCell ref="B2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.4705555555555556" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="64"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:P62"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="0.44140625" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col width="4" customWidth="1" style="2" min="1" max="1"/>
-    <col width="11.5546875" customWidth="1" min="2" max="2"/>
-    <col width="2.88671875" customWidth="1" min="3" max="3"/>
-    <col width="11.33203125" customWidth="1" min="4" max="4"/>
-    <col width="12.109375" customWidth="1" style="3" min="5" max="9"/>
-    <col width="16.5546875" customWidth="1" style="3" min="10" max="10"/>
-    <col width="4.33203125" customWidth="1" min="11" max="11"/>
-    <col width="12.33203125" customWidth="1" min="12" max="12"/>
-    <col width="12.5546875" customWidth="1" min="13" max="13"/>
-    <col width="27.6640625" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="21.33203125" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="35.1" customHeight="1">
-      <c r="A1" s="173" t="inlineStr">
-        <is>
-          <t>Prüfungsplan Klasse 11C2 | Plano das Provas Turma 11C2</t>
-        </is>
-      </c>
-      <c r="B1" s="307" t="n"/>
-      <c r="C1" s="307" t="n"/>
-      <c r="D1" s="307" t="n"/>
-      <c r="E1" s="307" t="n"/>
-      <c r="F1" s="307" t="n"/>
-      <c r="G1" s="307" t="n"/>
-      <c r="H1" s="307" t="n"/>
-      <c r="I1" s="307" t="n"/>
-      <c r="J1" s="67" t="inlineStr">
-        <is>
-          <t>Anzahl SuS |
-Número alunos:19</t>
-        </is>
-      </c>
-      <c r="N1" s="5" t="n"/>
-      <c r="O1" s="5" t="n"/>
-      <c r="P1" s="5" t="n"/>
-    </row>
-    <row r="2" ht="31.5" customFormat="1" customHeight="1" s="4">
-      <c r="A2" s="34" t="inlineStr">
-        <is>
-          <t>SW</t>
-        </is>
-      </c>
-      <c r="B2" s="308" t="inlineStr">
-        <is>
-          <t>Datum von bis</t>
-        </is>
-      </c>
-      <c r="C2" s="309" t="n"/>
-      <c r="D2" s="310" t="n"/>
-      <c r="E2" s="35" t="inlineStr">
-        <is>
-          <t>Montag
-Segunda</t>
-        </is>
-      </c>
-      <c r="F2" s="35" t="inlineStr">
-        <is>
-          <t>Dienstag
-Terça</t>
-        </is>
-      </c>
-      <c r="G2" s="35" t="inlineStr">
-        <is>
-          <t>Mittwoch
-Quarta</t>
-        </is>
-      </c>
-      <c r="H2" s="35" t="inlineStr">
-        <is>
-          <t>Donnerstag
-Quinta</t>
-        </is>
-      </c>
-      <c r="I2" s="35" t="inlineStr">
-        <is>
-          <t>Freitag
-Sexta</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>Samstag
-Sábado</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customFormat="1" customHeight="1" s="4">
-      <c r="A3" s="137" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="139" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C3" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D3" s="125">
-        <f>B3+4</f>
-        <v/>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Fach | Lehrkraft</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Matéria | Prof.</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="62" t="n"/>
-      <c r="J3" s="183" t="n"/>
-      <c r="K3" s="9" t="n"/>
-      <c r="L3" s="222" t="inlineStr">
-        <is>
-          <t>Fach | Lehrkraft</t>
-        </is>
-      </c>
-      <c r="M3" s="222" t="inlineStr">
-        <is>
-          <t>Matéria | Prof.</t>
-        </is>
-      </c>
-      <c r="N3" s="15" t="n"/>
-    </row>
-    <row r="4" ht="14.25" customFormat="1" customHeight="1" s="4">
-      <c r="A4" s="311" t="n"/>
-      <c r="B4" s="312" t="n"/>
-      <c r="C4" s="313" t="n"/>
-      <c r="D4" s="314" t="n"/>
-      <c r="E4" s="222" t="inlineStr">
-        <is>
-          <t>Raumwunsch</t>
-        </is>
-      </c>
-      <c r="F4" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Solicitação Sala</t>
-        </is>
-      </c>
-      <c r="G4" s="222" t="n"/>
-      <c r="H4" s="222" t="n"/>
-      <c r="I4" s="63" t="n"/>
-      <c r="J4" s="315" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="222" t="inlineStr">
-        <is>
-          <t>Raumwunsch</t>
-        </is>
-      </c>
-      <c r="M4" s="222" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Solicitação Sala</t>
-        </is>
-      </c>
-      <c r="N4" s="15" t="n"/>
-    </row>
-    <row r="5" customFormat="1" s="4">
-      <c r="A5" s="311" t="n"/>
-      <c r="B5" s="312" t="n"/>
-      <c r="C5" s="313" t="n"/>
-      <c r="D5" s="314" t="n"/>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>U-Stunden</t>
-        </is>
-      </c>
-      <c r="F5" s="222" t="inlineStr">
-        <is>
-          <t>Horário</t>
-        </is>
-      </c>
-      <c r="G5" s="222" t="n"/>
-      <c r="H5" s="222" t="n"/>
-      <c r="I5" s="63" t="n"/>
-      <c r="J5" s="315" t="n"/>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="222" t="inlineStr">
-        <is>
-          <t>U-Stunden</t>
-        </is>
-      </c>
-      <c r="M5" s="222" t="inlineStr">
-        <is>
-          <t>Horário</t>
-        </is>
-      </c>
-      <c r="N5" s="15" t="n"/>
-    </row>
-    <row r="6" customFormat="1" s="4">
-      <c r="A6" s="119">
-        <f>A3+1</f>
-        <v/>
-      </c>
-      <c r="B6" s="121">
-        <f>D3+3</f>
-        <v/>
-      </c>
-      <c r="C6" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="125">
-        <f>B6+4</f>
-        <v/>
-      </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="183" t="n"/>
-      <c r="K6" s="1" t="n"/>
-      <c r="L6" s="15" t="n"/>
-      <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-    </row>
-    <row r="7" ht="14.25" customFormat="1" customHeight="1" s="4">
-      <c r="A7" s="316" t="n"/>
-      <c r="B7" s="313" t="n"/>
-      <c r="C7" s="313" t="n"/>
-      <c r="D7" s="314" t="n"/>
-      <c r="E7" s="222" t="n"/>
-      <c r="F7" s="222" t="n"/>
-      <c r="G7" s="222" t="n"/>
-      <c r="H7" s="222" t="n"/>
-      <c r="I7" s="222" t="n"/>
-      <c r="J7" s="315" t="n"/>
-      <c r="K7" s="1" t="n"/>
-      <c r="L7" s="15" t="n"/>
-      <c r="M7" s="15" t="n"/>
-      <c r="N7" s="15" t="n"/>
-    </row>
-    <row r="8" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A8" s="316" t="n"/>
-      <c r="B8" s="313" t="n"/>
-      <c r="C8" s="313" t="n"/>
-      <c r="D8" s="314" t="n"/>
-      <c r="E8" s="222" t="n"/>
-      <c r="F8" s="222" t="n"/>
-      <c r="G8" s="222" t="n"/>
-      <c r="H8" s="222" t="n"/>
-      <c r="I8" s="222" t="n"/>
-      <c r="J8" s="315" t="n"/>
-      <c r="K8" s="1" t="n"/>
-      <c r="L8" s="33" t="inlineStr">
-        <is>
-          <t>Beispiel:</t>
-        </is>
-      </c>
-      <c r="M8" s="33" t="inlineStr">
-        <is>
-          <t>Exemplo:</t>
-        </is>
-      </c>
-      <c r="N8" s="15" t="n"/>
-    </row>
-    <row r="9" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A9" s="119">
-        <f>A6+1</f>
-        <v/>
-      </c>
-      <c r="B9" s="121">
-        <f>D6+3</f>
-        <v/>
-      </c>
-      <c r="C9" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="125">
-        <f>B9+4</f>
-        <v/>
-      </c>
-      <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="n"/>
-      <c r="J9" s="183" t="n"/>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>Mat | Sal</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="inlineStr">
-        <is>
-          <t>Pgram | Jana</t>
-        </is>
-      </c>
-      <c r="N9" s="15" t="n"/>
-    </row>
-    <row r="10" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A10" s="316" t="n"/>
-      <c r="B10" s="313" t="n"/>
-      <c r="C10" s="313" t="n"/>
-      <c r="D10" s="314" t="n"/>
-      <c r="E10" s="315" t="n"/>
-      <c r="F10" s="315" t="n"/>
-      <c r="G10" s="315" t="n"/>
-      <c r="H10" s="315" t="n"/>
-      <c r="I10" s="315" t="n"/>
-      <c r="J10" s="315" t="n"/>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>Prüfungsraum</t>
-        </is>
-      </c>
-      <c r="M10" s="16" t="inlineStr">
-        <is>
-          <t>Sala de Provas</t>
-        </is>
-      </c>
-      <c r="N10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A11" s="316" t="n"/>
-      <c r="B11" s="313" t="n"/>
-      <c r="C11" s="313" t="n"/>
-      <c r="D11" s="314" t="n"/>
-      <c r="E11" s="315" t="n"/>
-      <c r="F11" s="315" t="n"/>
-      <c r="G11" s="315" t="n"/>
-      <c r="H11" s="315" t="n"/>
-      <c r="I11" s="315" t="n"/>
-      <c r="J11" s="315" t="n"/>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>2.-3. Std.</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="inlineStr">
-        <is>
-          <t>2a e 3a aula</t>
-        </is>
-      </c>
-      <c r="N11" s="15" t="n"/>
-    </row>
-    <row r="12" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A12" s="119">
-        <f>A9+1</f>
-        <v/>
-      </c>
-      <c r="B12" s="121">
-        <f>D9+3</f>
-        <v/>
-      </c>
-      <c r="C12" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="125">
-        <f>B12+4</f>
-        <v/>
-      </c>
-      <c r="E12" s="409" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="416" t="inlineStr">
-        <is>
-          <t>S3-11
-2º ao 7º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="416" t="inlineStr">
-        <is>
-          <t>S3-11
-2º ao 7º tempos</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="412" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="J12" s="183" t="n"/>
-      <c r="L12" s="15" t="n"/>
-      <c r="M12" s="15" t="n"/>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="7" t="n"/>
-    </row>
-    <row r="13" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A13" s="316" t="n"/>
-      <c r="B13" s="313" t="n"/>
-      <c r="C13" s="313" t="n"/>
-      <c r="D13" s="314" t="n"/>
-      <c r="E13" s="405" t="n"/>
-      <c r="F13" s="405" t="n"/>
-      <c r="G13" s="405" t="n"/>
-      <c r="H13" s="222" t="n"/>
-      <c r="I13" s="405" t="n"/>
-      <c r="J13" s="315" t="n"/>
-      <c r="L13" s="15" t="n"/>
-      <c r="M13" s="15" t="n"/>
-      <c r="N13" s="15" t="n"/>
-      <c r="O13" s="7" t="n"/>
-    </row>
-    <row r="14" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A14" s="316" t="n"/>
-      <c r="B14" s="313" t="n"/>
-      <c r="C14" s="313" t="n"/>
-      <c r="D14" s="314" t="n"/>
-      <c r="E14" s="406" t="n"/>
-      <c r="F14" s="406" t="n"/>
-      <c r="G14" s="406" t="n"/>
-      <c r="H14" s="222" t="n"/>
-      <c r="I14" s="406" t="n"/>
-      <c r="J14" s="315" t="n"/>
-      <c r="L14" s="15" t="n"/>
-      <c r="M14" s="15" t="n"/>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A15" s="119">
-        <f>A12+1</f>
-        <v/>
-      </c>
-      <c r="B15" s="121">
-        <f>D12+3</f>
-        <v/>
-      </c>
-      <c r="C15" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="125">
-        <f>B15+4</f>
-        <v/>
-      </c>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="410" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="403" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="418" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="183" t="n"/>
-      <c r="L15" s="17" t="n"/>
-      <c r="M15" s="15" t="n"/>
-      <c r="N15" s="15" t="n"/>
-    </row>
-    <row r="16" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A16" s="316" t="n"/>
-      <c r="B16" s="313" t="n"/>
-      <c r="C16" s="313" t="n"/>
-      <c r="D16" s="314" t="n"/>
-      <c r="E16" s="222" t="n"/>
-      <c r="F16" s="405" t="n"/>
-      <c r="G16" s="405" t="n"/>
-      <c r="H16" s="405" t="n"/>
-      <c r="I16" s="222" t="n"/>
-      <c r="J16" s="315" t="n"/>
-      <c r="L16" s="141" t="n"/>
-      <c r="M16" s="317" t="n"/>
-      <c r="N16" s="317" t="n"/>
-      <c r="P16" s="8" t="n"/>
-    </row>
-    <row r="17" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A17" s="316" t="n"/>
-      <c r="B17" s="313" t="n"/>
-      <c r="C17" s="313" t="n"/>
-      <c r="D17" s="314" t="n"/>
-      <c r="E17" s="222" t="n"/>
-      <c r="F17" s="406" t="n"/>
-      <c r="G17" s="406" t="n"/>
-      <c r="H17" s="406" t="n"/>
-      <c r="I17" s="222" t="n"/>
-      <c r="J17" s="315" t="n"/>
-      <c r="L17" s="317" t="n"/>
-      <c r="M17" s="317" t="n"/>
-      <c r="N17" s="317" t="n"/>
-    </row>
-    <row r="18" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A18" s="119">
-        <f>A15+1</f>
-        <v/>
-      </c>
-      <c r="B18" s="121">
-        <f>D15+3</f>
-        <v/>
-      </c>
-      <c r="C18" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D18" s="125">
-        <f>B18+4</f>
-        <v/>
-      </c>
-      <c r="E18" s="183" t="inlineStr">
-        <is>
-          <t>unterrichtsfrei sem aula</t>
-        </is>
-      </c>
-      <c r="F18" s="408" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="407" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="382" t="n"/>
-      <c r="J18" s="183" t="n"/>
-      <c r="L18" s="17" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-    </row>
-    <row r="19" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A19" s="316" t="n"/>
-      <c r="B19" s="313" t="n"/>
-      <c r="C19" s="313" t="n"/>
-      <c r="D19" s="314" t="n"/>
-      <c r="E19" s="315" t="n"/>
-      <c r="F19" s="405" t="n"/>
-      <c r="G19" s="405" t="n"/>
-      <c r="H19" s="222" t="n"/>
-      <c r="I19" s="383" t="n"/>
-      <c r="J19" s="315" t="n"/>
-      <c r="L19" s="29" t="inlineStr">
-        <is>
-          <t>07.08</t>
-        </is>
-      </c>
-      <c r="M19" s="264" t="inlineStr">
-        <is>
-          <t>2,3 TLS turmas 10 palestra sobre ADOLESENCIA E COMPORTAMENTOS DE RISCO</t>
-        </is>
-      </c>
-      <c r="N19" s="317" t="n"/>
-    </row>
-    <row r="20" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A20" s="316" t="n"/>
-      <c r="B20" s="313" t="n"/>
-      <c r="C20" s="313" t="n"/>
-      <c r="D20" s="314" t="n"/>
-      <c r="E20" s="315" t="n"/>
-      <c r="F20" s="406" t="n"/>
-      <c r="G20" s="406" t="n"/>
-      <c r="H20" s="222" t="n"/>
-      <c r="I20" s="384" t="n"/>
-      <c r="J20" s="315" t="n"/>
-      <c r="L20" s="29" t="n"/>
-      <c r="M20" s="29" t="n"/>
-      <c r="N20" s="29" t="n"/>
-    </row>
-    <row r="21" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A21" s="119">
-        <f>A18+1</f>
-        <v/>
-      </c>
-      <c r="B21" s="121">
-        <f>D18+3</f>
-        <v/>
-      </c>
-      <c r="C21" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="125">
-        <f>B21+4</f>
-        <v/>
-      </c>
-      <c r="E21" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F21" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="423" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-9º ao 11º tempos</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="262" t="inlineStr">
-        <is>
-          <t>2CH 9,10,11,12</t>
-        </is>
-      </c>
-      <c r="L21" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15.09 </t>
-        </is>
-      </c>
-      <c r="M21" s="80" t="inlineStr">
-        <is>
-          <t>Cartas Azuis</t>
-        </is>
-      </c>
-      <c r="N21" s="15" t="n"/>
-    </row>
-    <row r="22" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A22" s="316" t="n"/>
-      <c r="B22" s="313" t="n"/>
-      <c r="C22" s="313" t="n"/>
-      <c r="D22" s="314" t="n"/>
-      <c r="E22" s="405" t="n"/>
-      <c r="F22" s="405" t="n"/>
-      <c r="G22" s="222" t="n"/>
-      <c r="H22" s="405" t="n"/>
-      <c r="I22" s="222" t="n"/>
-      <c r="J22" s="315" t="n"/>
-      <c r="L22" s="18" t="n"/>
-      <c r="M22" s="18" t="n"/>
-      <c r="N22" s="18" t="n"/>
-    </row>
-    <row r="23" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A23" s="316" t="n"/>
-      <c r="B23" s="313" t="n"/>
-      <c r="C23" s="313" t="n"/>
-      <c r="D23" s="314" t="n"/>
-      <c r="E23" s="406" t="n"/>
-      <c r="F23" s="406" t="n"/>
-      <c r="G23" s="222" t="n"/>
-      <c r="H23" s="406" t="n"/>
-      <c r="I23" s="222" t="n"/>
-      <c r="J23" s="315" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="19" t="n"/>
-      <c r="M23" s="19" t="n"/>
-      <c r="N23" s="15" t="n"/>
-    </row>
-    <row r="24" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A24" s="119">
-        <f>A21+1</f>
-        <v/>
-      </c>
-      <c r="B24" s="121">
-        <f>D21+3</f>
-        <v/>
-      </c>
-      <c r="C24" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="203">
-        <f>B24+4</f>
-        <v/>
-      </c>
-      <c r="E24" s="412" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
-      <c r="I24" s="427" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
-      <c r="J24" s="265" t="n"/>
-      <c r="L24" s="318" t="inlineStr">
-        <is>
-          <t>Nur Segmentleitung: Folgende Termine markieren:</t>
-        </is>
-      </c>
-      <c r="M24" s="319" t="n"/>
-      <c r="N24" s="320" t="n"/>
-    </row>
-    <row r="25" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A25" s="316" t="n"/>
-      <c r="B25" s="313" t="n"/>
-      <c r="C25" s="313" t="n"/>
-      <c r="D25" s="350" t="n"/>
-      <c r="E25" s="405" t="n"/>
-      <c r="F25" s="283" t="n"/>
-      <c r="G25" s="79" t="n"/>
-      <c r="H25" s="283" t="n"/>
-      <c r="I25" s="405" t="n"/>
-      <c r="J25" s="352" t="n"/>
-      <c r="L25" s="44" t="n"/>
-      <c r="M25" s="321" t="inlineStr">
-        <is>
-          <t>unterrichtsfrei | sem aula</t>
-        </is>
-      </c>
-      <c r="N25" s="322" t="n"/>
-    </row>
-    <row r="26" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A26" s="316" t="n"/>
-      <c r="B26" s="313" t="n"/>
-      <c r="C26" s="313" t="n"/>
-      <c r="D26" s="350" t="n"/>
-      <c r="E26" s="406" t="n"/>
-      <c r="F26" s="283" t="n"/>
-      <c r="G26" s="79" t="n"/>
-      <c r="H26" s="283" t="n"/>
-      <c r="I26" s="406" t="n"/>
-      <c r="J26" s="352" t="n"/>
-      <c r="L26" s="43" t="n"/>
-      <c r="M26" s="323" t="inlineStr">
-        <is>
-          <t>Nachschreibtermine | Segunda Chamada</t>
-        </is>
-      </c>
-      <c r="N26" s="324" t="n"/>
-    </row>
-    <row r="27" ht="30.75" customFormat="1" customHeight="1" s="4">
-      <c r="A27" s="119">
-        <f>A24+1</f>
-        <v/>
-      </c>
-      <c r="B27" s="121">
-        <f>D24+3</f>
-        <v/>
-      </c>
-      <c r="C27" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="203">
-        <f>B27+4</f>
-        <v/>
-      </c>
-      <c r="E27" s="78" t="n"/>
-      <c r="F27" s="410" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G27" s="426" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-9º tempo</t>
-        </is>
-      </c>
-      <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="n"/>
-      <c r="J27" s="265" t="n"/>
-      <c r="L27" s="45" t="n"/>
-      <c r="M27" s="323" t="inlineStr">
-        <is>
-          <t>Klassenfahrten | Viagem da Turma</t>
-        </is>
-      </c>
-      <c r="N27" s="324" t="n"/>
-    </row>
-    <row r="28" customFormat="1" s="4">
-      <c r="A28" s="316" t="n"/>
-      <c r="B28" s="313" t="n"/>
-      <c r="C28" s="313" t="n"/>
-      <c r="D28" s="350" t="n"/>
-      <c r="E28" s="78" t="n"/>
-      <c r="F28" s="405" t="n"/>
-      <c r="G28" s="405" t="n"/>
-      <c r="H28" s="283" t="n"/>
-      <c r="I28" s="283" t="n"/>
-      <c r="J28" s="352" t="n"/>
-      <c r="L28" s="23" t="n"/>
-      <c r="M28" s="325" t="inlineStr">
-        <is>
-          <t>Woche der dt. Sprache | Semana da língua alemã</t>
-        </is>
-      </c>
-      <c r="N28" s="326" t="n"/>
-    </row>
-    <row r="29" ht="15.75" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A29" s="316" t="n"/>
-      <c r="B29" s="313" t="n"/>
-      <c r="C29" s="313" t="n"/>
-      <c r="D29" s="350" t="n"/>
-      <c r="E29" s="78" t="n"/>
-      <c r="F29" s="406" t="n"/>
-      <c r="G29" s="406" t="n"/>
-      <c r="H29" s="283" t="n"/>
-      <c r="I29" s="283" t="n"/>
-      <c r="J29" s="352" t="n"/>
-      <c r="L29" s="46" t="n"/>
-      <c r="M29" s="157" t="inlineStr">
-        <is>
-          <t>Schulsamstag | Sábado letivo</t>
-        </is>
-      </c>
-      <c r="N29" s="327" t="n"/>
-    </row>
-    <row r="30" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A30" s="119">
-        <f>A27+1</f>
-        <v/>
-      </c>
-      <c r="B30" s="121">
-        <f>D27+3</f>
-        <v/>
-      </c>
-      <c r="C30" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="203">
-        <f>B30+4</f>
-        <v/>
-      </c>
-      <c r="E30" s="407" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
-      <c r="J30" s="183" t="inlineStr">
-        <is>
-          <t>unterrichtsfrei sem aula</t>
-        </is>
-      </c>
-      <c r="L30" s="22" t="n"/>
-      <c r="M30" s="25" t="inlineStr">
-        <is>
-          <t>Schriftliches Abitur | Abitur escrito</t>
-        </is>
-      </c>
-      <c r="N30" s="26" t="n"/>
-    </row>
-    <row r="31" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A31" s="316" t="n"/>
-      <c r="B31" s="313" t="n"/>
-      <c r="C31" s="313" t="n"/>
-      <c r="D31" s="350" t="n"/>
-      <c r="E31" s="405" t="n"/>
-      <c r="F31" s="283" t="n"/>
-      <c r="G31" s="283" t="n"/>
-      <c r="H31" s="283" t="n"/>
-      <c r="I31" s="283" t="n"/>
-      <c r="J31" s="315" t="n"/>
-      <c r="L31" s="27" t="n"/>
-      <c r="M31" s="328" t="inlineStr">
-        <is>
-          <t>Mündliches Abitur |Abitur oral</t>
-        </is>
-      </c>
-      <c r="N31" s="329" t="n"/>
-    </row>
-    <row r="32" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A32" s="316" t="n"/>
-      <c r="B32" s="313" t="n"/>
-      <c r="C32" s="313" t="n"/>
-      <c r="D32" s="350" t="n"/>
-      <c r="E32" s="406" t="n"/>
-      <c r="F32" s="283" t="n"/>
-      <c r="G32" s="283" t="n"/>
-      <c r="H32" s="283" t="n"/>
-      <c r="I32" s="283" t="n"/>
-      <c r="J32" s="315" t="n"/>
-      <c r="L32" s="28" t="n"/>
-      <c r="M32" s="15" t="n"/>
-      <c r="N32" s="15" t="n"/>
-    </row>
-    <row r="33" ht="22.5" customFormat="1" customHeight="1" s="4">
-      <c r="A33" s="127">
-        <f>A30+1</f>
-        <v/>
-      </c>
-      <c r="B33" s="129">
-        <f>D30+3</f>
-        <v/>
-      </c>
-      <c r="C33" s="132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D33" s="266">
-        <f>B33+4</f>
-        <v/>
-      </c>
-      <c r="E33" s="183" t="inlineStr">
-        <is>
-          <t>unterrichtsfrei sem aula</t>
-        </is>
-      </c>
-      <c r="F33" s="183" t="inlineStr">
-        <is>
-          <t>unterrichtsfrei sem aula</t>
-        </is>
-      </c>
-      <c r="G33" s="183" t="inlineStr">
-        <is>
-          <t>unterrichtsfrei sem aula</t>
-        </is>
-      </c>
-      <c r="H33" s="183" t="inlineStr">
-        <is>
-          <t>unterrichtsfrei sem aula</t>
-        </is>
-      </c>
-      <c r="I33" s="183" t="inlineStr">
-        <is>
-          <t>unterrichtsfrei sem aula</t>
-        </is>
-      </c>
-      <c r="J33" s="183" t="inlineStr">
-        <is>
-          <t>unterrichtsfrei sem aula</t>
-        </is>
-      </c>
-      <c r="L33" s="15" t="inlineStr">
-        <is>
-          <t>DATAS IMPORTANTES</t>
-        </is>
-      </c>
-      <c r="M33" s="15" t="n"/>
-      <c r="N33" s="29" t="n"/>
-    </row>
-    <row r="34" ht="26.25" customFormat="1" customHeight="1" s="4">
-      <c r="A34" s="330" t="n"/>
-      <c r="B34" s="331" t="n"/>
-      <c r="D34" s="366" t="n"/>
-      <c r="E34" s="315" t="n"/>
-      <c r="F34" s="315" t="n"/>
-      <c r="G34" s="315" t="n"/>
-      <c r="H34" s="315" t="n"/>
-      <c r="I34" s="315" t="n"/>
-      <c r="J34" s="315" t="n"/>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>13.05</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="N34" s="161" t="n"/>
-    </row>
-    <row r="35" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A35" s="330" t="n"/>
-      <c r="B35" s="332" t="n"/>
-      <c r="D35" s="385" t="n"/>
-      <c r="E35" s="315" t="n"/>
-      <c r="F35" s="315" t="n"/>
-      <c r="G35" s="315" t="n"/>
-      <c r="H35" s="315" t="n"/>
-      <c r="I35" s="315" t="n"/>
-      <c r="J35" s="315" t="n"/>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>27.04</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>LANÇAMENTO DE NOTAS NO PORTAL</t>
-        </is>
-      </c>
-      <c r="N35" s="15" t="n"/>
-    </row>
-    <row r="36" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A36" s="119">
-        <f>A33+1</f>
-        <v/>
-      </c>
-      <c r="B36" s="121">
-        <f>D33+3</f>
-        <v/>
-      </c>
-      <c r="C36" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="203">
-        <f>B36+4</f>
-        <v/>
-      </c>
-      <c r="E36" s="428" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-4º ao 6º tempos</t>
-        </is>
-      </c>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
-      <c r="H36" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I36" s="283" t="n"/>
-      <c r="J36" s="265" t="n"/>
-      <c r="L36" s="81" t="inlineStr">
-        <is>
-          <t>11.10 E 15.10</t>
-        </is>
-      </c>
-      <c r="M36" s="81" t="inlineStr">
-        <is>
-          <t>PROVAS DA PUC</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A37" s="316" t="n"/>
-      <c r="B37" s="313" t="n"/>
-      <c r="C37" s="313" t="n"/>
-      <c r="D37" s="350" t="n"/>
-      <c r="E37" s="405" t="n"/>
-      <c r="F37" s="283" t="n"/>
-      <c r="G37" s="283" t="n"/>
-      <c r="H37" s="405" t="n"/>
-      <c r="I37" s="283" t="n"/>
-      <c r="J37" s="352" t="n"/>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>18.08,19.08</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>curso para representantes de turmas 9,10,11</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A38" s="316" t="n"/>
-      <c r="B38" s="313" t="n"/>
-      <c r="C38" s="313" t="n"/>
-      <c r="D38" s="350" t="n"/>
-      <c r="E38" s="406" t="n"/>
-      <c r="F38" s="283" t="n"/>
-      <c r="G38" s="283" t="n"/>
-      <c r="H38" s="406" t="n"/>
-      <c r="I38" s="283" t="n"/>
-      <c r="J38" s="352" t="n"/>
-    </row>
-    <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A39" s="119">
-        <f>A36+1</f>
-        <v/>
-      </c>
-      <c r="B39" s="121">
-        <f>D36+3</f>
-        <v/>
-      </c>
-      <c r="C39" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="203">
-        <f>B39+4</f>
-        <v/>
-      </c>
-      <c r="E39" s="416" t="inlineStr">
-        <is>
-          <t>S4-11
-2º ao 7º tempos</t>
-        </is>
-      </c>
-      <c r="F39" s="416" t="inlineStr">
-        <is>
-          <t>S4-11
-2º ao 7º tempos</t>
-        </is>
-      </c>
-      <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
-      <c r="J39" s="265" t="n"/>
-    </row>
-    <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A40" s="316" t="n"/>
-      <c r="B40" s="313" t="n"/>
-      <c r="C40" s="313" t="n"/>
-      <c r="D40" s="350" t="n"/>
-      <c r="E40" s="405" t="n"/>
-      <c r="F40" s="405" t="n"/>
-      <c r="G40" s="283" t="n"/>
-      <c r="H40" s="283" t="n"/>
-      <c r="I40" s="283" t="n"/>
-      <c r="J40" s="352" t="n"/>
-    </row>
-    <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A41" s="316" t="n"/>
-      <c r="B41" s="313" t="n"/>
-      <c r="C41" s="313" t="n"/>
-      <c r="D41" s="350" t="n"/>
-      <c r="E41" s="406" t="n"/>
-      <c r="F41" s="406" t="n"/>
-      <c r="G41" s="283" t="n"/>
-      <c r="H41" s="283" t="n"/>
-      <c r="I41" s="283" t="n"/>
-      <c r="J41" s="352" t="n"/>
-    </row>
-    <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A42" s="119">
-        <f>A39+1</f>
-        <v/>
-      </c>
-      <c r="B42" s="121">
-        <f>D39+3</f>
-        <v/>
-      </c>
-      <c r="C42" s="123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="203">
-        <f>B42+4</f>
-        <v/>
-      </c>
-      <c r="E42" s="283" t="n"/>
-      <c r="F42" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-8º e 9º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="403" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="n"/>
-      <c r="J42" s="265" t="n"/>
-      <c r="L42" s="259" t="inlineStr">
-        <is>
-          <t>ENEM
-08.11,15.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A43" s="316" t="n"/>
-      <c r="B43" s="313" t="n"/>
-      <c r="C43" s="313" t="n"/>
-      <c r="D43" s="350" t="n"/>
-      <c r="E43" s="283" t="n"/>
-      <c r="F43" s="405" t="n"/>
-      <c r="G43" s="405" t="n"/>
-      <c r="H43" s="283" t="n"/>
-      <c r="I43" s="283" t="n"/>
-      <c r="J43" s="352" t="n"/>
-      <c r="L43" s="331" t="n"/>
-    </row>
-    <row r="44" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A44" s="316" t="n"/>
-      <c r="B44" s="313" t="n"/>
-      <c r="C44" s="313" t="n"/>
-      <c r="D44" s="350" t="n"/>
-      <c r="E44" s="283" t="n"/>
-      <c r="F44" s="406" t="n"/>
-      <c r="G44" s="406" t="n"/>
-      <c r="H44" s="283" t="n"/>
-      <c r="I44" s="283" t="n"/>
-      <c r="J44" s="352" t="n"/>
-      <c r="L44" s="331" t="n"/>
-    </row>
-    <row r="45" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A45" s="119">
-        <f>A42+1</f>
-        <v/>
-      </c>
-      <c r="B45" s="121">
-        <f>D42+3</f>
-        <v/>
-      </c>
-      <c r="C45" s="162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="203">
-        <f>B45+4</f>
-        <v/>
-      </c>
-      <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="409" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H45" s="283" t="n"/>
-      <c r="I45" s="386" t="n"/>
-      <c r="J45" s="269" t="n"/>
-      <c r="L45" s="331" t="n"/>
-    </row>
-    <row r="46" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A46" s="316" t="n"/>
-      <c r="B46" s="313" t="n"/>
-      <c r="C46" s="313" t="n"/>
-      <c r="D46" s="350" t="n"/>
-      <c r="E46" s="283" t="n"/>
-      <c r="F46" s="283" t="n"/>
-      <c r="G46" s="405" t="n"/>
-      <c r="H46" s="283" t="n"/>
-      <c r="I46" s="351" t="n"/>
-      <c r="J46" s="352" t="n"/>
-      <c r="L46" s="331" t="n"/>
-    </row>
-    <row r="47" ht="51" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A47" s="316" t="n"/>
-      <c r="B47" s="313" t="n"/>
-      <c r="C47" s="313" t="n"/>
-      <c r="D47" s="350" t="n"/>
-      <c r="E47" s="283" t="n"/>
-      <c r="F47" s="283" t="n"/>
-      <c r="G47" s="406" t="n"/>
-      <c r="H47" s="283" t="n"/>
-      <c r="I47" s="387" t="n"/>
-      <c r="J47" s="352" t="n"/>
-      <c r="L47" s="332" t="n"/>
-    </row>
-    <row r="48" ht="23.25" customFormat="1" customHeight="1" s="4">
-      <c r="A48" s="119">
-        <f>A45+1</f>
-        <v/>
-      </c>
-      <c r="B48" s="121">
-        <f>D45+3</f>
-        <v/>
-      </c>
-      <c r="C48" s="162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="203">
-        <f>B48+4</f>
-        <v/>
-      </c>
-      <c r="E48" s="283" t="n"/>
-      <c r="F48" s="429" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="G48" s="283" t="n"/>
-      <c r="H48" s="418" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I48" s="183" t="inlineStr">
-        <is>
-          <t>unterrichtsfrei sem aula</t>
-        </is>
-      </c>
-      <c r="J48" s="276" t="n"/>
-    </row>
-    <row r="49" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A49" s="316" t="n"/>
-      <c r="B49" s="313" t="n"/>
-      <c r="C49" s="313" t="n"/>
-      <c r="D49" s="350" t="n"/>
-      <c r="E49" s="283" t="n"/>
-      <c r="F49" s="351" t="n"/>
-      <c r="G49" s="283" t="n"/>
-      <c r="H49" s="405" t="n"/>
-      <c r="I49" s="315" t="n"/>
-      <c r="J49" s="352" t="n"/>
-    </row>
-    <row r="50" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A50" s="316" t="n"/>
-      <c r="B50" s="313" t="n"/>
-      <c r="C50" s="313" t="n"/>
-      <c r="D50" s="350" t="n"/>
-      <c r="E50" s="78" t="n"/>
-      <c r="F50" s="387" t="n"/>
-      <c r="G50" s="283" t="n"/>
-      <c r="H50" s="406" t="n"/>
-      <c r="I50" s="315" t="n"/>
-      <c r="J50" s="352" t="n"/>
-    </row>
-    <row r="51" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A51" s="119">
-        <f>A48+1</f>
-        <v/>
-      </c>
-      <c r="B51" s="121">
-        <f>D48+3</f>
-        <v/>
-      </c>
-      <c r="C51" s="162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="203">
-        <f>B51+4</f>
-        <v/>
-      </c>
-      <c r="E51" s="283" t="n"/>
-      <c r="F51" s="183" t="n"/>
-      <c r="G51" s="183" t="n"/>
-      <c r="H51" s="183" t="n"/>
-      <c r="I51" s="386" t="inlineStr">
-        <is>
-          <t>2CH
-9,11</t>
-        </is>
-      </c>
-      <c r="J51" s="274" t="n"/>
-    </row>
-    <row r="52" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A52" s="316" t="n"/>
-      <c r="B52" s="313" t="n"/>
-      <c r="C52" s="313" t="n"/>
-      <c r="D52" s="350" t="n"/>
-      <c r="E52" s="283" t="n"/>
-      <c r="F52" s="315" t="n"/>
-      <c r="G52" s="315" t="n"/>
-      <c r="H52" s="315" t="n"/>
-      <c r="I52" s="351" t="n"/>
-      <c r="J52" s="352" t="n"/>
-    </row>
-    <row r="53" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A53" s="316" t="n"/>
-      <c r="B53" s="313" t="n"/>
-      <c r="C53" s="313" t="n"/>
-      <c r="D53" s="350" t="n"/>
-      <c r="E53" s="283" t="n"/>
-      <c r="F53" s="315" t="n"/>
-      <c r="G53" s="315" t="n"/>
-      <c r="H53" s="315" t="n"/>
-      <c r="I53" s="387" t="n"/>
-      <c r="J53" s="352" t="n"/>
-    </row>
-    <row r="54" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A54" s="119">
-        <f>A51+1</f>
-        <v/>
-      </c>
-      <c r="B54" s="121">
-        <f>D51+3</f>
-        <v/>
-      </c>
-      <c r="C54" s="162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="203">
-        <f>B54+4</f>
-        <v/>
-      </c>
-      <c r="E54" s="183" t="n"/>
-      <c r="F54" s="183" t="n"/>
-      <c r="G54" s="183" t="n"/>
-      <c r="H54" s="183" t="n"/>
-      <c r="I54" s="183" t="n"/>
-      <c r="J54" s="274" t="n"/>
-    </row>
-    <row r="55" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A55" s="316" t="n"/>
-      <c r="B55" s="313" t="n"/>
-      <c r="C55" s="313" t="n"/>
-      <c r="D55" s="350" t="n"/>
-      <c r="E55" s="315" t="n"/>
-      <c r="F55" s="315" t="n"/>
-      <c r="G55" s="315" t="n"/>
-      <c r="H55" s="315" t="n"/>
-      <c r="I55" s="315" t="n"/>
-      <c r="J55" s="352" t="n"/>
-    </row>
-    <row r="56" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A56" s="316" t="n"/>
-      <c r="B56" s="313" t="n"/>
-      <c r="C56" s="313" t="n"/>
-      <c r="D56" s="350" t="n"/>
-      <c r="E56" s="315" t="n"/>
-      <c r="F56" s="315" t="n"/>
-      <c r="G56" s="315" t="n"/>
-      <c r="H56" s="315" t="n"/>
-      <c r="I56" s="315" t="n"/>
-      <c r="J56" s="352" t="n"/>
-    </row>
-    <row r="57" ht="25.5" customFormat="1" customHeight="1" s="4">
-      <c r="A57" s="119">
-        <f>A54+1</f>
-        <v/>
-      </c>
-      <c r="B57" s="121">
-        <f>D54+3</f>
-        <v/>
-      </c>
-      <c r="C57" s="162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="203">
-        <f>B57+4</f>
-        <v/>
-      </c>
-      <c r="E57" s="183" t="n"/>
-      <c r="F57" s="402" t="inlineStr">
-        <is>
-          <t>CC
-9,11</t>
-        </is>
-      </c>
-      <c r="G57" s="183" t="n"/>
-      <c r="H57" s="183" t="n"/>
-      <c r="I57" s="183" t="n"/>
-      <c r="J57" s="265" t="n"/>
-    </row>
-    <row r="58" ht="24" customFormat="1" customHeight="1" s="4">
-      <c r="A58" s="316" t="n"/>
-      <c r="B58" s="313" t="n"/>
-      <c r="C58" s="313" t="n"/>
-      <c r="D58" s="350" t="n"/>
-      <c r="E58" s="315" t="n"/>
-      <c r="F58" s="351" t="n"/>
-      <c r="G58" s="315" t="n"/>
-      <c r="H58" s="315" t="n"/>
-      <c r="I58" s="315" t="n"/>
-      <c r="J58" s="352" t="n"/>
-    </row>
-    <row r="59" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
-      <c r="A59" s="316" t="n"/>
-      <c r="B59" s="313" t="n"/>
-      <c r="C59" s="313" t="n"/>
-      <c r="D59" s="350" t="n"/>
-      <c r="E59" s="315" t="n"/>
-      <c r="F59" s="387" t="n"/>
-      <c r="G59" s="315" t="n"/>
-      <c r="H59" s="315" t="n"/>
-      <c r="I59" s="315" t="n"/>
-      <c r="J59" s="352" t="n"/>
-    </row>
-    <row r="60" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A60" s="281">
-        <f>A57+1</f>
-        <v/>
-      </c>
-      <c r="B60" s="131">
-        <f>D57+3</f>
-        <v/>
-      </c>
-      <c r="C60" s="282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="131">
-        <f>B60+4</f>
-        <v/>
-      </c>
-      <c r="E60" s="284" t="n"/>
-      <c r="F60" s="284" t="n"/>
-      <c r="G60" s="284" t="n"/>
-      <c r="H60" s="284" t="n"/>
-      <c r="I60" s="283" t="n"/>
-      <c r="J60" s="283" t="n"/>
-    </row>
-    <row r="61" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A61" s="331" t="n"/>
-      <c r="B61" s="331" t="n"/>
-      <c r="C61" s="331" t="n"/>
-      <c r="D61" s="331" t="n"/>
-      <c r="E61" s="351" t="n"/>
-      <c r="F61" s="351" t="n"/>
-      <c r="G61" s="351" t="n"/>
-      <c r="H61" s="351" t="n"/>
-      <c r="I61" s="351" t="n"/>
-      <c r="J61" s="351" t="n"/>
-    </row>
-    <row r="62" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A62" s="332" t="n"/>
-      <c r="B62" s="332" t="n"/>
-      <c r="C62" s="332" t="n"/>
-      <c r="D62" s="332" t="n"/>
-      <c r="E62" s="353" t="n"/>
-      <c r="F62" s="353" t="n"/>
-      <c r="G62" s="353" t="n"/>
-      <c r="H62" s="353" t="n"/>
-      <c r="I62" s="353" t="n"/>
-      <c r="J62" s="353" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="171">
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="G54:G56"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="I48:I50"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="H54:H56"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="L42:L47"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E60:E62"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="F51:F53"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="H51:H53"/>
-    <mergeCell ref="J24:J26"/>
-    <mergeCell ref="H60:H62"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="H57:H59"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="E30:E32"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="F27:F29"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="J18:J20"/>
-    <mergeCell ref="H33:H35"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="J33:J35"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="J42:J44"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="J60:J62"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="J57:J59"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="G57:G59"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="I57:I59"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="J30:J32"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="D48:D50"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="J54:J56"/>
-    <mergeCell ref="I33:I35"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="G60:G62"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="L16:N17"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="J48:J50"/>
-    <mergeCell ref="D51:D53"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="D60:D62"/>
-    <mergeCell ref="F60:F62"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="I54:I56"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="D45:D47"/>
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="J9:J11"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="F42:F44"/>
-    <mergeCell ref="H36:H38"/>
-    <mergeCell ref="J36:J38"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="J45:J47"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="I24:I26"/>
-    <mergeCell ref="I18:I20"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E57:E59"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="I51:I53"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="I60:I62"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="D54:D56"/>
-    <mergeCell ref="F48:F50"/>
-    <mergeCell ref="J12:J14"/>
-    <mergeCell ref="H48:H50"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="J39:J41"/>
-    <mergeCell ref="J51:J53"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="E33:E35"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="I45:I47"/>
-    <mergeCell ref="F54:F56"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>
@@ -19253,20 +19263,20 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="412" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="423" t="inlineStr">
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="421" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
-10º ao 12º tempos</t>
+9º ao 11º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="405" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -19279,10 +19289,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="405" t="n"/>
-      <c r="F13" s="405" t="n"/>
+      <c r="E13" s="222" t="n"/>
+      <c r="F13" s="406" t="n"/>
       <c r="G13" s="222" t="n"/>
-      <c r="H13" s="222" t="n"/>
+      <c r="H13" s="406" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -19295,10 +19305,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="406" t="n"/>
-      <c r="F14" s="406" t="n"/>
+      <c r="E14" s="222" t="n"/>
+      <c r="F14" s="407" t="n"/>
       <c r="G14" s="222" t="n"/>
-      <c r="H14" s="222" t="n"/>
+      <c r="H14" s="407" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -19324,26 +19334,26 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="408" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
+      <c r="E15" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n"/>
+      <c r="F15" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="418" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I15" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H15" s="408" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -19354,11 +19364,11 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="405" t="n"/>
-      <c r="F16" s="222" t="n"/>
+      <c r="E16" s="406" t="n"/>
+      <c r="F16" s="406" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="405" t="n"/>
-      <c r="I16" s="405" t="n"/>
+      <c r="H16" s="406" t="n"/>
+      <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -19370,11 +19380,11 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="406" t="n"/>
-      <c r="F17" s="222" t="n"/>
+      <c r="E17" s="407" t="n"/>
+      <c r="F17" s="407" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="406" t="n"/>
-      <c r="I17" s="406" t="n"/>
+      <c r="H17" s="407" t="n"/>
+      <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -19403,23 +19413,23 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Ale
+      <c r="F18" s="403" t="inlineStr">
+        <is>
+          <t>Hist - Wag
+11º e 12º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="409" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="432" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
 2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="403" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="430" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-4º e 5º tempos</t>
         </is>
       </c>
       <c r="J18" s="183" t="n"/>
@@ -19433,9 +19443,9 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="405" t="n"/>
+      <c r="F19" s="406" t="n"/>
       <c r="G19" s="222" t="n"/>
-      <c r="H19" s="405" t="n"/>
+      <c r="H19" s="406" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -19456,9 +19466,9 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="406" t="n"/>
+      <c r="F20" s="407" t="n"/>
       <c r="G20" s="222" t="n"/>
-      <c r="H20" s="406" t="n"/>
+      <c r="H20" s="407" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -19483,31 +19493,31 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="409" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
+      <c r="E21" s="411" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="420" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G21" s="416" t="inlineStr">
+      <c r="G21" s="418" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H21" s="416" t="inlineStr">
+      <c r="H21" s="418" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="407" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -19530,11 +19540,11 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="222" t="n"/>
-      <c r="F22" s="405" t="n"/>
-      <c r="G22" s="405" t="n"/>
-      <c r="H22" s="405" t="n"/>
-      <c r="I22" s="405" t="n"/>
+      <c r="E22" s="406" t="n"/>
+      <c r="F22" s="406" t="n"/>
+      <c r="G22" s="406" t="n"/>
+      <c r="H22" s="406" t="n"/>
+      <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -19545,11 +19555,11 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="222" t="n"/>
-      <c r="F23" s="406" t="n"/>
-      <c r="G23" s="406" t="n"/>
-      <c r="H23" s="406" t="n"/>
-      <c r="I23" s="406" t="n"/>
+      <c r="E23" s="407" t="n"/>
+      <c r="F23" s="407" t="n"/>
+      <c r="G23" s="407" t="n"/>
+      <c r="H23" s="407" t="n"/>
+      <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -19574,17 +19584,12 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="412" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="431" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
+      <c r="G24" s="433" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
@@ -19603,9 +19608,9 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="405" t="n"/>
+      <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="414" t="n"/>
+      <c r="G25" s="415" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
@@ -19622,9 +19627,9 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="406" t="n"/>
+      <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="415" t="n"/>
+      <c r="G26" s="416" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
@@ -19658,10 +19663,10 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="408" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
-6º e 7º tempos</t>
+      <c r="I27" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="J27" s="265" t="n"/>
@@ -19682,7 +19687,7 @@
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="405" t="n"/>
+      <c r="I28" s="406" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -19701,7 +19706,7 @@
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="406" t="n"/>
+      <c r="I29" s="407" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -19729,20 +19734,20 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="421" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="423" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-11º ao 13º tempos</t>
+      <c r="E30" s="283" t="n"/>
+      <c r="F30" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
+      <c r="H30" s="405" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
@@ -19762,10 +19767,10 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="405" t="n"/>
-      <c r="F31" s="405" t="n"/>
+      <c r="E31" s="283" t="n"/>
+      <c r="F31" s="406" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="283" t="n"/>
+      <c r="H31" s="406" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -19781,10 +19786,10 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="406" t="n"/>
-      <c r="F32" s="406" t="n"/>
+      <c r="E32" s="283" t="n"/>
+      <c r="F32" s="407" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="283" t="n"/>
+      <c r="H32" s="407" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -19910,20 +19915,20 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G36" s="410" t="inlineStr">
+      <c r="F36" s="403" t="inlineStr">
         <is>
           <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -19942,10 +19947,10 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="405" t="n"/>
-      <c r="G37" s="405" t="n"/>
+      <c r="F37" s="406" t="n"/>
+      <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="283" t="n"/>
+      <c r="I37" s="406" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -19964,10 +19969,10 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="406" t="n"/>
-      <c r="G38" s="406" t="n"/>
+      <c r="F38" s="407" t="n"/>
+      <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="283" t="n"/>
+      <c r="I38" s="407" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -19991,13 +19996,18 @@
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="403" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I39" s="283" t="n"/>
+      <c r="H39" s="420" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I39" s="411" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -20008,8 +20018,8 @@
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="405" t="n"/>
-      <c r="I40" s="283" t="n"/>
+      <c r="H40" s="406" t="n"/>
+      <c r="I40" s="406" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -20020,8 +20030,8 @@
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="406" t="n"/>
-      <c r="I41" s="283" t="n"/>
+      <c r="H41" s="407" t="n"/>
+      <c r="I41" s="407" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -20043,20 +20053,20 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="418" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="425" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
-      <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="n"/>
+      <c r="F42" s="283" t="n"/>
+      <c r="G42" s="283" t="n"/>
+      <c r="H42" s="408" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I42" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -20071,10 +20081,10 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="405" t="n"/>
-      <c r="G43" s="405" t="n"/>
-      <c r="H43" s="283" t="n"/>
-      <c r="I43" s="283" t="n"/>
+      <c r="F43" s="283" t="n"/>
+      <c r="G43" s="283" t="n"/>
+      <c r="H43" s="406" t="n"/>
+      <c r="I43" s="406" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -20084,10 +20094,10 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="406" t="n"/>
-      <c r="G44" s="406" t="n"/>
-      <c r="H44" s="283" t="n"/>
-      <c r="I44" s="283" t="n"/>
+      <c r="F44" s="283" t="n"/>
+      <c r="G44" s="283" t="n"/>
+      <c r="H44" s="407" t="n"/>
+      <c r="I44" s="407" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -20110,19 +20120,19 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="407" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="H45" s="409" t="inlineStr">
+      <c r="F45" s="409" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G45" s="427" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
@@ -20138,9 +20148,9 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="283" t="n"/>
-      <c r="G46" s="405" t="n"/>
-      <c r="H46" s="405" t="n"/>
+      <c r="F46" s="406" t="n"/>
+      <c r="G46" s="406" t="n"/>
+      <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -20151,9 +20161,9 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="283" t="n"/>
-      <c r="G47" s="406" t="n"/>
-      <c r="H47" s="406" t="n"/>
+      <c r="F47" s="407" t="n"/>
+      <c r="G47" s="407" t="n"/>
+      <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -20440,7 +20450,7 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
-    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -20456,11 +20466,11 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
-    <mergeCell ref="E30:E32"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="G45:G47"/>
+    <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -20468,11 +20478,11 @@
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
-    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="I15:I17"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
@@ -20482,13 +20492,11 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
-    <mergeCell ref="E24:E26"/>
     <mergeCell ref="F30:F32"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -20501,6 +20509,7 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
+    <mergeCell ref="I42:I44"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -20532,9 +20541,9 @@
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F45:F47"/>
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="F42:F44"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
@@ -20554,11 +20563,13 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
+    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -20568,8 +20579,8 @@
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="I27:I29"/>
-    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
+    <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -20578,7 +20589,6 @@
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -452,7 +452,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="111">
+  <borders count="116">
     <border>
       <left/>
       <right/>
@@ -1807,6 +1807,34 @@
       <right style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1814,7 +1842,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="434">
+  <cellXfs count="462">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3287,6 +3315,103 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="115" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5783,23 +5908,23 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="408" t="inlineStr">
+      <c r="E12" s="440" t="inlineStr">
         <is>
           <t>Ing - Isb
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F12" s="421" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-9º ao 11º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="405" t="inlineStr">
+      <c r="F12" s="405" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="420" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -5814,7 +5939,7 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="406" t="n"/>
+      <c r="E13" s="437" t="n"/>
       <c r="F13" s="406" t="n"/>
       <c r="G13" s="222" t="n"/>
       <c r="H13" s="406" t="n"/>
@@ -5830,7 +5955,7 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="407" t="n"/>
+      <c r="E14" s="439" t="n"/>
       <c r="F14" s="407" t="n"/>
       <c r="G14" s="222" t="n"/>
       <c r="H14" s="407" t="n"/>
@@ -5859,16 +5984,16 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="410" t="inlineStr">
+      <c r="E15" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+      <c r="F15" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+9º ao 11º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
@@ -5884,7 +6009,7 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="406" t="n"/>
+      <c r="E16" s="437" t="n"/>
       <c r="F16" s="406" t="n"/>
       <c r="G16" s="222" t="n"/>
       <c r="H16" s="222" t="n"/>
@@ -5900,7 +6025,7 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="407" t="n"/>
+      <c r="E17" s="439" t="n"/>
       <c r="F17" s="407" t="n"/>
       <c r="G17" s="222" t="n"/>
       <c r="H17" s="222" t="n"/>
@@ -5933,14 +6058,14 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="403" t="inlineStr">
+      <c r="F18" s="434" t="inlineStr">
         <is>
           <t>Hist - Wag
 11º e 12º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="409" t="inlineStr">
+      <c r="H18" s="441" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 4º e 5º tempos</t>
@@ -5963,9 +6088,9 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="406" t="n"/>
+      <c r="F19" s="437" t="n"/>
       <c r="G19" s="222" t="n"/>
-      <c r="H19" s="406" t="n"/>
+      <c r="H19" s="437" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -5986,9 +6111,9 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="407" t="n"/>
+      <c r="F20" s="439" t="n"/>
       <c r="G20" s="222" t="n"/>
-      <c r="H20" s="407" t="n"/>
+      <c r="H20" s="439" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -6013,25 +6138,25 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="411" t="inlineStr">
+      <c r="E21" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F21" s="420" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="418" t="inlineStr">
+      <c r="F21" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G21" s="450" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H21" s="418" t="inlineStr">
+      <c r="H21" s="450" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
@@ -6060,10 +6185,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="406" t="n"/>
+      <c r="E22" s="437" t="n"/>
       <c r="F22" s="406" t="n"/>
-      <c r="G22" s="406" t="n"/>
-      <c r="H22" s="406" t="n"/>
+      <c r="G22" s="437" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -6075,10 +6200,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="407" t="n"/>
+      <c r="E23" s="439" t="n"/>
       <c r="F23" s="407" t="n"/>
-      <c r="G23" s="407" t="n"/>
-      <c r="H23" s="407" t="n"/>
+      <c r="G23" s="439" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -6106,7 +6231,7 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="433" t="inlineStr">
+      <c r="G24" s="461" t="inlineStr">
         <is>
           <t>Soc - Kle
 2º tempo</t>
@@ -6130,7 +6255,7 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="415" t="n"/>
+      <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
@@ -6149,7 +6274,7 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="416" t="n"/>
+      <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
@@ -6179,16 +6304,21 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="429" t="inlineStr">
+      <c r="E27" s="460" t="inlineStr">
         <is>
           <t>Ing - Isb
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="427" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="421" t="inlineStr">
+      <c r="I27" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 1º ao 3º tempos</t>
@@ -6208,11 +6338,11 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="406" t="n"/>
+      <c r="E28" s="437" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="283" t="n"/>
+      <c r="G28" s="406" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="406" t="n"/>
+      <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -6227,11 +6357,11 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="407" t="n"/>
+      <c r="E29" s="439" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="283" t="n"/>
+      <c r="G29" s="407" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="407" t="n"/>
+      <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -6260,14 +6390,14 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="417" t="inlineStr">
+      <c r="F30" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º e 2º tempos</t>
         </is>
       </c>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="405" t="inlineStr">
+      <c r="H30" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
@@ -6293,9 +6423,9 @@
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
-      <c r="F31" s="406" t="n"/>
+      <c r="F31" s="437" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="406" t="n"/>
+      <c r="H31" s="437" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -6312,9 +6442,9 @@
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
-      <c r="F32" s="407" t="n"/>
+      <c r="F32" s="439" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="407" t="n"/>
+      <c r="H32" s="439" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -6440,7 +6570,7 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="403" t="inlineStr">
+      <c r="F36" s="434" t="inlineStr">
         <is>
           <t>Hist - Wag
 10º e 11º tempos</t>
@@ -6448,7 +6578,7 @@
       </c>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="410" t="inlineStr">
+      <c r="I36" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 2º e 3º tempos</t>
@@ -6472,10 +6602,10 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="406" t="n"/>
+      <c r="F37" s="437" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="406" t="n"/>
+      <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -6494,10 +6624,10 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="407" t="n"/>
+      <c r="F38" s="439" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="407" t="n"/>
+      <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6521,13 +6651,13 @@
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="420" t="inlineStr">
+      <c r="H39" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I39" s="411" t="inlineStr">
+      <c r="I39" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 6º e 7º tempos</t>
@@ -6543,8 +6673,8 @@
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="406" t="n"/>
-      <c r="I40" s="406" t="n"/>
+      <c r="H40" s="437" t="n"/>
+      <c r="I40" s="437" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -6555,8 +6685,8 @@
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="407" t="n"/>
-      <c r="I41" s="407" t="n"/>
+      <c r="H41" s="439" t="n"/>
+      <c r="I41" s="439" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6581,7 +6711,7 @@
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="419" t="inlineStr">
+      <c r="I42" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 4º e 5º tempos</t>
@@ -6604,7 +6734,7 @@
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
-      <c r="I43" s="406" t="n"/>
+      <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -6617,7 +6747,7 @@
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
-      <c r="I44" s="407" t="n"/>
+      <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -6640,18 +6770,13 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="409" t="inlineStr">
+      <c r="F45" s="441" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G45" s="427" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
+      <c r="G45" s="435" t="n"/>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
@@ -6668,8 +6793,8 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="406" t="n"/>
-      <c r="G46" s="406" t="n"/>
+      <c r="F46" s="437" t="n"/>
+      <c r="G46" s="438" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -6681,8 +6806,8 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="407" t="n"/>
-      <c r="G47" s="407" t="n"/>
+      <c r="F47" s="439" t="n"/>
+      <c r="G47" s="438" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -6989,7 +7114,6 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="G45:G47"/>
     <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
@@ -7099,6 +7223,7 @@
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="I27:I29"/>
+    <mergeCell ref="G27:G29"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>
@@ -9027,20 +9152,15 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="403" t="inlineStr">
+      <c r="F12" s="434" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G12" s="404" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G12" s="435" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="405" t="inlineStr">
+      <c r="I12" s="436" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
@@ -9058,10 +9178,10 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="222" t="n"/>
-      <c r="F13" s="406" t="n"/>
-      <c r="G13" s="406" t="n"/>
+      <c r="F13" s="437" t="n"/>
+      <c r="G13" s="438" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="406" t="n"/>
+      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -9074,10 +9194,10 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="222" t="n"/>
-      <c r="F14" s="407" t="n"/>
-      <c r="G14" s="407" t="n"/>
+      <c r="F14" s="439" t="n"/>
+      <c r="G14" s="438" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="407" t="n"/>
+      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -9104,9 +9224,14 @@
       </c>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
+      <c r="G15" s="404" t="inlineStr">
+        <is>
+          <t>Port - Jana
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="408" t="inlineStr">
+      <c r="I15" s="440" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -9124,9 +9249,9 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
       <c r="F16" s="222" t="n"/>
-      <c r="G16" s="222" t="n"/>
+      <c r="G16" s="406" t="n"/>
       <c r="H16" s="222" t="n"/>
-      <c r="I16" s="406" t="n"/>
+      <c r="I16" s="437" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -9140,9 +9265,9 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
       <c r="F17" s="222" t="n"/>
-      <c r="G17" s="222" t="n"/>
+      <c r="G17" s="407" t="n"/>
       <c r="H17" s="222" t="n"/>
-      <c r="I17" s="407" t="n"/>
+      <c r="I17" s="439" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -9171,13 +9296,13 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="409" t="inlineStr">
+      <c r="F18" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="G18" s="410" t="inlineStr">
+      <c r="G18" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -9196,8 +9321,8 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="406" t="n"/>
-      <c r="G19" s="406" t="n"/>
+      <c r="F19" s="437" t="n"/>
+      <c r="G19" s="437" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -9219,8 +9344,8 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="407" t="n"/>
-      <c r="G20" s="407" t="n"/>
+      <c r="F20" s="439" t="n"/>
+      <c r="G20" s="439" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -9247,14 +9372,14 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="411" t="inlineStr">
+      <c r="F21" s="443" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="412" t="inlineStr">
+      <c r="H21" s="444" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
@@ -9284,9 +9409,9 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="406" t="n"/>
+      <c r="F22" s="437" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="406" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -9299,9 +9424,9 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="407" t="n"/>
+      <c r="F23" s="439" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="407" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -9329,14 +9454,14 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="413" t="inlineStr">
+      <c r="G24" s="445" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="414" t="inlineStr">
+      <c r="I24" s="446" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
@@ -9358,9 +9483,9 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="415" t="n"/>
+      <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="406" t="n"/>
+      <c r="I25" s="437" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -9377,9 +9502,9 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="416" t="n"/>
+      <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="407" t="n"/>
+      <c r="I26" s="439" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -9409,14 +9534,14 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="417" t="inlineStr">
+      <c r="G27" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 3º tempo</t>
         </is>
       </c>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="418" t="inlineStr">
+      <c r="I27" s="450" t="inlineStr">
         <is>
           <t>AG9
 2º ao 7º tempos</t>
@@ -9438,9 +9563,9 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="406" t="n"/>
+      <c r="G28" s="437" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="406" t="n"/>
+      <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -9457,9 +9582,9 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="407" t="n"/>
+      <c r="G29" s="439" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="407" t="n"/>
+      <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -9489,7 +9614,7 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="419" t="inlineStr">
+      <c r="G30" s="451" t="inlineStr">
         <is>
           <t>Qui - Fab
 2º tempo</t>
@@ -9517,7 +9642,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="406" t="n"/>
+      <c r="G31" s="437" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -9536,7 +9661,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="407" t="n"/>
+      <c r="G32" s="439" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -9663,7 +9788,7 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="403" t="inlineStr">
+      <c r="F36" s="434" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
@@ -9671,7 +9796,7 @@
       </c>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="408" t="inlineStr">
+      <c r="I36" s="440" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -9695,10 +9820,10 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="406" t="n"/>
+      <c r="F37" s="437" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="406" t="n"/>
+      <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -9717,10 +9842,10 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="407" t="n"/>
+      <c r="F38" s="439" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="407" t="n"/>
+      <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9743,7 +9868,7 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="410" t="inlineStr">
+      <c r="G39" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -9760,7 +9885,7 @@
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="406" t="n"/>
+      <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
@@ -9772,7 +9897,7 @@
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="407" t="n"/>
+      <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
@@ -9797,7 +9922,7 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="409" t="inlineStr">
+      <c r="G42" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
@@ -9820,7 +9945,7 @@
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
-      <c r="G43" s="406" t="n"/>
+      <c r="G43" s="437" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -9833,7 +9958,7 @@
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
-      <c r="G44" s="407" t="n"/>
+      <c r="G44" s="439" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -9860,7 +9985,7 @@
       <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="411" t="inlineStr">
+      <c r="H45" s="443" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 1º e 2º tempos</t>
@@ -9878,7 +10003,7 @@
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
-      <c r="H46" s="406" t="n"/>
+      <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -9891,7 +10016,7 @@
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
-      <c r="H47" s="407" t="n"/>
+      <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -9914,7 +10039,7 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="420" t="inlineStr">
+      <c r="E48" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 2º tempo</t>
@@ -9922,7 +10047,7 @@
       </c>
       <c r="F48" s="402" t="n"/>
       <c r="G48" s="283" t="n"/>
-      <c r="H48" s="412" t="inlineStr">
+      <c r="H48" s="444" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
@@ -9940,10 +10065,10 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="406" t="n"/>
+      <c r="E49" s="437" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
-      <c r="H49" s="406" t="n"/>
+      <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -9952,10 +10077,10 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="407" t="n"/>
+      <c r="E50" s="439" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
-      <c r="H50" s="407" t="n"/>
+      <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -10270,7 +10395,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G12:G14"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -10283,6 +10407,7 @@
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="J36:J38"/>
+    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
@@ -10713,20 +10838,15 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="403" t="inlineStr">
+      <c r="F12" s="434" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G12" s="404" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G12" s="435" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="405" t="inlineStr">
+      <c r="I12" s="436" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
@@ -10744,10 +10864,10 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="222" t="n"/>
-      <c r="F13" s="406" t="n"/>
-      <c r="G13" s="406" t="n"/>
+      <c r="F13" s="437" t="n"/>
+      <c r="G13" s="438" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="406" t="n"/>
+      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -10760,10 +10880,10 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="222" t="n"/>
-      <c r="F14" s="407" t="n"/>
-      <c r="G14" s="407" t="n"/>
+      <c r="F14" s="439" t="n"/>
+      <c r="G14" s="438" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="407" t="n"/>
+      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -10790,9 +10910,14 @@
       </c>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
+      <c r="G15" s="404" t="inlineStr">
+        <is>
+          <t>Port - Jana
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="408" t="inlineStr">
+      <c r="I15" s="440" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -10810,9 +10935,9 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
       <c r="F16" s="222" t="n"/>
-      <c r="G16" s="222" t="n"/>
+      <c r="G16" s="406" t="n"/>
       <c r="H16" s="222" t="n"/>
-      <c r="I16" s="406" t="n"/>
+      <c r="I16" s="437" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -10826,9 +10951,9 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
       <c r="F17" s="222" t="n"/>
-      <c r="G17" s="222" t="n"/>
+      <c r="G17" s="407" t="n"/>
       <c r="H17" s="222" t="n"/>
-      <c r="I17" s="407" t="n"/>
+      <c r="I17" s="439" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -10857,13 +10982,13 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="409" t="inlineStr">
+      <c r="F18" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="G18" s="410" t="inlineStr">
+      <c r="G18" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -10882,8 +11007,8 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="406" t="n"/>
-      <c r="G19" s="406" t="n"/>
+      <c r="F19" s="437" t="n"/>
+      <c r="G19" s="437" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -10905,8 +11030,8 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="407" t="n"/>
-      <c r="G20" s="407" t="n"/>
+      <c r="F20" s="439" t="n"/>
+      <c r="G20" s="439" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -10933,14 +11058,14 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="411" t="inlineStr">
+      <c r="F21" s="443" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="412" t="inlineStr">
+      <c r="H21" s="444" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
@@ -10970,9 +11095,9 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="406" t="n"/>
+      <c r="F22" s="437" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="406" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -10985,9 +11110,9 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="407" t="n"/>
+      <c r="F23" s="439" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="407" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -11015,14 +11140,14 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="413" t="inlineStr">
+      <c r="G24" s="445" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="414" t="inlineStr">
+      <c r="I24" s="446" t="inlineStr">
         <is>
           <t>GL - Caro-EFr-Eth
 4º e 5º tempos</t>
@@ -11044,9 +11169,9 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="415" t="n"/>
+      <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="406" t="n"/>
+      <c r="I25" s="437" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -11063,9 +11188,9 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="416" t="n"/>
+      <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="407" t="n"/>
+      <c r="I26" s="439" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -11095,14 +11220,14 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="417" t="inlineStr">
+      <c r="G27" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 3º tempo</t>
         </is>
       </c>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="418" t="inlineStr">
+      <c r="I27" s="450" t="inlineStr">
         <is>
           <t>AG9
 2º ao 7º tempos</t>
@@ -11124,9 +11249,9 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="406" t="n"/>
+      <c r="G28" s="437" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="406" t="n"/>
+      <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -11143,9 +11268,9 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="407" t="n"/>
+      <c r="G29" s="439" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="407" t="n"/>
+      <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -11175,7 +11300,7 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="419" t="inlineStr">
+      <c r="G30" s="451" t="inlineStr">
         <is>
           <t>Qui - Fab
 2º tempo</t>
@@ -11203,7 +11328,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="406" t="n"/>
+      <c r="G31" s="437" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -11222,7 +11347,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="407" t="n"/>
+      <c r="G32" s="439" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -11349,7 +11474,7 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="403" t="inlineStr">
+      <c r="F36" s="434" t="inlineStr">
         <is>
           <t>Hist - JuLa
 4º e 5º tempos</t>
@@ -11357,7 +11482,7 @@
       </c>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="408" t="inlineStr">
+      <c r="I36" s="440" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
 2º e 3º tempos</t>
@@ -11381,10 +11506,10 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="406" t="n"/>
+      <c r="F37" s="437" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="406" t="n"/>
+      <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -11403,10 +11528,10 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="407" t="n"/>
+      <c r="F38" s="439" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="407" t="n"/>
+      <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11429,7 +11554,7 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="410" t="inlineStr">
+      <c r="G39" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -11446,7 +11571,7 @@
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="406" t="n"/>
+      <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
@@ -11458,7 +11583,7 @@
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="407" t="n"/>
+      <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
@@ -11483,7 +11608,7 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="409" t="inlineStr">
+      <c r="G42" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
@@ -11506,7 +11631,7 @@
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
-      <c r="G43" s="406" t="n"/>
+      <c r="G43" s="437" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -11519,7 +11644,7 @@
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
-      <c r="G44" s="407" t="n"/>
+      <c r="G44" s="439" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -11546,7 +11671,7 @@
       <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="411" t="inlineStr">
+      <c r="H45" s="443" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 1º e 2º tempos</t>
@@ -11564,7 +11689,7 @@
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
-      <c r="H46" s="406" t="n"/>
+      <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -11577,7 +11702,7 @@
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
-      <c r="H47" s="407" t="n"/>
+      <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -11600,7 +11725,7 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="420" t="inlineStr">
+      <c r="E48" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 2º tempo</t>
@@ -11608,7 +11733,7 @@
       </c>
       <c r="F48" s="402" t="n"/>
       <c r="G48" s="283" t="n"/>
-      <c r="H48" s="412" t="inlineStr">
+      <c r="H48" s="444" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
@@ -11626,10 +11751,10 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="406" t="n"/>
+      <c r="E49" s="437" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
-      <c r="H49" s="406" t="n"/>
+      <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -11638,10 +11763,10 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="407" t="n"/>
+      <c r="E50" s="439" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
-      <c r="H50" s="407" t="n"/>
+      <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -11956,7 +12081,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G12:G14"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -11969,6 +12093,7 @@
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="J36:J38"/>
+    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
@@ -12398,19 +12523,19 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="421" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="417" t="inlineStr">
+      <c r="E12" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="449" t="inlineStr">
         <is>
           <t>Bio - Lza
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="G12" s="405" t="inlineStr">
+      <c r="G12" s="436" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
@@ -12430,8 +12555,8 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="406" t="n"/>
-      <c r="F13" s="406" t="n"/>
-      <c r="G13" s="406" t="n"/>
+      <c r="F13" s="437" t="n"/>
+      <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
@@ -12446,8 +12571,8 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="407" t="n"/>
-      <c r="F14" s="407" t="n"/>
-      <c r="G14" s="407" t="n"/>
+      <c r="F14" s="439" t="n"/>
+      <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
@@ -12476,13 +12601,13 @@
       </c>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="422" t="inlineStr">
+      <c r="G15" s="453" t="inlineStr">
         <is>
           <t>Ing - APa
 3º e 4º tempos</t>
         </is>
       </c>
-      <c r="H15" s="420" t="inlineStr">
+      <c r="H15" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
@@ -12501,8 +12626,8 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
       <c r="F16" s="222" t="n"/>
-      <c r="G16" s="406" t="n"/>
-      <c r="H16" s="406" t="n"/>
+      <c r="G16" s="437" t="n"/>
+      <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -12517,8 +12642,8 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
       <c r="F17" s="222" t="n"/>
-      <c r="G17" s="407" t="n"/>
-      <c r="H17" s="407" t="n"/>
+      <c r="G17" s="439" t="n"/>
+      <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -12549,13 +12674,13 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="411" t="inlineStr">
+      <c r="G18" s="443" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H18" s="403" t="inlineStr">
+      <c r="H18" s="434" t="inlineStr">
         <is>
           <t>Hist - ALu
 2º e 3º tempos</t>
@@ -12579,8 +12704,8 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="406" t="n"/>
-      <c r="H19" s="406" t="n"/>
+      <c r="G19" s="437" t="n"/>
+      <c r="H19" s="437" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -12602,8 +12727,8 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="407" t="n"/>
-      <c r="H20" s="407" t="n"/>
+      <c r="G20" s="439" t="n"/>
+      <c r="H20" s="439" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -12628,15 +12753,15 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="419" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
+      <c r="E21" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="409" t="inlineStr">
+      <c r="H21" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
@@ -12668,7 +12793,7 @@
       <c r="E22" s="406" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="406" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -12683,7 +12808,7 @@
       <c r="E23" s="407" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="407" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -12713,7 +12838,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="424" t="inlineStr">
+      <c r="I24" s="454" t="inlineStr">
         <is>
           <t>AG10
 2º ao 7º tempos</t>
@@ -12737,7 +12862,7 @@
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="406" t="n"/>
+      <c r="I25" s="437" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -12756,7 +12881,7 @@
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="407" t="n"/>
+      <c r="I26" s="439" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -12784,7 +12909,7 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="425" t="inlineStr">
+      <c r="E27" s="455" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
@@ -12793,7 +12918,7 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="426" t="inlineStr">
+      <c r="I27" s="456" t="inlineStr">
         <is>
           <t>Soc - Kle
 5º tempo</t>
@@ -12813,11 +12938,11 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="406" t="n"/>
+      <c r="E28" s="437" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="406" t="n"/>
+      <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -12832,11 +12957,11 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="407" t="n"/>
+      <c r="E29" s="439" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="407" t="n"/>
+      <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -12867,13 +12992,13 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="420" t="inlineStr">
+      <c r="H30" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I30" s="410" t="inlineStr">
+      <c r="I30" s="442" t="inlineStr">
         <is>
           <t>Geo - Mlo
 2º e 3º tempos</t>
@@ -12900,8 +13025,8 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="406" t="n"/>
-      <c r="I31" s="406" t="n"/>
+      <c r="H31" s="437" t="n"/>
+      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -12919,8 +13044,8 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="407" t="n"/>
-      <c r="I32" s="407" t="n"/>
+      <c r="H32" s="439" t="n"/>
+      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -13044,20 +13169,20 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="408" t="inlineStr">
+      <c r="E36" s="440" t="inlineStr">
         <is>
           <t>Ing - APa
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="405" t="inlineStr">
+      <c r="G36" s="436" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H36" s="409" t="inlineStr">
+      <c r="H36" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
@@ -13081,10 +13206,10 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="406" t="n"/>
+      <c r="E37" s="437" t="n"/>
       <c r="F37" s="283" t="n"/>
-      <c r="G37" s="406" t="n"/>
-      <c r="H37" s="406" t="n"/>
+      <c r="G37" s="437" t="n"/>
+      <c r="H37" s="437" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -13103,10 +13228,10 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="407" t="n"/>
+      <c r="E38" s="439" t="n"/>
       <c r="F38" s="283" t="n"/>
-      <c r="G38" s="407" t="n"/>
-      <c r="H38" s="407" t="n"/>
+      <c r="G38" s="439" t="n"/>
+      <c r="H38" s="439" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -13130,13 +13255,13 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="427" t="inlineStr">
+      <c r="G39" s="457" t="inlineStr">
         <is>
           <t>Fil - LAn
 1º tempo</t>
         </is>
       </c>
-      <c r="H39" s="403" t="inlineStr">
+      <c r="H39" s="434" t="inlineStr">
         <is>
           <t>Hist - ALu
 2º e 3º tempos</t>
@@ -13152,8 +13277,8 @@
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="406" t="n"/>
-      <c r="H40" s="406" t="n"/>
+      <c r="G40" s="437" t="n"/>
+      <c r="H40" s="437" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
@@ -13164,8 +13289,8 @@
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="407" t="n"/>
-      <c r="H41" s="407" t="n"/>
+      <c r="G41" s="439" t="n"/>
+      <c r="H41" s="439" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
@@ -13188,13 +13313,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="417" t="inlineStr">
+      <c r="F42" s="449" t="inlineStr">
         <is>
           <t>Bio - Lza
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G42" s="411" t="inlineStr">
+      <c r="G42" s="443" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
@@ -13216,8 +13341,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="406" t="n"/>
-      <c r="G43" s="406" t="n"/>
+      <c r="F43" s="437" t="n"/>
+      <c r="G43" s="437" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -13229,8 +13354,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="407" t="n"/>
-      <c r="G44" s="407" t="n"/>
+      <c r="F44" s="439" t="n"/>
+      <c r="G44" s="439" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -13254,7 +13379,7 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="419" t="inlineStr">
+      <c r="E45" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
@@ -13277,7 +13402,7 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="406" t="n"/>
+      <c r="E46" s="437" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="283" t="n"/>
@@ -13290,7 +13415,7 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="407" t="n"/>
+      <c r="E47" s="439" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="283" t="n"/>
@@ -14101,19 +14226,19 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="421" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="417" t="inlineStr">
+      <c r="E12" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="449" t="inlineStr">
         <is>
           <t>Bio - Lza
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="G12" s="405" t="inlineStr">
+      <c r="G12" s="436" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
@@ -14133,8 +14258,8 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="406" t="n"/>
-      <c r="F13" s="406" t="n"/>
-      <c r="G13" s="406" t="n"/>
+      <c r="F13" s="437" t="n"/>
+      <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
@@ -14149,8 +14274,8 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="407" t="n"/>
-      <c r="F14" s="407" t="n"/>
-      <c r="G14" s="407" t="n"/>
+      <c r="F14" s="439" t="n"/>
+      <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
@@ -14178,14 +14303,14 @@
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
-      <c r="F15" s="408" t="inlineStr">
+      <c r="F15" s="440" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="420" t="inlineStr">
+      <c r="H15" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
@@ -14203,9 +14328,9 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
-      <c r="F16" s="406" t="n"/>
+      <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="406" t="n"/>
+      <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -14219,9 +14344,9 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
-      <c r="F17" s="407" t="n"/>
+      <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="407" t="n"/>
+      <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -14252,13 +14377,13 @@
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="411" t="inlineStr">
+      <c r="G18" s="443" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H18" s="403" t="inlineStr">
+      <c r="H18" s="434" t="inlineStr">
         <is>
           <t>Hist - ALu
 2º e 3º tempos</t>
@@ -14282,8 +14407,8 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="222" t="n"/>
-      <c r="G19" s="406" t="n"/>
-      <c r="H19" s="406" t="n"/>
+      <c r="G19" s="437" t="n"/>
+      <c r="H19" s="437" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -14305,8 +14430,8 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="222" t="n"/>
-      <c r="G20" s="407" t="n"/>
-      <c r="H20" s="407" t="n"/>
+      <c r="G20" s="439" t="n"/>
+      <c r="H20" s="439" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -14331,15 +14456,15 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="419" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
+      <c r="E21" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="409" t="inlineStr">
+      <c r="H21" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
@@ -14371,7 +14496,7 @@
       <c r="E22" s="406" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="406" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -14386,7 +14511,7 @@
       <c r="E23" s="407" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="407" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -14416,7 +14541,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="424" t="inlineStr">
+      <c r="I24" s="454" t="inlineStr">
         <is>
           <t>AG10
 2º ao 7º tempos</t>
@@ -14440,7 +14565,7 @@
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="79" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="406" t="n"/>
+      <c r="I25" s="437" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -14459,7 +14584,7 @@
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="79" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="407" t="n"/>
+      <c r="I26" s="439" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -14487,7 +14612,7 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="425" t="inlineStr">
+      <c r="E27" s="455" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
@@ -14496,7 +14621,7 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="426" t="inlineStr">
+      <c r="I27" s="456" t="inlineStr">
         <is>
           <t>Soc - Kle
 5º tempo</t>
@@ -14516,11 +14641,11 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="406" t="n"/>
+      <c r="E28" s="437" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="406" t="n"/>
+      <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -14535,11 +14660,11 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="407" t="n"/>
+      <c r="E29" s="439" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="407" t="n"/>
+      <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -14570,13 +14695,13 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="420" t="inlineStr">
+      <c r="H30" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I30" s="410" t="inlineStr">
+      <c r="I30" s="442" t="inlineStr">
         <is>
           <t>Geo - Mlo
 2º e 3º tempos</t>
@@ -14603,8 +14728,8 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="406" t="n"/>
-      <c r="I31" s="406" t="n"/>
+      <c r="H31" s="437" t="n"/>
+      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -14622,8 +14747,8 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="407" t="n"/>
-      <c r="I32" s="407" t="n"/>
+      <c r="H32" s="439" t="n"/>
+      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -14749,13 +14874,13 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="405" t="inlineStr">
+      <c r="G36" s="436" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H36" s="409" t="inlineStr">
+      <c r="H36" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
@@ -14781,8 +14906,8 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
-      <c r="G37" s="406" t="n"/>
-      <c r="H37" s="406" t="n"/>
+      <c r="G37" s="437" t="n"/>
+      <c r="H37" s="437" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -14803,8 +14928,8 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
-      <c r="G38" s="407" t="n"/>
-      <c r="H38" s="407" t="n"/>
+      <c r="G38" s="439" t="n"/>
+      <c r="H38" s="439" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -14828,13 +14953,13 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="427" t="inlineStr">
+      <c r="G39" s="457" t="inlineStr">
         <is>
           <t>Fil - LAn
 1º tempo</t>
         </is>
       </c>
-      <c r="H39" s="403" t="inlineStr">
+      <c r="H39" s="434" t="inlineStr">
         <is>
           <t>Hist - ALu
 2º e 3º tempos</t>
@@ -14850,8 +14975,8 @@
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="406" t="n"/>
-      <c r="H40" s="406" t="n"/>
+      <c r="G40" s="437" t="n"/>
+      <c r="H40" s="437" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
@@ -14862,8 +14987,8 @@
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="407" t="n"/>
-      <c r="H41" s="407" t="n"/>
+      <c r="G41" s="439" t="n"/>
+      <c r="H41" s="439" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
@@ -14886,13 +15011,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="417" t="inlineStr">
+      <c r="F42" s="449" t="inlineStr">
         <is>
           <t>Bio - Lza
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G42" s="411" t="inlineStr">
+      <c r="G42" s="443" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
@@ -14914,8 +15039,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="406" t="n"/>
-      <c r="G43" s="406" t="n"/>
+      <c r="F43" s="437" t="n"/>
+      <c r="G43" s="437" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -14927,8 +15052,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="407" t="n"/>
-      <c r="G44" s="407" t="n"/>
+      <c r="F44" s="439" t="n"/>
+      <c r="G44" s="439" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -14952,14 +15077,14 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="419" t="inlineStr">
+      <c r="E45" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="408" t="inlineStr">
+      <c r="G45" s="440" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
@@ -14980,9 +15105,9 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="406" t="n"/>
+      <c r="E46" s="437" t="n"/>
       <c r="F46" s="283" t="n"/>
-      <c r="G46" s="406" t="n"/>
+      <c r="G46" s="437" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -14993,9 +15118,9 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="407" t="n"/>
+      <c r="E47" s="439" t="n"/>
       <c r="F47" s="283" t="n"/>
-      <c r="G47" s="407" t="n"/>
+      <c r="G47" s="439" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -15822,30 +15947,25 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="408" t="inlineStr">
+      <c r="E12" s="440" t="inlineStr">
         <is>
           <t>Ing - Bea
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="F12" s="418" t="inlineStr">
+      <c r="F12" s="450" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G12" s="418" t="inlineStr">
+      <c r="G12" s="450" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="409" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H12" s="435" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -15858,10 +15978,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="406" t="n"/>
-      <c r="F13" s="406" t="n"/>
-      <c r="G13" s="406" t="n"/>
-      <c r="H13" s="406" t="n"/>
+      <c r="E13" s="437" t="n"/>
+      <c r="F13" s="437" t="n"/>
+      <c r="G13" s="437" t="n"/>
+      <c r="H13" s="438" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -15874,10 +15994,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="407" t="n"/>
-      <c r="F14" s="407" t="n"/>
-      <c r="G14" s="407" t="n"/>
-      <c r="H14" s="407" t="n"/>
+      <c r="E14" s="439" t="n"/>
+      <c r="F14" s="439" t="n"/>
+      <c r="G14" s="439" t="n"/>
+      <c r="H14" s="438" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -15903,20 +16023,20 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="410" t="inlineStr">
+      <c r="E15" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F15" s="403" t="inlineStr">
+      <c r="F15" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
 11º e 12º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="421" t="inlineStr">
+      <c r="H15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 9º ao 11º tempos</t>
@@ -15933,10 +16053,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="406" t="n"/>
-      <c r="F16" s="406" t="n"/>
+      <c r="E16" s="437" t="n"/>
+      <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="406" t="n"/>
+      <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -15949,10 +16069,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="407" t="n"/>
-      <c r="F17" s="407" t="n"/>
+      <c r="E17" s="439" t="n"/>
+      <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="407" t="n"/>
+      <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -15982,13 +16102,13 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="419" t="inlineStr">
+      <c r="F18" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="G18" s="411" t="inlineStr">
+      <c r="G18" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 6º e 7º tempos</t>
@@ -16007,8 +16127,8 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="406" t="n"/>
-      <c r="G19" s="406" t="n"/>
+      <c r="F19" s="437" t="n"/>
+      <c r="G19" s="437" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -16030,8 +16150,8 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="407" t="n"/>
-      <c r="G20" s="407" t="n"/>
+      <c r="F20" s="439" t="n"/>
+      <c r="G20" s="439" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -16057,20 +16177,20 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="417" t="inlineStr">
+      <c r="E21" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="405" t="inlineStr">
+      <c r="G21" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H21" s="420" t="inlineStr">
+      <c r="H21" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
 4º e 5º tempos</t>
@@ -16099,10 +16219,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="406" t="n"/>
+      <c r="E22" s="437" t="n"/>
       <c r="F22" s="63" t="n"/>
-      <c r="G22" s="406" t="n"/>
-      <c r="H22" s="406" t="n"/>
+      <c r="G22" s="437" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -16114,10 +16234,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="407" t="n"/>
+      <c r="E23" s="439" t="n"/>
       <c r="F23" s="63" t="n"/>
-      <c r="G23" s="407" t="n"/>
-      <c r="H23" s="407" t="n"/>
+      <c r="G23" s="439" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -16143,9 +16263,14 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="409" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="428" t="inlineStr">
+      <c r="G24" s="459" t="inlineStr">
         <is>
           <t>Fil - LAn
 9º tempo</t>
@@ -16167,9 +16292,9 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="283" t="n"/>
+      <c r="E25" s="406" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="415" t="n"/>
+      <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
@@ -16186,9 +16311,9 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="283" t="n"/>
+      <c r="E26" s="407" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="416" t="n"/>
+      <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
@@ -16218,13 +16343,13 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="429" t="inlineStr">
+      <c r="E27" s="460" t="inlineStr">
         <is>
           <t>Ing - Bea
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="F27" s="421" t="inlineStr">
+      <c r="F27" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 8º ao 10º tempos</t>
@@ -16247,8 +16372,8 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="406" t="n"/>
-      <c r="F28" s="406" t="n"/>
+      <c r="E28" s="437" t="n"/>
+      <c r="F28" s="437" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
@@ -16266,8 +16391,8 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="407" t="n"/>
-      <c r="F29" s="407" t="n"/>
+      <c r="E29" s="439" t="n"/>
+      <c r="F29" s="439" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
@@ -16298,7 +16423,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="410" t="inlineStr">
+      <c r="E30" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -16326,7 +16451,7 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="406" t="n"/>
+      <c r="E31" s="437" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="283" t="n"/>
@@ -16345,7 +16470,7 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="407" t="n"/>
+      <c r="E32" s="439" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="283" t="n"/>
@@ -16474,7 +16599,7 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="403" t="inlineStr">
+      <c r="F36" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
 9º e 10º tempos</t>
@@ -16482,7 +16607,7 @@
       </c>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="426" t="inlineStr">
+      <c r="I36" s="456" t="inlineStr">
         <is>
           <t>Soc - Kle
 4º tempo</t>
@@ -16506,10 +16631,10 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="406" t="n"/>
+      <c r="F37" s="437" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="406" t="n"/>
+      <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -16528,10 +16653,10 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="407" t="n"/>
+      <c r="F38" s="439" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="407" t="n"/>
+      <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -16552,19 +16677,19 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="418" t="inlineStr">
+      <c r="E39" s="450" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="F39" s="418" t="inlineStr">
+      <c r="F39" s="450" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G39" s="411" t="inlineStr">
+      <c r="G39" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 6º e 7º tempos</t>
@@ -16579,9 +16704,9 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="406" t="n"/>
-      <c r="F40" s="406" t="n"/>
-      <c r="G40" s="406" t="n"/>
+      <c r="E40" s="437" t="n"/>
+      <c r="F40" s="437" t="n"/>
+      <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
@@ -16591,9 +16716,9 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="407" t="n"/>
-      <c r="F41" s="407" t="n"/>
-      <c r="G41" s="407" t="n"/>
+      <c r="E41" s="439" t="n"/>
+      <c r="F41" s="439" t="n"/>
+      <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
@@ -16618,7 +16743,7 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="409" t="inlineStr">
+      <c r="G42" s="441" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
@@ -16641,7 +16766,7 @@
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
-      <c r="G43" s="406" t="n"/>
+      <c r="G43" s="437" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -16654,7 +16779,7 @@
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
-      <c r="G44" s="407" t="n"/>
+      <c r="G44" s="439" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -16679,13 +16804,13 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="417" t="inlineStr">
+      <c r="F45" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="G45" s="405" t="inlineStr">
+      <c r="G45" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
@@ -16702,8 +16827,8 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="406" t="n"/>
-      <c r="G46" s="406" t="n"/>
+      <c r="F46" s="437" t="n"/>
+      <c r="G46" s="437" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -16715,8 +16840,8 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="407" t="n"/>
-      <c r="G47" s="407" t="n"/>
+      <c r="F47" s="439" t="n"/>
+      <c r="G47" s="439" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -16748,7 +16873,7 @@
         </is>
       </c>
       <c r="G48" s="283" t="n"/>
-      <c r="H48" s="420" t="inlineStr">
+      <c r="H48" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
 4º e 5º tempos</t>
@@ -16769,7 +16894,7 @@
       <c r="E49" s="283" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
-      <c r="H49" s="406" t="n"/>
+      <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -16781,7 +16906,7 @@
       <c r="E50" s="78" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
-      <c r="H50" s="407" t="n"/>
+      <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -17062,6 +17187,7 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -17135,7 +17261,6 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
@@ -17544,24 +17669,19 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="418" t="inlineStr">
+      <c r="F12" s="450" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G12" s="418" t="inlineStr">
+      <c r="G12" s="450" t="inlineStr">
         <is>
           <t>S3-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="409" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H12" s="435" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -17575,9 +17695,9 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="222" t="n"/>
-      <c r="F13" s="406" t="n"/>
-      <c r="G13" s="406" t="n"/>
-      <c r="H13" s="406" t="n"/>
+      <c r="F13" s="437" t="n"/>
+      <c r="G13" s="437" t="n"/>
+      <c r="H13" s="438" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -17591,9 +17711,9 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="222" t="n"/>
-      <c r="F14" s="407" t="n"/>
-      <c r="G14" s="407" t="n"/>
-      <c r="H14" s="407" t="n"/>
+      <c r="F14" s="439" t="n"/>
+      <c r="G14" s="439" t="n"/>
+      <c r="H14" s="438" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -17619,20 +17739,20 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="410" t="inlineStr">
+      <c r="E15" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F15" s="403" t="inlineStr">
+      <c r="F15" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
 11º e 12º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="421" t="inlineStr">
+      <c r="H15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 9º ao 11º tempos</t>
@@ -17649,10 +17769,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="406" t="n"/>
-      <c r="F16" s="406" t="n"/>
+      <c r="E16" s="437" t="n"/>
+      <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="406" t="n"/>
+      <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -17665,10 +17785,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="407" t="n"/>
-      <c r="F17" s="407" t="n"/>
+      <c r="E17" s="439" t="n"/>
+      <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="407" t="n"/>
+      <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -17698,13 +17818,13 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="419" t="inlineStr">
+      <c r="F18" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="G18" s="411" t="inlineStr">
+      <c r="G18" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 6º e 7º tempos</t>
@@ -17728,8 +17848,8 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="406" t="n"/>
-      <c r="G19" s="406" t="n"/>
+      <c r="F19" s="437" t="n"/>
+      <c r="G19" s="437" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -17751,8 +17871,8 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="407" t="n"/>
-      <c r="G20" s="407" t="n"/>
+      <c r="F20" s="439" t="n"/>
+      <c r="G20" s="439" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -17778,20 +17898,20 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="417" t="inlineStr">
+      <c r="E21" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="405" t="inlineStr">
+      <c r="G21" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H21" s="420" t="inlineStr">
+      <c r="H21" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
 4º e 5º tempos</t>
@@ -17820,10 +17940,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="406" t="n"/>
+      <c r="E22" s="437" t="n"/>
       <c r="F22" s="63" t="n"/>
-      <c r="G22" s="406" t="n"/>
-      <c r="H22" s="406" t="n"/>
+      <c r="G22" s="437" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -17835,10 +17955,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="407" t="n"/>
+      <c r="E23" s="439" t="n"/>
       <c r="F23" s="63" t="n"/>
-      <c r="G23" s="407" t="n"/>
-      <c r="H23" s="407" t="n"/>
+      <c r="G23" s="439" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -17864,9 +17984,14 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="409" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="428" t="inlineStr">
+      <c r="G24" s="459" t="inlineStr">
         <is>
           <t>Fil - LAn
 9º tempo</t>
@@ -17888,9 +18013,9 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="283" t="n"/>
+      <c r="E25" s="406" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="415" t="n"/>
+      <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
@@ -17907,9 +18032,9 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="283" t="n"/>
+      <c r="E26" s="407" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="416" t="n"/>
+      <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
@@ -17940,7 +18065,7 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="421" t="inlineStr">
+      <c r="F27" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
 8º ao 10º tempos</t>
@@ -17964,7 +18089,7 @@
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
-      <c r="F28" s="406" t="n"/>
+      <c r="F28" s="437" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
@@ -17983,7 +18108,7 @@
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
-      <c r="F29" s="407" t="n"/>
+      <c r="F29" s="439" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
@@ -18014,7 +18139,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="410" t="inlineStr">
+      <c r="E30" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 6º e 7º tempos</t>
@@ -18042,7 +18167,7 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="406" t="n"/>
+      <c r="E31" s="437" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="283" t="n"/>
@@ -18061,7 +18186,7 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="407" t="n"/>
+      <c r="E32" s="439" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="283" t="n"/>
@@ -18189,13 +18314,13 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="408" t="inlineStr">
+      <c r="E36" s="440" t="inlineStr">
         <is>
           <t>Ing - PaH
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F36" s="403" t="inlineStr">
+      <c r="F36" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
 9º e 10º tempos</t>
@@ -18203,7 +18328,7 @@
       </c>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="426" t="inlineStr">
+      <c r="I36" s="456" t="inlineStr">
         <is>
           <t>Soc - Kle
 4º tempo</t>
@@ -18226,11 +18351,11 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="406" t="n"/>
-      <c r="F37" s="406" t="n"/>
+      <c r="E37" s="437" t="n"/>
+      <c r="F37" s="437" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="406" t="n"/>
+      <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -18248,11 +18373,11 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="407" t="n"/>
-      <c r="F38" s="407" t="n"/>
+      <c r="E38" s="439" t="n"/>
+      <c r="F38" s="439" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="407" t="n"/>
+      <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -18273,19 +18398,19 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="418" t="inlineStr">
+      <c r="E39" s="450" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="F39" s="418" t="inlineStr">
+      <c r="F39" s="450" t="inlineStr">
         <is>
           <t>S4-11
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G39" s="411" t="inlineStr">
+      <c r="G39" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
 6º e 7º tempos</t>
@@ -18300,9 +18425,9 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="406" t="n"/>
-      <c r="F40" s="406" t="n"/>
-      <c r="G40" s="406" t="n"/>
+      <c r="E40" s="437" t="n"/>
+      <c r="F40" s="437" t="n"/>
+      <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="283" t="n"/>
       <c r="J40" s="352" t="n"/>
@@ -18312,9 +18437,9 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="407" t="n"/>
-      <c r="F41" s="407" t="n"/>
-      <c r="G41" s="407" t="n"/>
+      <c r="E41" s="439" t="n"/>
+      <c r="F41" s="439" t="n"/>
+      <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="283" t="n"/>
       <c r="J41" s="352" t="n"/>
@@ -18339,7 +18464,7 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="409" t="inlineStr">
+      <c r="G42" s="441" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
@@ -18362,7 +18487,7 @@
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
-      <c r="G43" s="406" t="n"/>
+      <c r="G43" s="437" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -18375,7 +18500,7 @@
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
-      <c r="G44" s="407" t="n"/>
+      <c r="G44" s="439" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -18400,13 +18525,13 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="417" t="inlineStr">
+      <c r="F45" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="G45" s="405" t="inlineStr">
+      <c r="G45" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
@@ -18423,8 +18548,8 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="406" t="n"/>
-      <c r="G46" s="406" t="n"/>
+      <c r="F46" s="437" t="n"/>
+      <c r="G46" s="437" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -18436,8 +18561,8 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="407" t="n"/>
-      <c r="G47" s="407" t="n"/>
+      <c r="F47" s="439" t="n"/>
+      <c r="G47" s="439" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -18469,7 +18594,7 @@
         </is>
       </c>
       <c r="G48" s="283" t="n"/>
-      <c r="H48" s="420" t="inlineStr">
+      <c r="H48" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
 4º e 5º tempos</t>
@@ -18490,7 +18615,7 @@
       <c r="E49" s="283" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
-      <c r="H49" s="406" t="n"/>
+      <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -18502,7 +18627,7 @@
       <c r="E50" s="78" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
-      <c r="H50" s="407" t="n"/>
+      <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -18783,6 +18908,7 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -18855,7 +18981,6 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
@@ -19264,17 +19389,17 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="421" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-9º ao 11º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="405" t="inlineStr">
+      <c r="F12" s="405" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="420" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -19334,20 +19459,20 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="410" t="inlineStr">
+      <c r="E15" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="417" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+      <c r="F15" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+9º ao 11º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="408" t="inlineStr">
+      <c r="H15" s="440" t="inlineStr">
         <is>
           <t>Ing - PaH
 4º e 5º tempos</t>
@@ -19364,10 +19489,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="406" t="n"/>
+      <c r="E16" s="437" t="n"/>
       <c r="F16" s="406" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="406" t="n"/>
+      <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -19380,10 +19505,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="407" t="n"/>
+      <c r="E17" s="439" t="n"/>
       <c r="F17" s="407" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="407" t="n"/>
+      <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -19413,14 +19538,14 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="403" t="inlineStr">
+      <c r="F18" s="434" t="inlineStr">
         <is>
           <t>Hist - Wag
 11º e 12º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="409" t="inlineStr">
+      <c r="H18" s="441" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 4º e 5º tempos</t>
@@ -19443,9 +19568,9 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="406" t="n"/>
+      <c r="F19" s="437" t="n"/>
       <c r="G19" s="222" t="n"/>
-      <c r="H19" s="406" t="n"/>
+      <c r="H19" s="437" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -19466,9 +19591,9 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="407" t="n"/>
+      <c r="F20" s="439" t="n"/>
       <c r="G20" s="222" t="n"/>
-      <c r="H20" s="407" t="n"/>
+      <c r="H20" s="439" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -19493,25 +19618,25 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="411" t="inlineStr">
+      <c r="E21" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F21" s="420" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="418" t="inlineStr">
+      <c r="F21" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G21" s="450" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H21" s="418" t="inlineStr">
+      <c r="H21" s="450" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
@@ -19540,10 +19665,10 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="406" t="n"/>
+      <c r="E22" s="437" t="n"/>
       <c r="F22" s="406" t="n"/>
-      <c r="G22" s="406" t="n"/>
-      <c r="H22" s="406" t="n"/>
+      <c r="G22" s="437" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -19555,10 +19680,10 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="407" t="n"/>
+      <c r="E23" s="439" t="n"/>
       <c r="F23" s="407" t="n"/>
-      <c r="G23" s="407" t="n"/>
-      <c r="H23" s="407" t="n"/>
+      <c r="G23" s="439" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -19586,7 +19711,7 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="433" t="inlineStr">
+      <c r="G24" s="461" t="inlineStr">
         <is>
           <t>Soc - Kle
 2º tempo</t>
@@ -19610,7 +19735,7 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="415" t="n"/>
+      <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
@@ -19629,7 +19754,7 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="416" t="n"/>
+      <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
@@ -19661,9 +19786,14 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="427" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="421" t="inlineStr">
+      <c r="I27" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 1º ao 3º tempos</t>
@@ -19685,9 +19815,9 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="283" t="n"/>
+      <c r="G28" s="406" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="406" t="n"/>
+      <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -19704,9 +19834,9 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="283" t="n"/>
+      <c r="G29" s="407" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="407" t="n"/>
+      <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -19735,14 +19865,14 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="417" t="inlineStr">
+      <c r="F30" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º e 2º tempos</t>
         </is>
       </c>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="405" t="inlineStr">
+      <c r="H30" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
@@ -19768,9 +19898,9 @@
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
-      <c r="F31" s="406" t="n"/>
+      <c r="F31" s="437" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="406" t="n"/>
+      <c r="H31" s="437" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -19787,9 +19917,9 @@
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
-      <c r="F32" s="407" t="n"/>
+      <c r="F32" s="439" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="407" t="n"/>
+      <c r="H32" s="439" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -19915,7 +20045,7 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="403" t="inlineStr">
+      <c r="F36" s="434" t="inlineStr">
         <is>
           <t>Hist - Wag
 10º e 11º tempos</t>
@@ -19923,7 +20053,7 @@
       </c>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="410" t="inlineStr">
+      <c r="I36" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 2º e 3º tempos</t>
@@ -19947,10 +20077,10 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="406" t="n"/>
+      <c r="F37" s="437" t="n"/>
       <c r="G37" s="283" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="406" t="n"/>
+      <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -19969,10 +20099,10 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="407" t="n"/>
+      <c r="F38" s="439" t="n"/>
       <c r="G38" s="283" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="407" t="n"/>
+      <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -19996,13 +20126,13 @@
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="420" t="inlineStr">
+      <c r="H39" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I39" s="411" t="inlineStr">
+      <c r="I39" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 6º e 7º tempos</t>
@@ -20018,8 +20148,8 @@
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="283" t="n"/>
-      <c r="H40" s="406" t="n"/>
-      <c r="I40" s="406" t="n"/>
+      <c r="H40" s="437" t="n"/>
+      <c r="I40" s="437" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -20030,8 +20160,8 @@
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="283" t="n"/>
-      <c r="H41" s="407" t="n"/>
-      <c r="I41" s="407" t="n"/>
+      <c r="H41" s="439" t="n"/>
+      <c r="I41" s="439" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -20055,13 +20185,13 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="408" t="inlineStr">
+      <c r="H42" s="440" t="inlineStr">
         <is>
           <t>Ing - PaH
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I42" s="419" t="inlineStr">
+      <c r="I42" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 4º e 5º tempos</t>
@@ -20083,8 +20213,8 @@
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="283" t="n"/>
-      <c r="H43" s="406" t="n"/>
-      <c r="I43" s="406" t="n"/>
+      <c r="H43" s="437" t="n"/>
+      <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -20096,8 +20226,8 @@
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="283" t="n"/>
-      <c r="H44" s="407" t="n"/>
-      <c r="I44" s="407" t="n"/>
+      <c r="H44" s="439" t="n"/>
+      <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -20120,18 +20250,13 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="409" t="inlineStr">
+      <c r="F45" s="441" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G45" s="427" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
+      <c r="G45" s="435" t="n"/>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
@@ -20148,8 +20273,8 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="406" t="n"/>
-      <c r="G46" s="406" t="n"/>
+      <c r="F46" s="437" t="n"/>
+      <c r="G46" s="438" t="n"/>
       <c r="H46" s="283" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -20161,8 +20286,8 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="407" t="n"/>
-      <c r="G47" s="407" t="n"/>
+      <c r="F47" s="439" t="n"/>
+      <c r="G47" s="438" t="n"/>
       <c r="H47" s="283" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -20469,7 +20594,6 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="G45:G47"/>
     <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
@@ -20579,6 +20703,7 @@
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="I27:I29"/>
+    <mergeCell ref="G27:G29"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -1842,7 +1842,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="462">
+  <cellXfs count="464">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3413,6 +3413,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="25" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5914,14 +5922,14 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F12" s="405" t="inlineStr">
+      <c r="F12" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="420" t="inlineStr">
+      <c r="H12" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
 1º e 2º tempos</t>
@@ -5940,9 +5948,9 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="437" t="n"/>
-      <c r="F13" s="406" t="n"/>
+      <c r="F13" s="437" t="n"/>
       <c r="G13" s="222" t="n"/>
-      <c r="H13" s="406" t="n"/>
+      <c r="H13" s="437" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -5956,9 +5964,9 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="439" t="n"/>
-      <c r="F14" s="407" t="n"/>
+      <c r="F14" s="439" t="n"/>
       <c r="G14" s="222" t="n"/>
-      <c r="H14" s="407" t="n"/>
+      <c r="H14" s="439" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -5990,7 +5998,7 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="421" t="inlineStr">
+      <c r="F15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 9º ao 11º tempos</t>
@@ -6010,7 +6018,7 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
-      <c r="F16" s="406" t="n"/>
+      <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
       <c r="H16" s="222" t="n"/>
       <c r="I16" s="222" t="n"/>
@@ -6026,7 +6034,7 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
-      <c r="F17" s="407" t="n"/>
+      <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
       <c r="H17" s="222" t="n"/>
       <c r="I17" s="222" t="n"/>
@@ -6144,7 +6152,7 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F21" s="417" t="inlineStr">
+      <c r="F21" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
@@ -6186,7 +6194,7 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="437" t="n"/>
-      <c r="F22" s="406" t="n"/>
+      <c r="F22" s="437" t="n"/>
       <c r="G22" s="437" t="n"/>
       <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
@@ -6201,7 +6209,7 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="439" t="n"/>
-      <c r="F23" s="407" t="n"/>
+      <c r="F23" s="439" t="n"/>
       <c r="G23" s="439" t="n"/>
       <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
@@ -6311,7 +6319,7 @@
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="427" t="inlineStr">
+      <c r="G27" s="457" t="inlineStr">
         <is>
           <t>Fil - LAn
 4º tempo</t>
@@ -6340,7 +6348,7 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="437" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="406" t="n"/>
+      <c r="G28" s="437" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
@@ -6359,7 +6367,7 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="439" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="407" t="n"/>
+      <c r="G29" s="439" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
@@ -6390,12 +6398,7 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F30" s="435" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="436" t="inlineStr">
         <is>
@@ -6423,7 +6426,7 @@
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
-      <c r="F31" s="437" t="n"/>
+      <c r="F31" s="438" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="437" t="n"/>
       <c r="I31" s="283" t="n"/>
@@ -6442,7 +6445,7 @@
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
-      <c r="F32" s="439" t="n"/>
+      <c r="F32" s="438" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="439" t="n"/>
       <c r="I32" s="283" t="n"/>
@@ -6708,7 +6711,12 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
+      <c r="F42" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
       <c r="I42" s="451" t="inlineStr">
@@ -6731,7 +6739,7 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
+      <c r="F43" s="406" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="437" t="n"/>
@@ -6744,7 +6752,7 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
+      <c r="F44" s="407" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="439" t="n"/>
@@ -7136,7 +7144,6 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
-    <mergeCell ref="F30:F32"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -7188,6 +7195,7 @@
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
@@ -9224,7 +9232,7 @@
       </c>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="404" t="inlineStr">
+      <c r="G15" s="462" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
@@ -9249,7 +9257,7 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
       <c r="F16" s="222" t="n"/>
-      <c r="G16" s="406" t="n"/>
+      <c r="G16" s="437" t="n"/>
       <c r="H16" s="222" t="n"/>
       <c r="I16" s="437" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -9265,7 +9273,7 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
       <c r="F17" s="222" t="n"/>
-      <c r="G17" s="407" t="n"/>
+      <c r="G17" s="439" t="n"/>
       <c r="H17" s="222" t="n"/>
       <c r="I17" s="439" t="n"/>
       <c r="J17" s="315" t="n"/>
@@ -9454,12 +9462,7 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="445" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G24" s="438" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="446" t="inlineStr">
         <is>
@@ -9483,7 +9486,7 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="447" t="n"/>
+      <c r="G25" s="438" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="437" t="n"/>
       <c r="J25" s="352" t="n"/>
@@ -9502,7 +9505,7 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="448" t="n"/>
+      <c r="G26" s="438" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="439" t="n"/>
       <c r="J26" s="352" t="n"/>
@@ -9794,7 +9797,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="462" t="inlineStr">
+        <is>
+          <t>Port - Jana
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="440" t="inlineStr">
         <is>
@@ -9821,7 +9829,7 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="437" t="n"/>
-      <c r="G37" s="283" t="n"/>
+      <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -9843,7 +9851,7 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="439" t="n"/>
-      <c r="G38" s="283" t="n"/>
+      <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -10039,12 +10047,7 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="452" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E48" s="435" t="n"/>
       <c r="F48" s="402" t="n"/>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="444" t="inlineStr">
@@ -10065,7 +10068,7 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="437" t="n"/>
+      <c r="E49" s="438" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="437" t="n"/>
@@ -10077,7 +10080,7 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="439" t="n"/>
+      <c r="E50" s="438" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="439" t="n"/>
@@ -10102,7 +10105,12 @@
         <f>B51+4</f>
         <v/>
       </c>
-      <c r="E51" s="283" t="n"/>
+      <c r="E51" s="452" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
@@ -10119,7 +10127,7 @@
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
       <c r="D52" s="350" t="n"/>
-      <c r="E52" s="283" t="n"/>
+      <c r="E52" s="437" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
@@ -10131,7 +10139,7 @@
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
       <c r="D53" s="350" t="n"/>
-      <c r="E53" s="283" t="n"/>
+      <c r="E53" s="439" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
@@ -10316,6 +10324,7 @@
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="L42:L47"/>
     <mergeCell ref="B21:B23"/>
+    <mergeCell ref="E51:E53"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="G42:G44"/>
@@ -10352,7 +10361,6 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
-    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
@@ -10415,7 +10423,6 @@
     <mergeCell ref="G18:G20"/>
     <mergeCell ref="I24:I26"/>
     <mergeCell ref="I18:I20"/>
-    <mergeCell ref="G24:G26"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
     <mergeCell ref="D12:D14"/>
@@ -10443,6 +10450,7 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="G27:G29"/>
     <mergeCell ref="I27:I29"/>
+    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>
@@ -10910,7 +10918,7 @@
       </c>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="404" t="inlineStr">
+      <c r="G15" s="462" t="inlineStr">
         <is>
           <t>Port - Jana
 4º e 5º tempos</t>
@@ -10935,7 +10943,7 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="222" t="n"/>
       <c r="F16" s="222" t="n"/>
-      <c r="G16" s="406" t="n"/>
+      <c r="G16" s="437" t="n"/>
       <c r="H16" s="222" t="n"/>
       <c r="I16" s="437" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -10951,7 +10959,7 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="222" t="n"/>
       <c r="F17" s="222" t="n"/>
-      <c r="G17" s="407" t="n"/>
+      <c r="G17" s="439" t="n"/>
       <c r="H17" s="222" t="n"/>
       <c r="I17" s="439" t="n"/>
       <c r="J17" s="315" t="n"/>
@@ -11140,12 +11148,7 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="445" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G24" s="438" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="446" t="inlineStr">
         <is>
@@ -11169,7 +11172,7 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="447" t="n"/>
+      <c r="G25" s="438" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="437" t="n"/>
       <c r="J25" s="352" t="n"/>
@@ -11188,7 +11191,7 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="448" t="n"/>
+      <c r="G26" s="438" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="439" t="n"/>
       <c r="J26" s="352" t="n"/>
@@ -11480,7 +11483,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="462" t="inlineStr">
+        <is>
+          <t>Port - Jana
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="440" t="inlineStr">
         <is>
@@ -11507,7 +11515,7 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="437" t="n"/>
-      <c r="G37" s="283" t="n"/>
+      <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -11529,7 +11537,7 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="439" t="n"/>
-      <c r="G38" s="283" t="n"/>
+      <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -11725,12 +11733,7 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="452" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E48" s="435" t="n"/>
       <c r="F48" s="402" t="n"/>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="444" t="inlineStr">
@@ -11751,7 +11754,7 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="437" t="n"/>
+      <c r="E49" s="438" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="437" t="n"/>
@@ -11763,7 +11766,7 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="439" t="n"/>
+      <c r="E50" s="438" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="439" t="n"/>
@@ -11788,7 +11791,12 @@
         <f>B51+4</f>
         <v/>
       </c>
-      <c r="E51" s="283" t="n"/>
+      <c r="E51" s="452" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
@@ -11805,7 +11813,7 @@
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
       <c r="D52" s="350" t="n"/>
-      <c r="E52" s="283" t="n"/>
+      <c r="E52" s="437" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
@@ -11817,7 +11825,7 @@
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
       <c r="D53" s="350" t="n"/>
-      <c r="E53" s="283" t="n"/>
+      <c r="E53" s="439" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
@@ -12002,6 +12010,7 @@
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="L42:L47"/>
     <mergeCell ref="B21:B23"/>
+    <mergeCell ref="E51:E53"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="G42:G44"/>
@@ -12038,7 +12047,6 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
-    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
@@ -12101,7 +12109,6 @@
     <mergeCell ref="G18:G20"/>
     <mergeCell ref="I24:I26"/>
     <mergeCell ref="I18:I20"/>
-    <mergeCell ref="G24:G26"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
     <mergeCell ref="D12:D14"/>
@@ -12129,6 +12136,7 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="G27:G29"/>
     <mergeCell ref="I27:I29"/>
+    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>
@@ -12523,7 +12531,7 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="419" t="inlineStr">
+      <c r="E12" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
@@ -12554,7 +12562,7 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="406" t="n"/>
+      <c r="E13" s="437" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
@@ -12570,7 +12578,7 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="407" t="n"/>
+      <c r="E14" s="439" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
@@ -12599,7 +12607,12 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="453" t="inlineStr">
         <is>
@@ -12624,7 +12637,7 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="222" t="n"/>
+      <c r="E16" s="406" t="n"/>
       <c r="F16" s="222" t="n"/>
       <c r="G16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
@@ -12640,7 +12653,7 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="222" t="n"/>
+      <c r="E17" s="407" t="n"/>
       <c r="F17" s="222" t="n"/>
       <c r="G17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
@@ -12753,12 +12766,7 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="421" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="435" t="n"/>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="441" t="inlineStr">
@@ -12790,7 +12798,7 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="406" t="n"/>
+      <c r="E22" s="438" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
@@ -12805,7 +12813,7 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="407" t="n"/>
+      <c r="E23" s="438" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
@@ -13734,7 +13742,6 @@
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
-    <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -13797,6 +13804,7 @@
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="F42:F44"/>
     <mergeCell ref="H36:H38"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
@@ -14226,7 +14234,7 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="419" t="inlineStr">
+      <c r="E12" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
@@ -14257,7 +14265,7 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="406" t="n"/>
+      <c r="E13" s="437" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
@@ -14273,7 +14281,7 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="407" t="n"/>
+      <c r="E14" s="439" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
@@ -14302,7 +14310,12 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="440" t="inlineStr">
         <is>
           <t>Ing - Vir
@@ -14327,7 +14340,7 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="222" t="n"/>
+      <c r="E16" s="406" t="n"/>
       <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
       <c r="H16" s="437" t="n"/>
@@ -14343,7 +14356,7 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="222" t="n"/>
+      <c r="E17" s="407" t="n"/>
       <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
       <c r="H17" s="439" t="n"/>
@@ -14456,12 +14469,7 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="421" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E21" s="435" t="n"/>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="441" t="inlineStr">
@@ -14493,7 +14501,7 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="406" t="n"/>
+      <c r="E22" s="438" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
@@ -14508,7 +14516,7 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="407" t="n"/>
+      <c r="E23" s="438" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
@@ -15448,7 +15456,6 @@
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
-    <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -15511,6 +15518,7 @@
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="F42:F44"/>
     <mergeCell ref="H36:H38"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
@@ -16263,7 +16271,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="409" t="inlineStr">
+      <c r="E24" s="441" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
@@ -16292,7 +16300,7 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="406" t="n"/>
+      <c r="E25" s="437" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -16311,7 +16319,7 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="407" t="n"/>
+      <c r="E26" s="439" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -16866,12 +16874,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="430" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F48" s="435" t="n"/>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="452" t="inlineStr">
         <is>
@@ -16892,7 +16895,7 @@
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="351" t="n"/>
+      <c r="F49" s="438" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
@@ -16904,7 +16907,7 @@
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="387" t="n"/>
+      <c r="F50" s="438" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
@@ -16929,7 +16932,12 @@
         <v/>
       </c>
       <c r="E51" s="283" t="n"/>
-      <c r="F51" s="183" t="n"/>
+      <c r="F51" s="463" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
       <c r="I51" s="386" t="inlineStr">
@@ -17117,7 +17125,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="171">
+  <mergeCells count="170">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -17262,7 +17270,6 @@
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="D54:D56"/>
-    <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="H48:H50"/>
     <mergeCell ref="F57:F59"/>
@@ -17984,7 +17991,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="409" t="inlineStr">
+      <c r="E24" s="441" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 2º e 3º tempos</t>
@@ -18013,7 +18020,7 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="406" t="n"/>
+      <c r="E25" s="437" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -18032,7 +18039,7 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="407" t="n"/>
+      <c r="E26" s="439" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -18587,12 +18594,7 @@
         <v/>
       </c>
       <c r="E48" s="283" t="n"/>
-      <c r="F48" s="430" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F48" s="435" t="n"/>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="452" t="inlineStr">
         <is>
@@ -18613,7 +18615,7 @@
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
       <c r="E49" s="283" t="n"/>
-      <c r="F49" s="351" t="n"/>
+      <c r="F49" s="438" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
@@ -18625,7 +18627,7 @@
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
       <c r="E50" s="78" t="n"/>
-      <c r="F50" s="387" t="n"/>
+      <c r="F50" s="438" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
@@ -18650,7 +18652,12 @@
         <v/>
       </c>
       <c r="E51" s="283" t="n"/>
-      <c r="F51" s="183" t="n"/>
+      <c r="F51" s="463" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
       <c r="I51" s="386" t="inlineStr">
@@ -18838,7 +18845,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="170">
+  <mergeCells count="169">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -18982,7 +18989,6 @@
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
     <mergeCell ref="D54:D56"/>
-    <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="H48:H50"/>
     <mergeCell ref="F57:F59"/>
@@ -19389,14 +19395,14 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="405" t="inlineStr">
+      <c r="F12" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="420" t="inlineStr">
+      <c r="H12" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
 1º e 2º tempos</t>
@@ -19415,9 +19421,9 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="222" t="n"/>
-      <c r="F13" s="406" t="n"/>
+      <c r="F13" s="437" t="n"/>
       <c r="G13" s="222" t="n"/>
-      <c r="H13" s="406" t="n"/>
+      <c r="H13" s="437" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -19431,9 +19437,9 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="222" t="n"/>
-      <c r="F14" s="407" t="n"/>
+      <c r="F14" s="439" t="n"/>
       <c r="G14" s="222" t="n"/>
-      <c r="H14" s="407" t="n"/>
+      <c r="H14" s="439" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -19465,7 +19471,7 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="421" t="inlineStr">
+      <c r="F15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 9º ao 11º tempos</t>
@@ -19490,7 +19496,7 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
-      <c r="F16" s="406" t="n"/>
+      <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
@@ -19506,7 +19512,7 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
-      <c r="F17" s="407" t="n"/>
+      <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
@@ -19624,7 +19630,7 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F21" s="417" t="inlineStr">
+      <c r="F21" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 2º e 3º tempos</t>
@@ -19666,7 +19672,7 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="437" t="n"/>
-      <c r="F22" s="406" t="n"/>
+      <c r="F22" s="437" t="n"/>
       <c r="G22" s="437" t="n"/>
       <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
@@ -19681,7 +19687,7 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="439" t="n"/>
-      <c r="F23" s="407" t="n"/>
+      <c r="F23" s="439" t="n"/>
       <c r="G23" s="439" t="n"/>
       <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
@@ -19786,7 +19792,7 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="427" t="inlineStr">
+      <c r="G27" s="457" t="inlineStr">
         <is>
           <t>Fil - LAn
 4º tempo</t>
@@ -19815,7 +19821,7 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="406" t="n"/>
+      <c r="G28" s="437" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
@@ -19834,7 +19840,7 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="407" t="n"/>
+      <c r="G29" s="439" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
@@ -19865,12 +19871,7 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F30" s="435" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="436" t="inlineStr">
         <is>
@@ -19898,7 +19899,7 @@
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
-      <c r="F31" s="437" t="n"/>
+      <c r="F31" s="438" t="n"/>
       <c r="G31" s="283" t="n"/>
       <c r="H31" s="437" t="n"/>
       <c r="I31" s="283" t="n"/>
@@ -19917,7 +19918,7 @@
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
-      <c r="F32" s="439" t="n"/>
+      <c r="F32" s="438" t="n"/>
       <c r="G32" s="283" t="n"/>
       <c r="H32" s="439" t="n"/>
       <c r="I32" s="283" t="n"/>
@@ -20183,7 +20184,12 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
+      <c r="F42" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G42" s="283" t="n"/>
       <c r="H42" s="440" t="inlineStr">
         <is>
@@ -20211,7 +20217,7 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
+      <c r="F43" s="406" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="437" t="n"/>
       <c r="I43" s="437" t="n"/>
@@ -20224,7 +20230,7 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
+      <c r="F44" s="407" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="439" t="n"/>
       <c r="I44" s="439" t="n"/>
@@ -20616,7 +20622,6 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
-    <mergeCell ref="F30:F32"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -20668,6 +20673,7 @@
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -1842,7 +1842,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="464">
+  <cellXfs count="465">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3420,6 +3420,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="25" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="115" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
@@ -6239,12 +6242,7 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="461" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G24" s="438" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -6263,7 +6261,7 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="447" t="n"/>
+      <c r="G25" s="438" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
@@ -6282,7 +6280,7 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="448" t="n"/>
+      <c r="G26" s="438" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
@@ -6399,7 +6397,12 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="435" t="n"/>
-      <c r="G30" s="283" t="n"/>
+      <c r="G30" s="426" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
       <c r="H30" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
@@ -6427,7 +6430,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="438" t="n"/>
-      <c r="G31" s="283" t="n"/>
+      <c r="G31" s="406" t="n"/>
       <c r="H31" s="437" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -6446,7 +6449,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="438" t="n"/>
-      <c r="G32" s="283" t="n"/>
+      <c r="G32" s="407" t="n"/>
       <c r="H32" s="439" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -6711,7 +6714,7 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="417" t="inlineStr">
+      <c r="F42" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º e 2º tempos</t>
@@ -6739,7 +6742,7 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="406" t="n"/>
+      <c r="F43" s="437" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="283" t="n"/>
       <c r="I43" s="437" t="n"/>
@@ -6752,7 +6755,7 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="407" t="n"/>
+      <c r="F44" s="439" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="283" t="n"/>
       <c r="I44" s="439" t="n"/>
@@ -7122,6 +7125,7 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G30:G32"/>
     <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
@@ -7202,7 +7206,6 @@
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
-    <mergeCell ref="G24:G26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -9537,12 +9540,7 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-3º tempo</t>
-        </is>
-      </c>
+      <c r="G27" s="435" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="450" t="inlineStr">
         <is>
@@ -9566,7 +9564,7 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="437" t="n"/>
+      <c r="G28" s="438" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
@@ -9585,7 +9583,7 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="439" t="n"/>
+      <c r="G29" s="438" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
@@ -9617,12 +9615,7 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="451" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="435" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -9645,7 +9638,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="437" t="n"/>
+      <c r="G31" s="438" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -9664,7 +9657,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="439" t="n"/>
+      <c r="G32" s="438" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -9874,7 +9867,12 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="442" t="inlineStr">
         <is>
@@ -9883,7 +9881,12 @@
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
+      <c r="I39" s="419" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+7º tempo</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9891,11 +9894,11 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="283" t="n"/>
+      <c r="E40" s="406" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
-      <c r="I40" s="283" t="n"/>
+      <c r="I40" s="406" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -9903,11 +9906,11 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="283" t="n"/>
+      <c r="E41" s="407" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
-      <c r="I41" s="283" t="n"/>
+      <c r="I41" s="407" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9936,7 +9939,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H42" s="283" t="n"/>
+      <c r="H42" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+7º tempo</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -9954,7 +9962,7 @@
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="437" t="n"/>
-      <c r="H43" s="283" t="n"/>
+      <c r="H43" s="406" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -9967,7 +9975,7 @@
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="439" t="n"/>
-      <c r="H44" s="283" t="n"/>
+      <c r="H44" s="407" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -10050,12 +10058,7 @@
       <c r="E48" s="435" t="n"/>
       <c r="F48" s="402" t="n"/>
       <c r="G48" s="283" t="n"/>
-      <c r="H48" s="444" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -10071,7 +10074,7 @@
       <c r="E49" s="438" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
-      <c r="H49" s="437" t="n"/>
+      <c r="H49" s="438" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -10083,7 +10086,7 @@
       <c r="E50" s="438" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
-      <c r="H50" s="439" t="n"/>
+      <c r="H50" s="438" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -10105,10 +10108,10 @@
         <f>B51+4</f>
         <v/>
       </c>
-      <c r="E51" s="452" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
+      <c r="E51" s="422" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="F51" s="183" t="n"/>
@@ -10127,7 +10130,7 @@
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
       <c r="D52" s="350" t="n"/>
-      <c r="E52" s="437" t="n"/>
+      <c r="E52" s="406" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
@@ -10139,7 +10142,7 @@
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
       <c r="D53" s="350" t="n"/>
-      <c r="E53" s="439" t="n"/>
+      <c r="E53" s="407" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
@@ -10346,7 +10349,7 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -10354,6 +10357,7 @@
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="I15:I17"/>
@@ -10403,6 +10407,7 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -10437,7 +10442,6 @@
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
-    <mergeCell ref="H48:H50"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
     <mergeCell ref="J39:J41"/>
@@ -10448,7 +10452,6 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G27:G29"/>
     <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
@@ -11223,12 +11226,7 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-3º tempo</t>
-        </is>
-      </c>
+      <c r="G27" s="435" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="450" t="inlineStr">
         <is>
@@ -11252,7 +11250,7 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="437" t="n"/>
+      <c r="G28" s="438" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
@@ -11271,7 +11269,7 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="439" t="n"/>
+      <c r="G29" s="438" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
@@ -11303,12 +11301,7 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="451" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="435" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -11331,7 +11324,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="437" t="n"/>
+      <c r="G31" s="438" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -11350,7 +11343,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="439" t="n"/>
+      <c r="G32" s="438" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -11560,7 +11553,12 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="442" t="inlineStr">
         <is>
@@ -11569,7 +11567,12 @@
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
+      <c r="I39" s="419" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+7º tempo</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11577,11 +11580,11 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="283" t="n"/>
+      <c r="E40" s="406" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
-      <c r="I40" s="283" t="n"/>
+      <c r="I40" s="406" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -11589,11 +11592,11 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="283" t="n"/>
+      <c r="E41" s="407" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
-      <c r="I41" s="283" t="n"/>
+      <c r="I41" s="407" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11622,7 +11625,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H42" s="283" t="n"/>
+      <c r="H42" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+7º tempo</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -11640,7 +11648,7 @@
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="437" t="n"/>
-      <c r="H43" s="283" t="n"/>
+      <c r="H43" s="406" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -11653,7 +11661,7 @@
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="439" t="n"/>
-      <c r="H44" s="283" t="n"/>
+      <c r="H44" s="407" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -11736,12 +11744,7 @@
       <c r="E48" s="435" t="n"/>
       <c r="F48" s="402" t="n"/>
       <c r="G48" s="283" t="n"/>
-      <c r="H48" s="444" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -11757,7 +11760,7 @@
       <c r="E49" s="438" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
-      <c r="H49" s="437" t="n"/>
+      <c r="H49" s="438" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -11769,7 +11772,7 @@
       <c r="E50" s="438" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
-      <c r="H50" s="439" t="n"/>
+      <c r="H50" s="438" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -11791,10 +11794,10 @@
         <f>B51+4</f>
         <v/>
       </c>
-      <c r="E51" s="452" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
+      <c r="E51" s="422" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="F51" s="183" t="n"/>
@@ -11813,7 +11816,7 @@
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
       <c r="D52" s="350" t="n"/>
-      <c r="E52" s="437" t="n"/>
+      <c r="E52" s="406" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
@@ -11825,7 +11828,7 @@
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
       <c r="D53" s="350" t="n"/>
-      <c r="E53" s="439" t="n"/>
+      <c r="E53" s="407" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
@@ -12032,7 +12035,7 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -12040,6 +12043,7 @@
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="I15:I17"/>
@@ -12089,6 +12093,7 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -12123,7 +12128,6 @@
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
-    <mergeCell ref="H48:H50"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
     <mergeCell ref="J39:J41"/>
@@ -12134,7 +12138,6 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G27:G29"/>
     <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
@@ -12607,7 +12610,7 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="421" t="inlineStr">
+      <c r="E15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
@@ -12620,12 +12623,7 @@
 3º e 4º tempos</t>
         </is>
       </c>
-      <c r="H15" s="452" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="H15" s="435" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -12637,10 +12635,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="406" t="n"/>
+      <c r="E16" s="437" t="n"/>
       <c r="F16" s="222" t="n"/>
       <c r="G16" s="437" t="n"/>
-      <c r="H16" s="437" t="n"/>
+      <c r="H16" s="438" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -12653,10 +12651,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="407" t="n"/>
+      <c r="E17" s="439" t="n"/>
       <c r="F17" s="222" t="n"/>
       <c r="G17" s="439" t="n"/>
-      <c r="H17" s="439" t="n"/>
+      <c r="H17" s="438" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -12769,10 +12767,10 @@
       <c r="E21" s="435" t="n"/>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
+      <c r="H21" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -12801,7 +12799,7 @@
       <c r="E22" s="438" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="437" t="n"/>
+      <c r="H22" s="406" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -12816,7 +12814,7 @@
       <c r="E23" s="438" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="439" t="n"/>
+      <c r="H23" s="407" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -12917,12 +12915,7 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="455" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="464" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
@@ -12946,7 +12939,7 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="437" t="n"/>
+      <c r="E28" s="438" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
@@ -12965,7 +12958,7 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="439" t="n"/>
+      <c r="E29" s="438" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
@@ -13000,10 +12993,10 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="452" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
+      <c r="H30" s="409" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I30" s="442" t="inlineStr">
@@ -13033,7 +13026,7 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="437" t="n"/>
+      <c r="H31" s="406" t="n"/>
       <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -13052,7 +13045,7 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="439" t="n"/>
+      <c r="H32" s="407" t="n"/>
       <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -13190,10 +13183,10 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H36" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
+      <c r="H36" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
         </is>
       </c>
       <c r="I36" s="283" t="n"/>
@@ -13217,7 +13210,7 @@
       <c r="E37" s="437" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="437" t="n"/>
-      <c r="H37" s="437" t="n"/>
+      <c r="H37" s="406" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -13239,7 +13232,7 @@
       <c r="E38" s="439" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="439" t="n"/>
-      <c r="H38" s="439" t="n"/>
+      <c r="H38" s="407" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -13261,7 +13254,12 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="457" t="inlineStr">
         <is>
@@ -13283,7 +13281,7 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="283" t="n"/>
+      <c r="E40" s="406" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="437" t="n"/>
@@ -13295,7 +13293,7 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="283" t="n"/>
+      <c r="E41" s="407" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="439" t="n"/>
@@ -13395,7 +13393,12 @@
       </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
+      <c r="H45" s="409" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
@@ -13413,7 +13416,7 @@
       <c r="E46" s="437" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
-      <c r="H46" s="283" t="n"/>
+      <c r="H46" s="406" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -13426,7 +13429,7 @@
       <c r="E47" s="439" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
-      <c r="H47" s="283" t="n"/>
+      <c r="H47" s="407" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -13757,6 +13760,7 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
+    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -13769,7 +13773,6 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
-    <mergeCell ref="E27:E29"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -13781,7 +13784,6 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
-    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -13792,6 +13794,7 @@
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
     <mergeCell ref="G12:G14"/>
+    <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -14310,7 +14313,7 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="421" t="inlineStr">
+      <c r="E15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
@@ -14323,12 +14326,7 @@
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="452" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="H15" s="435" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -14340,10 +14338,10 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="406" t="n"/>
+      <c r="E16" s="437" t="n"/>
       <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="437" t="n"/>
+      <c r="H16" s="438" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -14356,10 +14354,10 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="407" t="n"/>
+      <c r="E17" s="439" t="n"/>
       <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="439" t="n"/>
+      <c r="H17" s="438" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -14472,10 +14470,10 @@
       <c r="E21" s="435" t="n"/>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
+      <c r="H21" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
@@ -14504,7 +14502,7 @@
       <c r="E22" s="438" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="437" t="n"/>
+      <c r="H22" s="406" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -14519,7 +14517,7 @@
       <c r="E23" s="438" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="439" t="n"/>
+      <c r="H23" s="407" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -14620,12 +14618,7 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="455" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="464" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
@@ -14649,7 +14642,7 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="437" t="n"/>
+      <c r="E28" s="438" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
@@ -14668,7 +14661,7 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="439" t="n"/>
+      <c r="E29" s="438" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
@@ -14703,10 +14696,10 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="452" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-9º e 10º tempos</t>
+      <c r="H30" s="409" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I30" s="442" t="inlineStr">
@@ -14736,7 +14729,7 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="437" t="n"/>
+      <c r="H31" s="406" t="n"/>
       <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -14755,7 +14748,7 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="439" t="n"/>
+      <c r="H32" s="407" t="n"/>
       <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -14888,10 +14881,10 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H36" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
+      <c r="H36" s="420" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+9º e 10º tempos</t>
         </is>
       </c>
       <c r="I36" s="283" t="n"/>
@@ -14915,7 +14908,7 @@
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="437" t="n"/>
-      <c r="H37" s="437" t="n"/>
+      <c r="H37" s="406" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -14937,7 +14930,7 @@
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="439" t="n"/>
-      <c r="H38" s="439" t="n"/>
+      <c r="H38" s="407" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -14959,7 +14952,12 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="457" t="inlineStr">
         <is>
@@ -14981,7 +14979,7 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="283" t="n"/>
+      <c r="E40" s="406" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="437" t="n"/>
@@ -14993,7 +14991,7 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="283" t="n"/>
+      <c r="E41" s="407" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="439" t="n"/>
@@ -15098,7 +15096,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H45" s="283" t="n"/>
+      <c r="H45" s="409" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
@@ -15116,7 +15119,7 @@
       <c r="E46" s="437" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="437" t="n"/>
-      <c r="H46" s="283" t="n"/>
+      <c r="H46" s="406" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -15129,7 +15132,7 @@
       <c r="E47" s="439" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="439" t="n"/>
-      <c r="H47" s="283" t="n"/>
+      <c r="H47" s="407" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -15471,6 +15474,7 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
+    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -15483,7 +15487,6 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
-    <mergeCell ref="E27:E29"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -15495,7 +15498,6 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
-    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -15506,6 +15508,7 @@
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
     <mergeCell ref="G12:G14"/>
+    <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -19717,12 +19720,7 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="461" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G24" s="438" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -19741,7 +19739,7 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="447" t="n"/>
+      <c r="G25" s="438" t="n"/>
       <c r="H25" s="283" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
@@ -19760,7 +19758,7 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="448" t="n"/>
+      <c r="G26" s="438" t="n"/>
       <c r="H26" s="283" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
@@ -19872,7 +19870,12 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="435" t="n"/>
-      <c r="G30" s="283" t="n"/>
+      <c r="G30" s="426" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
       <c r="H30" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
@@ -19900,7 +19903,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="438" t="n"/>
-      <c r="G31" s="283" t="n"/>
+      <c r="G31" s="406" t="n"/>
       <c r="H31" s="437" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -19919,7 +19922,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="438" t="n"/>
-      <c r="G32" s="283" t="n"/>
+      <c r="G32" s="407" t="n"/>
       <c r="H32" s="439" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -20184,7 +20187,7 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="417" t="inlineStr">
+      <c r="F42" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º e 2º tempos</t>
@@ -20217,7 +20220,7 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="406" t="n"/>
+      <c r="F43" s="437" t="n"/>
       <c r="G43" s="283" t="n"/>
       <c r="H43" s="437" t="n"/>
       <c r="I43" s="437" t="n"/>
@@ -20230,7 +20233,7 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="407" t="n"/>
+      <c r="F44" s="439" t="n"/>
       <c r="G44" s="283" t="n"/>
       <c r="H44" s="439" t="n"/>
       <c r="I44" s="439" t="n"/>
@@ -20600,6 +20603,7 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G30:G32"/>
     <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
@@ -20680,7 +20684,6 @@
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
-    <mergeCell ref="G24:G26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -5925,17 +5925,17 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F12" s="436" t="inlineStr">
+      <c r="F12" s="422" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="452" t="inlineStr">
+      <c r="H12" s="420" t="inlineStr">
         <is>
           <t>Fis - Cadu
-1º e 2º tempos</t>
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -5951,9 +5951,9 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="437" t="n"/>
-      <c r="F13" s="437" t="n"/>
+      <c r="F13" s="406" t="n"/>
       <c r="G13" s="222" t="n"/>
-      <c r="H13" s="437" t="n"/>
+      <c r="H13" s="406" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -5967,9 +5967,9 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="439" t="n"/>
-      <c r="F14" s="439" t="n"/>
+      <c r="F14" s="407" t="n"/>
       <c r="G14" s="222" t="n"/>
-      <c r="H14" s="439" t="n"/>
+      <c r="H14" s="407" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="435" t="n"/>
-      <c r="G30" s="426" t="inlineStr">
+      <c r="G30" s="456" t="inlineStr">
         <is>
           <t>Soc - Kle
 2º tempo</t>
@@ -6430,7 +6430,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="438" t="n"/>
-      <c r="G31" s="406" t="n"/>
+      <c r="G31" s="437" t="n"/>
       <c r="H31" s="437" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -6449,7 +6449,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="438" t="n"/>
-      <c r="G32" s="407" t="n"/>
+      <c r="G32" s="439" t="n"/>
       <c r="H32" s="439" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -9867,7 +9867,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="417" t="inlineStr">
+      <c r="E39" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º tempo</t>
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="419" t="inlineStr">
+      <c r="I39" s="451" t="inlineStr">
         <is>
           <t>Qui - Fab
 7º tempo</t>
@@ -9894,11 +9894,11 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="406" t="n"/>
+      <c r="E40" s="437" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
-      <c r="I40" s="406" t="n"/>
+      <c r="I40" s="437" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -9906,11 +9906,11 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="407" t="n"/>
+      <c r="E41" s="439" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
-      <c r="I41" s="407" t="n"/>
+      <c r="I41" s="439" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9939,7 +9939,7 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H42" s="420" t="inlineStr">
+      <c r="H42" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 7º tempo</t>
@@ -9962,7 +9962,7 @@
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="437" t="n"/>
-      <c r="H43" s="406" t="n"/>
+      <c r="H43" s="437" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -9975,7 +9975,7 @@
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="439" t="n"/>
-      <c r="H44" s="407" t="n"/>
+      <c r="H44" s="439" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -10108,10 +10108,10 @@
         <f>B51+4</f>
         <v/>
       </c>
-      <c r="E51" s="422" t="inlineStr">
+      <c r="E51" s="412" t="inlineStr">
         <is>
           <t>Redação - Raf
-3º e 4º tempos</t>
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="F51" s="183" t="n"/>
@@ -11553,7 +11553,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="417" t="inlineStr">
+      <c r="E39" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º tempo</t>
@@ -11567,7 +11567,7 @@
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="419" t="inlineStr">
+      <c r="I39" s="451" t="inlineStr">
         <is>
           <t>Qui - Fab
 7º tempo</t>
@@ -11580,11 +11580,11 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="406" t="n"/>
+      <c r="E40" s="437" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
-      <c r="I40" s="406" t="n"/>
+      <c r="I40" s="437" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -11592,11 +11592,11 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="407" t="n"/>
+      <c r="E41" s="439" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
-      <c r="I41" s="407" t="n"/>
+      <c r="I41" s="439" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11625,7 +11625,7 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H42" s="420" t="inlineStr">
+      <c r="H42" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 7º tempo</t>
@@ -11648,7 +11648,7 @@
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="G43" s="437" t="n"/>
-      <c r="H43" s="406" t="n"/>
+      <c r="H43" s="437" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -11661,7 +11661,7 @@
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="G44" s="439" t="n"/>
-      <c r="H44" s="407" t="n"/>
+      <c r="H44" s="439" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -11794,10 +11794,10 @@
         <f>B51+4</f>
         <v/>
       </c>
-      <c r="E51" s="422" t="inlineStr">
+      <c r="E51" s="412" t="inlineStr">
         <is>
           <t>Redação - Raf
-3º e 4º tempos</t>
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="F51" s="183" t="n"/>
@@ -12767,7 +12767,7 @@
       <c r="E21" s="435" t="n"/>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="420" t="inlineStr">
+      <c r="H21" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
@@ -12799,7 +12799,7 @@
       <c r="E22" s="438" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="406" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -12814,7 +12814,7 @@
       <c r="E23" s="438" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="407" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -12993,7 +12993,7 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="409" t="inlineStr">
+      <c r="H30" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
@@ -13026,7 +13026,7 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="406" t="n"/>
+      <c r="H31" s="437" t="n"/>
       <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -13045,7 +13045,7 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="407" t="n"/>
+      <c r="H32" s="439" t="n"/>
       <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -13183,7 +13183,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H36" s="420" t="inlineStr">
+      <c r="H36" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
@@ -13210,7 +13210,7 @@
       <c r="E37" s="437" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="437" t="n"/>
-      <c r="H37" s="406" t="n"/>
+      <c r="H37" s="437" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -13232,7 +13232,7 @@
       <c r="E38" s="439" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="439" t="n"/>
-      <c r="H38" s="407" t="n"/>
+      <c r="H38" s="439" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -13254,7 +13254,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="421" t="inlineStr">
+      <c r="E39" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
@@ -13281,7 +13281,7 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="406" t="n"/>
+      <c r="E40" s="437" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="437" t="n"/>
@@ -13293,7 +13293,7 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="407" t="n"/>
+      <c r="E41" s="439" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="439" t="n"/>
@@ -13393,7 +13393,7 @@
       </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="409" t="inlineStr">
+      <c r="H45" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
@@ -13416,7 +13416,7 @@
       <c r="E46" s="437" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="283" t="n"/>
-      <c r="H46" s="406" t="n"/>
+      <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -13429,7 +13429,7 @@
       <c r="E47" s="439" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="283" t="n"/>
-      <c r="H47" s="407" t="n"/>
+      <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -14470,7 +14470,7 @@
       <c r="E21" s="435" t="n"/>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="420" t="inlineStr">
+      <c r="H21" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
@@ -14502,7 +14502,7 @@
       <c r="E22" s="438" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="406" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -14517,7 +14517,7 @@
       <c r="E23" s="438" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="407" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -14696,7 +14696,7 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="409" t="inlineStr">
+      <c r="H30" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
@@ -14729,7 +14729,7 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="283" t="n"/>
-      <c r="H31" s="406" t="n"/>
+      <c r="H31" s="437" t="n"/>
       <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -14748,7 +14748,7 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="283" t="n"/>
-      <c r="H32" s="407" t="n"/>
+      <c r="H32" s="439" t="n"/>
       <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -14881,7 +14881,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H36" s="420" t="inlineStr">
+      <c r="H36" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
@@ -14908,7 +14908,7 @@
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="437" t="n"/>
-      <c r="H37" s="406" t="n"/>
+      <c r="H37" s="437" t="n"/>
       <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -14930,7 +14930,7 @@
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="439" t="n"/>
-      <c r="H38" s="407" t="n"/>
+      <c r="H38" s="439" t="n"/>
       <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -14952,7 +14952,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="421" t="inlineStr">
+      <c r="E39" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
@@ -14979,7 +14979,7 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="406" t="n"/>
+      <c r="E40" s="437" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="437" t="n"/>
@@ -14991,7 +14991,7 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="407" t="n"/>
+      <c r="E41" s="439" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="439" t="n"/>
@@ -15096,7 +15096,7 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H45" s="409" t="inlineStr">
+      <c r="H45" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
@@ -15119,7 +15119,7 @@
       <c r="E46" s="437" t="n"/>
       <c r="F46" s="283" t="n"/>
       <c r="G46" s="437" t="n"/>
-      <c r="H46" s="406" t="n"/>
+      <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -15132,7 +15132,7 @@
       <c r="E47" s="439" t="n"/>
       <c r="F47" s="283" t="n"/>
       <c r="G47" s="439" t="n"/>
-      <c r="H47" s="407" t="n"/>
+      <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -19398,17 +19398,17 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="436" t="inlineStr">
+      <c r="F12" s="422" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="452" t="inlineStr">
+      <c r="H12" s="420" t="inlineStr">
         <is>
           <t>Fis - Cadu
-1º e 2º tempos</t>
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -19424,9 +19424,9 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="222" t="n"/>
-      <c r="F13" s="437" t="n"/>
+      <c r="F13" s="406" t="n"/>
       <c r="G13" s="222" t="n"/>
-      <c r="H13" s="437" t="n"/>
+      <c r="H13" s="406" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -19440,9 +19440,9 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="222" t="n"/>
-      <c r="F14" s="439" t="n"/>
+      <c r="F14" s="407" t="n"/>
       <c r="G14" s="222" t="n"/>
-      <c r="H14" s="439" t="n"/>
+      <c r="H14" s="407" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -19870,7 +19870,7 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="435" t="n"/>
-      <c r="G30" s="426" t="inlineStr">
+      <c r="G30" s="456" t="inlineStr">
         <is>
           <t>Soc - Kle
 2º tempo</t>
@@ -19903,7 +19903,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="438" t="n"/>
-      <c r="G31" s="406" t="n"/>
+      <c r="G31" s="437" t="n"/>
       <c r="H31" s="437" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -19922,7 +19922,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="438" t="n"/>
-      <c r="G32" s="407" t="n"/>
+      <c r="G32" s="439" t="n"/>
       <c r="H32" s="439" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -5925,14 +5925,14 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F12" s="422" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-5º e 6º tempos</t>
+      <c r="F12" s="458" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+9º ao 11º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="420" t="inlineStr">
+      <c r="H12" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
@@ -5951,9 +5951,9 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="437" t="n"/>
-      <c r="F13" s="406" t="n"/>
+      <c r="F13" s="437" t="n"/>
       <c r="G13" s="222" t="n"/>
-      <c r="H13" s="406" t="n"/>
+      <c r="H13" s="437" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -5967,9 +5967,9 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="439" t="n"/>
-      <c r="F14" s="407" t="n"/>
+      <c r="F14" s="439" t="n"/>
       <c r="G14" s="222" t="n"/>
-      <c r="H14" s="407" t="n"/>
+      <c r="H14" s="439" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -6001,10 +6001,10 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="458" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-9º ao 11º tempos</t>
+      <c r="F15" s="453" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
@@ -6317,12 +6317,7 @@
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="457" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
+      <c r="G27" s="435" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="458" t="inlineStr">
         <is>
@@ -6346,7 +6341,7 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="437" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="437" t="n"/>
+      <c r="G28" s="438" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
@@ -6365,7 +6360,7 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="439" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="439" t="n"/>
+      <c r="G29" s="438" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
@@ -6397,12 +6392,7 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="435" t="n"/>
-      <c r="G30" s="456" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="435" t="n"/>
       <c r="H30" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
@@ -6430,7 +6420,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="438" t="n"/>
-      <c r="G31" s="437" t="n"/>
+      <c r="G31" s="438" t="n"/>
       <c r="H31" s="437" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -6449,7 +6439,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="438" t="n"/>
-      <c r="G32" s="439" t="n"/>
+      <c r="G32" s="438" t="n"/>
       <c r="H32" s="439" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -6582,7 +6572,12 @@
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="457" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+10º tempo</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="442" t="inlineStr">
         <is>
@@ -6609,7 +6604,7 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="437" t="n"/>
-      <c r="G37" s="283" t="n"/>
+      <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -6631,7 +6626,7 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="439" t="n"/>
-      <c r="G38" s="283" t="n"/>
+      <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -6656,7 +6651,12 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="456" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
       <c r="H39" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
@@ -6678,7 +6678,7 @@
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="283" t="n"/>
+      <c r="G40" s="437" t="n"/>
       <c r="H40" s="437" t="n"/>
       <c r="I40" s="437" t="n"/>
       <c r="J40" s="352" t="n"/>
@@ -6690,7 +6690,7 @@
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="283" t="n"/>
+      <c r="G41" s="439" t="n"/>
       <c r="H41" s="439" t="n"/>
       <c r="I41" s="439" t="n"/>
       <c r="J41" s="352" t="n"/>
@@ -7125,7 +7125,6 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="G30:G32"/>
     <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
@@ -7187,6 +7186,7 @@
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
     <mergeCell ref="G21:G23"/>
+    <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
@@ -7234,7 +7234,7 @@
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="I27:I29"/>
-    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>
@@ -9617,7 +9617,12 @@
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="440" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -9640,7 +9645,7 @@
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="283" t="n"/>
-      <c r="I31" s="283" t="n"/>
+      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -9659,7 +9664,7 @@
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="283" t="n"/>
-      <c r="I32" s="283" t="n"/>
+      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -9797,12 +9802,7 @@
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="440" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I36" s="435" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
       <c r="F37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="437" t="n"/>
+      <c r="I37" s="438" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
       <c r="F38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="439" t="n"/>
+      <c r="I38" s="438" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9867,12 +9867,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
+      <c r="E39" s="435" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="442" t="inlineStr">
         <is>
@@ -9894,7 +9889,7 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="437" t="n"/>
+      <c r="E40" s="438" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
@@ -9906,7 +9901,7 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="439" t="n"/>
+      <c r="E41" s="438" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
@@ -9999,7 +9994,12 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
+      <c r="F45" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="443" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="283" t="n"/>
+      <c r="F46" s="406" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
@@ -10030,7 +10030,7 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="283" t="n"/>
+      <c r="F47" s="407" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
@@ -10055,7 +10055,12 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="435" t="n"/>
+      <c r="E48" s="412" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F48" s="402" t="n"/>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="435" t="n"/>
@@ -10071,7 +10076,7 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="438" t="n"/>
+      <c r="E49" s="406" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="438" t="n"/>
@@ -10083,7 +10088,7 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="438" t="n"/>
+      <c r="E50" s="407" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="438" t="n"/>
@@ -10108,12 +10113,7 @@
         <f>B51+4</f>
         <v/>
       </c>
-      <c r="E51" s="412" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E51" s="435" t="n"/>
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
@@ -10130,7 +10130,7 @@
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
       <c r="D52" s="350" t="n"/>
-      <c r="E52" s="406" t="n"/>
+      <c r="E52" s="438" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
@@ -10142,7 +10142,7 @@
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
       <c r="D53" s="350" t="n"/>
-      <c r="E53" s="407" t="n"/>
+      <c r="E53" s="438" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
@@ -10327,7 +10327,6 @@
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="L42:L47"/>
     <mergeCell ref="B21:B23"/>
-    <mergeCell ref="E51:E53"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="G42:G44"/>
@@ -10365,6 +10364,7 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
@@ -10407,7 +10407,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -10418,6 +10417,7 @@
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="G15:G17"/>
@@ -10455,7 +10455,7 @@
     <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
-    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -11303,7 +11303,12 @@
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="440" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -11326,7 +11331,7 @@
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="283" t="n"/>
-      <c r="I31" s="283" t="n"/>
+      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -11345,7 +11350,7 @@
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="283" t="n"/>
-      <c r="I32" s="283" t="n"/>
+      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -11483,12 +11488,7 @@
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="440" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I36" s="435" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
       <c r="F37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="437" t="n"/>
+      <c r="I37" s="438" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
       <c r="F38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="439" t="n"/>
+      <c r="I38" s="438" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11553,12 +11553,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
+      <c r="E39" s="435" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="442" t="inlineStr">
         <is>
@@ -11580,7 +11575,7 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="437" t="n"/>
+      <c r="E40" s="438" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
@@ -11592,7 +11587,7 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="439" t="n"/>
+      <c r="E41" s="438" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
@@ -11685,7 +11680,12 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
+      <c r="F45" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="443" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="283" t="n"/>
+      <c r="F46" s="406" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
@@ -11716,7 +11716,7 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="283" t="n"/>
+      <c r="F47" s="407" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
@@ -11741,7 +11741,12 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="435" t="n"/>
+      <c r="E48" s="412" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F48" s="402" t="n"/>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="435" t="n"/>
@@ -11757,7 +11762,7 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="438" t="n"/>
+      <c r="E49" s="406" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="438" t="n"/>
@@ -11769,7 +11774,7 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="438" t="n"/>
+      <c r="E50" s="407" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="438" t="n"/>
@@ -11794,12 +11799,7 @@
         <f>B51+4</f>
         <v/>
       </c>
-      <c r="E51" s="412" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E51" s="435" t="n"/>
       <c r="F51" s="183" t="n"/>
       <c r="G51" s="183" t="n"/>
       <c r="H51" s="183" t="n"/>
@@ -11816,7 +11816,7 @@
       <c r="B52" s="313" t="n"/>
       <c r="C52" s="313" t="n"/>
       <c r="D52" s="350" t="n"/>
-      <c r="E52" s="406" t="n"/>
+      <c r="E52" s="438" t="n"/>
       <c r="F52" s="315" t="n"/>
       <c r="G52" s="315" t="n"/>
       <c r="H52" s="315" t="n"/>
@@ -11828,7 +11828,7 @@
       <c r="B53" s="313" t="n"/>
       <c r="C53" s="313" t="n"/>
       <c r="D53" s="350" t="n"/>
-      <c r="E53" s="407" t="n"/>
+      <c r="E53" s="438" t="n"/>
       <c r="F53" s="315" t="n"/>
       <c r="G53" s="315" t="n"/>
       <c r="H53" s="315" t="n"/>
@@ -12013,7 +12013,6 @@
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="L42:L47"/>
     <mergeCell ref="B21:B23"/>
-    <mergeCell ref="E51:E53"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="G42:G44"/>
@@ -12051,6 +12050,7 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
@@ -12093,7 +12093,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -12104,6 +12103,7 @@
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="G15:G17"/>
@@ -12141,7 +12141,7 @@
     <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
-    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -13391,14 +13391,14 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F45" s="283" t="n"/>
+      <c r="F45" s="441" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="435" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
@@ -13414,9 +13414,9 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="437" t="n"/>
-      <c r="F46" s="283" t="n"/>
+      <c r="F46" s="437" t="n"/>
       <c r="G46" s="283" t="n"/>
-      <c r="H46" s="437" t="n"/>
+      <c r="H46" s="438" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -13427,9 +13427,9 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="439" t="n"/>
-      <c r="F47" s="283" t="n"/>
+      <c r="F47" s="439" t="n"/>
       <c r="G47" s="283" t="n"/>
-      <c r="H47" s="439" t="n"/>
+      <c r="H47" s="438" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -13760,7 +13760,6 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -13803,6 +13802,7 @@
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F45:F47"/>
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="F42:F44"/>
@@ -14874,7 +14874,12 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
+      <c r="F36" s="440" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G36" s="436" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
@@ -14906,7 +14911,7 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="283" t="n"/>
+      <c r="F37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="437" t="n"/>
       <c r="I37" s="283" t="n"/>
@@ -14928,7 +14933,7 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="283" t="n"/>
+      <c r="F38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="439" t="n"/>
       <c r="I38" s="283" t="n"/>
@@ -15089,19 +15094,14 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F45" s="283" t="n"/>
-      <c r="G45" s="440" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H45" s="441" t="inlineStr">
+      <c r="F45" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G45" s="435" t="n"/>
+      <c r="H45" s="435" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
@@ -15117,9 +15117,9 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="437" t="n"/>
-      <c r="F46" s="283" t="n"/>
-      <c r="G46" s="437" t="n"/>
-      <c r="H46" s="437" t="n"/>
+      <c r="F46" s="437" t="n"/>
+      <c r="G46" s="438" t="n"/>
+      <c r="H46" s="438" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -15130,9 +15130,9 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="439" t="n"/>
-      <c r="F47" s="283" t="n"/>
-      <c r="G47" s="439" t="n"/>
-      <c r="H47" s="439" t="n"/>
+      <c r="F47" s="439" t="n"/>
+      <c r="G47" s="438" t="n"/>
+      <c r="H47" s="438" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -15449,7 +15449,6 @@
     <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="G45:G47"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -15474,7 +15473,6 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -15514,9 +15512,11 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
+    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F45:F47"/>
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="F42:F44"/>
@@ -16360,12 +16360,7 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="F27" s="458" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-8º ao 10º tempos</t>
-        </is>
-      </c>
+      <c r="F27" s="435" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
@@ -16384,7 +16379,7 @@
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="437" t="n"/>
-      <c r="F28" s="437" t="n"/>
+      <c r="F28" s="438" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
@@ -16403,7 +16398,7 @@
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="439" t="n"/>
-      <c r="F29" s="439" t="n"/>
+      <c r="F29" s="438" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
@@ -16754,13 +16749,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="441" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H42" s="283" t="n"/>
+      <c r="G42" s="435" t="n"/>
+      <c r="H42" s="458" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+9º ao 11º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -16777,8 +16772,8 @@
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
-      <c r="G43" s="437" t="n"/>
-      <c r="H43" s="283" t="n"/>
+      <c r="G43" s="438" t="n"/>
+      <c r="H43" s="437" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -16790,8 +16785,8 @@
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
-      <c r="G44" s="439" t="n"/>
-      <c r="H44" s="283" t="n"/>
+      <c r="G44" s="438" t="n"/>
+      <c r="H44" s="439" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -16878,7 +16873,12 @@
       </c>
       <c r="E48" s="283" t="n"/>
       <c r="F48" s="435" t="n"/>
-      <c r="G48" s="283" t="n"/>
+      <c r="G48" s="441" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H48" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
@@ -16899,7 +16899,7 @@
       <c r="D49" s="350" t="n"/>
       <c r="E49" s="283" t="n"/>
       <c r="F49" s="438" t="n"/>
-      <c r="G49" s="283" t="n"/>
+      <c r="G49" s="437" t="n"/>
       <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
@@ -16911,7 +16911,7 @@
       <c r="D50" s="350" t="n"/>
       <c r="E50" s="78" t="n"/>
       <c r="F50" s="438" t="n"/>
-      <c r="G50" s="283" t="n"/>
+      <c r="G50" s="439" t="n"/>
       <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
@@ -17157,7 +17157,6 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -17180,13 +17179,13 @@
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
-    <mergeCell ref="F27:F29"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -17194,6 +17193,7 @@
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
@@ -18075,12 +18075,7 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="458" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-8º ao 10º tempos</t>
-        </is>
-      </c>
+      <c r="F27" s="435" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
@@ -18099,7 +18094,7 @@
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
-      <c r="F28" s="437" t="n"/>
+      <c r="F28" s="438" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
@@ -18118,7 +18113,7 @@
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
-      <c r="F29" s="439" t="n"/>
+      <c r="F29" s="438" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
@@ -18474,13 +18469,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="441" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H42" s="283" t="n"/>
+      <c r="G42" s="435" t="n"/>
+      <c r="H42" s="458" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+9º ao 11º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -18497,8 +18492,8 @@
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
-      <c r="G43" s="437" t="n"/>
-      <c r="H43" s="283" t="n"/>
+      <c r="G43" s="438" t="n"/>
+      <c r="H43" s="437" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -18510,8 +18505,8 @@
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
-      <c r="G44" s="439" t="n"/>
-      <c r="H44" s="283" t="n"/>
+      <c r="G44" s="438" t="n"/>
+      <c r="H44" s="439" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -18598,7 +18593,12 @@
       </c>
       <c r="E48" s="283" t="n"/>
       <c r="F48" s="435" t="n"/>
-      <c r="G48" s="283" t="n"/>
+      <c r="G48" s="441" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H48" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
@@ -18619,7 +18619,7 @@
       <c r="D49" s="350" t="n"/>
       <c r="E49" s="283" t="n"/>
       <c r="F49" s="438" t="n"/>
-      <c r="G49" s="283" t="n"/>
+      <c r="G49" s="437" t="n"/>
       <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
@@ -18631,7 +18631,7 @@
       <c r="D50" s="350" t="n"/>
       <c r="E50" s="78" t="n"/>
       <c r="F50" s="438" t="n"/>
-      <c r="G50" s="283" t="n"/>
+      <c r="G50" s="439" t="n"/>
       <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
@@ -18877,7 +18877,6 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -18901,12 +18900,12 @@
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
-    <mergeCell ref="F27:F29"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="E21:E23"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -18914,6 +18913,7 @@
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
@@ -19398,14 +19398,14 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="422" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-5º e 6º tempos</t>
+      <c r="F12" s="458" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+9º ao 11º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="420" t="inlineStr">
+      <c r="H12" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
 2º e 3º tempos</t>
@@ -19424,9 +19424,9 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="E13" s="222" t="n"/>
-      <c r="F13" s="406" t="n"/>
+      <c r="F13" s="437" t="n"/>
       <c r="G13" s="222" t="n"/>
-      <c r="H13" s="406" t="n"/>
+      <c r="H13" s="437" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -19440,9 +19440,9 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="E14" s="222" t="n"/>
-      <c r="F14" s="407" t="n"/>
+      <c r="F14" s="439" t="n"/>
       <c r="G14" s="222" t="n"/>
-      <c r="H14" s="407" t="n"/>
+      <c r="H14" s="439" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -19474,10 +19474,10 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F15" s="458" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-9º ao 11º tempos</t>
+      <c r="F15" s="453" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
@@ -19790,12 +19790,7 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="457" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
+      <c r="G27" s="435" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="458" t="inlineStr">
         <is>
@@ -19819,7 +19814,7 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
-      <c r="G28" s="437" t="n"/>
+      <c r="G28" s="438" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
@@ -19838,7 +19833,7 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
-      <c r="G29" s="439" t="n"/>
+      <c r="G29" s="438" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
@@ -19870,12 +19865,7 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="435" t="n"/>
-      <c r="G30" s="456" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="435" t="n"/>
       <c r="H30" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
@@ -19903,7 +19893,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="438" t="n"/>
-      <c r="G31" s="437" t="n"/>
+      <c r="G31" s="438" t="n"/>
       <c r="H31" s="437" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -19922,7 +19912,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="438" t="n"/>
-      <c r="G32" s="439" t="n"/>
+      <c r="G32" s="438" t="n"/>
       <c r="H32" s="439" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -20055,7 +20045,12 @@
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="457" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+10º tempo</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="442" t="inlineStr">
         <is>
@@ -20082,7 +20077,7 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="437" t="n"/>
-      <c r="G37" s="283" t="n"/>
+      <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -20104,7 +20099,7 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="439" t="n"/>
-      <c r="G38" s="283" t="n"/>
+      <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -20129,7 +20124,12 @@
       </c>
       <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="456" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
       <c r="H39" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
@@ -20151,7 +20151,7 @@
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="283" t="n"/>
       <c r="F40" s="283" t="n"/>
-      <c r="G40" s="283" t="n"/>
+      <c r="G40" s="437" t="n"/>
       <c r="H40" s="437" t="n"/>
       <c r="I40" s="437" t="n"/>
       <c r="J40" s="352" t="n"/>
@@ -20163,7 +20163,7 @@
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="283" t="n"/>
       <c r="F41" s="283" t="n"/>
-      <c r="G41" s="283" t="n"/>
+      <c r="G41" s="439" t="n"/>
       <c r="H41" s="439" t="n"/>
       <c r="I41" s="439" t="n"/>
       <c r="J41" s="352" t="n"/>
@@ -20603,7 +20603,6 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="G30:G32"/>
     <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
@@ -20665,6 +20664,7 @@
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
     <mergeCell ref="G21:G23"/>
+    <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
@@ -20712,7 +20712,7 @@
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="I27:I29"/>
-    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -1842,7 +1842,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="465">
+  <cellXfs count="466">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3424,6 +3424,9 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="115" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -6161,18 +6164,8 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="G21" s="450" t="inlineStr">
-        <is>
-          <t>S4-12
-2º ao 7º tempos</t>
-        </is>
-      </c>
-      <c r="H21" s="450" t="inlineStr">
-        <is>
-          <t>S4-12
-2º ao 7º tempos</t>
-        </is>
-      </c>
+      <c r="G21" s="435" t="n"/>
+      <c r="H21" s="435" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
@@ -6198,8 +6191,8 @@
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="437" t="n"/>
       <c r="F22" s="437" t="n"/>
-      <c r="G22" s="437" t="n"/>
-      <c r="H22" s="437" t="n"/>
+      <c r="G22" s="438" t="n"/>
+      <c r="H22" s="438" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -6213,8 +6206,8 @@
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="439" t="n"/>
       <c r="F23" s="439" t="n"/>
-      <c r="G23" s="439" t="n"/>
-      <c r="H23" s="439" t="n"/>
+      <c r="G23" s="438" t="n"/>
+      <c r="H23" s="438" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -6242,8 +6235,18 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="438" t="n"/>
-      <c r="H24" s="283" t="n"/>
+      <c r="G24" s="465" t="inlineStr">
+        <is>
+          <t>S4-12
+2º ao 7º tempos</t>
+        </is>
+      </c>
+      <c r="H24" s="418" t="inlineStr">
+        <is>
+          <t>S4-12
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -6261,8 +6264,8 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="438" t="n"/>
-      <c r="H25" s="283" t="n"/>
+      <c r="G25" s="415" t="n"/>
+      <c r="H25" s="406" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
@@ -6280,8 +6283,8 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="438" t="n"/>
-      <c r="H26" s="283" t="n"/>
+      <c r="G26" s="416" t="n"/>
+      <c r="H26" s="407" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
@@ -7112,7 +7115,6 @@
     <mergeCell ref="B57:B59"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
-    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -7177,6 +7179,7 @@
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D60:D62"/>
+    <mergeCell ref="H24:H26"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
     <mergeCell ref="A36:A38"/>
@@ -7185,7 +7188,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G21:G23"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -7206,6 +7208,7 @@
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G24:G26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -9994,7 +9997,7 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="417" t="inlineStr">
+      <c r="F45" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º tempo</t>
@@ -10017,7 +10020,7 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="406" t="n"/>
+      <c r="F46" s="437" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
@@ -10030,7 +10033,7 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="407" t="n"/>
+      <c r="F47" s="439" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
@@ -10055,7 +10058,7 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="412" t="inlineStr">
+      <c r="E48" s="444" t="inlineStr">
         <is>
           <t>Redação - Raf
 6º e 7º tempos</t>
@@ -10076,7 +10079,7 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="406" t="n"/>
+      <c r="E49" s="437" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="438" t="n"/>
@@ -10088,7 +10091,7 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="407" t="n"/>
+      <c r="E50" s="439" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="438" t="n"/>
@@ -11680,7 +11683,7 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="417" t="inlineStr">
+      <c r="F45" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 1º tempo</t>
@@ -11703,7 +11706,7 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="406" t="n"/>
+      <c r="F46" s="437" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
@@ -11716,7 +11719,7 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="407" t="n"/>
+      <c r="F47" s="439" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
@@ -11741,7 +11744,7 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="412" t="inlineStr">
+      <c r="E48" s="444" t="inlineStr">
         <is>
           <t>Redação - Raf
 6º e 7º tempos</t>
@@ -11762,7 +11765,7 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="406" t="n"/>
+      <c r="E49" s="437" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="438" t="n"/>
@@ -11774,7 +11777,7 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="407" t="n"/>
+      <c r="E50" s="439" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="438" t="n"/>
@@ -19639,18 +19642,8 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="G21" s="450" t="inlineStr">
-        <is>
-          <t>S4-12
-2º ao 7º tempos</t>
-        </is>
-      </c>
-      <c r="H21" s="450" t="inlineStr">
-        <is>
-          <t>S4-12
-2º ao 7º tempos</t>
-        </is>
-      </c>
+      <c r="G21" s="435" t="n"/>
+      <c r="H21" s="435" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
@@ -19676,8 +19669,8 @@
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="437" t="n"/>
       <c r="F22" s="437" t="n"/>
-      <c r="G22" s="437" t="n"/>
-      <c r="H22" s="437" t="n"/>
+      <c r="G22" s="438" t="n"/>
+      <c r="H22" s="438" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -19691,8 +19684,8 @@
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="439" t="n"/>
       <c r="F23" s="439" t="n"/>
-      <c r="G23" s="439" t="n"/>
-      <c r="H23" s="439" t="n"/>
+      <c r="G23" s="438" t="n"/>
+      <c r="H23" s="438" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -19720,8 +19713,18 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="438" t="n"/>
-      <c r="H24" s="283" t="n"/>
+      <c r="G24" s="465" t="inlineStr">
+        <is>
+          <t>S4-12
+2º ao 7º tempos</t>
+        </is>
+      </c>
+      <c r="H24" s="418" t="inlineStr">
+        <is>
+          <t>S4-12
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -19739,8 +19742,8 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="438" t="n"/>
-      <c r="H25" s="283" t="n"/>
+      <c r="G25" s="415" t="n"/>
+      <c r="H25" s="406" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
@@ -19758,8 +19761,8 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="438" t="n"/>
-      <c r="H26" s="283" t="n"/>
+      <c r="G26" s="416" t="n"/>
+      <c r="H26" s="407" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
@@ -20590,7 +20593,6 @@
     <mergeCell ref="B57:B59"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
-    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -20655,6 +20657,7 @@
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
+    <mergeCell ref="H24:H26"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
     <mergeCell ref="A36:A38"/>
@@ -20663,7 +20666,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G21:G23"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -20684,6 +20686,7 @@
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
+    <mergeCell ref="G24:G26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -1842,7 +1842,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="466">
+  <cellXfs count="467">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3426,6 +3426,9 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6235,13 +6238,13 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="465" t="inlineStr">
+      <c r="G24" s="466" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H24" s="418" t="inlineStr">
+      <c r="H24" s="450" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
@@ -6264,8 +6267,8 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="415" t="n"/>
-      <c r="H25" s="406" t="n"/>
+      <c r="G25" s="447" t="n"/>
+      <c r="H25" s="437" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
@@ -6283,8 +6286,8 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="416" t="n"/>
-      <c r="H26" s="407" t="n"/>
+      <c r="G26" s="448" t="n"/>
+      <c r="H26" s="439" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
@@ -6322,12 +6325,7 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="435" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="458" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="I27" s="435" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -6346,7 +6344,7 @@
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="438" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="437" t="n"/>
+      <c r="I28" s="438" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -6365,7 +6363,7 @@
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="438" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="439" t="n"/>
+      <c r="I29" s="438" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -6402,7 +6400,12 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -6425,7 +6428,7 @@
       <c r="F31" s="438" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="437" t="n"/>
-      <c r="I31" s="283" t="n"/>
+      <c r="I31" s="406" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -6444,7 +6447,7 @@
       <c r="F32" s="438" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="439" t="n"/>
-      <c r="I32" s="283" t="n"/>
+      <c r="I32" s="407" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -7236,10 +7239,10 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
+    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -19713,13 +19716,13 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="465" t="inlineStr">
+      <c r="G24" s="466" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H24" s="418" t="inlineStr">
+      <c r="H24" s="450" t="inlineStr">
         <is>
           <t>S4-12
 2º ao 7º tempos</t>
@@ -19742,8 +19745,8 @@
       <c r="D25" s="350" t="n"/>
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
-      <c r="G25" s="415" t="n"/>
-      <c r="H25" s="406" t="n"/>
+      <c r="G25" s="447" t="n"/>
+      <c r="H25" s="437" t="n"/>
       <c r="I25" s="78" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
@@ -19761,8 +19764,8 @@
       <c r="D26" s="350" t="n"/>
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
-      <c r="G26" s="416" t="n"/>
-      <c r="H26" s="407" t="n"/>
+      <c r="G26" s="448" t="n"/>
+      <c r="H26" s="439" t="n"/>
       <c r="I26" s="78" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
@@ -19795,12 +19798,7 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="435" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="458" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="I27" s="435" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -19819,7 +19817,7 @@
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="438" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="437" t="n"/>
+      <c r="I28" s="438" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -19838,7 +19836,7 @@
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="438" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="439" t="n"/>
+      <c r="I29" s="438" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -19875,7 +19873,12 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -19898,7 +19901,7 @@
       <c r="F31" s="438" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="437" t="n"/>
-      <c r="I31" s="283" t="n"/>
+      <c r="I31" s="406" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -19917,7 +19920,7 @@
       <c r="F32" s="438" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="439" t="n"/>
-      <c r="I32" s="283" t="n"/>
+      <c r="I32" s="407" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -20714,10 +20717,10 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
+    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6316,15 +6316,15 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="460" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="464" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="435" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="405" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="435" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -6340,10 +6340,10 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="437" t="n"/>
+      <c r="E28" s="438" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="438" t="n"/>
-      <c r="H28" s="283" t="n"/>
+      <c r="H28" s="406" t="n"/>
       <c r="I28" s="438" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
@@ -6359,10 +6359,10 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="439" t="n"/>
+      <c r="E29" s="438" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="438" t="n"/>
-      <c r="H29" s="283" t="n"/>
+      <c r="H29" s="407" t="n"/>
       <c r="I29" s="438" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
@@ -6391,16 +6391,16 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="408" t="inlineStr">
+        <is>
+          <t>Ing - Isb
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="435" t="n"/>
       <c r="G30" s="435" t="n"/>
-      <c r="H30" s="436" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I30" s="421" t="inlineStr">
+      <c r="H30" s="435" t="n"/>
+      <c r="I30" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 1º ao 3º tempos</t>
@@ -6424,11 +6424,11 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="283" t="n"/>
+      <c r="E31" s="406" t="n"/>
       <c r="F31" s="438" t="n"/>
       <c r="G31" s="438" t="n"/>
-      <c r="H31" s="437" t="n"/>
-      <c r="I31" s="406" t="n"/>
+      <c r="H31" s="438" t="n"/>
+      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -6443,11 +6443,11 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="283" t="n"/>
+      <c r="E32" s="407" t="n"/>
       <c r="F32" s="438" t="n"/>
       <c r="G32" s="438" t="n"/>
-      <c r="H32" s="439" t="n"/>
-      <c r="I32" s="407" t="n"/>
+      <c r="H32" s="438" t="n"/>
+      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -7127,6 +7127,7 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E30:E32"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
@@ -7135,6 +7136,7 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H27:H29"/>
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
@@ -7169,7 +7171,6 @@
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
     <mergeCell ref="I42:I44"/>
-    <mergeCell ref="E27:E29"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -7230,7 +7231,6 @@
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
-    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -19797,7 +19797,12 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="435" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="405" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="435" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -19816,7 +19821,7 @@
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="438" t="n"/>
-      <c r="H28" s="283" t="n"/>
+      <c r="H28" s="406" t="n"/>
       <c r="I28" s="438" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
@@ -19835,7 +19840,7 @@
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="438" t="n"/>
-      <c r="H29" s="283" t="n"/>
+      <c r="H29" s="407" t="n"/>
       <c r="I29" s="438" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
@@ -19867,13 +19872,8 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="435" t="n"/>
       <c r="G30" s="435" t="n"/>
-      <c r="H30" s="436" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="I30" s="421" t="inlineStr">
+      <c r="H30" s="435" t="n"/>
+      <c r="I30" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 1º ao 3º tempos</t>
@@ -19900,8 +19900,8 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="438" t="n"/>
       <c r="G31" s="438" t="n"/>
-      <c r="H31" s="437" t="n"/>
-      <c r="I31" s="406" t="n"/>
+      <c r="H31" s="438" t="n"/>
+      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -19919,8 +19919,8 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="438" t="n"/>
       <c r="G32" s="438" t="n"/>
-      <c r="H32" s="439" t="n"/>
-      <c r="I32" s="407" t="n"/>
+      <c r="H32" s="438" t="n"/>
+      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -20613,6 +20613,7 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H27:H29"/>
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
@@ -20708,7 +20709,6 @@
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
-    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6319,7 +6319,7 @@
       <c r="E27" s="464" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="435" t="n"/>
-      <c r="H27" s="405" t="inlineStr">
+      <c r="H27" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
@@ -6343,7 +6343,7 @@
       <c r="E28" s="438" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="438" t="n"/>
-      <c r="H28" s="406" t="n"/>
+      <c r="H28" s="437" t="n"/>
       <c r="I28" s="438" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
@@ -6362,7 +6362,7 @@
       <c r="E29" s="438" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="438" t="n"/>
-      <c r="H29" s="407" t="n"/>
+      <c r="H29" s="439" t="n"/>
       <c r="I29" s="438" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
@@ -6391,7 +6391,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="408" t="inlineStr">
+      <c r="E30" s="440" t="inlineStr">
         <is>
           <t>Ing - Isb
 4º e 5º tempos</t>
@@ -6424,7 +6424,7 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="406" t="n"/>
+      <c r="E31" s="437" t="n"/>
       <c r="F31" s="438" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="438" t="n"/>
@@ -6443,7 +6443,7 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="407" t="n"/>
+      <c r="E32" s="439" t="n"/>
       <c r="F32" s="438" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="438" t="n"/>
@@ -16040,19 +16040,14 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="442" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="434" t="inlineStr">
+      <c r="E15" s="435" t="n"/>
+      <c r="F15" s="435" t="n"/>
+      <c r="G15" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
@@ -16070,9 +16065,9 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="437" t="n"/>
-      <c r="F16" s="437" t="n"/>
-      <c r="G16" s="222" t="n"/>
+      <c r="E16" s="438" t="n"/>
+      <c r="F16" s="438" t="n"/>
+      <c r="G16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -16086,9 +16081,9 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="439" t="n"/>
-      <c r="F17" s="439" t="n"/>
-      <c r="G17" s="222" t="n"/>
+      <c r="E17" s="438" t="n"/>
+      <c r="F17" s="438" t="n"/>
+      <c r="G17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
@@ -16367,7 +16362,7 @@
         </is>
       </c>
       <c r="F27" s="435" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="435" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
@@ -16386,7 +16381,7 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="437" t="n"/>
       <c r="F28" s="438" t="n"/>
-      <c r="G28" s="283" t="n"/>
+      <c r="G28" s="438" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
       <c r="J28" s="352" t="n"/>
@@ -16405,7 +16400,7 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="439" t="n"/>
       <c r="F29" s="438" t="n"/>
-      <c r="G29" s="283" t="n"/>
+      <c r="G29" s="438" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
       <c r="J29" s="352" t="n"/>
@@ -16435,14 +16430,14 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="442" t="inlineStr">
+      <c r="E30" s="435" t="n"/>
+      <c r="F30" s="283" t="n"/>
+      <c r="G30" s="410" t="inlineStr">
         <is>
           <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -16463,9 +16458,9 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="437" t="n"/>
+      <c r="E31" s="438" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="283" t="n"/>
+      <c r="G31" s="406" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -16482,9 +16477,9 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="439" t="n"/>
+      <c r="E32" s="438" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="283" t="n"/>
+      <c r="G32" s="407" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -16611,13 +16606,13 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="434" t="inlineStr">
+      <c r="F36" s="435" t="n"/>
+      <c r="G36" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="G36" s="283" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="456" t="inlineStr">
         <is>
@@ -16643,8 +16638,8 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="437" t="n"/>
-      <c r="G37" s="283" t="n"/>
+      <c r="F37" s="438" t="n"/>
+      <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -16665,8 +16660,8 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="439" t="n"/>
-      <c r="G38" s="283" t="n"/>
+      <c r="F38" s="438" t="n"/>
+      <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -16877,7 +16872,12 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="n"/>
+      <c r="E48" s="442" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F48" s="435" t="n"/>
       <c r="G48" s="441" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="283" t="n"/>
+      <c r="E49" s="437" t="n"/>
       <c r="F49" s="438" t="n"/>
       <c r="G49" s="437" t="n"/>
       <c r="H49" s="437" t="n"/>
@@ -16915,7 +16915,7 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="78" t="n"/>
+      <c r="E50" s="439" t="n"/>
       <c r="F50" s="438" t="n"/>
       <c r="G50" s="439" t="n"/>
       <c r="H50" s="439" t="n"/>
@@ -17162,7 +17162,6 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
-    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -17177,11 +17176,11 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
-    <mergeCell ref="E30:E32"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G30:G32"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -17198,6 +17197,7 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
@@ -17251,15 +17251,14 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
-    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
+    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
@@ -17291,6 +17290,7 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>
@@ -17755,19 +17755,14 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="442" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="434" t="inlineStr">
+      <c r="E15" s="435" t="n"/>
+      <c r="F15" s="435" t="n"/>
+      <c r="G15" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
@@ -17785,9 +17780,9 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="437" t="n"/>
-      <c r="F16" s="437" t="n"/>
-      <c r="G16" s="222" t="n"/>
+      <c r="E16" s="438" t="n"/>
+      <c r="F16" s="438" t="n"/>
+      <c r="G16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -17801,9 +17796,9 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="439" t="n"/>
-      <c r="F17" s="439" t="n"/>
-      <c r="G17" s="222" t="n"/>
+      <c r="E17" s="438" t="n"/>
+      <c r="F17" s="438" t="n"/>
+      <c r="G17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
@@ -18082,7 +18077,7 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="435" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="435" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
@@ -18101,7 +18096,7 @@
       <c r="D28" s="350" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="438" t="n"/>
-      <c r="G28" s="283" t="n"/>
+      <c r="G28" s="438" t="n"/>
       <c r="H28" s="283" t="n"/>
       <c r="I28" s="283" t="n"/>
       <c r="J28" s="352" t="n"/>
@@ -18120,7 +18115,7 @@
       <c r="D29" s="350" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="438" t="n"/>
-      <c r="G29" s="283" t="n"/>
+      <c r="G29" s="438" t="n"/>
       <c r="H29" s="283" t="n"/>
       <c r="I29" s="283" t="n"/>
       <c r="J29" s="352" t="n"/>
@@ -18150,14 +18145,14 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="442" t="inlineStr">
+      <c r="E30" s="435" t="n"/>
+      <c r="F30" s="283" t="n"/>
+      <c r="G30" s="410" t="inlineStr">
         <is>
           <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -18178,9 +18173,9 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="437" t="n"/>
+      <c r="E31" s="438" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="283" t="n"/>
+      <c r="G31" s="406" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -18197,9 +18192,9 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="439" t="n"/>
+      <c r="E32" s="438" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="283" t="n"/>
+      <c r="G32" s="407" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -18331,13 +18326,13 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F36" s="434" t="inlineStr">
+      <c r="F36" s="435" t="n"/>
+      <c r="G36" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="G36" s="283" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="456" t="inlineStr">
         <is>
@@ -18363,8 +18358,8 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="437" t="n"/>
-      <c r="F37" s="437" t="n"/>
-      <c r="G37" s="283" t="n"/>
+      <c r="F37" s="438" t="n"/>
+      <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -18385,8 +18380,8 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="439" t="n"/>
-      <c r="F38" s="439" t="n"/>
-      <c r="G38" s="283" t="n"/>
+      <c r="F38" s="438" t="n"/>
+      <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -18597,7 +18592,12 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="n"/>
+      <c r="E48" s="442" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F48" s="435" t="n"/>
       <c r="G48" s="441" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="283" t="n"/>
+      <c r="E49" s="437" t="n"/>
       <c r="F49" s="438" t="n"/>
       <c r="G49" s="437" t="n"/>
       <c r="H49" s="437" t="n"/>
@@ -18635,7 +18635,7 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="78" t="n"/>
+      <c r="E50" s="439" t="n"/>
       <c r="F50" s="438" t="n"/>
       <c r="G50" s="439" t="n"/>
       <c r="H50" s="439" t="n"/>
@@ -18882,7 +18882,6 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
-    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -18898,11 +18897,11 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="E36:E38"/>
-    <mergeCell ref="E30:E32"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G30:G32"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -18918,6 +18917,7 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
+    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
@@ -18970,15 +18970,14 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
-    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
+    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
@@ -19010,6 +19009,7 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>
@@ -19797,7 +19797,7 @@
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="435" t="n"/>
-      <c r="H27" s="405" t="inlineStr">
+      <c r="H27" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-EFr-Eth
 9º e 10º tempos</t>
@@ -19821,7 +19821,7 @@
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="438" t="n"/>
-      <c r="H28" s="406" t="n"/>
+      <c r="H28" s="437" t="n"/>
       <c r="I28" s="438" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
@@ -19840,7 +19840,7 @@
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="438" t="n"/>
-      <c r="H29" s="407" t="n"/>
+      <c r="H29" s="439" t="n"/>
       <c r="I29" s="438" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -16432,7 +16432,7 @@
       </c>
       <c r="E30" s="435" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="410" t="inlineStr">
+      <c r="G30" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 1º e 2º tempos</t>
@@ -16460,7 +16460,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="438" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="406" t="n"/>
+      <c r="G31" s="437" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -16479,7 +16479,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="438" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="407" t="n"/>
+      <c r="G32" s="439" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -16614,12 +16614,7 @@
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="456" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="I36" s="435" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -16641,7 +16636,7 @@
       <c r="F37" s="438" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="437" t="n"/>
+      <c r="I37" s="438" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -16663,7 +16658,7 @@
       <c r="F38" s="438" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="439" t="n"/>
+      <c r="I38" s="438" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -17134,7 +17129,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="170">
+  <mergeCells count="169">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -17292,7 +17287,6 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
-    <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -18147,7 +18141,7 @@
       </c>
       <c r="E30" s="435" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="410" t="inlineStr">
+      <c r="G30" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 1º e 2º tempos</t>
@@ -18175,7 +18169,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="438" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="406" t="n"/>
+      <c r="G31" s="437" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -18194,7 +18188,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="438" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="407" t="n"/>
+      <c r="G32" s="439" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -18334,12 +18328,7 @@
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="456" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="I36" s="435" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -18361,7 +18350,7 @@
       <c r="F37" s="438" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="437" t="n"/>
+      <c r="I37" s="438" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -18383,7 +18372,7 @@
       <c r="F38" s="438" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="439" t="n"/>
+      <c r="I38" s="438" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -18854,7 +18843,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="169">
+  <mergeCells count="168">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -19011,7 +19000,6 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
-    <mergeCell ref="I36:I38"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6391,12 +6391,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="440" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="435" t="n"/>
       <c r="F30" s="435" t="n"/>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="435" t="n"/>
@@ -6424,7 +6419,7 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="437" t="n"/>
+      <c r="E31" s="438" t="n"/>
       <c r="F31" s="438" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="438" t="n"/>
@@ -6443,7 +6438,7 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="439" t="n"/>
+      <c r="E32" s="438" t="n"/>
       <c r="F32" s="438" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="438" t="n"/>
@@ -7085,7 +7080,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="169">
+  <mergeCells count="168">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -7127,7 +7122,6 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
-    <mergeCell ref="E30:E32"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
@@ -20188,12 +20182,7 @@
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="440" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H42" s="435" t="n"/>
       <c r="I42" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
@@ -20216,7 +20205,7 @@
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="437" t="n"/>
       <c r="G43" s="283" t="n"/>
-      <c r="H43" s="437" t="n"/>
+      <c r="H43" s="438" t="n"/>
       <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -20229,7 +20218,7 @@
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="439" t="n"/>
       <c r="G44" s="283" t="n"/>
-      <c r="H44" s="439" t="n"/>
+      <c r="H44" s="438" t="n"/>
       <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -20551,7 +20540,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="169">
+  <mergeCells count="168">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -20607,7 +20596,6 @@
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="E21:E23"/>
-    <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -5925,10 +5925,10 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="440" t="inlineStr">
+      <c r="E12" s="422" t="inlineStr">
         <is>
           <t>Ing - Isb
-4º e 5º tempos</t>
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F12" s="458" t="inlineStr">
@@ -5956,7 +5956,7 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="437" t="n"/>
+      <c r="E13" s="406" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="222" t="n"/>
       <c r="H13" s="437" t="n"/>
@@ -5972,7 +5972,7 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="439" t="n"/>
+      <c r="E14" s="407" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="222" t="n"/>
       <c r="H14" s="439" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -5925,10 +5925,10 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="440" t="inlineStr">
+      <c r="E12" s="422" t="inlineStr">
         <is>
           <t>Ing - Isb
-4º e 5º tempos</t>
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F12" s="458" t="inlineStr">
@@ -5956,7 +5956,7 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="437" t="n"/>
+      <c r="E13" s="406" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="222" t="n"/>
       <c r="H13" s="437" t="n"/>
@@ -5972,7 +5972,7 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="439" t="n"/>
+      <c r="E14" s="407" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="222" t="n"/>
       <c r="H14" s="439" t="n"/>
@@ -6391,12 +6391,7 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="440" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="435" t="n"/>
       <c r="F30" s="435" t="n"/>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="435" t="n"/>
@@ -6424,7 +6419,7 @@
       <c r="B31" s="313" t="n"/>
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
-      <c r="E31" s="437" t="n"/>
+      <c r="E31" s="438" t="n"/>
       <c r="F31" s="438" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="438" t="n"/>
@@ -6443,7 +6438,7 @@
       <c r="B32" s="313" t="n"/>
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
-      <c r="E32" s="439" t="n"/>
+      <c r="E32" s="438" t="n"/>
       <c r="F32" s="438" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="438" t="n"/>
@@ -7085,7 +7080,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="169">
+  <mergeCells count="168">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -7127,7 +7122,6 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
-    <mergeCell ref="E30:E32"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
@@ -20188,12 +20182,7 @@
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="440" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H42" s="435" t="n"/>
       <c r="I42" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
@@ -20216,7 +20205,7 @@
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="437" t="n"/>
       <c r="G43" s="283" t="n"/>
-      <c r="H43" s="437" t="n"/>
+      <c r="H43" s="438" t="n"/>
       <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -20229,7 +20218,7 @@
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="439" t="n"/>
       <c r="G44" s="283" t="n"/>
-      <c r="H44" s="439" t="n"/>
+      <c r="H44" s="438" t="n"/>
       <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -20551,7 +20540,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="169">
+  <mergeCells count="168">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -20607,7 +20596,6 @@
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="E21:E23"/>
-    <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -1842,7 +1842,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="467">
+  <cellXfs count="468">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3430,6 +3430,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5925,7 +5929,7 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="422" t="inlineStr">
+      <c r="E12" s="453" t="inlineStr">
         <is>
           <t>Ing - Isb
 5º e 6º tempos</t>
@@ -5956,7 +5960,7 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="406" t="n"/>
+      <c r="E13" s="437" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="222" t="n"/>
       <c r="H13" s="437" t="n"/>
@@ -5972,7 +5976,7 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="407" t="n"/>
+      <c r="E14" s="439" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="222" t="n"/>
       <c r="H14" s="439" t="n"/>
@@ -9171,12 +9175,7 @@
       </c>
       <c r="G12" s="435" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="436" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="436" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -9192,7 +9191,6 @@
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="438" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -9208,7 +9206,6 @@
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="438" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -9396,7 +9393,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="436" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º tempo</t>
+        </is>
+      </c>
       <c r="J21" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -9423,7 +9425,7 @@
       <c r="F22" s="437" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
-      <c r="I22" s="222" t="n"/>
+      <c r="I22" s="437" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -9438,7 +9440,7 @@
       <c r="F23" s="439" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
-      <c r="I23" s="222" t="n"/>
+      <c r="I23" s="439" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -9467,12 +9469,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="438" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="446" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I24" s="446" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -9491,7 +9488,6 @@
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="438" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="437" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -9510,7 +9506,6 @@
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="438" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="439" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -10007,7 +10002,12 @@
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I45" s="386" t="n"/>
+      <c r="I45" s="467" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º tempo</t>
+        </is>
+      </c>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -10302,7 +10302,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="166">
+  <mergeCells count="165">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -10426,7 +10426,6 @@
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="G18:G20"/>
-    <mergeCell ref="I24:I26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -10462,9 +10461,9 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
-    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
+    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>
@@ -10857,12 +10856,7 @@
       </c>
       <c r="G12" s="435" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="436" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="436" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -10878,7 +10872,6 @@
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="438" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -10894,7 +10887,6 @@
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="438" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -11082,7 +11074,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="405" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º tempo</t>
+        </is>
+      </c>
       <c r="J21" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -11109,7 +11106,7 @@
       <c r="F22" s="437" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
-      <c r="I22" s="222" t="n"/>
+      <c r="I22" s="406" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -11124,7 +11121,7 @@
       <c r="F23" s="439" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
-      <c r="I23" s="222" t="n"/>
+      <c r="I23" s="407" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -11153,12 +11150,7 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="438" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="446" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I24" s="446" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -11177,7 +11169,6 @@
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="438" t="n"/>
       <c r="H25" s="283" t="n"/>
-      <c r="I25" s="437" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -11196,7 +11187,6 @@
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="438" t="n"/>
       <c r="H26" s="283" t="n"/>
-      <c r="I26" s="439" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -11693,7 +11683,12 @@
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="I45" s="386" t="n"/>
+      <c r="I45" s="467" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º tempo</t>
+        </is>
+      </c>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -11988,7 +11983,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="166">
+  <mergeCells count="165">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -12112,7 +12107,6 @@
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="G18:G20"/>
-    <mergeCell ref="I24:I26"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
@@ -12148,9 +12142,9 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
-    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
+    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -9380,12 +9380,7 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="443" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F21" s="443" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="444" t="inlineStr">
         <is>
@@ -9393,12 +9388,7 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I21" s="436" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I21" s="436" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -9422,10 +9412,8 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="437" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
-      <c r="I22" s="437" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -9437,10 +9425,8 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="439" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
-      <c r="I23" s="439" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -9863,7 +9849,12 @@
         <v/>
       </c>
       <c r="E39" s="435" t="n"/>
-      <c r="F39" s="283" t="n"/>
+      <c r="F39" s="443" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G39" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
@@ -9871,10 +9862,10 @@
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="451" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-7º tempo</t>
+      <c r="I39" s="436" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º tempo</t>
         </is>
       </c>
       <c r="J39" s="265" t="n"/>
@@ -9885,7 +9876,7 @@
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="438" t="n"/>
-      <c r="F40" s="283" t="n"/>
+      <c r="F40" s="437" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="437" t="n"/>
@@ -9897,7 +9888,7 @@
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="438" t="n"/>
-      <c r="F41" s="283" t="n"/>
+      <c r="F41" s="439" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="439" t="n"/>
@@ -9989,25 +9980,10 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
+      <c r="F45" s="449" t="n"/>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="443" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="467" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H45" s="443" t="n"/>
+      <c r="I45" s="467" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -10017,10 +9993,7 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="437" t="n"/>
       <c r="G46" s="283" t="n"/>
-      <c r="H46" s="437" t="n"/>
-      <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
@@ -10030,10 +10003,7 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="439" t="n"/>
       <c r="G47" s="283" t="n"/>
-      <c r="H47" s="439" t="n"/>
-      <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
@@ -10302,7 +10272,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="161">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -10317,6 +10287,7 @@
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D30:D32"/>
+    <mergeCell ref="F39:F41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="C24:C26"/>
@@ -10333,7 +10304,6 @@
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
-    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
@@ -10374,7 +10344,6 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -10417,7 +10386,6 @@
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
-    <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="G15:G17"/>
@@ -10456,14 +10424,12 @@
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
-    <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>
@@ -11061,12 +11027,7 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="443" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F21" s="443" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="444" t="inlineStr">
         <is>
@@ -11074,12 +11035,7 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I21" s="405" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I21" s="436" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -11103,10 +11059,8 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="437" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
-      <c r="I22" s="406" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -11118,10 +11072,8 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="439" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
-      <c r="I23" s="407" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -11544,7 +11496,12 @@
         <v/>
       </c>
       <c r="E39" s="435" t="n"/>
-      <c r="F39" s="283" t="n"/>
+      <c r="F39" s="443" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G39" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
@@ -11552,10 +11509,10 @@
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="451" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-7º tempo</t>
+      <c r="I39" s="436" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º tempo</t>
         </is>
       </c>
       <c r="J39" s="265" t="n"/>
@@ -11566,7 +11523,7 @@
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="438" t="n"/>
-      <c r="F40" s="283" t="n"/>
+      <c r="F40" s="437" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="437" t="n"/>
@@ -11578,7 +11535,7 @@
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="438" t="n"/>
-      <c r="F41" s="283" t="n"/>
+      <c r="F41" s="439" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="439" t="n"/>
@@ -11670,25 +11627,10 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
+      <c r="F45" s="449" t="n"/>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="443" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="467" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H45" s="443" t="n"/>
+      <c r="I45" s="467" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -11698,10 +11640,7 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
-      <c r="F46" s="437" t="n"/>
       <c r="G46" s="283" t="n"/>
-      <c r="H46" s="437" t="n"/>
-      <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
@@ -11711,10 +11650,7 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
-      <c r="F47" s="439" t="n"/>
       <c r="G47" s="283" t="n"/>
-      <c r="H47" s="439" t="n"/>
-      <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
@@ -11983,7 +11919,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="161">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -11998,6 +11934,7 @@
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D30:D32"/>
+    <mergeCell ref="F39:F41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="C24:C26"/>
@@ -12014,7 +11951,6 @@
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
-    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
@@ -12055,7 +11991,6 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -12098,7 +12033,6 @@
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
-    <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="G15:G17"/>
@@ -12137,14 +12071,12 @@
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
-    <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -264,7 +264,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="32">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
@@ -449,6 +449,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -1842,7 +1848,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="468">
+  <cellXfs count="471">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3432,6 +3438,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -9174,7 +9192,12 @@
         </is>
       </c>
       <c r="G12" s="435" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="470" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="436" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -9190,7 +9213,7 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="438" t="n"/>
-      <c r="H13" s="222" t="n"/>
+      <c r="H13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -9205,7 +9228,7 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="438" t="n"/>
-      <c r="H14" s="222" t="n"/>
+      <c r="H14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -9382,12 +9405,7 @@
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="443" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="444" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H21" s="444" t="n"/>
       <c r="I21" s="436" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
@@ -9413,7 +9431,6 @@
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="437" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -9426,7 +9443,6 @@
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="439" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -9769,13 +9785,13 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
-      <c r="F36" s="434" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+      <c r="E36" s="470" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="F36" s="434" t="n"/>
       <c r="G36" s="462" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -9801,8 +9817,7 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="283" t="n"/>
-      <c r="F37" s="437" t="n"/>
+      <c r="E37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="438" t="n"/>
@@ -9823,8 +9838,7 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="283" t="n"/>
-      <c r="F38" s="439" t="n"/>
+      <c r="E38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="438" t="n"/>
@@ -9980,7 +9994,12 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="449" t="n"/>
+      <c r="F45" s="470" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="443" t="n"/>
       <c r="I45" s="467" t="n"/>
@@ -9993,6 +10012,7 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
+      <c r="F46" s="437" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -10003,6 +10023,7 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
+      <c r="F47" s="439" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -10025,13 +10046,13 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="444" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F48" s="402" t="n"/>
+      <c r="E48" s="444" t="n"/>
+      <c r="F48" s="469" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+4º tempo</t>
+        </is>
+      </c>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
@@ -10046,7 +10067,6 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="437" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="438" t="n"/>
@@ -10058,7 +10078,6 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="439" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="438" t="n"/>
@@ -10305,7 +10324,6 @@
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
     <mergeCell ref="D57:D59"/>
-    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -10315,6 +10333,7 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
@@ -10334,7 +10353,6 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
-    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
@@ -10381,11 +10399,11 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
-    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="G15:G17"/>
@@ -10406,6 +10424,7 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
@@ -10821,7 +10840,12 @@
         </is>
       </c>
       <c r="G12" s="435" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="468" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="436" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -10837,7 +10861,7 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="438" t="n"/>
-      <c r="H13" s="222" t="n"/>
+      <c r="H13" s="406" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -10852,7 +10876,7 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="438" t="n"/>
-      <c r="H14" s="222" t="n"/>
+      <c r="H14" s="407" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -11029,12 +11053,7 @@
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="443" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="444" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H21" s="444" t="n"/>
       <c r="I21" s="436" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
@@ -11060,7 +11079,6 @@
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="437" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -11073,7 +11091,6 @@
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="439" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -11416,13 +11433,13 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
-      <c r="F36" s="434" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
+      <c r="E36" s="468" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="F36" s="434" t="n"/>
       <c r="G36" s="462" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -11448,8 +11465,7 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="283" t="n"/>
-      <c r="F37" s="437" t="n"/>
+      <c r="E37" s="406" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="438" t="n"/>
@@ -11470,8 +11486,7 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="283" t="n"/>
-      <c r="F38" s="439" t="n"/>
+      <c r="E38" s="407" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="438" t="n"/>
@@ -11627,7 +11642,12 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="449" t="n"/>
+      <c r="F45" s="468" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="443" t="n"/>
       <c r="I45" s="467" t="n"/>
@@ -11640,6 +11660,7 @@
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="283" t="n"/>
+      <c r="F46" s="406" t="n"/>
       <c r="G46" s="283" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -11650,6 +11671,7 @@
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="283" t="n"/>
+      <c r="F47" s="407" t="n"/>
       <c r="G47" s="283" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -11672,13 +11694,13 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="444" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F48" s="402" t="n"/>
+      <c r="E48" s="444" t="n"/>
+      <c r="F48" s="469" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+4º tempo</t>
+        </is>
+      </c>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
@@ -11693,7 +11715,6 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="437" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="438" t="n"/>
@@ -11705,7 +11726,6 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="439" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="438" t="n"/>
@@ -11952,7 +11972,6 @@
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
     <mergeCell ref="D57:D59"/>
-    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -11962,6 +11981,7 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
@@ -11981,7 +12001,6 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
-    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
@@ -12028,11 +12047,11 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
-    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="G15:G17"/>
@@ -12053,6 +12072,7 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -264,7 +264,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="32">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
@@ -449,6 +449,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -1842,7 +1848,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="468">
+  <cellXfs count="471">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3432,6 +3438,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="108" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="18" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -9174,7 +9192,12 @@
         </is>
       </c>
       <c r="G12" s="435" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="470" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="436" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -9190,7 +9213,7 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="438" t="n"/>
-      <c r="H13" s="222" t="n"/>
+      <c r="H13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -9205,7 +9228,7 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="438" t="n"/>
-      <c r="H14" s="222" t="n"/>
+      <c r="H14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -9380,25 +9403,10 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="443" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F21" s="443" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="444" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I21" s="436" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H21" s="444" t="n"/>
+      <c r="I21" s="436" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -9422,10 +9430,7 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="437" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="437" t="n"/>
-      <c r="I22" s="437" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -9437,10 +9442,7 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="439" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="439" t="n"/>
-      <c r="I23" s="439" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -9783,13 +9785,13 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
-      <c r="F36" s="434" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="470" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F36" s="434" t="n"/>
       <c r="G36" s="462" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -9815,8 +9817,7 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="283" t="n"/>
-      <c r="F37" s="437" t="n"/>
+      <c r="E37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="438" t="n"/>
@@ -9837,8 +9838,7 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="283" t="n"/>
-      <c r="F38" s="439" t="n"/>
+      <c r="E38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="438" t="n"/>
@@ -9863,7 +9863,12 @@
         <v/>
       </c>
       <c r="E39" s="435" t="n"/>
-      <c r="F39" s="283" t="n"/>
+      <c r="F39" s="443" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G39" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
@@ -9871,10 +9876,10 @@
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="451" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-7º tempo</t>
+      <c r="I39" s="436" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º tempo</t>
         </is>
       </c>
       <c r="J39" s="265" t="n"/>
@@ -9885,7 +9890,7 @@
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="438" t="n"/>
-      <c r="F40" s="283" t="n"/>
+      <c r="F40" s="437" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="437" t="n"/>
@@ -9897,7 +9902,7 @@
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="438" t="n"/>
-      <c r="F41" s="283" t="n"/>
+      <c r="F41" s="439" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="439" t="n"/>
@@ -9989,25 +9994,15 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
+      <c r="F45" s="470" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="443" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="467" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H45" s="443" t="n"/>
+      <c r="I45" s="467" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -10019,8 +10014,6 @@
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="437" t="n"/>
       <c r="G46" s="283" t="n"/>
-      <c r="H46" s="437" t="n"/>
-      <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
@@ -10032,8 +10025,6 @@
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="439" t="n"/>
       <c r="G47" s="283" t="n"/>
-      <c r="H47" s="439" t="n"/>
-      <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
@@ -10055,13 +10046,13 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="444" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F48" s="402" t="n"/>
+      <c r="E48" s="444" t="n"/>
+      <c r="F48" s="469" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
@@ -10076,7 +10067,6 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="437" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="438" t="n"/>
@@ -10088,7 +10078,6 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="439" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="438" t="n"/>
@@ -10302,7 +10291,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="161">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -10317,6 +10306,7 @@
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D30:D32"/>
+    <mergeCell ref="F39:F41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="C24:C26"/>
@@ -10333,9 +10323,7 @@
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
-    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
-    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -10345,6 +10333,7 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
@@ -10364,7 +10353,6 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
-    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
@@ -10374,7 +10362,6 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -10412,7 +10399,6 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
-    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
@@ -10438,6 +10424,7 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
@@ -10456,14 +10443,12 @@
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
-    <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>
@@ -10855,7 +10840,12 @@
         </is>
       </c>
       <c r="G12" s="435" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="470" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="436" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -10871,7 +10861,7 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="438" t="n"/>
-      <c r="H13" s="222" t="n"/>
+      <c r="H13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -10886,7 +10876,7 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="438" t="n"/>
-      <c r="H14" s="222" t="n"/>
+      <c r="H14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -11061,25 +11051,10 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="443" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F21" s="443" t="n"/>
       <c r="G21" s="11" t="n"/>
-      <c r="H21" s="444" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I21" s="405" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H21" s="444" t="n"/>
+      <c r="I21" s="436" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -11103,10 +11078,7 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
-      <c r="F22" s="437" t="n"/>
       <c r="G22" s="222" t="n"/>
-      <c r="H22" s="437" t="n"/>
-      <c r="I22" s="406" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -11118,10 +11090,7 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
-      <c r="F23" s="439" t="n"/>
       <c r="G23" s="222" t="n"/>
-      <c r="H23" s="439" t="n"/>
-      <c r="I23" s="407" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -11464,13 +11433,13 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
-      <c r="F36" s="434" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="470" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F36" s="434" t="n"/>
       <c r="G36" s="462" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -11496,8 +11465,7 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="283" t="n"/>
-      <c r="F37" s="437" t="n"/>
+      <c r="E37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="438" t="n"/>
@@ -11518,8 +11486,7 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="283" t="n"/>
-      <c r="F38" s="439" t="n"/>
+      <c r="E38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="438" t="n"/>
@@ -11544,7 +11511,12 @@
         <v/>
       </c>
       <c r="E39" s="435" t="n"/>
-      <c r="F39" s="283" t="n"/>
+      <c r="F39" s="443" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G39" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
@@ -11552,10 +11524,10 @@
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="451" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-7º tempo</t>
+      <c r="I39" s="436" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º tempo</t>
         </is>
       </c>
       <c r="J39" s="265" t="n"/>
@@ -11566,7 +11538,7 @@
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
       <c r="E40" s="438" t="n"/>
-      <c r="F40" s="283" t="n"/>
+      <c r="F40" s="437" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
       <c r="I40" s="437" t="n"/>
@@ -11578,7 +11550,7 @@
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
       <c r="E41" s="438" t="n"/>
-      <c r="F41" s="283" t="n"/>
+      <c r="F41" s="439" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
       <c r="I41" s="439" t="n"/>
@@ -11670,25 +11642,15 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
+      <c r="F45" s="470" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="443" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I45" s="467" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H45" s="443" t="n"/>
+      <c r="I45" s="467" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -11700,8 +11662,6 @@
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="437" t="n"/>
       <c r="G46" s="283" t="n"/>
-      <c r="H46" s="437" t="n"/>
-      <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
@@ -11713,8 +11673,6 @@
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="439" t="n"/>
       <c r="G47" s="283" t="n"/>
-      <c r="H47" s="439" t="n"/>
-      <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
@@ -11736,13 +11694,13 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="444" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F48" s="402" t="n"/>
+      <c r="E48" s="444" t="n"/>
+      <c r="F48" s="469" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
@@ -11757,7 +11715,6 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="E49" s="437" t="n"/>
       <c r="F49" s="351" t="n"/>
       <c r="G49" s="283" t="n"/>
       <c r="H49" s="438" t="n"/>
@@ -11769,7 +11726,6 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="E50" s="439" t="n"/>
       <c r="F50" s="387" t="n"/>
       <c r="G50" s="283" t="n"/>
       <c r="H50" s="438" t="n"/>
@@ -11983,7 +11939,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="161">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -11998,6 +11954,7 @@
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="D30:D32"/>
+    <mergeCell ref="F39:F41"/>
     <mergeCell ref="A15:A17"/>
     <mergeCell ref="A24:A26"/>
     <mergeCell ref="C24:C26"/>
@@ -12014,9 +11971,7 @@
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
-    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
-    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -12026,6 +11981,7 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
@@ -12045,7 +12001,6 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
-    <mergeCell ref="E48:E50"/>
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
@@ -12055,7 +12010,6 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -12093,7 +12047,6 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
-    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="F18:F20"/>
@@ -12119,6 +12072,7 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
@@ -12137,14 +12091,12 @@
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
-    <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="I21:I23"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="J27:J29"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -9785,12 +9785,7 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="470" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="470" t="n"/>
       <c r="F36" s="434" t="n"/>
       <c r="G36" s="462" t="inlineStr">
         <is>
@@ -9798,7 +9793,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H36" s="283" t="n"/>
+      <c r="H36" s="444" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I36" s="435" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -9817,9 +9817,8 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
-      <c r="H37" s="283" t="n"/>
+      <c r="H37" s="437" t="n"/>
       <c r="I37" s="438" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -9838,9 +9837,8 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
-      <c r="H38" s="283" t="n"/>
+      <c r="H38" s="439" t="n"/>
       <c r="I38" s="438" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -10333,7 +10331,6 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
-    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
@@ -10405,6 +10402,7 @@
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="H36:H38"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
@@ -11433,12 +11431,7 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="470" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="470" t="n"/>
       <c r="F36" s="434" t="n"/>
       <c r="G36" s="462" t="inlineStr">
         <is>
@@ -11446,7 +11439,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H36" s="283" t="n"/>
+      <c r="H36" s="412" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I36" s="435" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -11465,9 +11463,8 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
-      <c r="H37" s="283" t="n"/>
+      <c r="H37" s="406" t="n"/>
       <c r="I37" s="438" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -11486,9 +11483,8 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
-      <c r="H38" s="283" t="n"/>
+      <c r="H38" s="407" t="n"/>
       <c r="I38" s="438" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -11981,7 +11977,6 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
-    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
@@ -12053,6 +12048,7 @@
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="H36:H38"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -1848,7 +1848,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="471">
+  <cellXfs count="472">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3450,6 +3450,10 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="111" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="25" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -5866,7 +5870,13 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="n"/>
+      <c r="F9" s="471" t="inlineStr">
+        <is>
+          <t>DSD2
+Parte escrita
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
@@ -6036,7 +6046,13 @@
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
+      <c r="H15" s="418" t="inlineStr">
+        <is>
+          <t>DSD2
+Parte oral
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -6051,7 +6067,7 @@
       <c r="E16" s="437" t="n"/>
       <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="222" t="n"/>
+      <c r="H16" s="406" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -6067,7 +6083,7 @@
       <c r="E17" s="439" t="n"/>
       <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="222" t="n"/>
+      <c r="H17" s="407" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -7102,7 +7118,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="168">
+  <mergeCells count="169">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -7198,6 +7214,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="H24:H26"/>
     <mergeCell ref="F60:F62"/>
@@ -9104,7 +9121,13 @@
       </c>
       <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="n"/>
+      <c r="G9" s="471" t="inlineStr">
+        <is>
+          <t>DSD1
+Parte escrita
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
@@ -9253,8 +9276,20 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
+      <c r="E15" s="450" t="inlineStr">
+        <is>
+          <t>DSD1
+Parte oral
+2º ao 7º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="450" t="inlineStr">
+        <is>
+          <t>DSD1
+Parte oral
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="G15" s="462" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -9278,8 +9313,8 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="222" t="n"/>
-      <c r="F16" s="222" t="n"/>
+      <c r="E16" s="437" t="n"/>
+      <c r="F16" s="437" t="n"/>
       <c r="G16" s="437" t="n"/>
       <c r="H16" s="222" t="n"/>
       <c r="I16" s="437" t="n"/>
@@ -9294,8 +9329,8 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="222" t="n"/>
-      <c r="F17" s="222" t="n"/>
+      <c r="E17" s="439" t="n"/>
+      <c r="F17" s="439" t="n"/>
       <c r="G17" s="439" t="n"/>
       <c r="H17" s="222" t="n"/>
       <c r="I17" s="439" t="n"/>
@@ -9403,7 +9438,12 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="443" t="n"/>
+      <c r="F21" s="449" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="444" t="n"/>
       <c r="I21" s="436" t="n"/>
@@ -9430,6 +9470,7 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
+      <c r="F22" s="437" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -9442,6 +9483,7 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
+      <c r="F23" s="439" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -9874,12 +9916,7 @@
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="436" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I39" s="436" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9891,7 +9928,6 @@
       <c r="F40" s="437" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
-      <c r="I40" s="437" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -9903,7 +9939,6 @@
       <c r="F41" s="439" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
-      <c r="I41" s="439" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9926,12 +9961,7 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="441" t="n"/>
       <c r="H42" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
@@ -9954,7 +9984,6 @@
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
-      <c r="G43" s="437" t="n"/>
       <c r="H43" s="437" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -9967,7 +9996,6 @@
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
-      <c r="G44" s="439" t="n"/>
       <c r="H44" s="439" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -10000,7 +10028,12 @@
       </c>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="443" t="n"/>
-      <c r="I45" s="467" t="n"/>
+      <c r="I45" s="470" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º tempo</t>
+        </is>
+      </c>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -10012,6 +10045,7 @@
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="437" t="n"/>
       <c r="G46" s="283" t="n"/>
+      <c r="I46" s="437" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
@@ -10023,6 +10057,7 @@
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="439" t="n"/>
       <c r="G47" s="283" t="n"/>
+      <c r="I47" s="439" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
@@ -10045,13 +10080,18 @@
         <v/>
       </c>
       <c r="E48" s="444" t="n"/>
-      <c r="F48" s="469" t="inlineStr">
+      <c r="F48" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
-      <c r="G48" s="283" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G48" s="441" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
@@ -10065,8 +10105,8 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="F49" s="351" t="n"/>
-      <c r="G49" s="283" t="n"/>
+      <c r="F49" s="437" t="n"/>
+      <c r="G49" s="437" t="n"/>
       <c r="H49" s="438" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
@@ -10076,8 +10116,8 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="F50" s="387" t="n"/>
-      <c r="G50" s="283" t="n"/>
+      <c r="F50" s="439" t="n"/>
+      <c r="G50" s="439" t="n"/>
       <c r="H50" s="438" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
@@ -10289,7 +10329,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="161">
+  <mergeCells count="164">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -10317,10 +10357,11 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
-    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
@@ -10334,7 +10375,6 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -10351,6 +10391,7 @@
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
@@ -10403,6 +10444,7 @@
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="H36:H38"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
@@ -10441,6 +10483,7 @@
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
+    <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
@@ -10750,7 +10793,13 @@
       </c>
       <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="n"/>
+      <c r="G9" s="471" t="inlineStr">
+        <is>
+          <t>DSD1
+Parte escrita
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
@@ -10899,8 +10948,20 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
+      <c r="E15" s="450" t="inlineStr">
+        <is>
+          <t>DSD1
+Parte oral
+2º ao 7º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="450" t="inlineStr">
+        <is>
+          <t>DSD1
+Parte oral
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="G15" s="462" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -10924,8 +10985,8 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="222" t="n"/>
-      <c r="F16" s="222" t="n"/>
+      <c r="E16" s="437" t="n"/>
+      <c r="F16" s="437" t="n"/>
       <c r="G16" s="437" t="n"/>
       <c r="H16" s="222" t="n"/>
       <c r="I16" s="437" t="n"/>
@@ -10940,8 +11001,8 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="222" t="n"/>
-      <c r="F17" s="222" t="n"/>
+      <c r="E17" s="439" t="n"/>
+      <c r="F17" s="439" t="n"/>
       <c r="G17" s="439" t="n"/>
       <c r="H17" s="222" t="n"/>
       <c r="I17" s="439" t="n"/>
@@ -11049,7 +11110,12 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="443" t="n"/>
+      <c r="F21" s="449" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="444" t="n"/>
       <c r="I21" s="436" t="n"/>
@@ -11076,6 +11142,7 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
+      <c r="F22" s="437" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -11088,6 +11155,7 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
+      <c r="F23" s="439" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -11439,7 +11507,7 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H36" s="412" t="inlineStr">
+      <c r="H36" s="444" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
@@ -11464,7 +11532,7 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="G37" s="437" t="n"/>
-      <c r="H37" s="406" t="n"/>
+      <c r="H37" s="437" t="n"/>
       <c r="I37" s="438" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -11484,7 +11552,7 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="G38" s="439" t="n"/>
-      <c r="H38" s="407" t="n"/>
+      <c r="H38" s="439" t="n"/>
       <c r="I38" s="438" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -11520,12 +11588,7 @@
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="436" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I39" s="436" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11537,7 +11600,6 @@
       <c r="F40" s="437" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="283" t="n"/>
-      <c r="I40" s="437" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -11549,7 +11611,6 @@
       <c r="F41" s="439" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="283" t="n"/>
-      <c r="I41" s="439" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11572,12 +11633,7 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="441" t="n"/>
       <c r="H42" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
@@ -11600,7 +11656,6 @@
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
-      <c r="G43" s="437" t="n"/>
       <c r="H43" s="437" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -11613,7 +11668,6 @@
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
-      <c r="G44" s="439" t="n"/>
       <c r="H44" s="439" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -11646,7 +11700,12 @@
       </c>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="443" t="n"/>
-      <c r="I45" s="467" t="n"/>
+      <c r="I45" s="470" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º tempo</t>
+        </is>
+      </c>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -11658,6 +11717,7 @@
       <c r="E46" s="283" t="n"/>
       <c r="F46" s="437" t="n"/>
       <c r="G46" s="283" t="n"/>
+      <c r="I46" s="437" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
     </row>
@@ -11669,6 +11729,7 @@
       <c r="E47" s="283" t="n"/>
       <c r="F47" s="439" t="n"/>
       <c r="G47" s="283" t="n"/>
+      <c r="I47" s="439" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
     </row>
@@ -11691,13 +11752,18 @@
         <v/>
       </c>
       <c r="E48" s="444" t="n"/>
-      <c r="F48" s="469" t="inlineStr">
+      <c r="F48" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
-      <c r="G48" s="283" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G48" s="441" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
@@ -11711,8 +11777,8 @@
       <c r="B49" s="313" t="n"/>
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
-      <c r="F49" s="351" t="n"/>
-      <c r="G49" s="283" t="n"/>
+      <c r="F49" s="437" t="n"/>
+      <c r="G49" s="437" t="n"/>
       <c r="H49" s="438" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
@@ -11722,8 +11788,8 @@
       <c r="B50" s="313" t="n"/>
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
-      <c r="F50" s="387" t="n"/>
-      <c r="G50" s="283" t="n"/>
+      <c r="F50" s="439" t="n"/>
+      <c r="G50" s="439" t="n"/>
       <c r="H50" s="438" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
@@ -11935,7 +12001,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="161">
+  <mergeCells count="164">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -11963,10 +12029,11 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
-    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
@@ -11980,7 +12047,6 @@
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -11997,6 +12063,7 @@
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
@@ -12049,6 +12116,7 @@
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="H36:H38"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
@@ -12087,6 +12155,7 @@
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
+    <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
@@ -19246,7 +19315,13 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="n"/>
+      <c r="F9" s="471" t="inlineStr">
+        <is>
+          <t>DSD2
+Parte escrita
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
@@ -19327,7 +19402,12 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="n"/>
+      <c r="E12" s="440" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F12" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
@@ -19353,7 +19433,7 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="222" t="n"/>
+      <c r="E13" s="437" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="222" t="n"/>
       <c r="H13" s="437" t="n"/>
@@ -19369,7 +19449,7 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="222" t="n"/>
+      <c r="E14" s="439" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="222" t="n"/>
       <c r="H14" s="439" t="n"/>
@@ -19411,10 +19491,11 @@
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="440" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-4º e 5º tempos</t>
+      <c r="H15" s="450" t="inlineStr">
+        <is>
+          <t>DSD2
+Parte oral
+2º ao 7º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -20482,7 +20563,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="168">
+  <mergeCells count="169">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -20536,6 +20617,7 @@
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="418" t="inlineStr">
+      <c r="H15" s="450" t="inlineStr">
         <is>
           <t>DSD2
 Parte oral
@@ -6067,7 +6067,7 @@
       <c r="E16" s="437" t="n"/>
       <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
-      <c r="H16" s="406" t="n"/>
+      <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -6083,7 +6083,7 @@
       <c r="E17" s="439" t="n"/>
       <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
-      <c r="H17" s="407" t="n"/>
+      <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -9215,12 +9215,7 @@
         </is>
       </c>
       <c r="G12" s="435" t="n"/>
-      <c r="H12" s="470" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H12" s="470" t="n"/>
       <c r="I12" s="436" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -9236,7 +9231,6 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="438" t="n"/>
-      <c r="H13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -9251,7 +9245,6 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="438" t="n"/>
-      <c r="H14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -9290,13 +9283,13 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G15" s="462" t="inlineStr">
-        <is>
-          <t>Port - Jana
+      <c r="G15" s="462" t="n"/>
+      <c r="H15" s="444" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H15" s="11" t="n"/>
       <c r="I15" s="440" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
@@ -9315,8 +9308,7 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
       <c r="F16" s="437" t="n"/>
-      <c r="G16" s="437" t="n"/>
-      <c r="H16" s="222" t="n"/>
+      <c r="H16" s="437" t="n"/>
       <c r="I16" s="437" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -9331,8 +9323,7 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
       <c r="F17" s="439" t="n"/>
-      <c r="G17" s="439" t="n"/>
-      <c r="H17" s="222" t="n"/>
+      <c r="H17" s="439" t="n"/>
       <c r="I17" s="439" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -9362,10 +9353,10 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-9º e 10º tempos</t>
+      <c r="F18" s="462" t="inlineStr">
+        <is>
+          <t>Port - Jana
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G18" s="442" t="inlineStr">
@@ -9444,7 +9435,12 @@
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G21" s="11" t="n"/>
+      <c r="G21" s="441" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H21" s="444" t="n"/>
       <c r="I21" s="436" t="n"/>
       <c r="J21" s="262" t="inlineStr">
@@ -9471,7 +9467,7 @@
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
       <c r="F22" s="437" t="n"/>
-      <c r="G22" s="222" t="n"/>
+      <c r="G22" s="437" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -9484,7 +9480,7 @@
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
       <c r="F23" s="439" t="n"/>
-      <c r="G23" s="222" t="n"/>
+      <c r="G23" s="439" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -10423,6 +10419,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -10432,6 +10429,7 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G21:G23"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -10446,7 +10444,6 @@
     <mergeCell ref="H36:H38"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
-    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
@@ -10464,7 +10461,6 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
@@ -10887,12 +10883,7 @@
         </is>
       </c>
       <c r="G12" s="435" t="n"/>
-      <c r="H12" s="470" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H12" s="470" t="n"/>
       <c r="I12" s="436" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -10908,7 +10899,6 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="438" t="n"/>
-      <c r="H13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -10923,7 +10913,6 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="438" t="n"/>
-      <c r="H14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -10962,13 +10951,13 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="G15" s="462" t="inlineStr">
-        <is>
-          <t>Port - Jana
+      <c r="G15" s="462" t="n"/>
+      <c r="H15" s="412" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H15" s="11" t="n"/>
       <c r="I15" s="440" t="inlineStr">
         <is>
           <t>Ing - APa-PaH-Velo
@@ -10987,8 +10976,7 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
       <c r="F16" s="437" t="n"/>
-      <c r="G16" s="437" t="n"/>
-      <c r="H16" s="222" t="n"/>
+      <c r="H16" s="406" t="n"/>
       <c r="I16" s="437" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -11003,8 +10991,7 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
       <c r="F17" s="439" t="n"/>
-      <c r="G17" s="439" t="n"/>
-      <c r="H17" s="222" t="n"/>
+      <c r="H17" s="407" t="n"/>
       <c r="I17" s="439" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -11034,10 +11021,10 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-9º e 10º tempos</t>
+      <c r="F18" s="404" t="inlineStr">
+        <is>
+          <t>Port - Jana
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G18" s="442" t="inlineStr">
@@ -11059,7 +11046,7 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="437" t="n"/>
+      <c r="F19" s="406" t="n"/>
       <c r="G19" s="437" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
@@ -11082,7 +11069,7 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="439" t="n"/>
+      <c r="F20" s="407" t="n"/>
       <c r="G20" s="439" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
@@ -11116,7 +11103,12 @@
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G21" s="11" t="n"/>
+      <c r="G21" s="409" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H21" s="444" t="n"/>
       <c r="I21" s="436" t="n"/>
       <c r="J21" s="262" t="inlineStr">
@@ -11143,7 +11135,7 @@
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
       <c r="F22" s="437" t="n"/>
-      <c r="G22" s="222" t="n"/>
+      <c r="G22" s="406" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -11156,7 +11148,7 @@
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
       <c r="F23" s="439" t="n"/>
-      <c r="G23" s="222" t="n"/>
+      <c r="G23" s="407" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -12095,6 +12087,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -12104,6 +12097,7 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="G21:G23"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -12118,7 +12112,6 @@
     <mergeCell ref="H36:H38"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
-    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
@@ -12136,7 +12129,6 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6618,12 +6618,7 @@
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="442" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I36" s="442" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -6645,7 +6640,6 @@
       <c r="F37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -6667,7 +6661,6 @@
       <c r="F38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6819,7 +6812,12 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="441" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
@@ -6842,7 +6840,7 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="283" t="n"/>
+      <c r="E46" s="406" t="n"/>
       <c r="F46" s="437" t="n"/>
       <c r="G46" s="438" t="n"/>
       <c r="H46" s="283" t="n"/>
@@ -6855,7 +6853,7 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="283" t="n"/>
+      <c r="E47" s="407" t="n"/>
       <c r="F47" s="439" t="n"/>
       <c r="G47" s="438" t="n"/>
       <c r="H47" s="283" t="n"/>
@@ -7161,6 +7159,7 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="A12:A14"/>
+    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="I39:I41"/>
@@ -7274,7 +7273,6 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
-    <mergeCell ref="I36:I38"/>
     <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
@@ -10952,7 +10950,7 @@
         </is>
       </c>
       <c r="G15" s="462" t="n"/>
-      <c r="H15" s="412" t="inlineStr">
+      <c r="H15" s="444" t="inlineStr">
         <is>
           <t>Redação - Raf
 4º e 5º tempos</t>
@@ -10976,7 +10974,7 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
       <c r="F16" s="437" t="n"/>
-      <c r="H16" s="406" t="n"/>
+      <c r="H16" s="437" t="n"/>
       <c r="I16" s="437" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -10991,7 +10989,7 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
       <c r="F17" s="439" t="n"/>
-      <c r="H17" s="407" t="n"/>
+      <c r="H17" s="439" t="n"/>
       <c r="I17" s="439" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -11021,7 +11019,7 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="404" t="inlineStr">
+      <c r="F18" s="462" t="inlineStr">
         <is>
           <t>Port - Jana
 1º e 2º tempos</t>
@@ -11046,7 +11044,7 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="406" t="n"/>
+      <c r="F19" s="437" t="n"/>
       <c r="G19" s="437" t="n"/>
       <c r="H19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
@@ -11069,7 +11067,7 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="407" t="n"/>
+      <c r="F20" s="439" t="n"/>
       <c r="G20" s="439" t="n"/>
       <c r="H20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
@@ -11103,7 +11101,7 @@
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G21" s="409" t="inlineStr">
+      <c r="G21" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
@@ -11135,7 +11133,7 @@
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="222" t="n"/>
       <c r="F22" s="437" t="n"/>
-      <c r="G22" s="406" t="n"/>
+      <c r="G22" s="437" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
@@ -11148,7 +11146,7 @@
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="222" t="n"/>
       <c r="F23" s="439" t="n"/>
-      <c r="G23" s="407" t="n"/>
+      <c r="G23" s="439" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="19" t="n"/>
@@ -20055,12 +20053,7 @@
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="442" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I36" s="442" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -20082,7 +20075,6 @@
       <c r="F37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -20104,7 +20096,6 @@
       <c r="F38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -20256,7 +20247,12 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="442" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="441" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
@@ -20279,7 +20275,7 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="283" t="n"/>
+      <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
       <c r="G46" s="438" t="n"/>
       <c r="H46" s="283" t="n"/>
@@ -20292,7 +20288,7 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="283" t="n"/>
+      <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
       <c r="G47" s="438" t="n"/>
       <c r="H47" s="283" t="n"/>
@@ -20598,6 +20594,7 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="A12:A14"/>
+    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="I39:I41"/>
@@ -20711,7 +20708,6 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
-    <mergeCell ref="I36:I38"/>
     <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6812,7 +6812,7 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="410" t="inlineStr">
+      <c r="E45" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 5º e 6º tempos</t>
@@ -6840,7 +6840,7 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="406" t="n"/>
+      <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
       <c r="G46" s="438" t="n"/>
       <c r="H46" s="283" t="n"/>
@@ -6853,7 +6853,7 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="407" t="n"/>
+      <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
       <c r="G47" s="438" t="n"/>
       <c r="H47" s="283" t="n"/>
@@ -12618,13 +12618,13 @@
         </is>
       </c>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="453" t="inlineStr">
+      <c r="G15" s="453" t="n"/>
+      <c r="H15" s="408" t="inlineStr">
         <is>
           <t>Ing - APa
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="435" t="n"/>
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -12638,8 +12638,7 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
       <c r="F16" s="222" t="n"/>
-      <c r="G16" s="437" t="n"/>
-      <c r="H16" s="438" t="n"/>
+      <c r="H16" s="406" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -12654,8 +12653,7 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
       <c r="F17" s="222" t="n"/>
-      <c r="G17" s="439" t="n"/>
-      <c r="H17" s="438" t="n"/>
+      <c r="H17" s="407" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -13171,12 +13169,7 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="440" t="inlineStr">
-        <is>
-          <t>Ing - APa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="440" t="n"/>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="436" t="inlineStr">
         <is>
@@ -13208,7 +13201,6 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="437" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="437" t="n"/>
@@ -13230,7 +13222,6 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="439" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="439" t="n"/>
@@ -13332,7 +13323,12 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H42" s="283" t="n"/>
+      <c r="H42" s="408" t="inlineStr">
+        <is>
+          <t>Ing - APa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -13350,7 +13346,7 @@
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="437" t="n"/>
       <c r="G43" s="437" t="n"/>
-      <c r="H43" s="283" t="n"/>
+      <c r="H43" s="406" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -13363,7 +13359,7 @@
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="439" t="n"/>
       <c r="G44" s="439" t="n"/>
-      <c r="H44" s="283" t="n"/>
+      <c r="H44" s="407" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -13732,7 +13728,6 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
-    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
@@ -13746,6 +13741,7 @@
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
+    <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -13784,6 +13780,7 @@
     <mergeCell ref="J48:J50"/>
     <mergeCell ref="D51:D53"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
@@ -13810,7 +13807,6 @@
     <mergeCell ref="H36:H38"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
-    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -12619,7 +12619,7 @@
       </c>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="453" t="n"/>
-      <c r="H15" s="408" t="inlineStr">
+      <c r="H15" s="440" t="inlineStr">
         <is>
           <t>Ing - APa
 2º e 3º tempos</t>
@@ -12638,7 +12638,7 @@
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
       <c r="F16" s="222" t="n"/>
-      <c r="H16" s="406" t="n"/>
+      <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
@@ -12653,7 +12653,7 @@
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
       <c r="F17" s="222" t="n"/>
-      <c r="H17" s="407" t="n"/>
+      <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
@@ -13323,7 +13323,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H42" s="408" t="inlineStr">
+      <c r="H42" s="440" t="inlineStr">
         <is>
           <t>Ing - APa
 2º e 3º tempos</t>
@@ -13346,7 +13346,7 @@
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="437" t="n"/>
       <c r="G43" s="437" t="n"/>
-      <c r="H43" s="406" t="n"/>
+      <c r="H43" s="437" t="n"/>
       <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
@@ -13359,7 +13359,7 @@
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="439" t="n"/>
       <c r="G44" s="439" t="n"/>
-      <c r="H44" s="407" t="n"/>
+      <c r="H44" s="439" t="n"/>
       <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
@@ -16032,13 +16032,13 @@
         <v/>
       </c>
       <c r="E15" s="435" t="n"/>
-      <c r="F15" s="435" t="n"/>
-      <c r="G15" s="434" t="inlineStr">
+      <c r="F15" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
-1º e 2º tempos</t>
-        </is>
-      </c>
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="434" t="n"/>
       <c r="H15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
@@ -16057,8 +16057,7 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="438" t="n"/>
-      <c r="F16" s="438" t="n"/>
-      <c r="G16" s="437" t="n"/>
+      <c r="F16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -16073,8 +16072,7 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="438" t="n"/>
-      <c r="F17" s="438" t="n"/>
-      <c r="G17" s="439" t="n"/>
+      <c r="F17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
@@ -16598,12 +16596,7 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="435" t="n"/>
-      <c r="G36" s="434" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G36" s="434" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="435" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -16625,7 +16618,6 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="438" t="n"/>
-      <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="438" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -16647,7 +16639,6 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="438" t="n"/>
-      <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="438" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -16735,7 +16726,12 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
+      <c r="F42" s="434" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G42" s="435" t="n"/>
       <c r="H42" s="458" t="inlineStr">
         <is>
@@ -16758,7 +16754,7 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
+      <c r="F43" s="437" t="n"/>
       <c r="G43" s="438" t="n"/>
       <c r="H43" s="437" t="n"/>
       <c r="I43" s="283" t="n"/>
@@ -16771,7 +16767,7 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
+      <c r="F44" s="439" t="n"/>
       <c r="G44" s="438" t="n"/>
       <c r="H44" s="439" t="n"/>
       <c r="I44" s="283" t="n"/>
@@ -17148,6 +17144,7 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
+    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -17243,8 +17240,8 @@
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="J36:J38"/>
-    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
@@ -17276,7 +17273,6 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
@@ -17741,13 +17737,13 @@
         <v/>
       </c>
       <c r="E15" s="435" t="n"/>
-      <c r="F15" s="435" t="n"/>
-      <c r="G15" s="434" t="inlineStr">
+      <c r="F15" s="403" t="inlineStr">
         <is>
           <t>Hist - Ver
-1º e 2º tempos</t>
-        </is>
-      </c>
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="434" t="n"/>
       <c r="H15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
@@ -17766,8 +17762,7 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="438" t="n"/>
-      <c r="F16" s="438" t="n"/>
-      <c r="G16" s="437" t="n"/>
+      <c r="F16" s="406" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -17782,8 +17777,7 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="438" t="n"/>
-      <c r="F17" s="438" t="n"/>
-      <c r="G17" s="439" t="n"/>
+      <c r="F17" s="407" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
@@ -18312,12 +18306,7 @@
         </is>
       </c>
       <c r="F36" s="435" t="n"/>
-      <c r="G36" s="434" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G36" s="434" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="435" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -18339,7 +18328,6 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="437" t="n"/>
       <c r="F37" s="438" t="n"/>
-      <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="438" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -18361,7 +18349,6 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="439" t="n"/>
       <c r="F38" s="438" t="n"/>
-      <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="438" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -18449,7 +18436,12 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
+      <c r="F42" s="403" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G42" s="435" t="n"/>
       <c r="H42" s="458" t="inlineStr">
         <is>
@@ -18472,7 +18464,7 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="283" t="n"/>
+      <c r="F43" s="406" t="n"/>
       <c r="G43" s="438" t="n"/>
       <c r="H43" s="437" t="n"/>
       <c r="I43" s="283" t="n"/>
@@ -18485,7 +18477,7 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="283" t="n"/>
+      <c r="F44" s="407" t="n"/>
       <c r="G44" s="438" t="n"/>
       <c r="H44" s="439" t="n"/>
       <c r="I44" s="283" t="n"/>
@@ -18862,6 +18854,7 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
+    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -18956,8 +18949,8 @@
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
+    <mergeCell ref="F42:F44"/>
     <mergeCell ref="J36:J38"/>
-    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
@@ -18989,7 +18982,6 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -9650,12 +9650,7 @@
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="440" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I30" s="440" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -9678,7 +9673,6 @@
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="283" t="n"/>
-      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -9697,7 +9691,6 @@
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="283" t="n"/>
-      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -9962,7 +9955,12 @@
 7º tempo</t>
         </is>
       </c>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="440" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -9979,7 +9977,7 @@
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="H43" s="437" t="n"/>
-      <c r="I43" s="283" t="n"/>
+      <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -9991,7 +9989,7 @@
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="H44" s="439" t="n"/>
-      <c r="I44" s="283" t="n"/>
+      <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -10014,10 +10012,10 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="470" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
+      <c r="F45" s="449" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G45" s="283" t="n"/>
@@ -10074,10 +10072,10 @@
         <v/>
       </c>
       <c r="E48" s="444" t="n"/>
-      <c r="F48" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
+      <c r="F48" s="434" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G48" s="441" t="inlineStr">
@@ -10406,6 +10404,7 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
+    <mergeCell ref="I42:I44"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -10475,7 +10474,6 @@
     <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
-    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -11318,12 +11316,7 @@
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="440" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I30" s="440" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -11346,7 +11339,6 @@
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="283" t="n"/>
-      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -11365,7 +11357,6 @@
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="283" t="n"/>
-      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -11630,7 +11621,12 @@
 7º tempo</t>
         </is>
       </c>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="440" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -11647,7 +11643,7 @@
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
       <c r="H43" s="437" t="n"/>
-      <c r="I43" s="283" t="n"/>
+      <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -11659,7 +11655,7 @@
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
       <c r="H44" s="439" t="n"/>
-      <c r="I44" s="283" t="n"/>
+      <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -11682,10 +11678,10 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="470" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
+      <c r="F45" s="449" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G45" s="283" t="n"/>
@@ -11742,10 +11738,10 @@
         <v/>
       </c>
       <c r="E48" s="444" t="n"/>
-      <c r="F48" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
+      <c r="F48" s="434" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G48" s="441" t="inlineStr">
@@ -12074,6 +12070,7 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
+    <mergeCell ref="I42:I44"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -12143,7 +12140,6 @@
     <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
-    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -13183,7 +13179,7 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="456" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -13204,7 +13200,6 @@
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="437" t="n"/>
-      <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -13225,7 +13220,6 @@
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="439" t="n"/>
-      <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -14619,7 +14613,7 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="456" t="inlineStr">
+      <c r="I27" s="426" t="inlineStr">
         <is>
           <t>Soc - Kle
 5º tempo</t>
@@ -14643,7 +14637,7 @@
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="437" t="n"/>
+      <c r="I28" s="406" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -14662,7 +14656,7 @@
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="439" t="n"/>
+      <c r="I29" s="407" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -14889,7 +14883,7 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="456" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -14911,7 +14905,6 @@
       <c r="F37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="437" t="n"/>
-      <c r="I37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -14933,7 +14926,6 @@
       <c r="F38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="439" t="n"/>
-      <c r="I38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -15032,7 +15024,7 @@
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="456" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -15050,7 +15042,6 @@
       <c r="F43" s="437" t="n"/>
       <c r="G43" s="437" t="n"/>
       <c r="H43" s="283" t="n"/>
-      <c r="I43" s="283" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -15063,7 +15054,6 @@
       <c r="F44" s="439" t="n"/>
       <c r="G44" s="439" t="n"/>
       <c r="H44" s="283" t="n"/>
-      <c r="I44" s="283" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -17737,7 +17727,7 @@
         <v/>
       </c>
       <c r="E15" s="435" t="n"/>
-      <c r="F15" s="403" t="inlineStr">
+      <c r="F15" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
 2º e 3º tempos</t>
@@ -17762,7 +17752,7 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="438" t="n"/>
-      <c r="F16" s="406" t="n"/>
+      <c r="F16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -17777,7 +17767,7 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="438" t="n"/>
-      <c r="F17" s="407" t="n"/>
+      <c r="F17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
@@ -18436,7 +18426,7 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="403" t="inlineStr">
+      <c r="F42" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
 2º e 3º tempos</t>
@@ -18464,7 +18454,7 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="406" t="n"/>
+      <c r="F43" s="437" t="n"/>
       <c r="G43" s="438" t="n"/>
       <c r="H43" s="437" t="n"/>
       <c r="I43" s="283" t="n"/>
@@ -18477,7 +18467,7 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="407" t="n"/>
+      <c r="F44" s="439" t="n"/>
       <c r="G44" s="438" t="n"/>
       <c r="H44" s="439" t="n"/>
       <c r="I44" s="283" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -12914,12 +12914,7 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="456" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I27" s="456" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -12938,7 +12933,6 @@
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="437" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -12957,7 +12951,6 @@
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="439" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -13388,7 +13381,12 @@
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G45" s="283" t="n"/>
+      <c r="G45" s="456" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="H45" s="435" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
@@ -13406,7 +13404,7 @@
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
-      <c r="G46" s="283" t="n"/>
+      <c r="G46" s="437" t="n"/>
       <c r="H46" s="438" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -13419,7 +13417,7 @@
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
-      <c r="G47" s="283" t="n"/>
+      <c r="G47" s="439" t="n"/>
       <c r="H47" s="438" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -13726,6 +13724,7 @@
     <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -13833,7 +13832,6 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I30:I32"/>
@@ -14613,12 +14611,7 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="426" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I27" s="456" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -14637,7 +14630,6 @@
       <c r="F28" s="283" t="n"/>
       <c r="G28" s="283" t="n"/>
       <c r="H28" s="283" t="n"/>
-      <c r="I28" s="406" t="n"/>
       <c r="J28" s="352" t="n"/>
       <c r="L28" s="23" t="n"/>
       <c r="M28" s="325" t="inlineStr">
@@ -14656,7 +14648,6 @@
       <c r="F29" s="283" t="n"/>
       <c r="G29" s="283" t="n"/>
       <c r="H29" s="283" t="n"/>
-      <c r="I29" s="407" t="n"/>
       <c r="J29" s="352" t="n"/>
       <c r="L29" s="46" t="n"/>
       <c r="M29" s="157" t="inlineStr">
@@ -15024,7 +15015,12 @@
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="456" t="n"/>
+      <c r="I42" s="426" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -15042,6 +15038,7 @@
       <c r="F43" s="437" t="n"/>
       <c r="G43" s="437" t="n"/>
       <c r="H43" s="283" t="n"/>
+      <c r="I43" s="406" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -15054,6 +15051,7 @@
       <c r="F44" s="439" t="n"/>
       <c r="G44" s="439" t="n"/>
       <c r="H44" s="283" t="n"/>
+      <c r="I44" s="407" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -15472,6 +15470,7 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
+    <mergeCell ref="I42:I44"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -15542,7 +15541,6 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="I27:I29"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I30:I32"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6614,7 +6614,7 @@
       <c r="G36" s="457" t="inlineStr">
         <is>
           <t>Fil - LAn
-10º tempo</t>
+4º tempo</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
@@ -6686,7 +6686,7 @@
       <c r="G39" s="456" t="inlineStr">
         <is>
           <t>Soc - Kle
-2º tempo</t>
+6º tempo</t>
         </is>
       </c>
       <c r="H39" s="452" t="inlineStr">
@@ -14947,7 +14947,7 @@
       <c r="G39" s="457" t="inlineStr">
         <is>
           <t>Fil - LAn
-1º tempo</t>
+7º tempo</t>
         </is>
       </c>
       <c r="H39" s="434" t="inlineStr">
@@ -15015,7 +15015,7 @@
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="426" t="inlineStr">
+      <c r="I42" s="456" t="inlineStr">
         <is>
           <t>Soc - Kle
 5º tempo</t>
@@ -15038,7 +15038,7 @@
       <c r="F43" s="437" t="n"/>
       <c r="G43" s="437" t="n"/>
       <c r="H43" s="283" t="n"/>
-      <c r="I43" s="406" t="n"/>
+      <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -15051,7 +15051,7 @@
       <c r="F44" s="439" t="n"/>
       <c r="G44" s="439" t="n"/>
       <c r="H44" s="283" t="n"/>
-      <c r="I44" s="407" t="n"/>
+      <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -17972,7 +17972,7 @@
       <c r="G24" s="459" t="inlineStr">
         <is>
           <t>Fil - LAn
-9º tempo</t>
+11º tempo</t>
         </is>
       </c>
       <c r="H24" s="283" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6611,10 +6611,10 @@
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G36" s="457" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
+      <c r="G36" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+1º tempo</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
@@ -6638,7 +6638,7 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="437" t="n"/>
-      <c r="G37" s="437" t="n"/>
+      <c r="G37" s="406" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -6659,7 +6659,7 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="439" t="n"/>
-      <c r="G38" s="439" t="n"/>
+      <c r="G38" s="407" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -6746,20 +6746,15 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="283" t="n"/>
+      <c r="F42" s="449" t="n"/>
+      <c r="G42" s="457" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I42" s="451" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -6774,10 +6769,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="437" t="n"/>
-      <c r="G43" s="283" t="n"/>
+      <c r="G43" s="437" t="n"/>
       <c r="H43" s="283" t="n"/>
-      <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -6787,10 +6780,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="439" t="n"/>
-      <c r="G44" s="283" t="n"/>
+      <c r="G44" s="439" t="n"/>
       <c r="H44" s="283" t="n"/>
-      <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -6824,8 +6815,13 @@
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G45" s="435" t="n"/>
-      <c r="H45" s="283" t="n"/>
+      <c r="G45" s="449" t="n"/>
+      <c r="H45" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
@@ -6842,8 +6838,7 @@
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
-      <c r="G46" s="438" t="n"/>
-      <c r="H46" s="283" t="n"/>
+      <c r="H46" s="406" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -6855,8 +6850,7 @@
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
-      <c r="G47" s="438" t="n"/>
-      <c r="H47" s="283" t="n"/>
+      <c r="H47" s="407" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -7144,6 +7138,7 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -7189,6 +7184,7 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
+    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -7201,7 +7197,6 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
-    <mergeCell ref="I42:I44"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -7237,7 +7232,6 @@
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="F42:F44"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
@@ -20022,10 +20016,10 @@
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G36" s="457" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-10º tempo</t>
+      <c r="G36" s="451" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+1º tempo</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
@@ -20157,20 +20151,15 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="283" t="n"/>
+      <c r="F42" s="449" t="n"/>
+      <c r="G42" s="457" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+10º tempo</t>
+        </is>
+      </c>
       <c r="H42" s="435" t="n"/>
-      <c r="I42" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I42" s="451" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -20185,10 +20174,8 @@
       <c r="C43" s="313" t="n"/>
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
-      <c r="F43" s="437" t="n"/>
-      <c r="G43" s="283" t="n"/>
+      <c r="G43" s="437" t="n"/>
       <c r="H43" s="438" t="n"/>
-      <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -20198,10 +20185,8 @@
       <c r="C44" s="313" t="n"/>
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
-      <c r="F44" s="439" t="n"/>
-      <c r="G44" s="283" t="n"/>
+      <c r="G44" s="439" t="n"/>
       <c r="H44" s="438" t="n"/>
-      <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -20235,8 +20220,13 @@
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="G45" s="435" t="n"/>
-      <c r="H45" s="283" t="n"/>
+      <c r="G45" s="449" t="n"/>
+      <c r="H45" s="449" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
@@ -20253,8 +20243,7 @@
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
-      <c r="G46" s="438" t="n"/>
-      <c r="H46" s="283" t="n"/>
+      <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -20266,8 +20255,7 @@
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
-      <c r="G47" s="438" t="n"/>
-      <c r="H47" s="283" t="n"/>
+      <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -20555,6 +20543,7 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -20600,6 +20589,7 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
+    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -20612,7 +20602,6 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
-    <mergeCell ref="I42:I44"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -20648,7 +20637,6 @@
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="F42:F44"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6611,14 +6611,19 @@
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G36" s="419" t="inlineStr">
+      <c r="G36" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 1º tempo</t>
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="442" t="n"/>
+      <c r="I36" s="411" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -6638,8 +6643,9 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="437" t="n"/>
-      <c r="G37" s="406" t="n"/>
+      <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
+      <c r="I37" s="406" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -6659,8 +6665,9 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="439" t="n"/>
-      <c r="G38" s="407" t="n"/>
+      <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
+      <c r="I38" s="407" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6681,7 +6688,12 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="456" t="inlineStr">
         <is>
@@ -6695,12 +6707,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I39" s="443" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="I39" s="443" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6708,11 +6715,10 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="283" t="n"/>
+      <c r="E40" s="406" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="437" t="n"/>
-      <c r="I40" s="437" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -6720,11 +6726,10 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="283" t="n"/>
+      <c r="E41" s="407" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="439" t="n"/>
-      <c r="I41" s="439" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6803,12 +6808,7 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="442" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="E45" s="442" t="n"/>
       <c r="F45" s="441" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="G45" s="449" t="n"/>
-      <c r="H45" s="417" t="inlineStr">
+      <c r="H45" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 5º e 6º tempos</t>
@@ -6836,9 +6836,8 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
-      <c r="H46" s="406" t="n"/>
+      <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -6848,9 +6847,8 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
-      <c r="H47" s="407" t="n"/>
+      <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -7154,10 +7152,8 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="A12:A14"/>
-    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -7219,6 +7215,7 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -7267,6 +7264,7 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
+    <mergeCell ref="I36:I38"/>
     <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
@@ -20023,7 +20021,12 @@
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="442" t="n"/>
+      <c r="I36" s="443" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -20045,6 +20048,7 @@
       <c r="F37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
+      <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -20066,6 +20070,7 @@
       <c r="F38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
+      <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -20086,7 +20091,12 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
+      <c r="E39" s="442" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="456" t="inlineStr">
         <is>
@@ -20100,12 +20110,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I39" s="443" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="I39" s="443" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -20113,11 +20118,10 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="283" t="n"/>
+      <c r="E40" s="437" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="437" t="n"/>
-      <c r="I40" s="437" t="n"/>
       <c r="J40" s="352" t="n"/>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="4" thickBot="1">
@@ -20125,11 +20129,10 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="283" t="n"/>
+      <c r="E41" s="439" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="439" t="n"/>
-      <c r="I41" s="439" t="n"/>
       <c r="J41" s="352" t="n"/>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="4">
@@ -20208,12 +20211,7 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="442" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="E45" s="442" t="n"/>
       <c r="F45" s="441" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
@@ -20241,7 +20239,6 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
       <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
@@ -20253,7 +20250,6 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
       <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
@@ -20559,10 +20555,8 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="A12:A14"/>
-    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="I39:I41"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -20624,6 +20618,7 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
+    <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
     <mergeCell ref="B42:B44"/>
@@ -20672,6 +20667,7 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
+    <mergeCell ref="I36:I38"/>
     <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="411" t="inlineStr">
+      <c r="I36" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
 6º e 7º tempos</t>
@@ -6645,7 +6645,7 @@
       <c r="F37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
-      <c r="I37" s="406" t="n"/>
+      <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
       <c r="F38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
-      <c r="I38" s="407" t="n"/>
+      <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6688,7 +6688,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="410" t="inlineStr">
+      <c r="E39" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 5º e 6º tempos</t>
@@ -6715,7 +6715,7 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="406" t="n"/>
+      <c r="E40" s="437" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="437" t="n"/>
@@ -6726,7 +6726,7 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="407" t="n"/>
+      <c r="E41" s="439" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="439" t="n"/>
@@ -9940,7 +9940,12 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="441" t="n"/>
+      <c r="G42" s="451" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+2º tempo</t>
+        </is>
+      </c>
       <c r="H42" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
@@ -9968,6 +9973,7 @@
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
+      <c r="G43" s="437" t="n"/>
       <c r="H43" s="437" t="n"/>
       <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -9980,6 +9986,7 @@
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
+      <c r="G44" s="439" t="n"/>
       <c r="H44" s="439" t="n"/>
       <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -10313,7 +10320,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="165">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -10342,6 +10349,7 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -11606,7 +11614,12 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="441" t="n"/>
+      <c r="G42" s="419" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+2º tempo</t>
+        </is>
+      </c>
       <c r="H42" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
@@ -11634,6 +11647,7 @@
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
+      <c r="G43" s="406" t="n"/>
       <c r="H43" s="437" t="n"/>
       <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -11646,6 +11660,7 @@
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
+      <c r="G44" s="407" t="n"/>
       <c r="H44" s="439" t="n"/>
       <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -11979,7 +11994,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="164">
+  <mergeCells count="165">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -12008,6 +12023,7 @@
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
     <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G42:G44"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6611,12 +6611,7 @@
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G36" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-1º tempo</t>
-        </is>
-      </c>
+      <c r="G36" s="451" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="443" t="inlineStr">
         <is>
@@ -6643,7 +6638,6 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="437" t="n"/>
-      <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -6665,7 +6659,6 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="439" t="n"/>
-      <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -6808,7 +6801,12 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="442" t="n"/>
+      <c r="E45" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="441" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
@@ -6836,6 +6834,7 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
+      <c r="E46" s="406" t="n"/>
       <c r="F46" s="437" t="n"/>
       <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
@@ -6847,6 +6846,7 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
+      <c r="E47" s="407" t="n"/>
       <c r="F47" s="439" t="n"/>
       <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
@@ -7152,6 +7152,7 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="A12:A14"/>
+    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="B33:B35"/>
@@ -7262,7 +7263,6 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
     <mergeCell ref="I30:I32"/>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="419" t="inlineStr">
+      <c r="G42" s="451" t="inlineStr">
         <is>
           <t>Qui - Fab
 2º tempo</t>
@@ -11647,7 +11647,7 @@
       <c r="D43" s="350" t="n"/>
       <c r="E43" s="283" t="n"/>
       <c r="F43" s="283" t="n"/>
-      <c r="G43" s="406" t="n"/>
+      <c r="G43" s="437" t="n"/>
       <c r="H43" s="437" t="n"/>
       <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
@@ -11660,7 +11660,7 @@
       <c r="D44" s="350" t="n"/>
       <c r="E44" s="283" t="n"/>
       <c r="F44" s="283" t="n"/>
-      <c r="G44" s="407" t="n"/>
+      <c r="G44" s="439" t="n"/>
       <c r="H44" s="439" t="n"/>
       <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
@@ -20030,12 +20030,7 @@
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G36" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-1º tempo</t>
-        </is>
-      </c>
+      <c r="G36" s="451" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="443" t="inlineStr">
         <is>
@@ -20062,7 +20057,6 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="437" t="n"/>
-      <c r="G37" s="437" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -20084,7 +20078,6 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="439" t="n"/>
-      <c r="G38" s="439" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -20227,7 +20220,12 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="442" t="n"/>
+      <c r="E45" s="451" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="441" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
@@ -20255,6 +20253,7 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
+      <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
       <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
@@ -20266,6 +20265,7 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
+      <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
       <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
@@ -20571,6 +20571,7 @@
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
     <mergeCell ref="A12:A14"/>
+    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="B33:B35"/>
@@ -20681,7 +20682,6 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
     <mergeCell ref="I30:I32"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6801,7 +6801,7 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="419" t="inlineStr">
+      <c r="E45" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
 6º e 7º tempos</t>
@@ -6834,7 +6834,7 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="406" t="n"/>
+      <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
       <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
@@ -6846,7 +6846,7 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="407" t="n"/>
+      <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
       <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
@@ -14864,12 +14864,7 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="440" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F36" s="440" t="n"/>
       <c r="G36" s="436" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
@@ -14901,7 +14896,6 @@
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
-      <c r="F37" s="437" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
@@ -14922,7 +14916,6 @@
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
-      <c r="F38" s="439" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
@@ -15093,7 +15086,12 @@
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G45" s="435" t="n"/>
+      <c r="G45" s="408" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H45" s="435" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
@@ -15111,7 +15109,7 @@
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
-      <c r="G46" s="438" t="n"/>
+      <c r="G46" s="406" t="n"/>
       <c r="H46" s="438" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -15124,7 +15122,7 @@
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
-      <c r="G47" s="438" t="n"/>
+      <c r="G47" s="407" t="n"/>
       <c r="H47" s="438" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -15442,6 +15440,7 @@
     <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="G45:G47"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -15506,7 +15505,6 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="M26:N26"/>
-    <mergeCell ref="F36:F38"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="J9:J11"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -12988,7 +12988,12 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
+      <c r="G30" s="436" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
@@ -13021,7 +13026,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="283" t="n"/>
+      <c r="G31" s="437" t="n"/>
       <c r="H31" s="437" t="n"/>
       <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -13040,7 +13045,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="283" t="n"/>
+      <c r="G32" s="439" t="n"/>
       <c r="H32" s="439" t="n"/>
       <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -13166,12 +13171,17 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="440" t="n"/>
+      <c r="E36" s="458" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="436" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
+      <c r="G36" s="456" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
         </is>
       </c>
       <c r="H36" s="452" t="inlineStr">
@@ -13198,6 +13208,7 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
+      <c r="E37" s="437" t="n"/>
       <c r="F37" s="283" t="n"/>
       <c r="G37" s="437" t="n"/>
       <c r="H37" s="437" t="n"/>
@@ -13218,6 +13229,7 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
+      <c r="E38" s="439" t="n"/>
       <c r="F38" s="283" t="n"/>
       <c r="G38" s="439" t="n"/>
       <c r="H38" s="439" t="n"/>
@@ -13241,10 +13253,10 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="458" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+      <c r="E39" s="451" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F39" s="283" t="n"/>
@@ -13377,24 +13389,14 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E45" s="451" t="n"/>
       <c r="F45" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G45" s="456" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="G45" s="456" t="n"/>
       <c r="H45" s="435" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
@@ -13410,9 +13412,7 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
-      <c r="G46" s="437" t="n"/>
       <c r="H46" s="438" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -13423,9 +13423,7 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
-      <c r="G47" s="439" t="n"/>
       <c r="H47" s="438" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -13728,11 +13726,11 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
-    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G30:G32"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -14685,7 +14683,12 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
+      <c r="G30" s="405" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H30" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
@@ -14718,7 +14721,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="283" t="n"/>
+      <c r="G31" s="406" t="n"/>
       <c r="H31" s="437" t="n"/>
       <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -14737,7 +14740,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="283" t="n"/>
+      <c r="G32" s="407" t="n"/>
       <c r="H32" s="439" t="n"/>
       <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -14863,21 +14866,26 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
+      <c r="E36" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F36" s="440" t="n"/>
-      <c r="G36" s="436" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G36" s="436" t="n"/>
       <c r="H36" s="452" t="inlineStr">
         <is>
           <t>Fis - VSi
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I36" s="456" t="n"/>
+      <c r="I36" s="426" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -14895,9 +14903,9 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="283" t="n"/>
-      <c r="G37" s="437" t="n"/>
+      <c r="E37" s="406" t="n"/>
       <c r="H37" s="437" t="n"/>
+      <c r="I37" s="406" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -14915,9 +14923,9 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="283" t="n"/>
-      <c r="G38" s="439" t="n"/>
+      <c r="E38" s="407" t="n"/>
       <c r="H38" s="439" t="n"/>
+      <c r="I38" s="407" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -14938,10 +14946,10 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="458" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+      <c r="E39" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F39" s="283" t="n"/>
@@ -14965,7 +14973,7 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="437" t="n"/>
+      <c r="E40" s="406" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="437" t="n"/>
@@ -14977,7 +14985,7 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="439" t="n"/>
+      <c r="E41" s="407" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="439" t="n"/>
@@ -15016,12 +15024,7 @@
         </is>
       </c>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="456" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I42" s="456" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -15039,7 +15042,6 @@
       <c r="F43" s="437" t="n"/>
       <c r="G43" s="437" t="n"/>
       <c r="H43" s="283" t="n"/>
-      <c r="I43" s="437" t="n"/>
       <c r="J43" s="352" t="n"/>
       <c r="L43" s="331" t="n"/>
     </row>
@@ -15052,7 +15054,6 @@
       <c r="F44" s="439" t="n"/>
       <c r="G44" s="439" t="n"/>
       <c r="H44" s="283" t="n"/>
-      <c r="I44" s="439" t="n"/>
       <c r="J44" s="352" t="n"/>
       <c r="L44" s="331" t="n"/>
     </row>
@@ -15074,19 +15075,14 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E45" s="451" t="n"/>
       <c r="F45" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 10º e 11º tempos</t>
         </is>
       </c>
-      <c r="G45" s="408" t="inlineStr">
+      <c r="G45" s="440" t="inlineStr">
         <is>
           <t>Ing - Vir
 4º e 5º tempos</t>
@@ -15107,9 +15103,8 @@
       <c r="B46" s="313" t="n"/>
       <c r="C46" s="313" t="n"/>
       <c r="D46" s="350" t="n"/>
-      <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
-      <c r="G46" s="406" t="n"/>
+      <c r="G46" s="437" t="n"/>
       <c r="H46" s="438" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
@@ -15120,9 +15115,8 @@
       <c r="B47" s="313" t="n"/>
       <c r="C47" s="313" t="n"/>
       <c r="D47" s="350" t="n"/>
-      <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
-      <c r="G47" s="407" t="n"/>
+      <c r="G47" s="439" t="n"/>
       <c r="H47" s="438" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
@@ -15436,11 +15430,12 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
-    <mergeCell ref="E45:E47"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="G45:G47"/>
+    <mergeCell ref="G30:G32"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -15477,7 +15472,6 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
-    <mergeCell ref="I42:I44"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -15547,8 +15541,8 @@
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G36:G38"/>
     <mergeCell ref="A39:A41"/>
+    <mergeCell ref="I36:I38"/>
     <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6612,7 +6612,12 @@
         </is>
       </c>
       <c r="G36" s="451" t="n"/>
-      <c r="H36" s="283" t="n"/>
+      <c r="H36" s="417" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="I36" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
@@ -6638,7 +6643,7 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="437" t="n"/>
-      <c r="H37" s="283" t="n"/>
+      <c r="H37" s="406" t="n"/>
       <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -6659,7 +6664,7 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="439" t="n"/>
-      <c r="H38" s="283" t="n"/>
+      <c r="H38" s="407" t="n"/>
       <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -6814,12 +6819,7 @@
         </is>
       </c>
       <c r="G45" s="449" t="n"/>
-      <c r="H45" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="449" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
@@ -6836,7 +6836,6 @@
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
-      <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -6848,7 +6847,6 @@
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
-      <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -7181,7 +7179,6 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -7231,6 +7228,7 @@
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="E15:E17"/>
+    <mergeCell ref="H36:H38"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
@@ -14683,7 +14681,7 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="405" t="inlineStr">
+      <c r="G30" s="436" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
@@ -14721,7 +14719,7 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="406" t="n"/>
+      <c r="G31" s="437" t="n"/>
       <c r="H31" s="437" t="n"/>
       <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -14740,7 +14738,7 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="407" t="n"/>
+      <c r="G32" s="439" t="n"/>
       <c r="H32" s="439" t="n"/>
       <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -14866,7 +14864,7 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="421" t="inlineStr">
+      <c r="E36" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - BPad/MFo/SMo
 1º ao 3º tempos</t>
@@ -14880,7 +14878,7 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I36" s="426" t="inlineStr">
+      <c r="I36" s="456" t="inlineStr">
         <is>
           <t>Soc - Kle
 5º tempo</t>
@@ -14903,9 +14901,9 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="406" t="n"/>
+      <c r="E37" s="437" t="n"/>
       <c r="H37" s="437" t="n"/>
-      <c r="I37" s="406" t="n"/>
+      <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -14923,9 +14921,9 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="407" t="n"/>
+      <c r="E38" s="439" t="n"/>
       <c r="H38" s="439" t="n"/>
-      <c r="I38" s="407" t="n"/>
+      <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="4">
@@ -14946,7 +14944,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="419" t="inlineStr">
+      <c r="E39" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl
 4º e 5º tempos</t>
@@ -14973,7 +14971,7 @@
       <c r="B40" s="313" t="n"/>
       <c r="C40" s="313" t="n"/>
       <c r="D40" s="350" t="n"/>
-      <c r="E40" s="406" t="n"/>
+      <c r="E40" s="437" t="n"/>
       <c r="F40" s="283" t="n"/>
       <c r="G40" s="437" t="n"/>
       <c r="H40" s="437" t="n"/>
@@ -14985,7 +14983,7 @@
       <c r="B41" s="313" t="n"/>
       <c r="C41" s="313" t="n"/>
       <c r="D41" s="350" t="n"/>
-      <c r="E41" s="407" t="n"/>
+      <c r="E41" s="439" t="n"/>
       <c r="F41" s="283" t="n"/>
       <c r="G41" s="439" t="n"/>
       <c r="H41" s="439" t="n"/>
@@ -20023,7 +20021,12 @@
         </is>
       </c>
       <c r="G36" s="451" t="n"/>
-      <c r="H36" s="283" t="n"/>
+      <c r="H36" s="449" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="I36" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
@@ -20049,7 +20052,7 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="437" t="n"/>
-      <c r="H37" s="283" t="n"/>
+      <c r="H37" s="437" t="n"/>
       <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -20070,7 +20073,7 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="439" t="n"/>
-      <c r="H38" s="283" t="n"/>
+      <c r="H38" s="439" t="n"/>
       <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -20225,12 +20228,7 @@
         </is>
       </c>
       <c r="G45" s="449" t="n"/>
-      <c r="H45" s="449" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="449" t="n"/>
       <c r="I45" s="386" t="inlineStr">
         <is>
           <t>2CH
@@ -20247,7 +20245,6 @@
       <c r="D46" s="350" t="n"/>
       <c r="E46" s="437" t="n"/>
       <c r="F46" s="437" t="n"/>
-      <c r="H46" s="437" t="n"/>
       <c r="I46" s="351" t="n"/>
       <c r="J46" s="352" t="n"/>
       <c r="L46" s="331" t="n"/>
@@ -20259,7 +20256,6 @@
       <c r="D47" s="350" t="n"/>
       <c r="E47" s="439" t="n"/>
       <c r="F47" s="439" t="n"/>
-      <c r="H47" s="439" t="n"/>
       <c r="I47" s="387" t="n"/>
       <c r="J47" s="352" t="n"/>
       <c r="L47" s="332" t="n"/>
@@ -20592,7 +20588,6 @@
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="H45:H47"/>
     <mergeCell ref="J30:J32"/>
     <mergeCell ref="B48:B50"/>
     <mergeCell ref="D48:D50"/>
@@ -20642,6 +20637,7 @@
     <mergeCell ref="H39:H41"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="E15:E17"/>
+    <mergeCell ref="H36:H38"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="G36" s="451" t="n"/>
-      <c r="H36" s="417" t="inlineStr">
+      <c r="H36" s="449" t="inlineStr">
         <is>
           <t>Bio - Ale
 5º e 6º tempos</t>
@@ -6643,7 +6643,7 @@
       <c r="D37" s="350" t="n"/>
       <c r="E37" s="283" t="n"/>
       <c r="F37" s="437" t="n"/>
-      <c r="H37" s="406" t="n"/>
+      <c r="H37" s="437" t="n"/>
       <c r="I37" s="437" t="n"/>
       <c r="J37" s="352" t="n"/>
       <c r="L37" s="4" t="inlineStr">
@@ -6664,7 +6664,7 @@
       <c r="D38" s="350" t="n"/>
       <c r="E38" s="283" t="n"/>
       <c r="F38" s="439" t="n"/>
-      <c r="H38" s="407" t="n"/>
+      <c r="H38" s="439" t="n"/>
       <c r="I38" s="439" t="n"/>
       <c r="J38" s="352" t="n"/>
     </row>
@@ -12537,12 +12537,7 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E12" s="451" t="n"/>
       <c r="F12" s="449" t="inlineStr">
         <is>
           <t>Bio - Lza
@@ -12556,7 +12551,12 @@
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
+      <c r="I12" s="451" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -12568,11 +12568,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="437" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="222" t="n"/>
+      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -12584,11 +12583,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="439" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="222" t="n"/>
+      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -13736,7 +13734,6 @@
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
-    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="H42:H44"/>
     <mergeCell ref="J42:J44"/>
@@ -13845,6 +13842,7 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
+    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>
@@ -14230,12 +14228,7 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E12" s="451" t="n"/>
       <c r="F12" s="449" t="inlineStr">
         <is>
           <t>Bio - Lza
@@ -14249,7 +14242,12 @@
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
+      <c r="I12" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -14261,11 +14259,10 @@
       <c r="B13" s="313" t="n"/>
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
-      <c r="E13" s="437" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="222" t="n"/>
+      <c r="I13" s="406" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -14277,11 +14274,10 @@
       <c r="B14" s="313" t="n"/>
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
-      <c r="E14" s="439" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="222" t="n"/>
+      <c r="I14" s="407" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -15441,7 +15437,6 @@
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
-    <mergeCell ref="E12:E14"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
@@ -15548,6 +15543,7 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
+    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -10075,13 +10075,13 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G48" s="441" t="inlineStr">
+      <c r="G48" s="441" t="n"/>
+      <c r="H48" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -10095,8 +10095,7 @@
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
       <c r="F49" s="437" t="n"/>
-      <c r="G49" s="437" t="n"/>
-      <c r="H49" s="438" t="n"/>
+      <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -10106,8 +10105,7 @@
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
       <c r="F50" s="439" t="n"/>
-      <c r="G50" s="439" t="n"/>
-      <c r="H50" s="438" t="n"/>
+      <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -10381,7 +10379,6 @@
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
@@ -10459,6 +10456,7 @@
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
+    <mergeCell ref="H48:H50"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
     <mergeCell ref="J39:J41"/>
@@ -11749,13 +11747,13 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G48" s="441" t="inlineStr">
+      <c r="G48" s="441" t="n"/>
+      <c r="H48" s="409" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -11769,8 +11767,7 @@
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
       <c r="F49" s="437" t="n"/>
-      <c r="G49" s="437" t="n"/>
-      <c r="H49" s="438" t="n"/>
+      <c r="H49" s="406" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -11780,8 +11777,7 @@
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
       <c r="F50" s="439" t="n"/>
-      <c r="G50" s="439" t="n"/>
-      <c r="H50" s="438" t="n"/>
+      <c r="H50" s="407" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -12055,7 +12051,6 @@
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
@@ -12133,6 +12128,7 @@
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
+    <mergeCell ref="H48:H50"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
     <mergeCell ref="J39:J41"/>
@@ -14242,7 +14238,7 @@
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="419" t="inlineStr">
+      <c r="I12" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl
 3º e 4º tempos</t>
@@ -14262,7 +14258,7 @@
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="406" t="n"/>
+      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -14277,7 +14273,7 @@
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="407" t="n"/>
+      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6430,15 +6430,15 @@
         <v/>
       </c>
       <c r="E30" s="435" t="n"/>
-      <c r="F30" s="435" t="n"/>
+      <c r="F30" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+9º ao 11º tempos</t>
+        </is>
+      </c>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="435" t="n"/>
-      <c r="I30" s="458" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="I30" s="458" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -6458,10 +6458,9 @@
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="438" t="n"/>
-      <c r="F31" s="438" t="n"/>
+      <c r="F31" s="406" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="438" t="n"/>
-      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -6477,10 +6476,9 @@
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="438" t="n"/>
-      <c r="F32" s="438" t="n"/>
+      <c r="F32" s="407" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="438" t="n"/>
-      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -7175,6 +7173,7 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="F30:F32"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -7263,7 +7262,6 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
-    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -11748,7 +11746,7 @@
         </is>
       </c>
       <c r="G48" s="441" t="n"/>
-      <c r="H48" s="409" t="inlineStr">
+      <c r="H48" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
@@ -11767,7 +11765,7 @@
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
       <c r="F49" s="437" t="n"/>
-      <c r="H49" s="406" t="n"/>
+      <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -11777,7 +11775,7 @@
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
       <c r="F50" s="439" t="n"/>
-      <c r="H50" s="407" t="n"/>
+      <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -19831,15 +19829,15 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="435" t="n"/>
+      <c r="F30" s="458" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+9º ao 11º tempos</t>
+        </is>
+      </c>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="435" t="n"/>
-      <c r="I30" s="458" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="I30" s="458" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -19859,10 +19857,9 @@
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
-      <c r="F31" s="438" t="n"/>
+      <c r="F31" s="437" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="438" t="n"/>
-      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -19878,10 +19875,9 @@
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
-      <c r="F32" s="438" t="n"/>
+      <c r="F32" s="439" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="438" t="n"/>
-      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -20576,6 +20572,7 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="F30:F32"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -20664,7 +20661,6 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
-    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6430,15 +6430,15 @@
         <v/>
       </c>
       <c r="E30" s="435" t="n"/>
-      <c r="F30" s="421" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-9º ao 11º tempos</t>
-        </is>
-      </c>
+      <c r="F30" s="458" t="n"/>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="435" t="n"/>
-      <c r="I30" s="458" t="n"/>
+      <c r="I30" s="421" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -6458,9 +6458,9 @@
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="438" t="n"/>
-      <c r="F31" s="406" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="438" t="n"/>
+      <c r="I31" s="406" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -6476,9 +6476,9 @@
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="438" t="n"/>
-      <c r="F32" s="407" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="438" t="n"/>
+      <c r="I32" s="407" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -7173,7 +7173,6 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
-    <mergeCell ref="F30:F32"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -7262,6 +7261,7 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
+    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>
@@ -19829,15 +19829,15 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="458" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-9º ao 11º tempos</t>
-        </is>
-      </c>
+      <c r="F30" s="458" t="n"/>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="435" t="n"/>
-      <c r="I30" s="458" t="n"/>
+      <c r="I30" s="458" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -19857,9 +19857,9 @@
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
-      <c r="F31" s="437" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="438" t="n"/>
+      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -19875,9 +19875,9 @@
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
-      <c r="F32" s="439" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="438" t="n"/>
+      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -20572,7 +20572,6 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
-    <mergeCell ref="F30:F32"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -20661,6 +20660,7 @@
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="A39:A41"/>
     <mergeCell ref="I36:I38"/>
+    <mergeCell ref="I30:I32"/>
     <mergeCell ref="A48:A50"/>
     <mergeCell ref="I45:I47"/>
     <mergeCell ref="F54:F56"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6433,7 +6433,7 @@
       <c r="F30" s="458" t="n"/>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="435" t="n"/>
-      <c r="I30" s="421" t="inlineStr">
+      <c r="I30" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
 1º ao 3º tempos</t>
@@ -6460,7 +6460,7 @@
       <c r="E31" s="438" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="438" t="n"/>
-      <c r="I31" s="406" t="n"/>
+      <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
       <c r="M31" s="328" t="inlineStr">
@@ -6478,7 +6478,7 @@
       <c r="E32" s="438" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="438" t="n"/>
-      <c r="I32" s="407" t="n"/>
+      <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
       <c r="M32" s="15" t="n"/>
@@ -15949,7 +15949,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="435" t="n"/>
+      <c r="H12" s="441" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -15965,7 +15970,7 @@
       <c r="E13" s="437" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
-      <c r="H13" s="438" t="n"/>
+      <c r="H13" s="437" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -15981,7 +15986,7 @@
       <c r="E14" s="439" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
-      <c r="H14" s="438" t="n"/>
+      <c r="H14" s="439" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -16007,7 +16012,12 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="435" t="n"/>
+      <c r="E15" s="442" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
@@ -16032,7 +16042,7 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="438" t="n"/>
+      <c r="E16" s="437" t="n"/>
       <c r="F16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
@@ -16047,7 +16057,7 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="438" t="n"/>
+      <c r="E17" s="439" t="n"/>
       <c r="F17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
@@ -16240,12 +16250,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="441" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="441" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="459" t="inlineStr">
         <is>
@@ -16269,7 +16274,6 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="437" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -16288,7 +16292,6 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="439" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -16320,12 +16323,7 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="460" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="460" t="n"/>
       <c r="F27" s="435" t="n"/>
       <c r="G27" s="435" t="n"/>
       <c r="H27" s="283" t="n"/>
@@ -16344,7 +16342,6 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="437" t="n"/>
       <c r="F28" s="438" t="n"/>
       <c r="G28" s="438" t="n"/>
       <c r="H28" s="283" t="n"/>
@@ -16363,7 +16360,6 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="439" t="n"/>
       <c r="F29" s="438" t="n"/>
       <c r="G29" s="438" t="n"/>
       <c r="H29" s="283" t="n"/>
@@ -16397,12 +16393,7 @@
       </c>
       <c r="E30" s="435" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="442" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G30" s="442" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -16425,7 +16416,6 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="438" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="437" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -16444,7 +16434,6 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="438" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="439" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -16570,7 +16559,12 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
+      <c r="E36" s="440" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F36" s="435" t="n"/>
       <c r="G36" s="434" t="n"/>
       <c r="H36" s="283" t="n"/>
@@ -16592,7 +16586,7 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="283" t="n"/>
+      <c r="E37" s="437" t="n"/>
       <c r="F37" s="438" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="438" t="n"/>
@@ -16613,7 +16607,7 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="283" t="n"/>
+      <c r="E38" s="439" t="n"/>
       <c r="F38" s="438" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="438" t="n"/>
@@ -17135,11 +17129,11 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="G45:G47"/>
-    <mergeCell ref="G30:G32"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -17163,7 +17157,6 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
-    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -17180,7 +17173,6 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
-    <mergeCell ref="E27:E29"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -17217,6 +17209,7 @@
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="F42:F44"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
@@ -17236,6 +17229,7 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="H48:H50"/>
@@ -17654,7 +17648,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="435" t="n"/>
+      <c r="H12" s="409" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -17670,7 +17669,7 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
-      <c r="H13" s="438" t="n"/>
+      <c r="H13" s="406" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -17686,7 +17685,7 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
-      <c r="H14" s="438" t="n"/>
+      <c r="H14" s="407" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -17712,7 +17711,12 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="435" t="n"/>
+      <c r="E15" s="410" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
@@ -17737,7 +17741,7 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="438" t="n"/>
+      <c r="E16" s="406" t="n"/>
       <c r="F16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
@@ -17752,7 +17756,7 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="438" t="n"/>
+      <c r="E17" s="407" t="n"/>
       <c r="F17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
@@ -17950,12 +17954,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="441" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="441" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="459" t="inlineStr">
         <is>
@@ -17979,7 +17978,6 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="437" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -17998,7 +17996,6 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="439" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -18102,12 +18099,7 @@
       </c>
       <c r="E30" s="435" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="442" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G30" s="442" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -18130,7 +18122,6 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="438" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="437" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -18149,7 +18140,6 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="438" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="439" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -18850,7 +18840,6 @@
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="G45:G47"/>
-    <mergeCell ref="G30:G32"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -18873,7 +18862,6 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
-    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -18926,6 +18914,7 @@
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="F42:F44"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
@@ -18945,6 +18934,7 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="H48:H50"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -12757,7 +12757,12 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="435" t="n"/>
+      <c r="E21" s="441" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="452" t="inlineStr">
@@ -12789,7 +12794,7 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="438" t="n"/>
+      <c r="E22" s="437" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
@@ -12804,7 +12809,7 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="438" t="n"/>
+      <c r="E23" s="439" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
@@ -12984,12 +12989,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H30" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H30" s="441" t="n"/>
       <c r="I30" s="442" t="inlineStr">
         <is>
           <t>Geo - Mlo
@@ -13017,7 +13017,6 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="437" t="n"/>
-      <c r="H31" s="437" t="n"/>
       <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -13036,7 +13035,6 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="439" t="n"/>
-      <c r="H32" s="439" t="n"/>
       <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -13730,6 +13728,7 @@
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="H42:H44"/>
+    <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -13818,7 +13817,6 @@
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
-    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -14450,7 +14448,12 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="435" t="n"/>
+      <c r="E21" s="409" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="452" t="inlineStr">
@@ -14482,7 +14485,7 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="438" t="n"/>
+      <c r="E22" s="406" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
@@ -14497,7 +14500,7 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="438" t="n"/>
+      <c r="E23" s="407" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
@@ -14677,12 +14680,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H30" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H30" s="441" t="n"/>
       <c r="I30" s="442" t="inlineStr">
         <is>
           <t>Geo - Mlo
@@ -14710,7 +14708,6 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="437" t="n"/>
-      <c r="H31" s="437" t="n"/>
       <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -14729,7 +14726,6 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="439" t="n"/>
-      <c r="H32" s="439" t="n"/>
       <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -15432,6 +15428,7 @@
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
+    <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -15519,7 +15516,6 @@
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
-    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -17648,7 +17644,7 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="409" t="inlineStr">
+      <c r="H12" s="441" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
 1º e 2º tempos</t>
@@ -17669,7 +17665,7 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
-      <c r="H13" s="406" t="n"/>
+      <c r="H13" s="437" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -17685,7 +17681,7 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
-      <c r="H14" s="407" t="n"/>
+      <c r="H14" s="439" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -17711,7 +17707,7 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="410" t="inlineStr">
+      <c r="E15" s="442" t="inlineStr">
         <is>
           <t>Geo - Mar
 2º e 3º tempos</t>
@@ -17741,7 +17737,7 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="406" t="n"/>
+      <c r="E16" s="437" t="n"/>
       <c r="F16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
@@ -17756,7 +17752,7 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="407" t="n"/>
+      <c r="E17" s="439" t="n"/>
       <c r="F17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6430,7 +6430,7 @@
         <v/>
       </c>
       <c r="E30" s="435" t="n"/>
-      <c r="F30" s="435" t="n"/>
+      <c r="F30" s="458" t="n"/>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="435" t="n"/>
       <c r="I30" s="458" t="inlineStr">
@@ -6458,7 +6458,6 @@
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="438" t="n"/>
-      <c r="F31" s="438" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="438" t="n"/>
       <c r="I31" s="437" t="n"/>
@@ -6477,7 +6476,6 @@
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="438" t="n"/>
-      <c r="F32" s="438" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="438" t="n"/>
       <c r="I32" s="439" t="n"/>
@@ -10075,13 +10073,13 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G48" s="441" t="inlineStr">
+      <c r="G48" s="441" t="n"/>
+      <c r="H48" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -10095,8 +10093,7 @@
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
       <c r="F49" s="437" t="n"/>
-      <c r="G49" s="437" t="n"/>
-      <c r="H49" s="438" t="n"/>
+      <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -10106,8 +10103,7 @@
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
       <c r="F50" s="439" t="n"/>
-      <c r="G50" s="439" t="n"/>
-      <c r="H50" s="438" t="n"/>
+      <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -10381,7 +10377,6 @@
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
@@ -10459,6 +10454,7 @@
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
+    <mergeCell ref="H48:H50"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
     <mergeCell ref="J39:J41"/>
@@ -11749,13 +11745,13 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G48" s="441" t="inlineStr">
+      <c r="G48" s="441" t="n"/>
+      <c r="H48" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H48" s="435" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -11769,8 +11765,7 @@
       <c r="C49" s="313" t="n"/>
       <c r="D49" s="350" t="n"/>
       <c r="F49" s="437" t="n"/>
-      <c r="G49" s="437" t="n"/>
-      <c r="H49" s="438" t="n"/>
+      <c r="H49" s="437" t="n"/>
       <c r="I49" s="315" t="n"/>
       <c r="J49" s="352" t="n"/>
     </row>
@@ -11780,8 +11775,7 @@
       <c r="C50" s="313" t="n"/>
       <c r="D50" s="350" t="n"/>
       <c r="F50" s="439" t="n"/>
-      <c r="G50" s="439" t="n"/>
-      <c r="H50" s="438" t="n"/>
+      <c r="H50" s="439" t="n"/>
       <c r="I50" s="315" t="n"/>
       <c r="J50" s="352" t="n"/>
     </row>
@@ -12055,7 +12049,6 @@
     <mergeCell ref="J57:J59"/>
     <mergeCell ref="C54:C56"/>
     <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G48:G50"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
@@ -12133,6 +12126,7 @@
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="F48:F50"/>
     <mergeCell ref="J12:J14"/>
+    <mergeCell ref="H48:H50"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
     <mergeCell ref="J39:J41"/>
@@ -12763,7 +12757,12 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="435" t="n"/>
+      <c r="E21" s="441" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="452" t="inlineStr">
@@ -12795,7 +12794,7 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="438" t="n"/>
+      <c r="E22" s="437" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
@@ -12810,7 +12809,7 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="438" t="n"/>
+      <c r="E23" s="439" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
@@ -12990,12 +12989,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H30" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H30" s="441" t="n"/>
       <c r="I30" s="442" t="inlineStr">
         <is>
           <t>Geo - Mlo
@@ -13023,7 +13017,6 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="437" t="n"/>
-      <c r="H31" s="437" t="n"/>
       <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -13042,7 +13035,6 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="439" t="n"/>
-      <c r="H32" s="439" t="n"/>
       <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -13736,6 +13728,7 @@
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
     <mergeCell ref="H42:H44"/>
+    <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -13824,7 +13817,6 @@
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
-    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -14242,7 +14234,7 @@
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="419" t="inlineStr">
+      <c r="I12" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl
 3º e 4º tempos</t>
@@ -14262,7 +14254,7 @@
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="406" t="n"/>
+      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -14277,7 +14269,7 @@
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="407" t="n"/>
+      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -14456,7 +14448,12 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="435" t="n"/>
+      <c r="E21" s="409" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="452" t="inlineStr">
@@ -14488,7 +14485,7 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="438" t="n"/>
+      <c r="E22" s="406" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
@@ -14503,7 +14500,7 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="438" t="n"/>
+      <c r="E23" s="407" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
@@ -14683,12 +14680,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H30" s="441" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H30" s="441" t="n"/>
       <c r="I30" s="442" t="inlineStr">
         <is>
           <t>Geo - Mlo
@@ -14716,7 +14708,6 @@
       <c r="E31" s="283" t="n"/>
       <c r="F31" s="283" t="n"/>
       <c r="G31" s="437" t="n"/>
-      <c r="H31" s="437" t="n"/>
       <c r="I31" s="437" t="n"/>
       <c r="J31" s="315" t="n"/>
       <c r="L31" s="27" t="n"/>
@@ -14735,7 +14726,6 @@
       <c r="E32" s="283" t="n"/>
       <c r="F32" s="283" t="n"/>
       <c r="G32" s="439" t="n"/>
-      <c r="H32" s="439" t="n"/>
       <c r="I32" s="439" t="n"/>
       <c r="J32" s="315" t="n"/>
       <c r="L32" s="28" t="n"/>
@@ -15438,6 +15428,7 @@
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
+    <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="J60:J62"/>
@@ -15525,7 +15516,6 @@
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="F57:F59"/>
     <mergeCell ref="J21:J23"/>
-    <mergeCell ref="H30:H32"/>
     <mergeCell ref="J39:J41"/>
     <mergeCell ref="J51:J53"/>
     <mergeCell ref="C33:C35"/>
@@ -15955,7 +15945,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="435" t="n"/>
+      <c r="H12" s="441" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -15971,7 +15966,7 @@
       <c r="E13" s="437" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
-      <c r="H13" s="438" t="n"/>
+      <c r="H13" s="437" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -15987,7 +15982,7 @@
       <c r="E14" s="439" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
-      <c r="H14" s="438" t="n"/>
+      <c r="H14" s="439" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -16013,7 +16008,12 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="435" t="n"/>
+      <c r="E15" s="442" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
@@ -16038,7 +16038,7 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="438" t="n"/>
+      <c r="E16" s="437" t="n"/>
       <c r="F16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
@@ -16053,7 +16053,7 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="438" t="n"/>
+      <c r="E17" s="439" t="n"/>
       <c r="F17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
@@ -16246,12 +16246,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="441" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="441" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="459" t="inlineStr">
         <is>
@@ -16275,7 +16270,6 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="437" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -16294,7 +16288,6 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="439" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -16326,12 +16319,7 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="460" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="460" t="n"/>
       <c r="F27" s="435" t="n"/>
       <c r="G27" s="435" t="n"/>
       <c r="H27" s="283" t="n"/>
@@ -16350,7 +16338,6 @@
       <c r="B28" s="313" t="n"/>
       <c r="C28" s="313" t="n"/>
       <c r="D28" s="350" t="n"/>
-      <c r="E28" s="437" t="n"/>
       <c r="F28" s="438" t="n"/>
       <c r="G28" s="438" t="n"/>
       <c r="H28" s="283" t="n"/>
@@ -16369,7 +16356,6 @@
       <c r="B29" s="313" t="n"/>
       <c r="C29" s="313" t="n"/>
       <c r="D29" s="350" t="n"/>
-      <c r="E29" s="439" t="n"/>
       <c r="F29" s="438" t="n"/>
       <c r="G29" s="438" t="n"/>
       <c r="H29" s="283" t="n"/>
@@ -16403,12 +16389,7 @@
       </c>
       <c r="E30" s="435" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="442" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G30" s="442" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -16431,7 +16412,6 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="438" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="437" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -16450,7 +16430,6 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="438" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="439" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -16576,7 +16555,12 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
+      <c r="E36" s="440" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F36" s="435" t="n"/>
       <c r="G36" s="434" t="n"/>
       <c r="H36" s="283" t="n"/>
@@ -16598,7 +16582,7 @@
       <c r="B37" s="313" t="n"/>
       <c r="C37" s="313" t="n"/>
       <c r="D37" s="350" t="n"/>
-      <c r="E37" s="283" t="n"/>
+      <c r="E37" s="437" t="n"/>
       <c r="F37" s="438" t="n"/>
       <c r="H37" s="283" t="n"/>
       <c r="I37" s="438" t="n"/>
@@ -16619,7 +16603,7 @@
       <c r="B38" s="313" t="n"/>
       <c r="C38" s="313" t="n"/>
       <c r="D38" s="350" t="n"/>
-      <c r="E38" s="283" t="n"/>
+      <c r="E38" s="439" t="n"/>
       <c r="F38" s="438" t="n"/>
       <c r="H38" s="283" t="n"/>
       <c r="I38" s="438" t="n"/>
@@ -17141,11 +17125,11 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="H57:H59"/>
+    <mergeCell ref="E36:E38"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="G45:G47"/>
-    <mergeCell ref="G30:G32"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -17169,7 +17153,6 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
-    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -17186,7 +17169,6 @@
     <mergeCell ref="A18:A20"/>
     <mergeCell ref="E9:E11"/>
     <mergeCell ref="C27:C29"/>
-    <mergeCell ref="E27:E29"/>
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="D24:D26"/>
@@ -17223,6 +17205,7 @@
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="F42:F44"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
@@ -17242,6 +17225,7 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="H48:H50"/>
@@ -17660,7 +17644,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="435" t="n"/>
+      <c r="H12" s="441" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -17676,7 +17665,7 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
-      <c r="H13" s="438" t="n"/>
+      <c r="H13" s="437" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -17692,7 +17681,7 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
-      <c r="H14" s="438" t="n"/>
+      <c r="H14" s="439" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -17718,7 +17707,12 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="435" t="n"/>
+      <c r="E15" s="442" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="434" t="inlineStr">
         <is>
           <t>Hist - Ver
@@ -17743,7 +17737,7 @@
       <c r="B16" s="313" t="n"/>
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
-      <c r="E16" s="438" t="n"/>
+      <c r="E16" s="437" t="n"/>
       <c r="F16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
@@ -17758,7 +17752,7 @@
       <c r="B17" s="313" t="n"/>
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
-      <c r="E17" s="438" t="n"/>
+      <c r="E17" s="439" t="n"/>
       <c r="F17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
@@ -17956,12 +17950,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="441" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="441" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="459" t="inlineStr">
         <is>
@@ -17985,7 +17974,6 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="437" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -18004,7 +17992,6 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="439" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -18108,12 +18095,7 @@
       </c>
       <c r="E30" s="435" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="442" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G30" s="442" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -18136,7 +18118,6 @@
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="438" t="n"/>
       <c r="F31" s="283" t="n"/>
-      <c r="G31" s="437" t="n"/>
       <c r="H31" s="283" t="n"/>
       <c r="I31" s="283" t="n"/>
       <c r="J31" s="315" t="n"/>
@@ -18155,7 +18136,6 @@
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="438" t="n"/>
       <c r="F32" s="283" t="n"/>
-      <c r="G32" s="439" t="n"/>
       <c r="H32" s="283" t="n"/>
       <c r="I32" s="283" t="n"/>
       <c r="J32" s="315" t="n"/>
@@ -18856,7 +18836,6 @@
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="G45:G47"/>
-    <mergeCell ref="G30:G32"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
@@ -18879,7 +18858,6 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
-    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -18932,6 +18910,7 @@
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="F42:F44"/>
+    <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
@@ -18951,6 +18930,7 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="H48:H50"/>
@@ -19835,7 +19815,7 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="435" t="n"/>
+      <c r="F30" s="458" t="n"/>
       <c r="G30" s="435" t="n"/>
       <c r="H30" s="435" t="n"/>
       <c r="I30" s="458" t="inlineStr">
@@ -19863,7 +19843,6 @@
       <c r="C31" s="313" t="n"/>
       <c r="D31" s="350" t="n"/>
       <c r="E31" s="283" t="n"/>
-      <c r="F31" s="438" t="n"/>
       <c r="G31" s="438" t="n"/>
       <c r="H31" s="438" t="n"/>
       <c r="I31" s="437" t="n"/>
@@ -19882,7 +19861,6 @@
       <c r="C32" s="313" t="n"/>
       <c r="D32" s="350" t="n"/>
       <c r="E32" s="283" t="n"/>
-      <c r="F32" s="438" t="n"/>
       <c r="G32" s="438" t="n"/>
       <c r="H32" s="438" t="n"/>
       <c r="I32" s="439" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -14448,7 +14448,7 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="409" t="inlineStr">
+      <c r="E21" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 1º e 2º tempos</t>
@@ -14485,7 +14485,7 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="406" t="n"/>
+      <c r="E22" s="437" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
@@ -14500,7 +14500,7 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="407" t="n"/>
+      <c r="E23" s="439" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
@@ -15945,12 +15945,7 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="441" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="H12" s="441" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -15966,7 +15961,6 @@
       <c r="E13" s="437" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
-      <c r="H13" s="437" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -15982,7 +15976,6 @@
       <c r="E14" s="439" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
-      <c r="H14" s="439" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -16097,7 +16090,12 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n"/>
+      <c r="H18" s="441" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I18" s="382" t="n"/>
       <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
@@ -16112,7 +16110,7 @@
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="437" t="n"/>
       <c r="G19" s="437" t="n"/>
-      <c r="H19" s="222" t="n"/>
+      <c r="H19" s="437" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -16135,7 +16133,7 @@
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="439" t="n"/>
       <c r="G20" s="439" t="n"/>
-      <c r="H20" s="222" t="n"/>
+      <c r="H20" s="439" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -17134,6 +17132,7 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="E12:E14"/>
@@ -17225,7 +17224,6 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="H48:H50"/>
@@ -17644,13 +17642,13 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="441" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
+      <c r="H12" s="441" t="n"/>
+      <c r="I12" s="408" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -17665,8 +17663,7 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
-      <c r="H13" s="437" t="n"/>
-      <c r="I13" s="222" t="n"/>
+      <c r="I13" s="406" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -17681,8 +17678,7 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
-      <c r="H14" s="439" t="n"/>
-      <c r="I14" s="222" t="n"/>
+      <c r="I14" s="407" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -17796,13 +17792,13 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="431" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="H18" s="441" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="431" t="n"/>
       <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="15" t="n"/>
@@ -17816,8 +17812,7 @@
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="437" t="n"/>
       <c r="G19" s="437" t="n"/>
-      <c r="H19" s="222" t="n"/>
-      <c r="I19" s="383" t="n"/>
+      <c r="H19" s="437" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
         <is>
@@ -17839,8 +17834,7 @@
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="439" t="n"/>
       <c r="G20" s="439" t="n"/>
-      <c r="H20" s="222" t="n"/>
-      <c r="I20" s="384" t="n"/>
+      <c r="H20" s="439" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
@@ -18840,6 +18834,7 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
@@ -18918,7 +18913,6 @@
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="G18:G20"/>
     <mergeCell ref="G24:G26"/>
-    <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
     <mergeCell ref="D12:D14"/>
@@ -18930,7 +18924,6 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="H48:H50"/>
@@ -18951,6 +18944,7 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
+    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -12545,12 +12545,7 @@
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="451" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -12565,7 +12560,6 @@
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -12580,7 +12574,6 @@
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -12619,7 +12612,12 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="n"/>
+      <c r="I15" s="451" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -12633,7 +12631,7 @@
       <c r="E16" s="437" t="n"/>
       <c r="F16" s="222" t="n"/>
       <c r="H16" s="437" t="n"/>
-      <c r="I16" s="222" t="n"/>
+      <c r="I16" s="437" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -12648,7 +12646,7 @@
       <c r="E17" s="439" t="n"/>
       <c r="F17" s="222" t="n"/>
       <c r="H17" s="439" t="n"/>
-      <c r="I17" s="222" t="n"/>
+      <c r="I17" s="439" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -13731,6 +13729,7 @@
     <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="I15:I17"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
@@ -13834,7 +13833,6 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
-    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>
@@ -14234,12 +14232,7 @@
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="451" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -14254,7 +14247,6 @@
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -14269,7 +14261,6 @@
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -14308,7 +14299,12 @@
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="435" t="n"/>
-      <c r="I15" s="11" t="n"/>
+      <c r="I15" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -14323,7 +14319,7 @@
       <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
       <c r="H16" s="438" t="n"/>
-      <c r="I16" s="222" t="n"/>
+      <c r="I16" s="406" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -14339,7 +14335,7 @@
       <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
       <c r="H17" s="438" t="n"/>
-      <c r="I17" s="222" t="n"/>
+      <c r="I17" s="407" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -15431,6 +15427,7 @@
     <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="I15:I17"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
@@ -15533,7 +15530,6 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
-    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>
@@ -17643,7 +17639,7 @@
         </is>
       </c>
       <c r="H12" s="441" t="n"/>
-      <c r="I12" s="408" t="inlineStr">
+      <c r="I12" s="440" t="inlineStr">
         <is>
           <t>Ing - PaH
 6º e 7º tempos</t>
@@ -17663,7 +17659,7 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
-      <c r="I13" s="406" t="n"/>
+      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -17678,7 +17674,7 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
-      <c r="I14" s="407" t="n"/>
+      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -12545,12 +12545,7 @@
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="451" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -12565,7 +12560,6 @@
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -12580,7 +12574,6 @@
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -12619,7 +12612,12 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="n"/>
+      <c r="I15" s="451" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -12633,7 +12631,7 @@
       <c r="E16" s="437" t="n"/>
       <c r="F16" s="222" t="n"/>
       <c r="H16" s="437" t="n"/>
-      <c r="I16" s="222" t="n"/>
+      <c r="I16" s="437" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -12648,7 +12646,7 @@
       <c r="E17" s="439" t="n"/>
       <c r="F17" s="222" t="n"/>
       <c r="H17" s="439" t="n"/>
-      <c r="I17" s="222" t="n"/>
+      <c r="I17" s="439" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -13731,6 +13729,7 @@
     <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="I15:I17"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
@@ -13834,7 +13833,6 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
-    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>
@@ -14234,12 +14232,7 @@
         </is>
       </c>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="I12" s="451" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -14254,7 +14247,6 @@
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
-      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -14269,7 +14261,6 @@
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
-      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -14308,7 +14299,12 @@
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="435" t="n"/>
-      <c r="I15" s="11" t="n"/>
+      <c r="I15" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -14323,7 +14319,7 @@
       <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
       <c r="H16" s="438" t="n"/>
-      <c r="I16" s="222" t="n"/>
+      <c r="I16" s="406" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -14339,7 +14335,7 @@
       <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
       <c r="H17" s="438" t="n"/>
-      <c r="I17" s="222" t="n"/>
+      <c r="I17" s="407" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -14448,7 +14444,7 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="409" t="inlineStr">
+      <c r="E21" s="441" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 1º e 2º tempos</t>
@@ -14485,7 +14481,7 @@
       <c r="B22" s="313" t="n"/>
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
-      <c r="E22" s="406" t="n"/>
+      <c r="E22" s="437" t="n"/>
       <c r="F22" s="63" t="n"/>
       <c r="G22" s="222" t="n"/>
       <c r="H22" s="437" t="n"/>
@@ -14500,7 +14496,7 @@
       <c r="B23" s="313" t="n"/>
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
-      <c r="E23" s="407" t="n"/>
+      <c r="E23" s="439" t="n"/>
       <c r="F23" s="63" t="n"/>
       <c r="G23" s="222" t="n"/>
       <c r="H23" s="439" t="n"/>
@@ -15431,6 +15427,7 @@
     <mergeCell ref="E21:E23"/>
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="I15:I17"/>
     <mergeCell ref="J60:J62"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="J57:J59"/>
@@ -15533,7 +15530,6 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
-    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>
@@ -15945,12 +15941,7 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="441" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="H12" s="441" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -15966,7 +15957,6 @@
       <c r="E13" s="437" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
-      <c r="H13" s="437" t="n"/>
       <c r="I13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -15982,7 +15972,6 @@
       <c r="E14" s="439" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
-      <c r="H14" s="439" t="n"/>
       <c r="I14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -16097,7 +16086,12 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n"/>
+      <c r="H18" s="441" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I18" s="382" t="n"/>
       <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
@@ -16112,7 +16106,7 @@
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="437" t="n"/>
       <c r="G19" s="437" t="n"/>
-      <c r="H19" s="222" t="n"/>
+      <c r="H19" s="437" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -16135,7 +16129,7 @@
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="439" t="n"/>
       <c r="G20" s="439" t="n"/>
-      <c r="H20" s="222" t="n"/>
+      <c r="H20" s="439" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -17134,6 +17128,7 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="E12:E14"/>
@@ -17225,7 +17220,6 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="H48:H50"/>
@@ -17644,13 +17638,13 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="441" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
+      <c r="H12" s="441" t="n"/>
+      <c r="I12" s="440" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -17665,8 +17659,7 @@
       <c r="E13" s="222" t="n"/>
       <c r="F13" s="437" t="n"/>
       <c r="G13" s="437" t="n"/>
-      <c r="H13" s="437" t="n"/>
-      <c r="I13" s="222" t="n"/>
+      <c r="I13" s="437" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="15" t="n"/>
@@ -17681,8 +17674,7 @@
       <c r="E14" s="222" t="n"/>
       <c r="F14" s="439" t="n"/>
       <c r="G14" s="439" t="n"/>
-      <c r="H14" s="439" t="n"/>
-      <c r="I14" s="222" t="n"/>
+      <c r="I14" s="439" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
       <c r="M14" s="15" t="n"/>
@@ -17796,13 +17788,13 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="431" t="inlineStr">
-        <is>
-          <t>Ing - PaH
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="H18" s="441" t="inlineStr">
+        <is>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="431" t="n"/>
       <c r="J18" s="183" t="n"/>
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="15" t="n"/>
@@ -17816,8 +17808,7 @@
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="437" t="n"/>
       <c r="G19" s="437" t="n"/>
-      <c r="H19" s="222" t="n"/>
-      <c r="I19" s="383" t="n"/>
+      <c r="H19" s="437" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
         <is>
@@ -17839,8 +17830,7 @@
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="439" t="n"/>
       <c r="G20" s="439" t="n"/>
-      <c r="H20" s="222" t="n"/>
-      <c r="I20" s="384" t="n"/>
+      <c r="H20" s="439" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="29" t="n"/>
@@ -18840,6 +18830,7 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
+    <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="J33:J35"/>
@@ -18918,7 +18909,6 @@
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="G18:G20"/>
     <mergeCell ref="G24:G26"/>
-    <mergeCell ref="I18:I20"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="C57:C59"/>
     <mergeCell ref="D12:D14"/>
@@ -18930,7 +18920,6 @@
     <mergeCell ref="E54:E56"/>
     <mergeCell ref="I60:I62"/>
     <mergeCell ref="B54:B56"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="D54:D56"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="H48:H50"/>
@@ -18951,6 +18940,7 @@
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B18:B20"/>
+    <mergeCell ref="I12:I14"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="F33:F35"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -14299,7 +14299,7 @@
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="435" t="n"/>
-      <c r="I15" s="419" t="inlineStr">
+      <c r="I15" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl
 3º e 4º tempos</t>
@@ -14319,7 +14319,7 @@
       <c r="F16" s="437" t="n"/>
       <c r="G16" s="222" t="n"/>
       <c r="H16" s="438" t="n"/>
-      <c r="I16" s="406" t="n"/>
+      <c r="I16" s="437" t="n"/>
       <c r="J16" s="315" t="n"/>
       <c r="L16" s="141" t="n"/>
       <c r="M16" s="317" t="n"/>
@@ -14335,7 +14335,7 @@
       <c r="F17" s="439" t="n"/>
       <c r="G17" s="222" t="n"/>
       <c r="H17" s="438" t="n"/>
-      <c r="I17" s="407" t="n"/>
+      <c r="I17" s="439" t="n"/>
       <c r="J17" s="315" t="n"/>
       <c r="L17" s="317" t="n"/>
       <c r="M17" s="317" t="n"/>
@@ -16003,13 +16003,13 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F15" s="434" t="inlineStr">
+      <c r="F15" s="434" t="n"/>
+      <c r="G15" s="470" t="inlineStr">
         <is>
           <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="434" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
@@ -16028,7 +16028,7 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
-      <c r="F16" s="437" t="n"/>
+      <c r="G16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -16043,7 +16043,7 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
-      <c r="F17" s="439" t="n"/>
+      <c r="G17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
@@ -17104,7 +17104,6 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
-    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -17202,6 +17201,7 @@
     <mergeCell ref="F42:F44"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
+    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
@@ -17705,13 +17705,13 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F15" s="434" t="inlineStr">
+      <c r="F15" s="434" t="n"/>
+      <c r="G15" s="468" t="inlineStr">
         <is>
           <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="434" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
@@ -17730,7 +17730,7 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
-      <c r="F16" s="437" t="n"/>
+      <c r="G16" s="406" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -17745,7 +17745,7 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
-      <c r="F17" s="439" t="n"/>
+      <c r="G17" s="407" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
@@ -18806,7 +18806,6 @@
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="E60:E62"/>
-    <mergeCell ref="F15:F17"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
@@ -18903,6 +18902,7 @@
     <mergeCell ref="F42:F44"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
+    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -12538,12 +12538,7 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="G12" s="436" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G12" s="436" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="451" t="n"/>
       <c r="J12" s="183" t="n"/>
@@ -12558,7 +12553,6 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="F13" s="437" t="n"/>
-      <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -12572,7 +12566,6 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="F14" s="439" t="n"/>
-      <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -13670,7 +13663,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="168">
+  <mergeCells count="167">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -13776,7 +13769,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G12:G14"/>
     <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
@@ -14225,12 +14217,7 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="G12" s="436" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G12" s="436" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="451" t="n"/>
       <c r="J12" s="183" t="n"/>
@@ -14245,7 +14232,6 @@
       <c r="C13" s="313" t="n"/>
       <c r="D13" s="314" t="n"/>
       <c r="F13" s="437" t="n"/>
-      <c r="G13" s="437" t="n"/>
       <c r="H13" s="222" t="n"/>
       <c r="J13" s="315" t="n"/>
       <c r="L13" s="15" t="n"/>
@@ -14259,7 +14245,6 @@
       <c r="C14" s="313" t="n"/>
       <c r="D14" s="314" t="n"/>
       <c r="F14" s="439" t="n"/>
-      <c r="G14" s="439" t="n"/>
       <c r="H14" s="222" t="n"/>
       <c r="J14" s="315" t="n"/>
       <c r="L14" s="15" t="n"/>
@@ -15367,7 +15352,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="168">
+  <mergeCells count="167">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -15473,7 +15458,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G12:G14"/>
     <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="D27:D29"/>
@@ -17706,7 +17690,7 @@
         </is>
       </c>
       <c r="F15" s="434" t="n"/>
-      <c r="G15" s="468" t="inlineStr">
+      <c r="G15" s="470" t="inlineStr">
         <is>
           <t>Hist - Ver
 1º e 2º tempos</t>
@@ -17730,7 +17714,7 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
-      <c r="G16" s="406" t="n"/>
+      <c r="G16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -17745,7 +17729,7 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
-      <c r="G17" s="407" t="n"/>
+      <c r="G17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -16058,12 +16058,7 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="451" t="n"/>
       <c r="G18" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
@@ -16088,7 +16083,6 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="437" t="n"/>
       <c r="G19" s="437" t="n"/>
       <c r="H19" s="437" t="n"/>
       <c r="I19" s="383" t="n"/>
@@ -16111,7 +16105,6 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="439" t="n"/>
       <c r="G20" s="439" t="n"/>
       <c r="H20" s="439" t="n"/>
       <c r="I20" s="384" t="n"/>
@@ -16144,13 +16137,13 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="436" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F21" s="451" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G21" s="436" t="n"/>
       <c r="H21" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
@@ -16181,8 +16174,7 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="437" t="n"/>
-      <c r="F22" s="63" t="n"/>
-      <c r="G22" s="437" t="n"/>
+      <c r="F22" s="437" t="n"/>
       <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
@@ -16196,8 +16188,7 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="439" t="n"/>
-      <c r="F23" s="63" t="n"/>
-      <c r="G23" s="439" t="n"/>
+      <c r="F23" s="439" t="n"/>
       <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
@@ -16224,7 +16215,12 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="441" t="n"/>
+      <c r="E24" s="436" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="459" t="inlineStr">
         <is>
@@ -16248,6 +16244,7 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
+      <c r="E25" s="437" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -16266,6 +16263,7 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
+      <c r="E26" s="439" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -17091,6 +17089,7 @@
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
@@ -17131,6 +17130,7 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -17168,7 +17168,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G21:G23"/>
     <mergeCell ref="G12:G14"/>
     <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
@@ -17178,7 +17177,6 @@
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
-    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
@@ -17760,12 +17758,7 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="451" t="n"/>
       <c r="G18" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
@@ -17790,7 +17783,6 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="437" t="n"/>
       <c r="G19" s="437" t="n"/>
       <c r="H19" s="437" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -17812,7 +17804,6 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="439" t="n"/>
       <c r="G20" s="439" t="n"/>
       <c r="H20" s="439" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -17844,13 +17835,13 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="436" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F21" s="419" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G21" s="436" t="n"/>
       <c r="H21" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
@@ -17881,8 +17872,7 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="437" t="n"/>
-      <c r="F22" s="63" t="n"/>
-      <c r="G22" s="437" t="n"/>
+      <c r="F22" s="406" t="n"/>
       <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
@@ -17896,8 +17886,7 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="439" t="n"/>
-      <c r="F23" s="63" t="n"/>
-      <c r="G23" s="439" t="n"/>
+      <c r="F23" s="407" t="n"/>
       <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
@@ -17924,7 +17913,12 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="441" t="n"/>
+      <c r="E24" s="405" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="459" t="inlineStr">
         <is>
@@ -17948,6 +17942,7 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
+      <c r="E25" s="406" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -17966,6 +17961,7 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
+      <c r="E26" s="407" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -18793,6 +18789,7 @@
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
@@ -18832,6 +18829,7 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -18869,7 +18867,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G21:G23"/>
     <mergeCell ref="G12:G14"/>
     <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
@@ -18879,7 +18876,6 @@
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
-    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -9494,7 +9494,12 @@
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="438" t="n"/>
-      <c r="H24" s="283" t="n"/>
+      <c r="H24" s="443" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="446" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -9513,7 +9518,7 @@
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="438" t="n"/>
-      <c r="H25" s="283" t="n"/>
+      <c r="H25" s="437" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -9531,7 +9536,7 @@
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="438" t="n"/>
-      <c r="H26" s="283" t="n"/>
+      <c r="H26" s="439" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -10314,7 +10319,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="166">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -10411,6 +10416,7 @@
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
+    <mergeCell ref="H24:H26"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
     <mergeCell ref="A36:A38"/>
@@ -11166,7 +11172,12 @@
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="438" t="n"/>
-      <c r="H24" s="283" t="n"/>
+      <c r="H24" s="411" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="446" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -11185,7 +11196,7 @@
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="438" t="n"/>
-      <c r="H25" s="283" t="n"/>
+      <c r="H25" s="406" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -11203,7 +11214,7 @@
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="438" t="n"/>
-      <c r="H26" s="283" t="n"/>
+      <c r="H26" s="407" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -11986,7 +11997,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="166">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -12083,6 +12094,7 @@
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
+    <mergeCell ref="H24:H26"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
     <mergeCell ref="A36:A38"/>
@@ -17835,7 +17847,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="419" t="inlineStr">
+      <c r="F21" s="451" t="inlineStr">
         <is>
           <t>Qui - CAl
 2º e 3º tempos</t>
@@ -17872,7 +17884,7 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="437" t="n"/>
-      <c r="F22" s="406" t="n"/>
+      <c r="F22" s="437" t="n"/>
       <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
@@ -17886,7 +17898,7 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="439" t="n"/>
-      <c r="F23" s="407" t="n"/>
+      <c r="F23" s="439" t="n"/>
       <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
@@ -17913,7 +17925,7 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="405" t="inlineStr">
+      <c r="E24" s="436" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
 4º e 5º tempos</t>
@@ -17942,7 +17954,7 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
-      <c r="E25" s="406" t="n"/>
+      <c r="E25" s="437" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -17961,7 +17973,7 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
-      <c r="E26" s="407" t="n"/>
+      <c r="E26" s="439" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -9494,7 +9494,12 @@
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="438" t="n"/>
-      <c r="H24" s="283" t="n"/>
+      <c r="H24" s="443" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="446" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -9513,7 +9518,7 @@
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="438" t="n"/>
-      <c r="H25" s="283" t="n"/>
+      <c r="H25" s="437" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -9531,7 +9536,7 @@
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="438" t="n"/>
-      <c r="H26" s="283" t="n"/>
+      <c r="H26" s="439" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -10314,7 +10319,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="166">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -10411,6 +10416,7 @@
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
+    <mergeCell ref="H24:H26"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
     <mergeCell ref="A36:A38"/>
@@ -11166,7 +11172,12 @@
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="438" t="n"/>
-      <c r="H24" s="283" t="n"/>
+      <c r="H24" s="411" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I24" s="446" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -11185,7 +11196,7 @@
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="438" t="n"/>
-      <c r="H25" s="283" t="n"/>
+      <c r="H25" s="406" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -11203,7 +11214,7 @@
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="438" t="n"/>
-      <c r="H26" s="283" t="n"/>
+      <c r="H26" s="407" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -11986,7 +11997,7 @@
       <c r="J62" s="353" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="166">
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="G54:G56"/>
     <mergeCell ref="C21:C23"/>
@@ -12083,6 +12094,7 @@
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="D60:D62"/>
+    <mergeCell ref="H24:H26"/>
     <mergeCell ref="F60:F62"/>
     <mergeCell ref="M31:N31"/>
     <mergeCell ref="A36:A38"/>
@@ -16058,12 +16070,7 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="451" t="n"/>
       <c r="G18" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
@@ -16088,7 +16095,6 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="437" t="n"/>
       <c r="G19" s="437" t="n"/>
       <c r="H19" s="437" t="n"/>
       <c r="I19" s="383" t="n"/>
@@ -16111,7 +16117,6 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="439" t="n"/>
       <c r="G20" s="439" t="n"/>
       <c r="H20" s="439" t="n"/>
       <c r="I20" s="384" t="n"/>
@@ -16144,13 +16149,13 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="436" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F21" s="451" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G21" s="436" t="n"/>
       <c r="H21" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
@@ -16181,8 +16186,7 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="437" t="n"/>
-      <c r="F22" s="63" t="n"/>
-      <c r="G22" s="437" t="n"/>
+      <c r="F22" s="437" t="n"/>
       <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
@@ -16196,8 +16200,7 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="439" t="n"/>
-      <c r="F23" s="63" t="n"/>
-      <c r="G23" s="439" t="n"/>
+      <c r="F23" s="439" t="n"/>
       <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
@@ -16224,7 +16227,12 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="441" t="n"/>
+      <c r="E24" s="436" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="459" t="inlineStr">
         <is>
@@ -16248,6 +16256,7 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
+      <c r="E25" s="437" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -16266,6 +16275,7 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
+      <c r="E26" s="439" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -17091,6 +17101,7 @@
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
@@ -17131,6 +17142,7 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -17168,7 +17180,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G21:G23"/>
     <mergeCell ref="G12:G14"/>
     <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
@@ -17178,7 +17189,6 @@
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
-    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
@@ -17760,12 +17770,7 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="451" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="451" t="n"/>
       <c r="G18" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
@@ -17790,7 +17795,6 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="437" t="n"/>
       <c r="G19" s="437" t="n"/>
       <c r="H19" s="437" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -17812,7 +17816,6 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="439" t="n"/>
       <c r="G20" s="439" t="n"/>
       <c r="H20" s="439" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -17844,13 +17847,13 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="n"/>
-      <c r="G21" s="436" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F21" s="451" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G21" s="436" t="n"/>
       <c r="H21" s="452" t="inlineStr">
         <is>
           <t>Fis - Cadu
@@ -17881,8 +17884,7 @@
       <c r="C22" s="313" t="n"/>
       <c r="D22" s="314" t="n"/>
       <c r="E22" s="437" t="n"/>
-      <c r="F22" s="63" t="n"/>
-      <c r="G22" s="437" t="n"/>
+      <c r="F22" s="437" t="n"/>
       <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
@@ -17896,8 +17898,7 @@
       <c r="C23" s="313" t="n"/>
       <c r="D23" s="314" t="n"/>
       <c r="E23" s="439" t="n"/>
-      <c r="F23" s="63" t="n"/>
-      <c r="G23" s="439" t="n"/>
+      <c r="F23" s="439" t="n"/>
       <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
@@ -17924,7 +17925,12 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="441" t="n"/>
+      <c r="E24" s="436" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="459" t="inlineStr">
         <is>
@@ -17948,6 +17954,7 @@
       <c r="B25" s="313" t="n"/>
       <c r="C25" s="313" t="n"/>
       <c r="D25" s="350" t="n"/>
+      <c r="E25" s="437" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="447" t="n"/>
       <c r="H25" s="283" t="n"/>
@@ -17966,6 +17973,7 @@
       <c r="B26" s="313" t="n"/>
       <c r="C26" s="313" t="n"/>
       <c r="D26" s="350" t="n"/>
+      <c r="E26" s="439" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="448" t="n"/>
       <c r="H26" s="283" t="n"/>
@@ -18793,6 +18801,7 @@
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
@@ -18832,6 +18841,7 @@
     <mergeCell ref="G57:G59"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="I57:I59"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="J6:J8"/>
     <mergeCell ref="A54:A56"/>
@@ -18869,7 +18879,6 @@
     <mergeCell ref="I54:I56"/>
     <mergeCell ref="C30:C32"/>
     <mergeCell ref="C45:C47"/>
-    <mergeCell ref="G21:G23"/>
     <mergeCell ref="G12:G14"/>
     <mergeCell ref="E39:E41"/>
     <mergeCell ref="G39:G41"/>
@@ -18879,7 +18888,6 @@
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
-    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6120,12 +6120,7 @@
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="441" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H18" s="441" t="n"/>
       <c r="I18" s="432" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
@@ -6145,7 +6140,6 @@
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="437" t="n"/>
       <c r="G19" s="222" t="n"/>
-      <c r="H19" s="437" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -6168,7 +6162,6 @@
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="439" t="n"/>
       <c r="G20" s="222" t="n"/>
-      <c r="H20" s="439" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -6206,7 +6199,12 @@
         </is>
       </c>
       <c r="G21" s="435" t="n"/>
-      <c r="H21" s="435" t="n"/>
+      <c r="H21" s="409" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
@@ -6233,7 +6231,7 @@
       <c r="E22" s="437" t="n"/>
       <c r="F22" s="437" t="n"/>
       <c r="G22" s="438" t="n"/>
-      <c r="H22" s="438" t="n"/>
+      <c r="H22" s="406" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -6248,7 +6246,7 @@
       <c r="E23" s="439" t="n"/>
       <c r="F23" s="439" t="n"/>
       <c r="G23" s="438" t="n"/>
-      <c r="H23" s="438" t="n"/>
+      <c r="H23" s="407" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -7138,6 +7136,7 @@
     <mergeCell ref="B57:B59"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
+    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -7156,7 +7155,6 @@
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="H27:H29"/>
-    <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="E12:E14"/>
@@ -11172,7 +11170,7 @@
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="438" t="n"/>
-      <c r="H24" s="411" t="inlineStr">
+      <c r="H24" s="443" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
 1º e 2º tempos</t>
@@ -11196,7 +11194,7 @@
       <c r="E25" s="283" t="n"/>
       <c r="F25" s="283" t="n"/>
       <c r="G25" s="438" t="n"/>
-      <c r="H25" s="406" t="n"/>
+      <c r="H25" s="437" t="n"/>
       <c r="J25" s="352" t="n"/>
       <c r="L25" s="44" t="n"/>
       <c r="M25" s="321" t="inlineStr">
@@ -11214,7 +11212,7 @@
       <c r="E26" s="283" t="n"/>
       <c r="F26" s="283" t="n"/>
       <c r="G26" s="438" t="n"/>
-      <c r="H26" s="407" t="n"/>
+      <c r="H26" s="439" t="n"/>
       <c r="J26" s="352" t="n"/>
       <c r="L26" s="43" t="n"/>
       <c r="M26" s="323" t="inlineStr">
@@ -19487,12 +19485,7 @@
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="441" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H18" s="441" t="n"/>
       <c r="I18" s="432" t="inlineStr">
         <is>
           <t>Qui - CAl/Fab
@@ -19512,7 +19505,6 @@
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="437" t="n"/>
       <c r="G19" s="222" t="n"/>
-      <c r="H19" s="437" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -19535,7 +19527,6 @@
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="439" t="n"/>
       <c r="G20" s="222" t="n"/>
-      <c r="H20" s="439" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -19573,7 +19564,12 @@
         </is>
       </c>
       <c r="G21" s="435" t="n"/>
-      <c r="H21" s="435" t="n"/>
+      <c r="H21" s="441" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="262" t="inlineStr">
         <is>
@@ -19600,7 +19596,7 @@
       <c r="E22" s="437" t="n"/>
       <c r="F22" s="437" t="n"/>
       <c r="G22" s="438" t="n"/>
-      <c r="H22" s="438" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -19615,7 +19611,7 @@
       <c r="E23" s="439" t="n"/>
       <c r="F23" s="439" t="n"/>
       <c r="G23" s="438" t="n"/>
-      <c r="H23" s="438" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -20505,6 +20501,7 @@
     <mergeCell ref="B57:B59"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="D57:D59"/>
+    <mergeCell ref="H21:H23"/>
     <mergeCell ref="F51:F53"/>
     <mergeCell ref="J15:J17"/>
     <mergeCell ref="H51:H53"/>
@@ -20523,7 +20520,6 @@
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="H27:H29"/>
-    <mergeCell ref="H18:H20"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="H33:H35"/>
     <mergeCell ref="E12:E14"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="G21" s="435" t="n"/>
-      <c r="H21" s="409" t="inlineStr">
+      <c r="H21" s="441" t="inlineStr">
         <is>
           <t>Mat - Bre/JJ
 4º e 5º tempos</t>
@@ -6231,7 +6231,7 @@
       <c r="E22" s="437" t="n"/>
       <c r="F22" s="437" t="n"/>
       <c r="G22" s="438" t="n"/>
-      <c r="H22" s="406" t="n"/>
+      <c r="H22" s="437" t="n"/>
       <c r="I22" s="222" t="n"/>
       <c r="J22" s="315" t="n"/>
       <c r="L22" s="18" t="n"/>
@@ -6246,7 +6246,7 @@
       <c r="E23" s="439" t="n"/>
       <c r="F23" s="439" t="n"/>
       <c r="G23" s="438" t="n"/>
-      <c r="H23" s="407" t="n"/>
+      <c r="H23" s="439" t="n"/>
       <c r="I23" s="222" t="n"/>
       <c r="J23" s="315" t="n"/>
       <c r="K23" s="6" t="n"/>
@@ -15998,12 +15998,7 @@
         </is>
       </c>
       <c r="F15" s="434" t="n"/>
-      <c r="G15" s="470" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G15" s="470" t="n"/>
       <c r="H15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
@@ -16022,7 +16017,6 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
-      <c r="G16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -16037,7 +16031,6 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
-      <c r="G17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
@@ -16068,7 +16061,12 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="451" t="n"/>
+      <c r="F18" s="470" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
@@ -16093,6 +16091,7 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
+      <c r="F19" s="437" t="n"/>
       <c r="G19" s="437" t="n"/>
       <c r="H19" s="437" t="n"/>
       <c r="I19" s="383" t="n"/>
@@ -16115,6 +16114,7 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
+      <c r="F20" s="439" t="n"/>
       <c r="G20" s="439" t="n"/>
       <c r="H20" s="439" t="n"/>
       <c r="I20" s="384" t="n"/>
@@ -17187,13 +17187,13 @@
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
+    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="F42:F44"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
-    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>
@@ -17698,12 +17698,7 @@
         </is>
       </c>
       <c r="F15" s="434" t="n"/>
-      <c r="G15" s="470" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G15" s="470" t="n"/>
       <c r="H15" s="458" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
@@ -17722,7 +17717,6 @@
       <c r="C16" s="313" t="n"/>
       <c r="D16" s="314" t="n"/>
       <c r="E16" s="437" t="n"/>
-      <c r="G16" s="437" t="n"/>
       <c r="H16" s="437" t="n"/>
       <c r="I16" s="222" t="n"/>
       <c r="J16" s="315" t="n"/>
@@ -17737,7 +17731,6 @@
       <c r="C17" s="313" t="n"/>
       <c r="D17" s="314" t="n"/>
       <c r="E17" s="439" t="n"/>
-      <c r="G17" s="439" t="n"/>
       <c r="H17" s="439" t="n"/>
       <c r="I17" s="222" t="n"/>
       <c r="J17" s="315" t="n"/>
@@ -17768,7 +17761,12 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="451" t="n"/>
+      <c r="F18" s="468" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="443" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
@@ -17793,6 +17791,7 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
+      <c r="F19" s="406" t="n"/>
       <c r="G19" s="437" t="n"/>
       <c r="H19" s="437" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -17814,6 +17813,7 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
+      <c r="F20" s="407" t="n"/>
       <c r="G20" s="439" t="n"/>
       <c r="H20" s="439" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -18886,13 +18886,13 @@
     <mergeCell ref="M26:N26"/>
     <mergeCell ref="D45:D47"/>
     <mergeCell ref="H9:H11"/>
+    <mergeCell ref="F18:F20"/>
     <mergeCell ref="J9:J11"/>
     <mergeCell ref="F45:F47"/>
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="F42:F44"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="J36:J38"/>
-    <mergeCell ref="G15:G17"/>
     <mergeCell ref="J45:J47"/>
     <mergeCell ref="C60:C62"/>
     <mergeCell ref="B6:B8"/>

--- a/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_3_Calendario_Provas_2026_2SEM.xlsx
@@ -6113,13 +6113,13 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="434" t="inlineStr">
+      <c r="F18" s="468" t="inlineStr">
         <is>
           <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="n"/>
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="470" t="n"/>
       <c r="H18" s="441" t="n"/>
       <c r="I18" s="432" t="inlineStr">
         <is>
@@ -6138,8 +6138,7 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="437" t="n"/>
-      <c r="G19" s="222" t="n"/>
+      <c r="F19" s="406" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -6160,8 +6159,7 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="439" t="n"/>
-      <c r="G20" s="222" t="n"/>
+      <c r="F20" s="407" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
@@ -17761,7 +17759,7 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="468" t="inlineStr">
+      <c r="F18" s="470" t="inlineStr">
         <is>
           <t>Hist - Ver
 10º e 11º tempos</t>
@@ -17791,7 +17789,7 @@
       <c r="C19" s="313" t="n"/>
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
-      <c r="F19" s="406" t="n"/>
+      <c r="F19" s="437" t="n"/>
       <c r="G19" s="437" t="n"/>
       <c r="H19" s="437" t="n"/>
       <c r="J19" s="315" t="n"/>
@@ -17813,7 +17811,7 @@
       <c r="C20" s="313" t="n"/>
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
-      <c r="F20" s="407" t="n"/>
+      <c r="F20" s="439" t="n"/>
       <c r="G20" s="439" t="n"/>
       <c r="H20" s="439" t="n"/>
       <c r="J20" s="315" t="n"/>
@@ -19478,13 +19476,13 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="434" t="inlineStr">
+      <c r="F18" s="470" t="inlineStr">
         <is>
           <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="n"/>
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="470" t="n"/>
       <c r="H18" s="441" t="n"/>
       <c r="I18" s="432" t="inlineStr">
         <is>
@@ -19504,7 +19502,6 @@
       <c r="D19" s="314" t="n"/>
       <c r="E19" s="315" t="n"/>
       <c r="F19" s="437" t="n"/>
-      <c r="G19" s="222" t="n"/>
       <c r="I19" s="383" t="n"/>
       <c r="J19" s="315" t="n"/>
       <c r="L19" s="29" t="inlineStr">
@@ -19526,7 +19523,6 @@
       <c r="D20" s="314" t="n"/>
       <c r="E20" s="315" t="n"/>
       <c r="F20" s="439" t="n"/>
-      <c r="G20" s="222" t="n"/>
       <c r="I20" s="384" t="n"/>
       <c r="J20" s="315" t="n"/>
       <c r="L20" s="29" t="n"/>
